--- a/data/output/authors_empty_names_elastic.xlsx
+++ b/data/output/authors_empty_names_elastic.xlsx
@@ -577,17 +577,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-02-03T07:57:25Z</t>
+          <t>2026-06-17T18:15:36Z</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00033599']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027256']</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>['socio', 'edu']</t>
+          <t>['relig', 'litt']</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -601,7 +601,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>__-ovY2V8WJaJtQE9crlcID</t>
+          <t>__-lON76W5CSnNMbkPAYezr</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -625,17 +625,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-02-21T07:47:40Z</t>
+          <t>2026-08-14T13:09:35Z</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00007424']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00029930']</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>['scipo', 'envir']</t>
+          <t>['psy', 'lang']</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -649,7 +649,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>__-naeIh99PuU3iN80QFVuS</t>
+          <t>__-IaGDaXcYTDnsBd3RzrgY</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -673,17 +673,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-17T18:15:36Z</t>
+          <t>2026-02-03T07:57:25Z</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027256']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00033599']</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>['relig', 'litt']</t>
+          <t>['socio', 'edu']</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -697,7 +697,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>__-lON76W5CSnNMbkPAYezr</t>
+          <t>__-ovY2V8WJaJtQE9crlcID</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -721,17 +721,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-14T13:09:35Z</t>
+          <t>2026-02-21T07:47:40Z</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00029930']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00007424']</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>['psy', 'lang']</t>
+          <t>['scipo', 'envir']</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -745,7 +745,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>__-IaGDaXcYTDnsBd3RzrgY</t>
+          <t>__-naeIh99PuU3iN80QFVuS</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -769,17 +769,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02-03T07:57:29Z</t>
+          <t>2026-08-08T17:09:21Z</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00033599']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00016878']</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>['socio', 'edu']</t>
+          <t>['scipo', 'droit']</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -793,7 +793,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>__0T8inb4rnvx93h5vRc2Wz</t>
+          <t>__178mD65TgTNLB_U4mfAMi</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -817,17 +817,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-13T04:58:54Z</t>
+          <t>2026-08-13T04:58:51Z</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00026875']</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>['anthro-se', 'hist']</t>
+          <t>['relig', 'anthro-se']</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -841,12 +841,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>__1bKMVZRF2lGHXw5BAhc6F</t>
+          <t>__0gouguXks2rqD7ALw3QCU</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
@@ -865,17 +865,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-13T14:25:52Z</t>
+          <t>2026-02-03T07:57:29Z</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027343']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00033599']</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>['hisphilso', 'hist']</t>
+          <t>['socio', 'edu']</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -889,7 +889,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>__1RN_-bmxxkGhUlVjIxZF3</t>
+          <t>__0T8inb4rnvx93h5vRc2Wz</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -913,17 +913,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-13T04:58:51Z</t>
+          <t>2026-08-13T04:58:54Z</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00026875']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>['relig', 'anthro-se']</t>
+          <t>['anthro-se', 'hist']</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -937,12 +937,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>__0gouguXks2rqD7ALw3QCU</t>
+          <t>__1bKMVZRF2lGHXw5BAhc6F</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
@@ -1057,17 +1057,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-08T17:09:21Z</t>
+          <t>2026-08-13T14:25:52Z</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00016878']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027343']</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>['scipo', 'droit']</t>
+          <t>['hisphilso', 'hist']</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>__178mD65TgTNLB_U4mfAMi</t>
+          <t>__1RN_-bmxxkGhUlVjIxZF3</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -1345,17 +1345,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-13T05:07:20Z</t>
+          <t>2026-08-10T07:04:30Z</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00029742']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00007948']</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>['genre', 'socio']</t>
+          <t>['phil', 'edu']</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>__3_t58xs1cQLEgcxtJJpog</t>
+          <t>__3_jse8IHzt0CU0dNALT6S</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -1393,17 +1393,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-20T08:04:15Z</t>
+          <t>2026-08-13T05:07:20Z</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00001726']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00029742']</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>['info', 'stat']</t>
+          <t>['genre', 'socio']</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>__43texLZBHHfWpznk4gK0n</t>
+          <t>__3_t58xs1cQLEgcxtJJpog</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -1441,17 +1441,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-14T13:09:35Z</t>
+          <t>2026-02-20T08:04:15Z</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00029930']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00001726']</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>['psy', 'lang']</t>
+          <t>['info', 'stat']</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>__4ImgOXJRBqVTNim6hS9B9</t>
+          <t>__43texLZBHHfWpznk4gK0n</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -1489,17 +1489,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-10T07:04:30Z</t>
+          <t>2026-08-14T13:09:35Z</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00007948']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00029930']</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>['phil', 'edu']</t>
+          <t>['psy', 'lang']</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>__3_jse8IHzt0CU0dNALT6S</t>
+          <t>__4ImgOXJRBqVTNim6hS9B9</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -1537,17 +1537,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-08T12:24:26Z</t>
+          <t>2026-08-14T11:54:29Z</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00025085']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00039136']</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>['museo']</t>
+          <t>['psy', 'lang']</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>__4KN7H5ulJXhqUvCG7ZrPJ</t>
+          <t>__4eIpzAs05B4ZRv-5WGPUS</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -1585,17 +1585,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-23T14:36:04Z</t>
+          <t>2026-06-08T12:24:26Z</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00006179']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00025085']</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>['demo', 'socio']</t>
+          <t>['museo']</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>__4hQrT1f8FDe4OtrtQJSDK</t>
+          <t>__4KN7H5ulJXhqUvCG7ZrPJ</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -1633,17 +1633,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-14T11:54:29Z</t>
+          <t>2026-02-23T14:36:04Z</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00039136']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00006179']</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>['psy', 'lang']</t>
+          <t>['demo', 'socio']</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>__4eIpzAs05B4ZRv-5WGPUS</t>
+          <t>__4hQrT1f8FDe4OtrtQJSDK</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -1681,17 +1681,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-06T02:58:45Z</t>
+          <t>2026-07-31T03:29:31Z</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00039179']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00002963']</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>['lang']</t>
+          <t>['phil', 'scipo']</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>__59RnpZxfku6b3ydsd2b9k</t>
+          <t>__4lDRom4gaaw1FTIom5IUp</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -1729,17 +1729,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-31T03:29:31Z</t>
+          <t>2026-06-06T02:58:45Z</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00002963']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00039179']</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>['phil', 'scipo']</t>
+          <t>['lang']</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>__4lDRom4gaaw1FTIom5IUp</t>
+          <t>__59RnpZxfku6b3ydsd2b9k</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -1777,17 +1777,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-20T08:04:15Z</t>
+          <t>2026-08-14T11:52:54Z</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00001726']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027456']</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>['info', 'stat']</t>
+          <t>['lang', 'litt']</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>__5y4ls4xd7qwyrCEC7bS7V</t>
+          <t>__65dd7Tb00ujcdzdslmcEh</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -1825,17 +1825,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-14T11:52:54Z</t>
+          <t>2026-07-17T15:59:34Z</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027456']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00017062']</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>['lang', 'litt']</t>
+          <t>['droit', 'hist']</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>__65dd7Tb00ujcdzdslmcEh</t>
+          <t>__6yIH-mPB4rmIpeYYAsJMV</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -1873,17 +1873,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-17T15:59:34Z</t>
+          <t>2026-08-13T14:25:51Z</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00017062']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027332']</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>['droit', 'hist']</t>
+          <t>['hist', 'socio']</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>__6yIH-mPB4rmIpeYYAsJMV</t>
+          <t>__722aVCcrfxx0yzVebTYZp</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
@@ -1921,17 +1921,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-13T14:25:51Z</t>
+          <t>2026-02-20T08:04:15Z</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027332']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00001726']</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>['hist', 'socio']</t>
+          <t>['info', 'stat']</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>__722aVCcrfxx0yzVebTYZp</t>
+          <t>__5y4ls4xd7qwyrCEC7bS7V</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -2209,17 +2209,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-13T10:19:47Z</t>
+          <t>2026-08-08T17:09:27Z</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031667']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027113']</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>['hist', 'droit']</t>
+          <t>['scipo', 'hisphilso']</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>__9uiaL2Kr6Uuw0yf_D42gg</t>
+          <t>__A2PObfvhgd1RDg_NvM_A5</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -2305,17 +2305,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-08T17:09:27Z</t>
+          <t>2026-08-08T17:09:30Z</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027113']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031502']</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>['scipo', 'hisphilso']</t>
+          <t>['scipo', 'edu']</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>__A2PObfvhgd1RDg_NvM_A5</t>
+          <t>__AqJW4n8fEFgGBusAOhOaM</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -2353,17 +2353,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-14T13:21:00Z</t>
+          <t>2026-07-13T10:19:47Z</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031059']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031667']</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>['psy', 'edu']</t>
+          <t>['hist', 'droit']</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>__AfBBvrYreueEw-popoXhG</t>
+          <t>__9uiaL2Kr6Uuw0yf_D42gg</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -2401,17 +2401,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-08T17:09:30Z</t>
+          <t>2026-08-14T13:21:00Z</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031502']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031059']</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>['scipo', 'edu']</t>
+          <t>['psy', 'edu']</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>__AqJW4n8fEFgGBusAOhOaM</t>
+          <t>__AfBBvrYreueEw-popoXhG</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -2689,17 +2689,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-14T11:53:07Z</t>
+          <t>2026-03-10T12:38:36Z</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00039194']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00001588']</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>['lang', 'phil']</t>
+          <t>['envir']</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>__D2UfFsdGPlI0AB-DGqAoq</t>
+          <t>__DhAO02eKMaJ9ZK2imFJqx</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
@@ -2737,17 +2737,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-13T05:07:19Z</t>
+          <t>2026-08-14T13:21:00Z</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00029742']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031059']</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>['genre', 'socio']</t>
+          <t>['psy', 'edu']</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>__Dp5Fssm0mw7OOLf5E7Ryo</t>
+          <t>__DnXXLW1m6dfh9rHD7mIu4</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
@@ -2785,17 +2785,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-10T12:38:36Z</t>
+          <t>2026-08-13T05:07:19Z</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00001588']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00029742']</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>['envir']</t>
+          <t>['genre', 'socio']</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>__DhAO02eKMaJ9ZK2imFJqx</t>
+          <t>__Dp5Fssm0mw7OOLf5E7Ryo</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
@@ -2833,17 +2833,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-14T13:21:00Z</t>
+          <t>2026-08-18T07:01:25Z</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031059']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00002865', 'ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00030989']</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>['psy', 'edu']</t>
+          <t>['edu', 'lang', 'litt', 'phil', 'hisphilso']</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>__DnXXLW1m6dfh9rHD7mIu4</t>
+          <t>__CbwQdx-gEWFktXcVYb8ME</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J51" t="b">
         <v>0</v>
@@ -2881,17 +2881,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-18T07:01:25Z</t>
+          <t>2026-08-14T11:53:07Z</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00002865', 'ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00030989']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00039194']</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>['edu', 'lang', 'litt', 'phil', 'hisphilso']</t>
+          <t>['lang', 'phil']</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>__CbwQdx-gEWFktXcVYb8ME</t>
+          <t>__D2UfFsdGPlI0AB-DGqAoq</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J52" t="b">
         <v>0</v>
@@ -2929,17 +2929,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-14T12:01:40Z</t>
+          <t>2026-02-23T14:36:04Z</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00000402']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00006179']</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>['lang', 'litt']</t>
+          <t>['demo', 'socio']</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>__EJSrO8lPe5qaCdq3DysOG</t>
+          <t>__Dxuo_uNaUGg3mumbQFchm</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
@@ -3025,17 +3025,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-02-23T14:36:04Z</t>
+          <t>2026-08-14T12:01:40Z</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00006179']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00000402']</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>['demo', 'socio']</t>
+          <t>['lang', 'litt']</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>__Dxuo_uNaUGg3mumbQFchm</t>
+          <t>__EJSrO8lPe5qaCdq3DysOG</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
@@ -3217,17 +3217,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-07-09T19:15:26Z</t>
+          <t>2026-08-08T16:49:51Z</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00026817']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00025114']</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>['genre', 'demo']</t>
+          <t>['phil', 'hisphilso']</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>__FJyKuEEQXm-obCqakt7Db</t>
+          <t>__EskvkYA0LYjn7dcQKSB0I</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
@@ -3265,17 +3265,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-08T16:49:51Z</t>
+          <t>2026-07-09T19:15:26Z</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00025114']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00026817']</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>['phil', 'hisphilso']</t>
+          <t>['genre', 'demo']</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>__EskvkYA0LYjn7dcQKSB0I</t>
+          <t>__FJyKuEEQXm-obCqakt7Db</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
@@ -3409,17 +3409,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-08T17:09:32Z</t>
+          <t>2026-08-14T11:52:59Z</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031717']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>['scipo', 'socio']</t>
+          <t>['lang', 'litt']</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>__GeJ0lOVILlQKFGngrsGqa</t>
+          <t>__HLjlO4VJyjm1jh6y4hlYX</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J63" t="b">
         <v>0</v>
@@ -3457,17 +3457,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-08T12:37:17Z</t>
+          <t>2026-08-08T17:09:32Z</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>['ftunivromairis:oai:iris.uniroma1.it:11573_1183823', 'ftchacadscienegi:oai:ir.xjlas.org:365004_10838']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031717']</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>['psy', 'socio', 'demo', 'eco']</t>
+          <t>['scipo', 'socio']</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>__DpaWUjHZQMo7B_9GMMD1x</t>
+          <t>__GeJ0lOVILlQKFGngrsGqa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J64" t="b">
         <v>0</v>
@@ -3505,17 +3505,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-07-31T03:29:34Z</t>
+          <t>2026-08-08T12:37:17Z</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00007367']</t>
+          <t>['ftunivromairis:oai:iris.uniroma1.it:11573_1183823', 'ftchacadscienegi:oai:ir.xjlas.org:365004_10838']</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>['scipo', 'hist']</t>
+          <t>['psy', 'socio', 'demo', 'eco']</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>__GulDaDah1yGGWLg-Cl8Yc</t>
+          <t>__DpaWUjHZQMo7B_9GMMD1x</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J65" t="b">
         <v>0</v>
@@ -3553,17 +3553,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-14T11:52:59Z</t>
+          <t>2026-07-31T03:29:34Z</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00007367']</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>['lang', 'litt']</t>
+          <t>['scipo', 'hist']</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -3577,12 +3577,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>__HLjlO4VJyjm1jh6y4hlYX</t>
+          <t>__GulDaDah1yGGWLg-Cl8Yc</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J66" t="b">
         <v>0</v>
@@ -3649,17 +3649,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-13T22:45:58Z</t>
+          <t>2026-07-13T10:19:41Z</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00007987']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031517']</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>['lang', 'demo']</t>
+          <t>['scipo', 'hist']</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>__Ic3qvlSt2gMH81OUwECWq</t>
+          <t>__HORV6k_x5UWJWiUb82kJc</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
@@ -3697,17 +3697,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-07-13T10:19:41Z</t>
+          <t>2026-08-13T22:45:58Z</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031517']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00007987']</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>['scipo', 'hist']</t>
+          <t>['lang', 'demo']</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>__HORV6k_x5UWJWiUb82kJc</t>
+          <t>__Ic3qvlSt2gMH81OUwECWq</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
@@ -3745,17 +3745,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-14T13:09:36Z</t>
+          <t>2026-08-08T17:09:22Z</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00029930']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00016946']</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>['psy', 'lang']</t>
+          <t>['scipo', 'socio']</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>__IhMd4k0GK6q60sMEFCtNR</t>
+          <t>__IiVpgWALlwDqvM5_urj6S</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
@@ -3793,17 +3793,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-08T17:09:22Z</t>
+          <t>2026-08-14T13:09:36Z</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00016946']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00029930']</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>['scipo', 'socio']</t>
+          <t>['psy', 'lang']</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>__IiVpgWALlwDqvM5_urj6S</t>
+          <t>__IhMd4k0GK6q60sMEFCtNR</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
@@ -3889,17 +3889,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-08T17:09:25Z</t>
+          <t>2026-07-13T14:57:17Z</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00017707']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031323']</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>['hist', 'socio']</t>
+          <t>['socio', 'litt']</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>__JUPhcMA-nBLk8duDUzo4g</t>
+          <t>__JsUS-TJQq2MeqQOXz2j3e</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
@@ -3937,17 +3937,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-07-13T14:57:17Z</t>
+          <t>2026-08-08T17:09:25Z</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031323']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00017707']</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>['socio', 'litt']</t>
+          <t>['hist', 'socio']</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>__JsUS-TJQq2MeqQOXz2j3e</t>
+          <t>__JUPhcMA-nBLk8duDUzo4g</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
@@ -3985,17 +3985,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-06-07T23:57:06Z</t>
+          <t>2026-08-14T13:09:36Z</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00030534']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00029930']</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>['relig', 'hisphilso']</t>
+          <t>['psy', 'lang']</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>__Kn_alAO1yru5IfyMnNh99</t>
+          <t>__K8U1IzoCR_pny3OPWLsv5</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
@@ -4033,17 +4033,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-08-14T13:09:36Z</t>
+          <t>2026-06-07T23:57:06Z</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00029930']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00030534']</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>['psy', 'lang']</t>
+          <t>['relig', 'hisphilso']</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>__K8U1IzoCR_pny3OPWLsv5</t>
+          <t>__Kn_alAO1yru5IfyMnNh99</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
@@ -4081,17 +4081,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-02-20T08:04:15Z</t>
+          <t>2026-06-07T11:02:07Z</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00001726']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027479']</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>['info', 'stat']</t>
+          <t>['lang', 'litt']</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>__L00MemwgttgXlcetVWQz8</t>
+          <t>__Kx2k4Pin1eTDdzQsDycZN</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
@@ -4129,17 +4129,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-08-14T11:53:44Z</t>
+          <t>2026-02-20T08:04:15Z</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027549']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00001726']</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>['lang', 'litt']</t>
+          <t>['info', 'stat']</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>__LBtqT5kr37uJ7wjutlun5</t>
+          <t>__L00MemwgttgXlcetVWQz8</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
@@ -4177,12 +4177,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-06-07T11:02:07Z</t>
+          <t>2026-08-14T11:53:44Z</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027479']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027549']</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>__Kx2k4Pin1eTDdzQsDycZN</t>
+          <t>__LBtqT5kr37uJ7wjutlun5</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
@@ -4321,17 +4321,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-08-10T07:13:51Z</t>
+          <t>2026-07-13T10:19:37Z</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00028528']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00025143']</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>['socio', 'psy']</t>
+          <t>['lang', 'hisphilso']</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>__MULZnpMXeBHFci0iVcCK6</t>
+          <t>__LlIeHSXS7_3jX0-67Odha</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
@@ -4369,17 +4369,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-07-13T10:19:37Z</t>
+          <t>2026-08-13T22:46:15Z</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00025143']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00027122']</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>['lang', 'hisphilso']</t>
+          <t>['lang', 'litt']</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>__LlIeHSXS7_3jX0-67Odha</t>
+          <t>__MEvh03EPyCTDz8xEecDnx</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
@@ -4417,17 +4417,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-08-13T22:46:15Z</t>
+          <t>2026-08-10T07:13:51Z</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00027122']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00028528']</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>['lang', 'litt']</t>
+          <t>['socio', 'psy']</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>__MEvh03EPyCTDz8xEecDnx</t>
+          <t>__MULZnpMXeBHFci0iVcCK6</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
@@ -4561,17 +4561,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-08-14T12:01:40Z</t>
+          <t>2026-08-08T17:09:23Z</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00000402']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00017058']</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>['lang', 'litt']</t>
+          <t>['scipo', 'hist']</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>__OT_5CrYbEI4IxQkuGBI9x</t>
+          <t>__OHTo8WdCa2SUVHNshP2d7</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
@@ -4609,17 +4609,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-08-13T04:59:15Z</t>
+          <t>2026-08-14T12:01:40Z</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031051']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00000402']</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>['hisphilso', 'socio']</t>
+          <t>['lang', 'litt']</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>__Oar71J7VzZOSGkXrIjV9g</t>
+          <t>__OT_5CrYbEI4IxQkuGBI9x</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
@@ -4705,17 +4705,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-07-13T12:24:54Z</t>
+          <t>2026-08-13T04:59:09Z</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031087']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>['anthro-se', 'hisphilso']</t>
+          <t>['archeo', 'hist']</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>__Ov0QH6Msk9Rx9OHgWOqad</t>
+          <t>__P92IJiRexY6MZa_XDO4q9</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J90" t="b">
         <v>0</v>
@@ -4753,17 +4753,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-08-13T04:59:09Z</t>
+          <t>2026-08-13T04:59:15Z</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031051']</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>['archeo', 'hist']</t>
+          <t>['hisphilso', 'socio']</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>__P92IJiRexY6MZa_XDO4q9</t>
+          <t>__Oar71J7VzZOSGkXrIjV9g</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J91" t="b">
         <v>0</v>
@@ -4801,17 +4801,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-08-08T17:09:23Z</t>
+          <t>2026-07-17T15:59:21Z</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00017058']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031635']</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>['scipo', 'hist']</t>
+          <t>['droit', 'socio']</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>__OHTo8WdCa2SUVHNshP2d7</t>
+          <t>__P2Nz3NiYJNvlDhXWpPcP8</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
@@ -4897,17 +4897,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-08-10T07:13:50Z</t>
+          <t>2026-07-13T12:24:54Z</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00028528']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031087']</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>['socio', 'psy']</t>
+          <t>['anthro-se', 'hisphilso']</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>__P9CtP_bkIRKQwUfHRKIgr</t>
+          <t>__Ov0QH6Msk9Rx9OHgWOqad</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
@@ -4945,17 +4945,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-08-07T16:01:47Z</t>
+          <t>2026-08-10T07:13:50Z</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00026859']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00028528']</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>['hist', 'archi']</t>
+          <t>['socio', 'psy']</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>__PyEOaoi8CHBdziFLeHRna</t>
+          <t>__P9CtP_bkIRKQwUfHRKIgr</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
@@ -4993,17 +4993,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-08-14T11:52:54Z</t>
+          <t>2026-08-07T16:01:47Z</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027488']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00026859']</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>['lang', 'phil']</t>
+          <t>['hist', 'archi']</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -5017,7 +5017,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>__Q8PhgVa3HWHZSD_Ly4OUE</t>
+          <t>__PyEOaoi8CHBdziFLeHRna</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
@@ -5041,17 +5041,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-07-17T15:59:21Z</t>
+          <t>2026-08-14T11:52:54Z</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031635']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027488']</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>['droit', 'socio']</t>
+          <t>['lang', 'phil']</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>__P2Nz3NiYJNvlDhXWpPcP8</t>
+          <t>__Q8PhgVa3HWHZSD_Ly4OUE</t>
         </is>
       </c>
       <c r="H97" t="inlineStr"/>

--- a/data/output/authors_empty_names_elastic.xlsx
+++ b/data/output/authors_empty_names_elastic.xlsx
@@ -577,17 +577,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-17T18:15:36Z</t>
+          <t>2026-02-21T07:47:40Z</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027256']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00007424']</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>['relig', 'litt']</t>
+          <t>['scipo', 'envir']</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -601,7 +601,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>__-lON76W5CSnNMbkPAYezr</t>
+          <t>__-naeIh99PuU3iN80QFVuS</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -625,17 +625,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-14T13:09:35Z</t>
+          <t>2026-02-03T07:57:25Z</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00029930']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00033599']</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>['psy', 'lang']</t>
+          <t>['socio', 'edu']</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -649,7 +649,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>__-IaGDaXcYTDnsBd3RzrgY</t>
+          <t>__-ovY2V8WJaJtQE9crlcID</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -673,7 +673,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-02-03T07:57:25Z</t>
+          <t>2026-02-03T07:57:29Z</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>__-ovY2V8WJaJtQE9crlcID</t>
+          <t>__0T8inb4rnvx93h5vRc2Wz</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -721,17 +721,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-02-21T07:47:40Z</t>
+          <t>2026-08-14T13:09:35Z</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00007424']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00029930']</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>['scipo', 'envir']</t>
+          <t>['psy', 'lang']</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -745,7 +745,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>__-naeIh99PuU3iN80QFVuS</t>
+          <t>__-IaGDaXcYTDnsBd3RzrgY</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -865,17 +865,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-03T07:57:29Z</t>
+          <t>2026-06-17T18:15:36Z</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00033599']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027256']</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>['socio', 'edu']</t>
+          <t>['relig', 'litt']</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -889,7 +889,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>__0T8inb4rnvx93h5vRc2Wz</t>
+          <t>__-lON76W5CSnNMbkPAYezr</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -961,17 +961,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-10T12:38:36Z</t>
+          <t>2026-06-25T04:51:30Z</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00001588']</t>
+          <t>['10670_1.eyu20y']</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>['envir']</t>
+          <t>['psy', 'stat', 'hist', 'phil']</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -985,7 +985,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>__1aP0xuCfoRyhGZRbrpPcT</t>
+          <t>__200V7kjAxUieJXfJ7v_00</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -1009,17 +1009,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-25T04:51:30Z</t>
+          <t>2026-03-10T12:38:36Z</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>['10670_1.eyu20y']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00001588']</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>['psy', 'stat', 'hist', 'phil']</t>
+          <t>['envir']</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>__200V7kjAxUieJXfJ7v_00</t>
+          <t>__1aP0xuCfoRyhGZRbrpPcT</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -1537,17 +1537,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-14T11:54:29Z</t>
+          <t>2026-06-08T12:24:26Z</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00039136']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00025085']</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>['psy', 'lang']</t>
+          <t>['museo']</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>__4eIpzAs05B4ZRv-5WGPUS</t>
+          <t>__4KN7H5ulJXhqUvCG7ZrPJ</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -1585,17 +1585,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-08T12:24:26Z</t>
+          <t>2026-08-14T11:54:29Z</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00025085']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00039136']</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>['museo']</t>
+          <t>['psy', 'lang']</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>__4KN7H5ulJXhqUvCG7ZrPJ</t>
+          <t>__4eIpzAs05B4ZRv-5WGPUS</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -1777,17 +1777,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-14T11:52:54Z</t>
+          <t>2026-02-20T08:04:15Z</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027456']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00001726']</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>['lang', 'litt']</t>
+          <t>['info', 'stat']</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>__65dd7Tb00ujcdzdslmcEh</t>
+          <t>__5y4ls4xd7qwyrCEC7bS7V</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -1825,17 +1825,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-17T15:59:34Z</t>
+          <t>2026-08-14T11:52:54Z</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00017062']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027456']</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>['droit', 'hist']</t>
+          <t>['lang', 'litt']</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>__6yIH-mPB4rmIpeYYAsJMV</t>
+          <t>__65dd7Tb00ujcdzdslmcEh</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -1873,17 +1873,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-13T14:25:51Z</t>
+          <t>2026-07-17T15:59:34Z</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027332']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00017062']</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>['hist', 'socio']</t>
+          <t>['droit', 'hist']</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>__722aVCcrfxx0yzVebTYZp</t>
+          <t>__6yIH-mPB4rmIpeYYAsJMV</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
@@ -1921,17 +1921,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-20T08:04:15Z</t>
+          <t>2026-08-13T14:25:51Z</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00001726']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027332']</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>['info', 'stat']</t>
+          <t>['hist', 'socio']</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>__5y4ls4xd7qwyrCEC7bS7V</t>
+          <t>__722aVCcrfxx0yzVebTYZp</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -2209,17 +2209,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-08T17:09:27Z</t>
+          <t>2026-07-13T10:19:47Z</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027113']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031667']</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>['scipo', 'hisphilso']</t>
+          <t>['hist', 'droit']</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>__A2PObfvhgd1RDg_NvM_A5</t>
+          <t>__9uiaL2Kr6Uuw0yf_D42gg</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -2257,17 +2257,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-08T17:09:23Z</t>
+          <t>2026-08-08T17:09:27Z</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00017330']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027113']</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>['scipo', 'socio']</t>
+          <t>['scipo', 'hisphilso']</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>__AZJfY1ACEit1ct4I0AMIn</t>
+          <t>__A2PObfvhgd1RDg_NvM_A5</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -2305,17 +2305,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-08T17:09:30Z</t>
+          <t>2026-08-08T17:09:23Z</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031502']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00017330']</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>['scipo', 'edu']</t>
+          <t>['scipo', 'socio']</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>__AqJW4n8fEFgGBusAOhOaM</t>
+          <t>__AZJfY1ACEit1ct4I0AMIn</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -2353,17 +2353,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-13T10:19:47Z</t>
+          <t>2026-08-14T13:21:00Z</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031667']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031059']</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>['hist', 'droit']</t>
+          <t>['psy', 'edu']</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>__9uiaL2Kr6Uuw0yf_D42gg</t>
+          <t>__AfBBvrYreueEw-popoXhG</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -2401,17 +2401,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-14T13:21:00Z</t>
+          <t>2026-08-08T17:09:30Z</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031059']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031502']</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>['psy', 'edu']</t>
+          <t>['scipo', 'edu']</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>__AfBBvrYreueEw-popoXhG</t>
+          <t>__AqJW4n8fEFgGBusAOhOaM</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -2689,17 +2689,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-10T12:38:36Z</t>
+          <t>2026-08-14T11:53:07Z</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00001588']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00039194']</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>['envir']</t>
+          <t>['lang', 'phil']</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>__DhAO02eKMaJ9ZK2imFJqx</t>
+          <t>__D2UfFsdGPlI0AB-DGqAoq</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
@@ -2737,17 +2737,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-14T13:21:00Z</t>
+          <t>2026-03-10T12:38:36Z</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031059']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00001588']</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>['psy', 'edu']</t>
+          <t>['envir']</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>__DnXXLW1m6dfh9rHD7mIu4</t>
+          <t>__DhAO02eKMaJ9ZK2imFJqx</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
@@ -2785,17 +2785,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-13T05:07:19Z</t>
+          <t>2026-08-14T13:21:00Z</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00029742']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031059']</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>['genre', 'socio']</t>
+          <t>['psy', 'edu']</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>__Dp5Fssm0mw7OOLf5E7Ryo</t>
+          <t>__DnXXLW1m6dfh9rHD7mIu4</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
@@ -2833,17 +2833,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-18T07:01:25Z</t>
+          <t>2026-08-13T05:07:19Z</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00002865', 'ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00030989']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00029742']</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>['edu', 'lang', 'litt', 'phil', 'hisphilso']</t>
+          <t>['genre', 'socio']</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>__CbwQdx-gEWFktXcVYb8ME</t>
+          <t>__Dp5Fssm0mw7OOLf5E7Ryo</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J51" t="b">
         <v>0</v>
@@ -2881,17 +2881,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-14T11:53:07Z</t>
+          <t>2026-08-18T07:01:25Z</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00039194']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00002865', 'ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00030989']</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>['lang', 'phil']</t>
+          <t>['edu', 'lang', 'litt', 'phil', 'hisphilso']</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>__D2UfFsdGPlI0AB-DGqAoq</t>
+          <t>__CbwQdx-gEWFktXcVYb8ME</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J52" t="b">
         <v>0</v>
@@ -3025,17 +3025,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-14T12:01:40Z</t>
+          <t>2026-08-10T07:13:49Z</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00000402']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00028528']</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>['lang', 'litt']</t>
+          <t>['socio', 'psy']</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>__EJSrO8lPe5qaCdq3DysOG</t>
+          <t>__ENb7Xr-KjlfzFqvkOeyam</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
@@ -3073,17 +3073,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-10T07:13:49Z</t>
+          <t>2026-03-10T12:38:36Z</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00028528']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00001588']</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>['socio', 'psy']</t>
+          <t>['envir']</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>__ENb7Xr-KjlfzFqvkOeyam</t>
+          <t>__EVanYtOCG9OmAx8tajr_1</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
@@ -3121,17 +3121,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-03-10T12:38:36Z</t>
+          <t>2026-08-14T12:01:40Z</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00001588']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00000402']</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>['envir']</t>
+          <t>['lang', 'litt']</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>__EVanYtOCG9OmAx8tajr_1</t>
+          <t>__EJSrO8lPe5qaCdq3DysOG</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
@@ -3169,17 +3169,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-13T10:19:40Z</t>
+          <t>2026-08-08T16:49:51Z</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027254']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00025114']</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>['anthro-se', 'lang']</t>
+          <t>['phil', 'hisphilso']</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -3193,7 +3193,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>__Ei0v0_SPsoHnPp66dBoX5</t>
+          <t>__EskvkYA0LYjn7dcQKSB0I</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
@@ -3217,17 +3217,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-08T16:49:51Z</t>
+          <t>2026-07-13T10:19:40Z</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00025114']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027254']</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>['phil', 'hisphilso']</t>
+          <t>['anthro-se', 'lang']</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>__EskvkYA0LYjn7dcQKSB0I</t>
+          <t>__Ei0v0_SPsoHnPp66dBoX5</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
@@ -3265,17 +3265,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-07-09T19:15:26Z</t>
+          <t>2026-08-08T12:37:17Z</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00026817']</t>
+          <t>['ftunivromairis:oai:iris.uniroma1.it:11573_1183823', 'ftchacadscienegi:oai:ir.xjlas.org:365004_10838']</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>['genre', 'demo']</t>
+          <t>['psy', 'socio', 'demo', 'eco']</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>__FJyKuEEQXm-obCqakt7Db</t>
+          <t>__DpaWUjHZQMo7B_9GMMD1x</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J60" t="b">
         <v>0</v>
@@ -3313,17 +3313,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-06-07T11:02:07Z</t>
+          <t>2026-07-09T19:15:26Z</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027555']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00026817']</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>['lang', 'litt']</t>
+          <t>['genre', 'demo']</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>__FYw0tp9QQzm2nmDDa5X_T</t>
+          <t>__FJyKuEEQXm-obCqakt7Db</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
@@ -3361,17 +3361,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-06-17T18:29:08Z</t>
+          <t>2026-06-07T11:02:07Z</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00003030']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027555']</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>['lang', 'info']</t>
+          <t>['lang', 'litt']</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>__FhCfRPCmfXALcusT0Rwkz</t>
+          <t>__FYw0tp9QQzm2nmDDa5X_T</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
@@ -3457,17 +3457,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-08T17:09:32Z</t>
+          <t>2026-06-17T18:29:08Z</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031717']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00003030']</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>['scipo', 'socio']</t>
+          <t>['lang', 'info']</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>__GeJ0lOVILlQKFGngrsGqa</t>
+          <t>__FhCfRPCmfXALcusT0Rwkz</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
@@ -3505,17 +3505,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-08T12:37:17Z</t>
+          <t>2026-08-08T17:09:32Z</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>['ftunivromairis:oai:iris.uniroma1.it:11573_1183823', 'ftchacadscienegi:oai:ir.xjlas.org:365004_10838']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031717']</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>['psy', 'socio', 'demo', 'eco']</t>
+          <t>['scipo', 'socio']</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>__DpaWUjHZQMo7B_9GMMD1x</t>
+          <t>__GeJ0lOVILlQKFGngrsGqa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J65" t="b">
         <v>0</v>
@@ -3745,17 +3745,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-08T17:09:22Z</t>
+          <t>2026-08-14T13:09:36Z</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00016946']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00029930']</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>['scipo', 'socio']</t>
+          <t>['psy', 'lang']</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>__IiVpgWALlwDqvM5_urj6S</t>
+          <t>__IhMd4k0GK6q60sMEFCtNR</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
@@ -3793,17 +3793,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-14T13:09:36Z</t>
+          <t>2026-08-08T17:09:22Z</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00029930']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00016946']</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>['psy', 'lang']</t>
+          <t>['scipo', 'socio']</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>__IhMd4k0GK6q60sMEFCtNR</t>
+          <t>__IiVpgWALlwDqvM5_urj6S</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
@@ -3889,17 +3889,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-07-13T14:57:17Z</t>
+          <t>2026-08-08T17:09:25Z</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031323']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00017707']</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>['socio', 'litt']</t>
+          <t>['hist', 'socio']</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>__JsUS-TJQq2MeqQOXz2j3e</t>
+          <t>__JUPhcMA-nBLk8duDUzo4g</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
@@ -3937,17 +3937,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-08-08T17:09:25Z</t>
+          <t>2026-07-13T14:57:17Z</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00017707']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031323']</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>['hist', 'socio']</t>
+          <t>['socio', 'litt']</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>__JUPhcMA-nBLk8duDUzo4g</t>
+          <t>__JsUS-TJQq2MeqQOXz2j3e</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
@@ -4657,17 +4657,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-02-23T14:36:04Z</t>
+          <t>2026-08-13T04:59:15Z</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00006179']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031051']</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>['demo', 'socio']</t>
+          <t>['hisphilso', 'socio']</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>__OrVD1QaUTurw_uBpYfn3i</t>
+          <t>__Oar71J7VzZOSGkXrIjV9g</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
@@ -4753,17 +4753,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-08-13T04:59:15Z</t>
+          <t>2026-07-13T12:24:54Z</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031051']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031087']</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>['hisphilso', 'socio']</t>
+          <t>['anthro-se', 'hisphilso']</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>__Oar71J7VzZOSGkXrIjV9g</t>
+          <t>__Ov0QH6Msk9Rx9OHgWOqad</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
@@ -4897,17 +4897,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-07-13T12:24:54Z</t>
+          <t>2026-02-23T14:36:04Z</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031087']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00006179']</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>['anthro-se', 'hisphilso']</t>
+          <t>['demo', 'socio']</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>__Ov0QH6Msk9Rx9OHgWOqad</t>
+          <t>__OrVD1QaUTurw_uBpYfn3i</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
@@ -4993,17 +4993,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-08-07T16:01:47Z</t>
+          <t>2026-08-14T11:52:54Z</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00026859']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027488']</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>['hist', 'archi']</t>
+          <t>['lang', 'phil']</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -5017,7 +5017,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>__PyEOaoi8CHBdziFLeHRna</t>
+          <t>__Q8PhgVa3HWHZSD_Ly4OUE</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
@@ -5041,17 +5041,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-08-14T11:52:54Z</t>
+          <t>2026-08-07T16:01:47Z</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027488']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00026859']</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>['lang', 'phil']</t>
+          <t>['hist', 'archi']</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>__Q8PhgVa3HWHZSD_Ly4OUE</t>
+          <t>__PyEOaoi8CHBdziFLeHRna</t>
         </is>
       </c>
       <c r="H97" t="inlineStr"/>

--- a/data/output/authors_empty_names_elastic.xlsx
+++ b/data/output/authors_empty_names_elastic.xlsx
@@ -67,30 +67,30 @@
     <t>2026-02-03T07:57:25Z</t>
   </si>
   <si>
+    <t>2026-08-14T13:09:35Z</t>
+  </si>
+  <si>
+    <t>2026-08-23T16:24:42Z</t>
+  </si>
+  <si>
     <t>2026-08-23T20:37:03Z</t>
   </si>
   <si>
-    <t>2026-08-14T13:09:35Z</t>
-  </si>
-  <si>
-    <t>2026-08-23T16:24:42Z</t>
-  </si>
-  <si>
     <t>2026-02-03T07:57:29Z</t>
   </si>
   <si>
     <t>2026-08-13T04:58:54Z</t>
   </si>
   <si>
+    <t>2026-08-08T17:09:21Z</t>
+  </si>
+  <si>
+    <t>2026-03-10T12:38:36Z</t>
+  </si>
+  <si>
     <t>2026-08-13T14:25:52Z</t>
   </si>
   <si>
-    <t>2026-08-08T17:09:21Z</t>
-  </si>
-  <si>
-    <t>2026-03-10T12:38:36Z</t>
-  </si>
-  <si>
     <t>2026-06-25T04:51:30Z</t>
   </si>
   <si>
@@ -115,18 +115,18 @@
     <t>2026-08-24T20:08:47Z</t>
   </si>
   <si>
+    <t>2026-08-23T12:22:52Z</t>
+  </si>
+  <si>
+    <t>2026-09-01T19:23:36Z</t>
+  </si>
+  <si>
+    <t>2026-09-01T09:34:54Z</t>
+  </si>
+  <si>
     <t>2026-02-23T14:36:04Z</t>
   </si>
   <si>
-    <t>2026-09-01T19:23:36Z</t>
-  </si>
-  <si>
-    <t>2026-08-23T12:22:52Z</t>
-  </si>
-  <si>
-    <t>2026-09-01T09:34:54Z</t>
-  </si>
-  <si>
     <t>2026-08-10T07:04:30Z</t>
   </si>
   <si>
@@ -175,18 +175,18 @@
     <t>2026-08-23T20:03:28Z</t>
   </si>
   <si>
+    <t>2026-08-08T17:09:27Z</t>
+  </si>
+  <si>
+    <t>2026-08-24T21:31:45Z</t>
+  </si>
+  <si>
+    <t>2026-08-14T13:21:00Z</t>
+  </si>
+  <si>
     <t>2026-07-13T10:19:47Z</t>
   </si>
   <si>
-    <t>2026-08-24T21:31:45Z</t>
-  </si>
-  <si>
-    <t>2026-08-08T17:09:27Z</t>
-  </si>
-  <si>
-    <t>2026-08-14T13:21:00Z</t>
-  </si>
-  <si>
     <t>2026-08-08T17:09:30Z</t>
   </si>
   <si>
@@ -199,12 +199,12 @@
     <t>2026-08-14T11:53:07Z</t>
   </si>
   <si>
+    <t>2026-08-18T07:01:25Z</t>
+  </si>
+  <si>
     <t>2026-08-13T05:07:19Z</t>
   </si>
   <si>
-    <t>2026-08-18T07:01:25Z</t>
-  </si>
-  <si>
     <t>2026-08-07T02:17:53Z</t>
   </si>
   <si>
@@ -214,6 +214,9 @@
     <t>2026-08-10T07:13:49Z</t>
   </si>
   <si>
+    <t>2026-08-08T12:37:17Z</t>
+  </si>
+  <si>
     <t>2026-07-13T10:19:40Z</t>
   </si>
   <si>
@@ -226,21 +229,18 @@
     <t>2026-06-07T11:02:07Z</t>
   </si>
   <si>
+    <t>2026-08-14T11:52:59Z</t>
+  </si>
+  <si>
     <t>2026-08-25T11:35:50Z</t>
   </si>
   <si>
-    <t>2026-08-14T11:52:59Z</t>
-  </si>
-  <si>
     <t>2026-08-08T17:09:32Z</t>
   </si>
   <si>
     <t>2026-07-31T03:29:34Z</t>
   </si>
   <si>
-    <t>2026-08-08T12:37:17Z</t>
-  </si>
-  <si>
     <t>2026-07-13T10:19:41Z</t>
   </si>
   <si>
@@ -307,78 +307,78 @@
     <t>2026-08-07T16:01:47Z</t>
   </si>
   <si>
+    <t>2026-08-08T17:09:35Z</t>
+  </si>
+  <si>
     <t>2026-09-01T09:34:52Z</t>
   </si>
   <si>
-    <t>2026-08-08T17:09:35Z</t>
+    <t>2026-08-23T12:22:48Z</t>
+  </si>
+  <si>
+    <t>2026-08-31T13:09:26Z</t>
   </si>
   <si>
     <t>2026-06-07T21:50:52Z</t>
   </si>
   <si>
-    <t>2026-08-23T12:22:48Z</t>
-  </si>
-  <si>
-    <t>2026-08-31T13:09:26Z</t>
-  </si>
-  <si>
     <t>2026-08-23T22:07:28Z</t>
   </si>
   <si>
+    <t>2026-08-31T11:01:24Z</t>
+  </si>
+  <si>
+    <t>2026-06-26T04:05:21Z</t>
+  </si>
+  <si>
     <t>2026-08-08T17:09:28Z</t>
   </si>
   <si>
+    <t>2026-08-07T02:17:45Z</t>
+  </si>
+  <si>
     <t>2026-06-07T11:48:22Z</t>
   </si>
   <si>
-    <t>2026-08-07T02:17:45Z</t>
-  </si>
-  <si>
     <t>2026-06-06T02:58:44Z</t>
   </si>
   <si>
-    <t>2026-08-31T11:01:24Z</t>
-  </si>
-  <si>
-    <t>2026-06-26T04:05:21Z</t>
-  </si>
-  <si>
     <t>2026-08-13T04:58:50Z</t>
   </si>
   <si>
+    <t>2026-08-10T07:04:34Z</t>
+  </si>
+  <si>
     <t>2026-08-14T11:54:32Z</t>
   </si>
   <si>
-    <t>2026-08-10T07:04:34Z</t>
+    <t>2026-08-23T18:28:07Z</t>
   </si>
   <si>
     <t>2026-08-14T11:53:48Z</t>
   </si>
   <si>
-    <t>2026-08-23T18:28:07Z</t>
-  </si>
-  <si>
     <t>2026-07-17T17:16:01Z</t>
   </si>
   <si>
+    <t>2026-08-08T17:09:26Z</t>
+  </si>
+  <si>
     <t>2026-08-23T21:32:22Z</t>
   </si>
   <si>
-    <t>2026-08-08T17:09:26Z</t>
-  </si>
-  <si>
     <t>2026-06-17T18:17:43Z</t>
   </si>
   <si>
+    <t>2026-02-02T07:46:02Z</t>
+  </si>
+  <si>
     <t>2026-08-08T17:10:56Z</t>
   </si>
   <si>
     <t>2026-08-14T11:52:56Z</t>
   </si>
   <si>
-    <t>2026-02-02T07:46:02Z</t>
-  </si>
-  <si>
     <t>2026-08-10T07:04:27Z</t>
   </si>
   <si>
@@ -391,21 +391,21 @@
     <t>2026-08-02T07:15:31Z</t>
   </si>
   <si>
+    <t>2026-08-25T11:35:49Z</t>
+  </si>
+  <si>
+    <t>2026-08-13T04:59:12Z</t>
+  </si>
+  <si>
     <t>2026-08-08T17:09:31Z</t>
   </si>
   <si>
+    <t>2026-06-13T01:26:07Z</t>
+  </si>
+  <si>
     <t>2026-01-31T09:20:37Z</t>
   </si>
   <si>
-    <t>2026-08-13T04:59:12Z</t>
-  </si>
-  <si>
-    <t>2026-06-13T01:26:07Z</t>
-  </si>
-  <si>
-    <t>2026-08-25T11:35:49Z</t>
-  </si>
-  <si>
     <t>2026-08-23T20:03:27Z</t>
   </si>
   <si>
@@ -421,87 +421,87 @@
     <t>2026-08-23T20:03:49Z</t>
   </si>
   <si>
+    <t>2026-08-13T14:25:54Z</t>
+  </si>
+  <si>
+    <t>2026-06-07T10:32:07Z</t>
+  </si>
+  <si>
     <t>2026-07-13T12:24:53Z</t>
   </si>
   <si>
-    <t>2026-06-07T10:32:07Z</t>
-  </si>
-  <si>
-    <t>2026-08-13T14:25:54Z</t>
-  </si>
-  <si>
     <t>2026-07-13T14:57:15Z</t>
   </si>
   <si>
     <t>2026-03-10T07:11:03Z</t>
   </si>
   <si>
+    <t>2026-06-27T19:43:03Z</t>
+  </si>
+  <si>
     <t>2026-08-23T11:34:38Z</t>
   </si>
   <si>
-    <t>2026-06-27T19:43:03Z</t>
-  </si>
-  <si>
     <t>2026-08-23T12:22:44Z</t>
   </si>
   <si>
     <t>2026-08-13T22:46:04Z</t>
   </si>
   <si>
+    <t>2026-06-07T11:02:06Z</t>
+  </si>
+  <si>
+    <t>2026-08-13T04:58:48Z</t>
+  </si>
+  <si>
     <t>2026-08-13T22:46:13Z</t>
   </si>
   <si>
-    <t>2026-08-13T04:58:48Z</t>
+    <t>2026-08-23T20:03:32Z</t>
   </si>
   <si>
     <t>2026-08-08T17:09:24Z</t>
   </si>
   <si>
-    <t>2026-06-07T11:02:06Z</t>
-  </si>
-  <si>
-    <t>2026-08-23T20:03:32Z</t>
-  </si>
-  <si>
     <t>2026-08-13T04:59:14Z</t>
   </si>
   <si>
+    <t>2026-08-31T08:08:22Z</t>
+  </si>
+  <si>
+    <t>2026-08-10T07:04:25Z</t>
+  </si>
+  <si>
     <t>2026-08-23T20:03:42Z</t>
   </si>
   <si>
-    <t>2026-08-31T08:08:22Z</t>
-  </si>
-  <si>
     <t>2026-06-07T11:02:11Z</t>
   </si>
   <si>
     <t>2026-08-13T04:58:43Z</t>
   </si>
   <si>
+    <t>2026-07-13T11:01:01Z</t>
+  </si>
+  <si>
+    <t>2026-08-13T14:25:48Z</t>
+  </si>
+  <si>
+    <t>2026-06-06T02:58:41Z</t>
+  </si>
+  <si>
+    <t>2026-08-08T17:09:34Z</t>
+  </si>
+  <si>
+    <t>2026-08-13T14:25:55Z</t>
+  </si>
+  <si>
+    <t>2026-08-23T20:03:31Z</t>
+  </si>
+  <si>
     <t>2026-02-23T16:19:48Z</t>
   </si>
   <si>
-    <t>2026-08-10T07:04:25Z</t>
-  </si>
-  <si>
-    <t>2026-06-06T02:58:41Z</t>
-  </si>
-  <si>
-    <t>2026-07-13T11:01:01Z</t>
-  </si>
-  <si>
-    <t>2026-08-13T14:25:48Z</t>
-  </si>
-  <si>
-    <t>2026-08-23T20:03:31Z</t>
-  </si>
-  <si>
-    <t>2026-08-13T14:25:55Z</t>
-  </si>
-  <si>
-    <t>2026-08-08T17:09:34Z</t>
-  </si>
-  <si>
     <t>2026-08-08T17:09:29Z</t>
   </si>
   <si>
@@ -517,15 +517,15 @@
     <t>2026-08-13T22:46:06Z</t>
   </si>
   <si>
+    <t>2026-09-01T09:34:51Z</t>
+  </si>
+  <si>
+    <t>2026-06-24T02:00:55Z</t>
+  </si>
+  <si>
     <t>2026-08-12T13:09:26Z</t>
   </si>
   <si>
-    <t>2026-09-01T09:34:51Z</t>
-  </si>
-  <si>
-    <t>2026-06-24T02:00:55Z</t>
-  </si>
-  <si>
     <t>2026-06-21T14:25:04Z</t>
   </si>
   <si>
@@ -538,51 +538,51 @@
     <t>2026-08-23T11:34:41Z</t>
   </si>
   <si>
+    <t>2026-06-20T12:51:15Z</t>
+  </si>
+  <si>
+    <t>2026-07-26T20:22:04Z</t>
+  </si>
+  <si>
+    <t>2026-02-03T18:55:17Z</t>
+  </si>
+  <si>
+    <t>2026-06-25T04:39:01Z</t>
+  </si>
+  <si>
+    <t>2026-07-18T12:28:26Z</t>
+  </si>
+  <si>
+    <t>2026-06-27T04:39:48Z</t>
+  </si>
+  <si>
+    <t>2026-03-03T06:57:48Z</t>
+  </si>
+  <si>
+    <t>2026-06-26T04:39:44Z</t>
+  </si>
+  <si>
+    <t>2026-06-24T02:26:53Z</t>
+  </si>
+  <si>
     <t>2026-02-02T18:46:22Z</t>
   </si>
   <si>
-    <t>2026-06-20T12:51:15Z</t>
-  </si>
-  <si>
-    <t>2026-07-26T20:22:04Z</t>
-  </si>
-  <si>
-    <t>2026-02-03T18:55:17Z</t>
-  </si>
-  <si>
-    <t>2026-06-25T04:39:01Z</t>
-  </si>
-  <si>
-    <t>2026-06-27T04:39:48Z</t>
-  </si>
-  <si>
-    <t>2026-06-24T02:26:53Z</t>
-  </si>
-  <si>
-    <t>2026-03-03T06:57:48Z</t>
-  </si>
-  <si>
-    <t>2026-07-18T12:28:26Z</t>
-  </si>
-  <si>
     <t>2026-06-20T17:37:14Z</t>
   </si>
   <si>
-    <t>2026-06-26T04:39:44Z</t>
+    <t>2026-08-04T09:48:55Z</t>
   </si>
   <si>
     <t>2026-08-12T19:43:21Z</t>
   </si>
   <si>
-    <t>2026-08-04T09:48:55Z</t>
+    <t>2026-06-13T01:25:11Z</t>
   </si>
   <si>
     <t>2026-07-17T13:45:49Z</t>
   </si>
   <si>
-    <t>2026-06-13T01:25:11Z</t>
-  </si>
-  <si>
     <t>2026-06-24T04:00:06Z</t>
   </si>
   <si>
@@ -598,54 +598,54 @@
     <t>2026-09-01T04:38:47Z</t>
   </si>
   <si>
+    <t>2026-02-03T18:47:17Z</t>
+  </si>
+  <si>
+    <t>2026-08-18T22:45:46Z</t>
+  </si>
+  <si>
+    <t>2026-06-23T20:08:20Z</t>
+  </si>
+  <si>
+    <t>2026-06-24T09:51:23Z</t>
+  </si>
+  <si>
+    <t>2026-08-18T22:45:47Z</t>
+  </si>
+  <si>
+    <t>2026-06-24T16:45:16Z</t>
+  </si>
+  <si>
+    <t>2026-06-24T20:56:22Z</t>
+  </si>
+  <si>
     <t>2026-07-14T17:41:25Z</t>
   </si>
   <si>
-    <t>2026-02-03T18:47:17Z</t>
-  </si>
-  <si>
-    <t>2026-06-23T20:08:20Z</t>
-  </si>
-  <si>
-    <t>2026-08-18T22:45:46Z</t>
-  </si>
-  <si>
-    <t>2026-06-24T09:51:23Z</t>
-  </si>
-  <si>
-    <t>2026-06-24T20:56:22Z</t>
-  </si>
-  <si>
-    <t>2026-08-18T22:45:47Z</t>
-  </si>
-  <si>
-    <t>2026-06-24T16:45:16Z</t>
-  </si>
-  <si>
     <t>2026-05-18T07:08:02Z</t>
   </si>
   <si>
     <t>2026-06-12T14:38:30Z</t>
   </si>
   <si>
+    <t>2026-06-12T14:38:08Z</t>
+  </si>
+  <si>
+    <t>2026-05-20T06:48:39Z</t>
+  </si>
+  <si>
+    <t>2026-08-04T09:16:44Z</t>
+  </si>
+  <si>
+    <t>2026-02-04T18:53:06Z</t>
+  </si>
+  <si>
+    <t>2026-05-30T17:04:06Z</t>
+  </si>
+  <si>
     <t>2026-03-02T20:55:13Z</t>
   </si>
   <si>
-    <t>2026-06-12T14:38:08Z</t>
-  </si>
-  <si>
-    <t>2026-05-20T06:48:39Z</t>
-  </si>
-  <si>
-    <t>2026-02-04T18:53:06Z</t>
-  </si>
-  <si>
-    <t>2026-08-04T09:16:44Z</t>
-  </si>
-  <si>
-    <t>2026-05-30T17:04:06Z</t>
-  </si>
-  <si>
     <t>2026-06-24T04:41:52Z</t>
   </si>
   <si>
@@ -664,27 +664,27 @@
     <t>2026-07-17T18:48:36Z</t>
   </si>
   <si>
+    <t>2026-08-12T01:21:21Z</t>
+  </si>
+  <si>
     <t>2026-06-14T09:51:46Z</t>
   </si>
   <si>
     <t>2026-08-14T22:48:43Z</t>
   </si>
   <si>
-    <t>2026-08-12T01:21:21Z</t>
-  </si>
-  <si>
     <t>2026-06-24T01:51:04Z</t>
   </si>
   <si>
     <t>2026-02-14T09:15:24Z</t>
   </si>
   <si>
+    <t>2026-08-10T08:59:46Z</t>
+  </si>
+  <si>
     <t>2026-08-13T20:46:55Z</t>
   </si>
   <si>
-    <t>2026-08-10T08:59:46Z</t>
-  </si>
-  <si>
     <t>2026-07-16T17:55:15Z</t>
   </si>
   <si>
@@ -802,174 +802,174 @@
     <t>2026-07-15T12:39:19Z</t>
   </si>
   <si>
+    <t>2026-09-01T15:09:28Z</t>
+  </si>
+  <si>
+    <t>2026-06-17T17:06:45Z</t>
+  </si>
+  <si>
     <t>2026-06-15T01:25:05Z</t>
   </si>
   <si>
-    <t>2026-06-17T17:06:45Z</t>
-  </si>
-  <si>
     <t>2026-01-31T19:25:46Z</t>
   </si>
   <si>
     <t>2026-05-19T09:49:43Z</t>
   </si>
   <si>
+    <t>2026-09-01T17:14:04Z</t>
+  </si>
+  <si>
+    <t>2026-02-10T19:10:26Z</t>
+  </si>
+  <si>
+    <t>2026-02-22T18:57:50Z</t>
+  </si>
+  <si>
     <t>2026-08-12T22:47:13Z</t>
   </si>
   <si>
+    <t>2026-07-24T12:49:34Z</t>
+  </si>
+  <si>
     <t>2026-07-24T12:49:35Z</t>
   </si>
   <si>
-    <t>2026-02-10T19:10:26Z</t>
-  </si>
-  <si>
-    <t>2026-02-22T18:57:50Z</t>
-  </si>
-  <si>
-    <t>2026-07-24T12:49:34Z</t>
+    <t>2026-06-10T01:25:09Z</t>
+  </si>
+  <si>
+    <t>2026-06-10T01:25:08Z</t>
   </si>
   <si>
     <t>2026-04-28T18:34:51Z</t>
   </si>
   <si>
+    <t>2026-06-10T01:25:10Z</t>
+  </si>
+  <si>
+    <t>2026-06-10T01:25:05Z</t>
+  </si>
+  <si>
+    <t>2026-06-11T01:25:35Z</t>
+  </si>
+  <si>
+    <t>2026-06-27T04:38:05Z</t>
+  </si>
+  <si>
+    <t>2026-06-10T01:25:23Z</t>
+  </si>
+  <si>
+    <t>2026-03-01T06:13:17Z</t>
+  </si>
+  <si>
     <t>2026-06-10T01:25:11Z</t>
   </si>
   <si>
-    <t>2026-06-10T01:25:09Z</t>
-  </si>
-  <si>
-    <t>2026-06-10T01:25:08Z</t>
+    <t>2026-06-14T01:25:24Z</t>
+  </si>
+  <si>
+    <t>2026-06-27T04:39:43Z</t>
+  </si>
+  <si>
+    <t>2026-05-19T01:22:26Z</t>
+  </si>
+  <si>
+    <t>2026-06-24T04:40:22Z</t>
+  </si>
+  <si>
+    <t>2026-06-02T04:44:07Z</t>
+  </si>
+  <si>
+    <t>2026-05-19T01:49:25Z</t>
+  </si>
+  <si>
+    <t>2026-06-24T04:40:08Z</t>
+  </si>
+  <si>
+    <t>2026-06-21T04:40:01Z</t>
+  </si>
+  <si>
+    <t>2026-02-27T06:20:02Z</t>
+  </si>
+  <si>
+    <t>2026-08-06T23:06:22Z</t>
+  </si>
+  <si>
+    <t>2026-06-27T04:38:28Z</t>
+  </si>
+  <si>
+    <t>2026-02-19T14:53:01Z</t>
+  </si>
+  <si>
+    <t>2026-06-26T04:38:47Z</t>
   </si>
   <si>
     <t>2026-06-21T04:40:06Z</t>
   </si>
   <si>
-    <t>2026-06-10T01:25:10Z</t>
-  </si>
-  <si>
-    <t>2026-06-10T01:25:05Z</t>
-  </si>
-  <si>
-    <t>2026-06-11T01:25:35Z</t>
-  </si>
-  <si>
-    <t>2026-06-27T04:38:05Z</t>
-  </si>
-  <si>
-    <t>2026-06-10T01:25:23Z</t>
-  </si>
-  <si>
-    <t>2026-03-01T06:13:17Z</t>
-  </si>
-  <si>
-    <t>2026-06-27T04:39:43Z</t>
-  </si>
-  <si>
-    <t>2026-06-14T01:25:24Z</t>
-  </si>
-  <si>
-    <t>2026-05-19T01:22:26Z</t>
-  </si>
-  <si>
-    <t>2026-06-24T04:40:22Z</t>
-  </si>
-  <si>
-    <t>2026-06-02T04:44:07Z</t>
-  </si>
-  <si>
-    <t>2026-05-19T01:49:25Z</t>
-  </si>
-  <si>
-    <t>2026-06-26T04:38:47Z</t>
-  </si>
-  <si>
-    <t>2026-06-24T04:40:08Z</t>
-  </si>
-  <si>
-    <t>2026-06-21T04:40:01Z</t>
-  </si>
-  <si>
-    <t>2026-02-27T06:20:02Z</t>
-  </si>
-  <si>
-    <t>2026-08-06T23:06:22Z</t>
-  </si>
-  <si>
-    <t>2026-06-27T04:38:28Z</t>
-  </si>
-  <si>
-    <t>2026-02-19T14:53:01Z</t>
-  </si>
-  <si>
-    <t>2026-09-01T15:09:28Z</t>
+    <t>2026-03-02T06:21:37Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T01:26:02Z</t>
   </si>
   <si>
     <t>2026-06-13T01:26:03Z</t>
   </si>
   <si>
-    <t>2026-06-13T01:26:02Z</t>
-  </si>
-  <si>
-    <t>2026-03-02T06:21:37Z</t>
+    <t>2026-06-20T15:02:26Z</t>
+  </si>
+  <si>
+    <t>2026-03-08T18:43:42Z</t>
+  </si>
+  <si>
+    <t>2026-08-17T22:45:29Z</t>
+  </si>
+  <si>
+    <t>2026-08-04T09:44:16Z</t>
+  </si>
+  <si>
+    <t>2026-02-16T19:13:54Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T01:25:32Z</t>
   </si>
   <si>
     <t>2026-07-19T00:35:03Z</t>
   </si>
   <si>
-    <t>2026-06-13T01:25:32Z</t>
-  </si>
-  <si>
-    <t>2026-06-20T15:02:26Z</t>
-  </si>
-  <si>
-    <t>2026-03-08T18:43:42Z</t>
-  </si>
-  <si>
-    <t>2026-08-04T09:44:16Z</t>
-  </si>
-  <si>
-    <t>2026-08-17T22:45:29Z</t>
-  </si>
-  <si>
-    <t>2026-02-16T19:13:54Z</t>
+    <t>2026-05-18T14:16:58Z</t>
+  </si>
+  <si>
+    <t>2026-03-03T08:16:56Z</t>
   </si>
   <si>
     <t>2026-05-18T22:04:50Z</t>
   </si>
   <si>
-    <t>2026-05-18T14:16:58Z</t>
-  </si>
-  <si>
-    <t>2026-03-03T08:16:56Z</t>
-  </si>
-  <si>
     <t>2026-06-20T15:03:01Z</t>
   </si>
   <si>
+    <t>2026-02-03T08:16:51Z</t>
+  </si>
+  <si>
+    <t>2026-06-11T01:25:14Z</t>
+  </si>
+  <si>
+    <t>2026-06-12T01:25:06Z</t>
+  </si>
+  <si>
+    <t>2026-06-23T22:40:47Z</t>
+  </si>
+  <si>
+    <t>2026-06-24T22:26:15Z</t>
+  </si>
+  <si>
+    <t>2026-06-25T04:39:03Z</t>
+  </si>
+  <si>
     <t>2026-03-03T07:20:54Z</t>
   </si>
   <si>
-    <t>2026-06-11T01:25:14Z</t>
-  </si>
-  <si>
-    <t>2026-09-01T17:14:04Z</t>
-  </si>
-  <si>
-    <t>2026-02-03T08:16:51Z</t>
-  </si>
-  <si>
-    <t>2026-06-12T01:25:06Z</t>
-  </si>
-  <si>
-    <t>2026-06-23T22:40:47Z</t>
-  </si>
-  <si>
-    <t>2026-06-24T22:26:15Z</t>
-  </si>
-  <si>
-    <t>2026-06-25T04:39:03Z</t>
-  </si>
-  <si>
     <t>2026-06-06T21:04:18Z</t>
   </si>
   <si>
@@ -982,12 +982,12 @@
     <t>2026-01-30T19:57:29Z</t>
   </si>
   <si>
+    <t>2026-06-26T09:37:17Z</t>
+  </si>
+  <si>
     <t>2026-07-17T12:36:52Z</t>
   </si>
   <si>
-    <t>2026-06-26T09:37:17Z</t>
-  </si>
-  <si>
     <t>2026-06-13T01:25:23Z</t>
   </si>
   <si>
@@ -1018,24 +1018,27 @@
     <t>2026-06-15T01:25:19Z</t>
   </si>
   <si>
+    <t>2026-07-17T15:20:38Z</t>
+  </si>
+  <si>
     <t>2026-06-14T01:25:52Z</t>
   </si>
   <si>
+    <t>2026-06-15T01:25:13Z</t>
+  </si>
+  <si>
+    <t>2026-06-24T04:38:39Z</t>
+  </si>
+  <si>
+    <t>2026-06-22T04:40:24Z</t>
+  </si>
+  <si>
+    <t>2026-02-02T18:45:46Z</t>
+  </si>
+  <si>
     <t>2026-06-15T01:25:20Z</t>
   </si>
   <si>
-    <t>2026-06-15T01:25:13Z</t>
-  </si>
-  <si>
-    <t>2026-06-24T04:38:39Z</t>
-  </si>
-  <si>
-    <t>2026-06-22T04:40:24Z</t>
-  </si>
-  <si>
-    <t>2026-02-02T18:45:46Z</t>
-  </si>
-  <si>
     <t>2026-06-14T01:25:41Z</t>
   </si>
   <si>
@@ -1054,33 +1057,30 @@
     <t>2026-06-14T01:25:31Z</t>
   </si>
   <si>
+    <t>2026-03-04T06:35:02Z</t>
+  </si>
+  <si>
+    <t>2026-04-28T19:12:44Z</t>
+  </si>
+  <si>
+    <t>2026-08-09T22:45:34Z</t>
+  </si>
+  <si>
+    <t>2026-03-04T06:25:58Z</t>
+  </si>
+  <si>
+    <t>2026-05-22T18:44:18Z</t>
+  </si>
+  <si>
+    <t>2026-02-27T06:15:15Z</t>
+  </si>
+  <si>
+    <t>2026-06-10T01:25:25Z</t>
+  </si>
+  <si>
     <t>2026-05-19T00:41:40Z</t>
   </si>
   <si>
-    <t>2026-03-04T06:35:02Z</t>
-  </si>
-  <si>
-    <t>2026-04-28T19:12:44Z</t>
-  </si>
-  <si>
-    <t>2026-07-17T15:20:38Z</t>
-  </si>
-  <si>
-    <t>2026-08-09T22:45:34Z</t>
-  </si>
-  <si>
-    <t>2026-03-04T06:25:58Z</t>
-  </si>
-  <si>
-    <t>2026-05-22T18:44:18Z</t>
-  </si>
-  <si>
-    <t>2026-02-27T06:15:15Z</t>
-  </si>
-  <si>
-    <t>2026-06-10T01:25:25Z</t>
-  </si>
-  <si>
     <t>2026-06-13T01:25:57Z</t>
   </si>
   <si>
@@ -1135,18 +1135,18 @@
     <t>2026-08-06T15:58:24Z</t>
   </si>
   <si>
+    <t>2026-06-15T07:20:54Z</t>
+  </si>
+  <si>
+    <t>2026-06-22T04:39:28Z</t>
+  </si>
+  <si>
     <t>2026-08-25T22:48:38Z</t>
   </si>
   <si>
-    <t>2026-06-22T04:39:28Z</t>
-  </si>
-  <si>
     <t>2026-06-22T04:40:09Z</t>
   </si>
   <si>
-    <t>2026-06-15T07:20:54Z</t>
-  </si>
-  <si>
     <t>2026-08-11T08:53:09Z</t>
   </si>
   <si>
@@ -1186,12 +1186,12 @@
     <t>2026-06-24T04:39:16Z</t>
   </si>
   <si>
+    <t>2026-08-25T22:48:26Z</t>
+  </si>
+  <si>
     <t>2026-06-27T04:39:38Z</t>
   </si>
   <si>
-    <t>2026-08-25T22:48:26Z</t>
-  </si>
-  <si>
     <t>2026-06-25T19:15:56Z</t>
   </si>
   <si>
@@ -1216,42 +1216,42 @@
     <t>2026-02-13T19:03:53Z</t>
   </si>
   <si>
+    <t>2026-06-26T04:39:20Z</t>
+  </si>
+  <si>
+    <t>2026-03-02T07:51:39Z</t>
+  </si>
+  <si>
+    <t>2026-07-15T12:40:22Z</t>
+  </si>
+  <si>
     <t>2026-08-01T15:05:17Z</t>
   </si>
   <si>
-    <t>2026-06-26T04:39:20Z</t>
-  </si>
-  <si>
-    <t>2026-07-15T12:40:22Z</t>
-  </si>
-  <si>
-    <t>2026-03-02T07:51:39Z</t>
-  </si>
-  <si>
     <t>2026-04-28T18:14:14Z</t>
   </si>
   <si>
     <t>2026-08-18T22:47:41Z</t>
   </si>
   <si>
+    <t>2026-07-16T12:26:58Z</t>
+  </si>
+  <si>
+    <t>2026-07-26T12:24:35Z</t>
+  </si>
+  <si>
+    <t>2026-07-15T12:40:07Z</t>
+  </si>
+  <si>
+    <t>2026-07-15T12:40:05Z</t>
+  </si>
+  <si>
+    <t>2026-08-17T22:45:34Z</t>
+  </si>
+  <si>
     <t>2026-08-14T14:27:52Z</t>
   </si>
   <si>
-    <t>2026-07-26T12:24:35Z</t>
-  </si>
-  <si>
-    <t>2026-07-15T12:40:07Z</t>
-  </si>
-  <si>
-    <t>2026-07-15T12:40:05Z</t>
-  </si>
-  <si>
-    <t>2026-07-16T12:26:58Z</t>
-  </si>
-  <si>
-    <t>2026-08-17T22:45:34Z</t>
-  </si>
-  <si>
     <t>2026-08-18T19:02:07Z</t>
   </si>
   <si>
@@ -1270,27 +1270,27 @@
     <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00033599']</t>
   </si>
   <si>
+    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00029930']</t>
+  </si>
+  <si>
+    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027256']</t>
+  </si>
+  <si>
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00051183']</t>
   </si>
   <si>
-    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00029930']</t>
-  </si>
-  <si>
-    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027256']</t>
-  </si>
-  <si>
     <t>[]</t>
   </si>
   <si>
+    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00016878']</t>
+  </si>
+  <si>
+    <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00001588']</t>
+  </si>
+  <si>
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027343']</t>
   </si>
   <si>
-    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00016878']</t>
-  </si>
-  <si>
-    <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00001588']</t>
-  </si>
-  <si>
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00026875']</t>
   </si>
   <si>
@@ -1309,18 +1309,18 @@
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027149']</t>
   </si>
   <si>
+    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00054797']</t>
+  </si>
+  <si>
+    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00053950']</t>
+  </si>
+  <si>
+    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00051138']</t>
+  </si>
+  <si>
     <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00006179']</t>
   </si>
   <si>
-    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00053950']</t>
-  </si>
-  <si>
-    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00054797']</t>
-  </si>
-  <si>
-    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00051138']</t>
-  </si>
-  <si>
     <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00007948']</t>
   </si>
   <si>
@@ -1369,21 +1369,21 @@
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00054796']</t>
   </si>
   <si>
+    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027113']</t>
+  </si>
+  <si>
+    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00051403']</t>
+  </si>
+  <si>
+    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00017330']</t>
+  </si>
+  <si>
+    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031059']</t>
+  </si>
+  <si>
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031667']</t>
   </si>
   <si>
-    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00051403']</t>
-  </si>
-  <si>
-    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027113']</t>
-  </si>
-  <si>
-    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031059']</t>
-  </si>
-  <si>
-    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00017330']</t>
-  </si>
-  <si>
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031502']</t>
   </si>
   <si>
@@ -1405,6 +1405,9 @@
     <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00028528']</t>
   </si>
   <si>
+    <t>['ftunivromairis:oai:iris.uniroma1.it:11573_1183823', 'ftchacadscienegi:oai:ir.xjlas.org:365004_10838']</t>
+  </si>
+  <si>
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027254']</t>
   </si>
   <si>
@@ -1426,9 +1429,6 @@
     <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00007367']</t>
   </si>
   <si>
-    <t>['ftunivromairis:oai:iris.uniroma1.it:11573_1183823', 'ftchacadscienegi:oai:ir.xjlas.org:365004_10838']</t>
-  </si>
-  <si>
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031517']</t>
   </si>
   <si>
@@ -1459,24 +1459,24 @@
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00017706']</t>
   </si>
   <si>
+    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00039162']</t>
+  </si>
+  <si>
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00025143']</t>
   </si>
   <si>
-    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00039162']</t>
-  </si>
-  <si>
     <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00027122']</t>
   </si>
   <si>
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00042635']</t>
   </si>
   <si>
+    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00017254']</t>
+  </si>
+  <si>
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00017058']</t>
   </si>
   <si>
-    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00017254']</t>
-  </si>
-  <si>
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00049323']</t>
   </si>
   <si>
@@ -1498,15 +1498,21 @@
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00037313']</t>
   </si>
   <si>
+    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00037200']</t>
+  </si>
+  <si>
     <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00007323']</t>
   </si>
   <si>
-    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00037200']</t>
-  </si>
-  <si>
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00049255']</t>
   </si>
   <si>
+    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027296']</t>
+  </si>
+  <si>
+    <t>['10.4000_studifrancesi.29891', 'oai:revues.org:studifrancesi_29891']</t>
+  </si>
+  <si>
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027347']</t>
   </si>
   <si>
@@ -1516,87 +1522,81 @@
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027505']</t>
   </si>
   <si>
-    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027296']</t>
-  </si>
-  <si>
-    <t>['10.4000_studifrancesi.29891', 'oai:revues.org:studifrancesi_29891']</t>
-  </si>
-  <si>
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00017331']</t>
   </si>
   <si>
+    <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00007512']</t>
+  </si>
+  <si>
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00039177']</t>
   </si>
   <si>
-    <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00007512']</t>
+    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00052047']</t>
   </si>
   <si>
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00039209']</t>
   </si>
   <si>
-    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00052047']</t>
-  </si>
-  <si>
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031570']</t>
   </si>
   <si>
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027467']</t>
   </si>
   <si>
+    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00017321']</t>
+  </si>
+  <si>
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00047593']</t>
   </si>
   <si>
+    <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00007328']</t>
+  </si>
+  <si>
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00017206']</t>
   </si>
   <si>
-    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00017321']</t>
+    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00049001']</t>
   </si>
   <si>
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00039169']</t>
   </si>
   <si>
-    <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00007328']</t>
-  </si>
-  <si>
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027307']</t>
   </si>
   <si>
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00025316']</t>
   </si>
   <si>
+    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027484']</t>
+  </si>
+  <si>
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031519']</t>
   </si>
   <si>
-    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00049001']</t>
+    <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00007310']</t>
+  </si>
+  <si>
+    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027516']</t>
   </si>
   <si>
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00039193']</t>
   </si>
   <si>
-    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027516']</t>
-  </si>
-  <si>
-    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027484']</t>
-  </si>
-  <si>
-    <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00007310']</t>
-  </si>
-  <si>
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027298']</t>
   </si>
   <si>
+    <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00030989']</t>
+  </si>
+  <si>
+    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031158']</t>
+  </si>
+  <si>
+    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00041631']</t>
+  </si>
+  <si>
     <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00001808', 'ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00030895', 'ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00001726']</t>
   </si>
   <si>
-    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031158']</t>
-  </si>
-  <si>
-    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00041631']</t>
-  </si>
-  <si>
-    <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00030989']</t>
-  </si>
-  <si>
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00030463']</t>
   </si>
   <si>
@@ -1630,49 +1630,52 @@
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00048986']</t>
   </si>
   <si>
+    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027203']</t>
+  </si>
+  <si>
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00026968']</t>
   </si>
   <si>
     <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00007964']</t>
   </si>
   <si>
-    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027203']</t>
-  </si>
-  <si>
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00039312']</t>
   </si>
   <si>
+    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027258']</t>
+  </si>
+  <si>
+    <t>['ftdnbreiheo:99101393X']</t>
+  </si>
+  <si>
+    <t>['10670_1.nqy19h']</t>
+  </si>
+  <si>
+    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00025128']</t>
+  </si>
+  <si>
+    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00054812']</t>
+  </si>
+  <si>
+    <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00034193']</t>
+  </si>
+  <si>
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00026944']</t>
   </si>
   <si>
-    <t>['ftdnbreiheo:99101393X']</t>
-  </si>
-  <si>
-    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027258']</t>
-  </si>
-  <si>
-    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00025128']</t>
-  </si>
-  <si>
-    <t>['10670_1.nqy19h']</t>
-  </si>
-  <si>
-    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00054812']</t>
-  </si>
-  <si>
-    <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00034193']</t>
+    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027504']</t>
   </si>
   <si>
     <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00007995']</t>
   </si>
   <si>
+    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00054805']</t>
+  </si>
+  <si>
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00017203']</t>
   </si>
   <si>
-    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027504']</t>
-  </si>
-  <si>
-    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00054805']</t>
+    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00037196']</t>
   </si>
   <si>
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00017207']</t>
@@ -1681,48 +1684,45 @@
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031508']</t>
   </si>
   <si>
-    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00037196']</t>
+    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00000400']</t>
+  </si>
+  <si>
+    <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00004133']</t>
   </si>
   <si>
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00053483']</t>
   </si>
   <si>
-    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00000400']</t>
+    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00039167']</t>
   </si>
   <si>
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00054063']</t>
   </si>
   <si>
-    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00039167']</t>
+    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027026']</t>
+  </si>
+  <si>
+    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031088']</t>
+  </si>
+  <si>
+    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027293']</t>
+  </si>
+  <si>
+    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00039168']</t>
+  </si>
+  <si>
+    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00037312']</t>
+  </si>
+  <si>
+    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027221']</t>
+  </si>
+  <si>
+    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00049418']</t>
   </si>
   <si>
     <t>['ftkingscollondon:oai:pure.atira.dk:publications_4bf6bc48-ae79-4430-91f2-f2ccde9d69da', 'ftmacquarieunicr:oai:https:__researchers.mq.edu.au:publications_8edd908e-bb65-49ef-add7-90db3e5580eb', 'ftmacquarieunicr:oai:https:__researchers.mq.edu.au:publications_ee33aa0d-b7c9-4741-852d-f00d34269a67', 'ftkingscollondon:oai:pure.atira.dk:publications_63441d11-d044-4b57-9e14-e1d69b555496', 'ftmacquarieunicr:oai:https:__researchers.mq.edu.au:publications_bba016f2-7bfe-4b61-9d91-9e2fb9fa291c', 'ftkingscollondon:oai:pure.atira.dk:publications_572ac9cf-2922-4c19-8129-97629110da35', 'ftkingscollondon:oai:pure.atira.dk:publications_78e566ca-7408-4d28-bf73-74732c5dac93', 'ftkingscollondon:oai:pure.atira.dk:publications_93379499-4afd-4b12-b979-36188760284e', 'ftkingscollondon:oai:pure.atira.dk:publications_37df3d41-0d47-45bd-aa7d-57238cb941ff', 'ftkingscollondon:oai:pure.atira.dk:publications_4900be2f-56e8-4cf4-8d30-d3bd6348a583', 'ftkingscollondon:oai:pure.atira.dk:publications_8a983616-a457-4c3d-93db-73d270216c1e', 'ftkingscollondon:oai:pure.atira.dk:publications_16c33286-b032-4402-bf39-71126ac8b210', 'ftkingscollondon:oai:pure.atira.dk:publications_5365231a-abf8-42a2-b6c7-e7595e75d407', 'ftkingscollondon:oai:pure.atira.dk:publications_5c853fc8-004b-463e-a7bf-5ed79bc5f314', 'ftkingscollondon:oai:pure.atira.dk:publications_c8a42efe-34b5-4711-8156-7db488eecaff', 'ftkingscollondon:oai:pure.atira.dk:publications_026400bd-f68b-4011-aedc-082682bd6b19', 'ftkingscollondon:oai:pure.atira.dk:publications_c14666b4-7a93-47ae-8716-95ee7977f04a', 'ftccsdartic:oai:HAL:hal-01210193v1', 'ftagrocampouest:oai:HAL:hal-01210193v1', 'ftkingscollondon:oai:pure.atira.dk:publications_7695618c-26cd-4bba-82e0-24ab078bc25e', 'ftkingscollondon:oai:pure.atira.dk:publications_d2e1d2f9-4450-444e-9725-4983beff615d', 'ftkingscollondon:oai:pure.atira.dk:publications_459adbf1-0835-4a40-a706-f87a0a5da0a3', 'ftkingscollondon:oai:pure.atira.dk:publications_80266798-d7bd-46db-8239-b2c794b6f6c7', 'ftmacquarieunicr:oai:https:__researchers.mq.edu.au:publications_6a440ed6-0081-40f1-811f-caafb23348fd', 'ftmacquarieunicr:oai:https:__researchers.mq.edu.au:publications_07c19af3-48d2-4fb4-9b39-10be5b356946', 'ftmacquarieunicr:oai:https:__researchers.mq.edu.au:publications_b9589408-c9d3-4f0f-a5f5-0fbbbac4e4f2', 'ftmacquarieunicr:oai:https:__researchers.mq.edu.au:publications_ea43af58-5c19-400c-89c6-0ad998908278', 'ftmacquarieunicr:oai:https:__researchers.mq.edu.au:publications_d274e698-e856-445b-8254-962eca1fb7d8', 'ftpensoft:10.3897_ese.2022.e86910', 'ftzenodo:oai:zenodo.org:1001844', 'ftkingscollondon:oai:pure.atira.dk:publications_511877c0-3b6c-4259-ae9b-87ec7eb09a2b', 'ftkingscollondon:oai:pure.atira.dk:publications_b991b32f-5366-4ab3-82dc-603c76fdf02a', 'ftkingscollondon:oai:pure.atira.dk:publications_4433f79e-1582-4617-af8e-5ee32d89168d', 'ftjeffersonuniv:oai:jdc.jefferson.edu:medfp-1265', 'ftkingscollondon:oai:pure.atira.dk:publications_52af3f7c-04c7-4d7b-92be-8a0caac96f66', 'ftunivbathcris:oai:purehost.bath.ac.uk:publications_d2e1d919-b7b8-48df-8c3b-8692cb446aed', 'ftunivbathcris:oai:purehost.bath.ac.uk:publications_6fd1e916-cb40-4bcd-833c-9b60d86ff91a', 'ftkingscollondon:oai:pure.atira.dk:publications_470dda0c-7b7c-439c-a478-6ff16a765bb0', 'ftkingscollondon:oai:pure.atira.dk:publications_5837e4fe-466f-4516-897b-0966eeeeb617', 'ftkingscollondon:oai:pure.atira.dk:publications_e8cb5c61-7e3a-45aa-8eef-51a2d81c6916', 'ftmyresearchjour:oai:ojs.myresearchjournals.com:article_5875', 'ftkingscollondon:oai:pure.atira.dk:publications_89bd4390-c82e-47dd-af46-2c4699ed01c0', 'ftkingscollondon:oai:pure.atira.dk:publications_d3750172-cb7a-4fa2-aeb6-03119c3640ca', 'ftunivmassboston:oai:works.bepress.com:maria_ivanova-1026', 'oai:revues.org:conflits_187', 'oai:revues.org:conflits_58', 'oai:ojs.zrc-sazu.si:article_7056', 'oai:ojs.zrc-sazu.si:article_6702', 'oai:ojs.zrc-sazu.si:article_6701', 'oai:bibliotekanauki.pl:616003', 'oai:bibliotekanauki.pl:616005', 'oai:bibliotekanauki.pl:568134', 'oai:bibliotekanauki.pl:568132', 'oai:bibliotekanauki.pl:568122', 'oai:bibliotekanauki.pl:616187', 'oai:bibliotekanauki.pl:616207', 'oai:bibliotekanauki.pl:616198', 'oai:bibliotekanauki.pl:616224', 'oai:bibliotekanauki.pl:616019', 'oai:bibliotekanauki.pl:642618', 'oai:bibliotekanauki.pl:616154', 'oai:bibliotekanauki.pl:616150', 'oai:bibliotekanauki.pl:616144', 'oai:bibliotekanauki.pl:781487', 'oai:bibliotekanauki.pl:642797', 'oai:bibliotekanauki.pl:615810', 'oai:bibliotekanauki.pl:781430', 'oai:bibliotekanauki.pl:641767', 'oai:bibliotekanauki.pl:616310', 'oai:bibliotekanauki.pl:625550', 'oai:bibliotekanauki.pl:625532', 'oai:bibliotekanauki.pl:625534', 'oai:bibliotekanauki.pl:616140', 'oai:bibliotekanauki.pl:781217', 'oai:bibliotekanauki.pl:923144', 'oai:bibliotekanauki.pl:625469', 'oai:bibliotekanauki.pl:642226', 'oai:bibliotekanauki.pl:616436', 'oai:bibliotekanauki.pl:616430', 'oai:bibliotekanauki.pl:687315', 'oai:bibliotekanauki.pl:1029929', 'oai:bibliotekanauki.pl:909837', 'oai:bibliotekanauki.pl:625247', 'oai:bibliotekanauki.pl:642315', 'oai:bibliotekanauki.pl:642313', 'oai:bibliotekanauki.pl:909496', 'oai:bibliotekanauki.pl:615798', 'oai:bibliotekanauki.pl:615778', 'oai:bibliotekanauki.pl:615786', 'oai:bibliotekanauki.pl:642856', 'oai:bibliotekanauki.pl:642884', 'oai:bibliotekanauki.pl:616794', 'oai:bibliotekanauki.pl:923198', 'oai:bibliotekanauki.pl:616086', 'oai:bibliotekanauki.pl:625345', 'oai:bibliotekanauki.pl:625343', 'oai:bibliotekanauki.pl:909558', 'oai:bibliotekanauki.pl:642719', 'oai:bibliotekanauki.pl:615690', 'oai:bibliotekanauki.pl:620475', 'oai:bibliotekanauki.pl:620472', 'oai:bibliotekanauki.pl:615728', 'oai:bibliotekanauki.pl:616964', 'oai:bibliotekanauki.pl:642246', 'oai:bibliotekanauki.pl:642242', 'oai:bibliotekanauki.pl:641853', 'oai:bibliotekanauki.pl:641867', 'oai:bibliotekanauki.pl:641869', 'oai:bibliotekanauki.pl:615896', 'oai:bibliotekanauki.pl:615908', 'oai:bibliotekanauki.pl:625741', 'oai:bibliotekanauki.pl:695775', 'oai:bibliotekanauki.pl:695777', 'oai:bibliotekanauki.pl:642317', 'oai:bibliotekanauki.pl:642319', 'oai:bibliotekanauki.pl:642099', 'oai:bibliotekanauki.pl:687223', 'oai:bibliotekanauki.pl:641953', 'oai:bibliotekanauki.pl:641955', 'oai:bibliotekanauki.pl:642583', 'oai:bibliotekanauki.pl:641795', 'oai:bibliotekanauki.pl:625843', 'oai:bibliotekanauki.pl:618071', 'oai:bibliotekanauki.pl:618069', 'oai:bibliotekanauki.pl:568040', 'oai:bibliotekanauki.pl:568042', 'oai:bibliotekanauki.pl:642678', 'oai:bibliotekanauki.pl:642652', 'oai:bibliotekanauki.pl:642819', 'oai:bibliotekanauki.pl:616332', 'oai:bibliotekanauki.pl:642381', 'oai:bibliotekanauki.pl:642391', 'oai:bibliotekanauki.pl:616354', 'oai:bibliotekanauki.pl:642379', 'oai:bibliotekanauki.pl:642365', 'oai:bibliotekanauki.pl:615776', '10670_1.dsuk4q', '10670_1.nmt64x', '10670_1.8epaeq', '10670_1.vknmj2', '10670_1.x9kbtp', '10670_1.191k89', '10670_1.8b2e1i', '10670_1.cg0fc4', '10670_1.6yl2ek']</t>
   </si>
   <si>
-    <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00004133']</t>
-  </si>
-  <si>
-    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027026']</t>
-  </si>
-  <si>
-    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00039168']</t>
-  </si>
-  <si>
-    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031088']</t>
-  </si>
-  <si>
-    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027293']</t>
-  </si>
-  <si>
-    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00049418']</t>
-  </si>
-  <si>
-    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027221']</t>
-  </si>
-  <si>
-    <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00037312']</t>
-  </si>
-  <si>
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00037158']</t>
   </si>
   <si>
@@ -1732,24 +1732,24 @@
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027469']</t>
   </si>
   <si>
+    <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00007955']</t>
+  </si>
+  <si>
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027524']</t>
   </si>
   <si>
-    <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00007955']</t>
-  </si>
-  <si>
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00029825']</t>
   </si>
   <si>
     <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00007988']</t>
   </si>
   <si>
+    <t>['http:__hdl.handle.net_2078.1_93371']</t>
+  </si>
+  <si>
     <t>['ftunivgranada:oai:digibug.ugr.es:10481_101254']</t>
   </si>
   <si>
-    <t>['http:__hdl.handle.net_2078.1_93371']</t>
-  </si>
-  <si>
     <t>['http:__hdl.handle.net_2078.1_157386']</t>
   </si>
   <si>
@@ -1762,51 +1762,51 @@
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00016930']</t>
   </si>
   <si>
+    <t>['http:__hdl.handle.net_2078.1_119207']</t>
+  </si>
+  <si>
+    <t>['ftunibolognairis:oai:cris.unibo.it:11585_996293']</t>
+  </si>
+  <si>
+    <t>['oai:doaj.org_article:0a5c7a6ead684c1dabc01f9fa8198803']</t>
+  </si>
+  <si>
+    <t>['10670_1.bmrgmu']</t>
+  </si>
+  <si>
+    <t>['ftunivutahsqcl:oai:dc.law.utah.edu:ulr-1950']</t>
+  </si>
+  <si>
+    <t>['ftcoventryuniv:tle:086edc0d-902a-9d3a-ebec-45c5e6aea198:2fa872f8-6189-4232-b228-bd31f47934f5:1', 'ftcoventryuniv:tle:7f6b3989-3bc9-a314-f868-3f84b6985c0e:2fa872f8-6189-4232-b228-bd31f47934f5:1', 'ftunibolognairis:oai:cris.unibo.it:11585_784318', 'ftcoventryuniv:tle:0e5eb7b7-931a-f9ea-9052-1ee4dddd6bec:2fa872f8-6189-4232-b228-bd31f47934f5:1', 'ftcoventryuniv:tle:9bc599aa-75eb-46df-974f-a2fa8d0927eb:2fa872f8-6189-4232-b228-bd31f47934f5:1', 'ftcoventryuniv:tle:a1b6d5a3-550f-513c-7fd4-a86f37315aa6:2fa872f8-6189-4232-b228-bd31f47934f5:1']</t>
+  </si>
+  <si>
+    <t>['oai:doaj.org_article:4678abb0f1ce44a291a2365976c3d3ea', 'oai:doaj.org_article:569b16e88fe8454eabd2c12aa8fd149e', 'oai:doaj.org_article:a24dc89b77ab4505ba31c658810251ae']</t>
+  </si>
+  <si>
+    <t>['10.12681_hnps.2868']</t>
+  </si>
+  <si>
+    <t>['10670_1.tvbcxa']</t>
+  </si>
+  <si>
     <t>['oai:doaj.org_article:5b0f18f989334bc2a87f811e7da0e886']</t>
   </si>
   <si>
-    <t>['http:__hdl.handle.net_2078.1_119207']</t>
-  </si>
-  <si>
-    <t>['ftunibolognairis:oai:cris.unibo.it:11585_996293']</t>
-  </si>
-  <si>
-    <t>['oai:doaj.org_article:0a5c7a6ead684c1dabc01f9fa8198803']</t>
-  </si>
-  <si>
-    <t>['10670_1.bmrgmu']</t>
-  </si>
-  <si>
-    <t>['ftcoventryuniv:tle:086edc0d-902a-9d3a-ebec-45c5e6aea198:2fa872f8-6189-4232-b228-bd31f47934f5:1', 'ftcoventryuniv:tle:7f6b3989-3bc9-a314-f868-3f84b6985c0e:2fa872f8-6189-4232-b228-bd31f47934f5:1', 'ftunibolognairis:oai:cris.unibo.it:11585_784318', 'ftcoventryuniv:tle:0e5eb7b7-931a-f9ea-9052-1ee4dddd6bec:2fa872f8-6189-4232-b228-bd31f47934f5:1', 'ftcoventryuniv:tle:9bc599aa-75eb-46df-974f-a2fa8d0927eb:2fa872f8-6189-4232-b228-bd31f47934f5:1', 'ftcoventryuniv:tle:a1b6d5a3-550f-513c-7fd4-a86f37315aa6:2fa872f8-6189-4232-b228-bd31f47934f5:1']</t>
-  </si>
-  <si>
-    <t>['10670_1.tvbcxa']</t>
-  </si>
-  <si>
-    <t>['oai:doaj.org_article:4678abb0f1ce44a291a2365976c3d3ea', 'oai:doaj.org_article:569b16e88fe8454eabd2c12aa8fd149e', 'oai:doaj.org_article:a24dc89b77ab4505ba31c658810251ae']</t>
-  </si>
-  <si>
-    <t>['ftunivutahsqcl:oai:dc.law.utah.edu:ulr-1950']</t>
-  </si>
-  <si>
     <t>['http:__hdl.handle.net_2078.1_157371']</t>
   </si>
   <si>
-    <t>['10.12681_hnps.2868']</t>
+    <t>['ftunivmonsojs:oai:orbi.umons.ac.be:20.500.12907_11744']</t>
   </si>
   <si>
     <t>['ftunivmonsojs:oai:orbi.umons.ac.be:20.500.12907_7768']</t>
   </si>
   <si>
-    <t>['ftunivmonsojs:oai:orbi.umons.ac.be:20.500.12907_11744']</t>
+    <t>['oai:doaj.org_article:6cad0918c18b4152bfaf8ce87c4ab44c', 'oai:doaj.org_article:a89e7cc9df4b478b9e88112b802bfe17']</t>
   </si>
   <si>
     <t>['ftmdpi:oai:mdpi.com:_2077-1444_10_7_402_']</t>
   </si>
   <si>
-    <t>['oai:doaj.org_article:6cad0918c18b4152bfaf8ce87c4ab44c', 'oai:doaj.org_article:a89e7cc9df4b478b9e88112b802bfe17']</t>
-  </si>
-  <si>
     <t>['10670_1.aevltb']</t>
   </si>
   <si>
@@ -1819,54 +1819,54 @@
     <t>['ftvuamstcris:oai:research.vu.nl:publications_ef0639da-1acb-4610-86f7-6c117fb5d2a0']</t>
   </si>
   <si>
+    <t>['oai:doaj.org_article:686d347e8a394eb4a0770fe914d6215d']</t>
+  </si>
+  <si>
+    <t>['ftnowahutadl:oai:cyfrowa.biblioteka.krakow.pl:687']</t>
+  </si>
+  <si>
+    <t>['http:__hdl.handle.net_2078.1_157380']</t>
+  </si>
+  <si>
+    <t>['10670_1.7lxfk7']</t>
+  </si>
+  <si>
+    <t>['ftnowahutadl:oai:cyfrowa.biblioteka.krakow.pl:490']</t>
+  </si>
+  <si>
+    <t>['ftunivlausanne:oai:serval.unil.ch:BIB_41058']</t>
+  </si>
+  <si>
+    <t>['http:__hdl.handle.net_2078.1_132973']</t>
+  </si>
+  <si>
     <t>['ftumeauniv:oai:DiVA.org:umu-181780']</t>
   </si>
   <si>
-    <t>['oai:doaj.org_article:686d347e8a394eb4a0770fe914d6215d']</t>
-  </si>
-  <si>
-    <t>['http:__hdl.handle.net_2078.1_157380']</t>
-  </si>
-  <si>
-    <t>['ftnowahutadl:oai:cyfrowa.biblioteka.krakow.pl:687']</t>
-  </si>
-  <si>
-    <t>['10670_1.7lxfk7']</t>
-  </si>
-  <si>
-    <t>['http:__hdl.handle.net_2078.1_132973']</t>
-  </si>
-  <si>
-    <t>['ftnowahutadl:oai:cyfrowa.biblioteka.krakow.pl:490']</t>
-  </si>
-  <si>
-    <t>['ftunivlausanne:oai:serval.unil.ch:BIB_41058']</t>
-  </si>
-  <si>
     <t>['oai:doaj.org_article:b0cd4eaeb7a64886979501d310987458', 'oai:doaj.org_article:a29f88c6393f4f75834c16f57cae6838', 'oai:doaj.org_article:ce05941d1526401c8526e85fe542f64b', 'oai:doaj.org_article:4c9a0e5fbe714893999e8d5d5e83d343', 'oai:doaj.org_article:a4e50597f9714842a6b16e45c8776c1f', 'oai:doaj.org_article:400339d6c0fe4785afc281bf9866b282', 'oai:doaj.org_article:fa3a2a4b05bd4995bdd630b1ce3b41ed', 'oai:doaj.org_article:2c96ee74f5a2436ab1461aa805b41e3c', 'oai:doaj.org_article:86ebda34c6304e3bafa1d1ef0bc07fac', 'oai:doaj.org_article:e1fc88feb747424ab90bb7755fc1b1a8']</t>
   </si>
   <si>
     <t>['oai:doaj.org_article:bb43aade4eaa4d3b820061e8efafe752']</t>
   </si>
   <si>
+    <t>['oai:doaj.org_article:d03a577abc2845d8b3d9e39056bf65f9']</t>
+  </si>
+  <si>
+    <t>['ftunikualalumpur:oai:localhost:123456789_8073']</t>
+  </si>
+  <si>
+    <t>['ftunivgent:oai:archive.ugent.be:8630237']</t>
+  </si>
+  <si>
+    <t>['oai:doaj.org_article:55058a2046bb4b8f9d31bbef710eaa05', 'oai:doaj.org_article:2fb4d89f4c14476a84aa363385cfb248']</t>
+  </si>
+  <si>
+    <t>['ftmdpi:oai:mdpi.com:_2571-9408_2_3_120_']</t>
+  </si>
+  <si>
     <t>['ftjmonthlyrev:oai:ojs.monthlyreviewarchives.org:article_5656', 'ftjmonthlyrev:oai:ojs.monthlyreviewarchives.org:article_5135', 'ftjmonthlyrev:oai:ojs.monthlyreviewarchives.org:article_4457', 'ftjmonthlyrev:oai:ojs.monthlyreviewarchives.org:article_5141', 'ftjmonthlyrev:oai:ojs.monthlyreviewarchives.org:article_4687', 'ftjmonthlyrev:oai:ojs.monthlyreviewarchives.org:article_5874', 'ftjmonthlyrev:oai:ojs.monthlyreviewarchives.org:article_4594', 'ftjmonthlyrev:oai:ojs.monthlyreviewarchives.org:article_4283', 'ftjmonthlyrev:oai:ojs.monthlyreviewarchives.org:article_5352', 'ftjmonthlyrev:oai:ojs.monthlyreviewarchives.org:article_4509', 'ftjmonthlyrev:oai:ojs.monthlyreviewarchives.org:article_4500', 'ftjmonthlyrev:oai:ojs.monthlyreviewarchives.org:article_2644', 'ftjmonthlyrev:oai:ojs.monthlyreviewarchives.org:article_4425', 'ftjmonthlyrev:oai:ojs.monthlyreviewarchives.org:article_5287']</t>
   </si>
   <si>
-    <t>['oai:doaj.org_article:d03a577abc2845d8b3d9e39056bf65f9']</t>
-  </si>
-  <si>
-    <t>['ftunikualalumpur:oai:localhost:123456789_8073']</t>
-  </si>
-  <si>
-    <t>['oai:doaj.org_article:55058a2046bb4b8f9d31bbef710eaa05', 'oai:doaj.org_article:2fb4d89f4c14476a84aa363385cfb248']</t>
-  </si>
-  <si>
-    <t>['ftunivgent:oai:archive.ugent.be:8630237']</t>
-  </si>
-  <si>
-    <t>['ftmdpi:oai:mdpi.com:_2571-9408_2_3_120_']</t>
-  </si>
-  <si>
     <t>['10670_1.rjfbda', 'oai:doaj.org_article:07821213814b4972bf3c04fb424e4def']</t>
   </si>
   <si>
@@ -1885,27 +1885,27 @@
     <t>['ftvifarecht:oai:intrechtdok.de:mir_mods_00019803']</t>
   </si>
   <si>
+    <t>['ftunivarkansasdc:oai:digitalcollections.uark.edu:OzarkFolkSong_1077']</t>
+  </si>
+  <si>
     <t>['ftdoajarticles:oai:doaj.org_article:2ce3722692a049c79230a4494a2a4b8e', 'ftdoajarticles:oai:doaj.org_article:6ddd2eb853a94b97be9ec51cf5e35238']</t>
   </si>
   <si>
     <t>['ftuniljubljanaff:oai:ojs.revije.ff.uni-lj.si:article_9444', 'ftuniljubljanaff:oai:ojs.revije.ff.uni-lj.si:article_9445', 'ftuniljubljanaff:oai:ojs.revije.ff.uni-lj.si:article_9866']</t>
   </si>
   <si>
-    <t>['ftunivarkansasdc:oai:digitalcollections.uark.edu:OzarkFolkSong_1077']</t>
-  </si>
-  <si>
     <t>['10670_1.od585o']</t>
   </si>
   <si>
     <t>['ftopenagrarojs:oai:jki:article_1609']</t>
   </si>
   <si>
+    <t>['ftnyorkheritage:oai:cdm16694.contentdm.oclc.org:cgc_222', 'ftnyorkheritage:oai:cdm16694.contentdm.oclc.org:cgc_223']</t>
+  </si>
+  <si>
     <t>['ftolavideuniv:oai:rio.upo.es:10433_15228', 'oai:doaj.org_article:f76f6a25c373490e8d95706e43469583', 'http:__hdl.handle.net_10251_138776', 'ftunivpvalencia:oai:riunet.upv.es:10251_138776']</t>
   </si>
   <si>
-    <t>['ftnyorkheritage:oai:cdm16694.contentdm.oclc.org:cgc_222', 'ftnyorkheritage:oai:cdm16694.contentdm.oclc.org:cgc_223']</t>
-  </si>
-  <si>
     <t>['ftopenedition:oai:hypotheses.org:academies_9742', 'ftopenedition:oai:hypotheses.org:academies_9781', 'ftopenedition:oai:hypotheses.org:academies_9627', 'ftopenedition:oai:hypotheses.org:academies_9859', 'ftopenedition:oai:hypotheses.org:academies_9649', 'ftopenedition:oai:hypotheses.org:academies_9822', 'ftopenedition:oai:hypotheses.org:academies_9806', 'ftopenedition:oai:hypotheses.org:academies_9867']</t>
   </si>
   <si>
@@ -2026,189 +2026,189 @@
     <t>['ftcolumbiauniojs:oai:ojs.cu.submissions:article_13569', 'ftcolumbiauniojs:oai:ojs.cu.submissions:article_13651', 'ftcolumbiauniojs:oai:ojs.cu.submissions:article_13583']</t>
   </si>
   <si>
+    <t>['oai:doaj.org_article:8369fdd2df1d45149f1d9c8d7a017968', 'oai:doaj.org_article:6df2a7a8b1c94a4c9223c3c9f9823033', 'ftkingscollondon:oai:pure.atira.dk:publications_4582a4de-6744-4d1d-9021-28cffba5a4fa', 'ftunivgeneve:oai:unige.ch:unige:155232', 'ftinserm:oai:HAL:hal-03691657v1', 'ftoslouniv:oai:www.duo.uio.no:10852_93886', 'ftpubmed:oai:pubmedcentral.nih.gov:9010705', 'ftriip:oai:HAL:hal-03691657v1', 'ftpubmed:oai:pubmedcentral.nih.gov:9432753', 'ftpubmed:oai:pubmedcentral.nih.gov:4073248', 'ftworldbank:oai:openknowledge.worldbank.org:10986_34814', 'ftworldbank:oai:openknowledge.worldbank.org:10986_34926', 'oai:journals.um.si:article_97', 'oai:doaj.org_article:07c100a6ce324817b377171803c4855c', 'oai:doaj.org_article:5e6e2148c23c49a895791f48e61e0f85', 'ftunivliverpool:oai:livrepository.liverpool.ac.uk:3025011', 'ftpubmed:oai:pubmedcentral.nih.gov:9367745', 'ftdoajarticles:oai:doaj.org_article:95551ebe180740758115cd881e9ac8b7', 'ftdoajarticles:oai:doaj.org_article:c140614342044ce4bbde4a30eaac9bf0', 'ftleedsuniv:oai:eprints.whiterose.ac.uk:104170', 'ftunivessex:oai:repository.essex.ac.uk:33461', 'ftpubmed:oai:pubmedcentral.nih.gov:4593291', 'ftunivliverpool:oai:livrepository.liverpool.ac.uk:3154321', 'ftleedsuniv:oai:eprints.whiterose.ac.uk:185808', 'ftcovenantuniv:oai:generic.eprints.org:5719', 'ftdoajarticles:oai:doaj.org_article:3a88852d88af4eb6aa73cbcffaf685f1', 'ftdoajarticles:oai:doaj.org_article:fc6357040ca64fc984ecc96e77c19246', 'ftunivleuven:oai:lirias.kuleuven.be:123456789_186665', 'ftceon:oai:depot.ceon.pl:123456789_956', 'ftphilpapers:oai:philpapers.org_rec_BROPEI-3', 'fthrcak:oai:hrcak.srce.hr:23346', 'fthrcak:oai:hrcak.srce.hr:183381', 'ftpubmed:oai:pubmedcentral.nih.gov:9475410', 'ftpubmed:oai:pubmedcentral.nih.gov:6720555', 'ftpubmed:oai:pubmedcentral.nih.gov:6889688', 'ftdoajarticles:oai:doaj.org_article:e16060828b60400c8603cd37cc9c8bca', 'ftdoajarticles:oai:doaj.org_article:36a225556c5a49b59def089a10a3279d', 'ftpubmed:oai:pubmedcentral.nih.gov:3933755', 'ftliverpoolstm:oai:archive.lstmed.ac.uk:7509', 'ftumanchesterpub:oai:pure.atira.dk:publications_33ff92cc-eed4-48f0-994c-1d0acd19f1b1', 'ftihswien:oai::5894', 'fthrcak:oai:hrcak.srce.hr:305985', 'ftdoajarticles:oai:doaj.org_article:26792694c774410fa08312683c886acb', 'ftpubmed:oai:pubmedcentral.nih.gov:7249676', 'ftfrontimediafig:oai:figshare.com:article_24277543', 'ftkingscollondon:oai:pure.atira.dk:publications_61e4ab0e-4f28-4d5d-8892-ff443575e192', 'ftpubmed:oai:pubmedcentral.nih.gov:7791849', 'ftunivmilanobic:oai:boa.unimib.it:10281_17214', 'ftunivgeneve:oai:unige.ch:aou:unige:155232', 'ftlinnaeusuniv:oai:DiVA.org:lnu-40549', 'ftuniaarhuspubl:oai:pure.atira.dk:publications_c056e602-53da-4e83-b6c2-e824ed1fad77', 'ftkingscollondon:oai:pure.atira.dk:publications_33739829-bd87-4d41-aefa-a2682b49261f', 'ftunivbrescia:oai:iris.unibs.it:11379_539015', 'ftunivmoliseiris:oai:iris.unimol.it:11695_477', 'ftunivsplit:oai:repozitorij.svkst.unist.hr:forenzikast_383', 'ftsydanskunivpub:oai:sdu.dk:publications_5fe40505-6d15-48d8-a337-8a4b619715a9', 'ftuabarcelonapb:oai:ddd.uab.cat:289634', 'ftupompeufabra:oai:repositori.upf.edu:10230_49193', 'fthrcak:oai:hrcak.srce.hr:246902', 'ftkingscollondon:oai:pure.atira.dk:publications_7639c966-fbe8-40b8-a325-b2e0ef05c1eb', 'ftcopenhagenunip:oai:pure.atira.dk:publications_ad997fd8-6115-47bf-aeba-71be699f3876', 'ftdnbreiheo:1250067170', 'ftunivgenova:oai:iris.unige.it:11567_503755', 'ftunivrijeka:oai:www.unirepository.svkri.uniri.hr:fthm_2708', 'ftunivrijeka:oai:www.unirepository.svkri.uniri.hr:fthm_3186', 'ftuwarwick:oai:wrap.warwick.ac.uk:146855', 'ftunivzuerich:oai:www.zora.uzh.ch:124548', 'ftiesbelgrad:oai:ebooks.ien.bg.ac.rs:115', 'ftdoajarticles:oai:doaj.org_article:9ca531890bfb427aa611cda3a2e33f51', 'ftpubmed:oai:pubmedcentral.nih.gov:7721354', 'ftvuamstcris:oai:research.vu.nl:publications_b8285cbe-722e-4f6f-b330-ec080e36b8f0', 'ftlondoneconom:oai:eprints.lse.ac.uk:116626', 'ftvuamsterumc:oai:pure.atira.dk:publications_05a186a1-525e-4360-85df-e8d088513ba5', 'ftvuamsterumc:oai:pure.atira.dk:publications_68587b22-f052-4021-ba9c-bafee1b35498', 'ftworldbank:oai:openknowledge.worldbank.org:10986_30579', 'ftglasgowcucris:oai:researchonline.gcu.ac.uk:publications_920c5054-23ff-4a67-ba8d-058a6a413fc5', 'ftnulzagrebzir:oai:zir.nsk.hr:fthm_2708', 'ftnulzagrebzir:oai:zir.nsk.hr:fthm_3186', 'ftnulzagrebzir:oai:zir.nsk.hr:foi_442', 'ftdoajarticles:oai:doaj.org_article:5bf847ecd95046399d35d251c2e96ab7', 'ftdoajarticles:oai:doaj.org_article:e7ac765c353c4cb28b645bafecf3f137', 'oai:doaj.org_article:9ca531890bfb427aa611cda3a2e33f51', 'oai:doaj.org_article:78d8cf2c62c6480eafa3c6b132418c86', 'oai:doaj.org_article:26792694c774410fa08312683c886acb', 'ftlitinstagrecon:oai:elaba:11675971', 'ftpubmed:oai:pubmedcentral.nih.gov:8356263', 'ftpubmed:oai:pubmedcentral.nih.gov:7798200', 'ftpubmed:oai:pubmedcentral.nih.gov:6418058', 'ftzenodo:oai:zenodo.org:7533130', 'ftzenodo:oai:zenodo.org:6683292', 'fthrcak:oai:hrcak.srce.hr:244498', 'ftunivhongkonghu:oai:hub.hku.hk:10722_87806', 'ftdoajarticles:oai:doaj.org_article:25d15b75e8874c7fa5f32662e476caf9', 'ftdoajarticles:oai:doaj.org_article:453b9faf9aa74ebbb23fe2c796485514', 'ftdoajarticles:oai:doaj.org_article:459f202aac0342c2ae503e16f12bce90', 'ftpubmed:oai:pubmedcentral.nih.gov:7231414', 'ftunivfreiburg:oai:freidok.uni-freiburg.de:154085', 'ftpubmed:oai:pubmedcentral.nih.gov:6925899', 'ftunivmaribor:oai:dk.um.si:IzpisGradiva.php?id=67004', 'ftiesbelgrad:oai:ebooks.ien.bg.ac.rs:356', 'ftpubmed:oai:pubmedcentral.nih.gov:6451281', 'ftmdpi:oai:mdpi.com:_1660-4601_19_15_9515_', 'ftuniveastangl:oai:ueaeprints.uea.ac.uk:61475', 'ftnulzagrebzir:oai:zir.nsk.hr:pravo_2876', 'ftiesbelgrad:oai:ebooks.ien.bg.ac.rs:238', 'oai:hrcak.srce.hr:23346', 'oai:hrcak.srce.hr:23005', 'ftjnepaljo:oai:ojs.pkp.sfu.ca:article_2434', 'ftubristolcris:oai:research-information.bris.ac.uk:publications_651775d8-7ee6-436c-ad29-0dab5252df3c', 'ftuniaarhuspubl:oai:pure.atira.dk:publications_6c0494b3-d369-4c19-9bbc-54834abd6d95', 'oai:doaj.org_article:b9dd420ea5f14cf9b67fed9754b57048', 'ftvuamsterumc:oai:pure.atira.dk:publications_eedd93f1-76f9-4d7b-a572-446dacbdc9ed', 'oai:doaj.org_article:453b9faf9aa74ebbb23fe2c796485514', 'ftunivbrescia:oai:iris.unibs.it:11379_503691', 'ftpubmed:oai:pubmedcentral.nih.gov:10293907', 'oai:revues.org:revus_1060', 'ftdoajarticles:oai:doaj.org_article:f2aa7a59ae6241d380fa088455f596e6', 'ftdoajarticles:oai:doaj.org_article:728ec30c13804eac99a0d4999d26f8d6', 'ftdoajarticles:oai:doaj.org_article:43ad06da6431404eb2bbbcbce5774ec5', 'ftdoajarticles:oai:doaj.org_article:05b7aadba8d34aa48204516ded9e20dd', 'ftdoajarticles:oai:doaj.org_article:c519986b58ab4a11be171975d5415cab', 'ftccsdartic:oai:HAL:hal-03691657v1', 'oai:hrcak.srce.hr:19672', 'ftdoajarticles:oai:doaj.org_article:6bf5928a8b2942259fad89ac075e0649', 'ftdoajarticles:oai:doaj.org_article:ca1e7faddd3a4029aeb7c14f8b22aa66', 'ftdoajarticles:oai:doaj.org_article:d4ad8cc55f254374a8b772b18e5943f8', 'ftdoajarticles:oai:doaj.org_article:ff3b08fc39144a38a14621323673e9e6', 'fthighwire:oai:open-archive.highwire.org:jech:78_1_61', 'ftdoajarticles:oai:doaj.org_article:31eab59e7f4d4a6baffa663cc5685c0d', 'ftdoajarticles:oai:doaj.org_article:8369fdd2df1d45149f1d9c8d7a017968', 'ftdoajarticles:oai:doaj.org_article:6df2a7a8b1c94a4c9223c3c9f9823033', 'ftdoajarticles:oai:doaj.org_article:4eb73630c4a84f2391e45f3248532bc7', 'ftdoajarticles:oai:doaj.org_article:7c4919f5c98f49b3abe2837fb4898ce2', 'fthrcak:oai:hrcak.srce.hr:22798', 'ftpensoft:10.3897_ese.2022.e95247', 'fthrcak:oai:hrcak.srce.hr:337619', 'fthrcak:oai:hrcak.srce.hr:125365', 'ftunivzagrebmsr:oai:medlib.mef.hr:553', 'ftbiomed:oai:biomedcentral.com:s12909-014-0277-y', 'oai:hrcak.srce.hr:20480', 'oai:doaj.org_article:93fa8cb5d99f42d980be69cdbadfc07d', 'oai:doaj.org_article:4eb73630c4a84f2391e45f3248532bc7', 'ftdoajarticles:oai:doaj.org_article:7a692845a9424463a76043636a5aa1db', 'ftangliruskinfig:oai:figshare.com:article_30071859', 'ftangliruskinfig:oai:figshare.com:article_30071856', 'ftdoajarticles:oai:doaj.org_article:441242d7bf9542bea056868961cac762', 'ftdoajarticles:oai:doaj.org_article:4a56d18e88ee46ea91428146037e4692', 'ftdoajarticles:oai:doaj.org_article:24367a74268147acac4e47cea97ae70e', 'ftdoajarticles:oai:doaj.org_article:6a605dfe9461456abfa2f9e2f4500fae', 'ftbiomed:oai:biomedcentral.com:s12916-015-0476-3', '10.4000_revus.1060', '10.3406_chime.1993.1893', '10.4000_revus.93', 'oai:HAL:hal-05300284v1', 'oai:HAL:hal-05044988v1', 'ftnulzagrebzir:oai:zir.nsk.hr:fdmz_917', 'ftmdpi:oai:mdpi.com:_2227-9032_14_6_735_', 'ftunivosijek:oai:repozitorij.unios.hr:fdmz_917', 'ftunivalencia:oai:roderic.uv.es:10550_119462', 'ftunivmalmoe:oai:DiVA.org:mau-67033', 'ftuppsalauniv:oai:DiVA.org:uu-536601', 'fthrcak:oai:hrcak.srce.hr:329259', 'ftdoajarticles:oai:doaj.org_article:dfd362bb54704a6f91d6af61453f0325', 'ftagderuniv:oai:uia.brage.unit.no:11250_2989662', 'ftdoajarticles:oai:doaj.org_article:ea0865f07546424db8fa54139c05909e', 'ftdnbreiheo:123161756X', 'ftdnbreiheo:1245268635', 'fthrcak:oai:hrcak.srce.hr:20480', 'ftdoajarticles:oai:doaj.org_article:93fa8cb5d99f42d980be69cdbadfc07d', 'ftdoajarticles:oai:doaj.org_article:b9dd420ea5f14cf9b67fed9754b57048', 'ftcsic:oai:digital.csic.es:10261_403762', 'ftdnbreiheo:1208012568', 'ftdnbreiheo:1276937911', 'ftdoajarticles:oai:doaj.org_article:c30c559c93994b4e8f722fc1fd867678', 'fthrcak:oai:hrcak.srce.hr:38309', 'fthrcak:oai:hrcak.srce.hr:47886', 'ftid14132:oai:lirias2repo.kuleuven.be:123456789_676637', 'ftihswien:oai:irihs.ihs.ac.at:5894', 'ftbritmuseumfig:oai:figshare.com:article_30071856', 'ftbritmuseumfig:oai:figshare.com:article_30071859', 'ftcardiffmetufig:oai:figshare.com:article_30071856', 'ftcardiffmetufig:oai:figshare.com:article_30071859', 'ftfrontimediafig:oai:figshare.com:article_22597705', 'fthrcak:oai:hrcak.srce.hr:315400', 'ftid14132:oai:lirias2repo.kuleuven.be:20.500.12942_717523', 'ftinraparis:oai:HAL:hal-05300284v1', 'ftlincolnunivfig:oai:figshare.com:article_30071856', 'ftlincolnunivfig:oai:figshare.com:article_30071859', 'ftopenunivfig:oai:figshare.com:article_30071856', 'ftopenunivfig:oai:figshare.com:article_30071859', 'ftoskarbordeaux:oai:oskar-bordeaux.fr:20.500.12278_207735', 'ftarxivpreprints:oai:arXiv.org:2302.06655', 'ftcdlib:oai:escholarship.org:ark:_13030_qt4nm2w7b9', 'ftgeorgetownuniv:oai:repository.library.georgetown.edu:10822_962729', 'ftid14148:oai:pubfactory.com:_journals_11192_86_1_article-p227.xml', 'ftuniaucklandfig:oai:figshare.com:article_30071856', 'ftuniaucklandfig:oai:figshare.com:article_30071859', 'ftunivbathspafig:oai:figshare.com:article_30071859', 'ftunivbathspafig:oai:figshare.com:article_30071856', 'ftunivlimericfig:oai:figshare.com:article_30071859', 'ftunivlimericfig:oai:figshare.com:article_30071856', 'ftvivofig:oai:figshare.com:article_30071859', 'ftvivofig:oai:figshare.com:article_30071856', 'ftdoajarticles:oai:doaj.org_article:0e6360e78a3c48d99c0f901a05dca04a', 'ftdoajarticles:oai:doaj.org_article:15c474ee5a014402b080e2600d99ad2e', 'ftfolkehelseins:oai:fhi.brage.unit.no:11250_2420564', 'ftdoajarticles:oai:doaj.org_article:fc52b043a9fb4174b1bc067b9c95e03e', 'ftdoajarticles:oai:doaj.org_article:d45ad091a574447a83998c4d833e38d7', 'ftlenus:oai:www.lenus.ie:10147_644011', 'ftlondoneconom:oai:researchonline.lse.ac.uk:118814', 'ftndcdu:oai:generic.eprints.org:14234', 'ftumanchesterpub:oai:pure.atira.dk:publications_6eec9730-fcf8-4386-b79d-f11d81465fd8', 'ftuniaarhuspubl:oai:pure.atira.dk:publications_bc864434-71fe-4fa4-b741-3630311ae919', 'ftuniaarhuspubl:oai:pure.atira.dk:openaire_5b1ed7a4-0ef9-41a4-a725-894d42ff50ac', 'ftuniaarhuspubl:oai:pure.atira.dk:openaire_bc864434-71fe-4fa4-b741-3630311ae919', 'ftuniaarhuspubl:oai:pure.atira.dk:publications_5b1ed7a4-0ef9-41a4-a725-894d42ff50ac', 'ftunivleiden:oai:scholarlypublications.universiteitleiden.nl:item_3206719', 'ftunivmilanoair:oai:air.unimi.it:2434_808163', 'ftunivmilanoair:oai:air.unimi.it:2434_727506', 'ftunivnewcastnsw:uon:49041', 'ftunivsplit:oai:repozitorij.svkst.unist.hr:mefst_2942', 'ftunivsplit:oai:repozitorij.svkst.unist.hr:mefst_2947', 'ftunivstirling:oai:dspace.stir.ac.uk:1893_12985', 'ftunnottinghamrr:oai:nottingham-repository.worktribe.com:46170155', 'ftdublininstt:oai:arrow.tudublin.ie:scschcomart-1109', 'ftgriffithuniv:oai:research-repository.griffith.edu.au:10072_33555', 'ftkingscollondon:oai:kclpure.kcl.ac.uk:publications_4582a4de-6744-4d1d-9021-28cffba5a4fa', 'ftkingscollondon:oai:kclpure.kcl.ac.uk:publications_7639c966-fbe8-40b8-a325-b2e0ef05c1eb', 'ftmdpi:oai:mdpi.com:_2227-9032_13_16_1959_', 'ftuniljubljanaff:oai:ojs.revije.ff.uni-lj.si:article_20994', 'ftchalmersuniv:oai:research.chalmers.se:547318', 'fthrcak:oai:hrcak.srce.hr:325041', 'ftunibolognairis:oai:cris.unibo.it:11585_1051901', 'ftid14132:oai:lirias2repo.kuleuven.be:123456789_186665', 'ftgriffithuniv:oai:research-repository.griffith.edu.au:10072_26145', 'ftkentuniv:oai:kar.kent.ac.uk:24630', 'ftkingscollondon:oai:kclpure.kcl.ac.uk:publications_33739829-bd87-4d41-aefa-a2682b49261f', 'ftuniaarhuspubl:oai:pure.atira.dk:publications_f0f71c90-f833-11dd-8f9a-000ea68e967b', 'ftid14132:oai:lirias2repo.kuleuven.be:20.500.12942_722639', 'fthrcak:oai:hrcak.srce.hr:41340', 'fthrcak:oai:hrcak.srce.hr:59287', 'ftjnepaljo:oai:nepjol.info:article_2434', 'ftvilniusuniv:oai:vu.lt:elaba:229697589', 'ftutrentoiris:oai:iris.unitn.it:11572_373548', 'ftvuamstcris:oai:research.vu.nl:publications_bde919a7-1da3-4a9a-a4be-43a310b77d5f']</t>
+  </si>
+  <si>
+    <t>['oai:doaj.org_article:696f2620e2154f62b5cbdd10623de25f', 'oai:doaj.org_article:0b43d2a31965430f91f4f62fc6366b52']</t>
+  </si>
+  <si>
+    <t>['oai:doaj.org_article:0e4430bfe46d4f3a93af18d08f9d0eff']</t>
+  </si>
+  <si>
     <t>['oai:doaj.org_article:5548338054514e34be71dbe17d53f52e', 'oai:doaj.org_article:a9b757d251ee410ab74032d1bab9afa5', 'oai:doaj.org_article:160d29f9f8d942019b3366108e5bc983', 'oai:doaj.org_article:33ce9c306d954245a2823687b30d96cd', 'oai:doaj.org_article:315bda437b2e4765bcca5cb24550d585', 'oai:doaj.org_article:1fbd5e5dc4ab4d3cb34639ec113294ac', 'oai:doaj.org_article:160b9e7ffae24519a36db42f14781d43', 'oai:doaj.org_article:a9192bebb3884dc5ab7adb355472adb4', 'oai:doaj.org_article:af9e3bb8d681420f9528a8202d747cd5', 'oai:doaj.org_article:b2024dfba1a34f6696b286a57b5c8dcb', 'oai:doaj.org_article:63f5aa39f9564b078230dd9d39684ffc', 'oai:doaj.org_article:1b30b37a901d41319f9cd5173b062611', 'oai:doaj.org_article:5a437c5a8d644411a313bcff12ed41bc', 'oai:doaj.org_article:d6a096ce5fb1421891fd56b75c9e7c0e', 'oai:doaj.org_article:887f39ca363f42958a63ac238f7ee901', 'oai:doaj.org_article:b41906cf3e334c57afae55f3b95961eb', 'oai:doaj.org_article:f20e2ca5f45e4511b11ddb60d61248e7', 'oai:doaj.org_article:9a3d61ee7a0d43cd8159fe736a4f4ea8', 'oai:doaj.org_article:2f0e215d0e5b4b1e869bf8ed9620f585', 'oai:doaj.org_article:a2c9c882224546aab59cbe77e2997d8f', 'oai:doaj.org_article:a9157b9eea8645bd8ed2dde704f6ce6a', 'oai:doaj.org_article:283732a809ed4a36a3e1b578742d7eb9', 'oai:doaj.org_article:bc049703cdc14a48b4d631f831615798']</t>
   </si>
   <si>
-    <t>['oai:doaj.org_article:696f2620e2154f62b5cbdd10623de25f', 'oai:doaj.org_article:0b43d2a31965430f91f4f62fc6366b52']</t>
-  </si>
-  <si>
-    <t>['oai:doaj.org_article:0e4430bfe46d4f3a93af18d08f9d0eff']</t>
-  </si>
-  <si>
     <t>['oai:doaj.org_article:0eaf623e3fc24168a39b225402edacb3']</t>
   </si>
   <si>
     <t>['ftunivccolomb:oai:repository.ucc.edu.co:20.500.12494_61753', 'ftunivccolomb:oai:repository.ucc.edu.co:20.500.12494_61754', 'ftunivccolomb:oai:repository.ucc.edu.co:20.500.12494_61755', 'ftunivccolomb:oai:repository.ucc.edu.co:20.500.12494_61779', 'ftunivccolomb:oai:repository.ucc.edu.co:20.500.12494_61778', 'ftunivccolomb:oai:repository.ucc.edu.co:20.500.12494_61777']</t>
   </si>
   <si>
+    <t>['oai:doaj.org_article:8369fdd2df1d45149f1d9c8d7a017968', 'oai:doaj.org_article:6df2a7a8b1c94a4c9223c3c9f9823033', 'ftkingscollondon:oai:pure.atira.dk:publications_4582a4de-6744-4d1d-9021-28cffba5a4fa', 'ftunivgeneve:oai:unige.ch:unige:155232', 'ftinserm:oai:HAL:hal-03691657v1', 'ftoslouniv:oai:www.duo.uio.no:10852_93886', 'ftpubmed:oai:pubmedcentral.nih.gov:9010705', 'ftriip:oai:HAL:hal-03691657v1', 'ftpubmed:oai:pubmedcentral.nih.gov:9432753', 'ftpubmed:oai:pubmedcentral.nih.gov:4073248', 'ftworldbank:oai:openknowledge.worldbank.org:10986_34814', 'ftworldbank:oai:openknowledge.worldbank.org:10986_34926', 'oai:journals.um.si:article_97', 'oai:doaj.org_article:07c100a6ce324817b377171803c4855c', 'oai:doaj.org_article:5e6e2148c23c49a895791f48e61e0f85', 'ftunivliverpool:oai:livrepository.liverpool.ac.uk:3025011', 'ftpubmed:oai:pubmedcentral.nih.gov:9367745', 'ftdoajarticles:oai:doaj.org_article:95551ebe180740758115cd881e9ac8b7', 'ftdoajarticles:oai:doaj.org_article:c140614342044ce4bbde4a30eaac9bf0', 'ftleedsuniv:oai:eprints.whiterose.ac.uk:104170', 'ftunivessex:oai:repository.essex.ac.uk:33461', 'ftpubmed:oai:pubmedcentral.nih.gov:4593291', 'ftunivliverpool:oai:livrepository.liverpool.ac.uk:3154321', 'ftleedsuniv:oai:eprints.whiterose.ac.uk:185808', 'ftcovenantuniv:oai:generic.eprints.org:5719', 'ftdoajarticles:oai:doaj.org_article:3a88852d88af4eb6aa73cbcffaf685f1', 'ftdoajarticles:oai:doaj.org_article:fc6357040ca64fc984ecc96e77c19246', 'ftunivleuven:oai:lirias.kuleuven.be:123456789_186665', 'ftceon:oai:depot.ceon.pl:123456789_956', 'ftphilpapers:oai:philpapers.org_rec_BROPEI-3', 'fthrcak:oai:hrcak.srce.hr:23346', 'fthrcak:oai:hrcak.srce.hr:183381', 'ftpubmed:oai:pubmedcentral.nih.gov:9475410', 'ftpubmed:oai:pubmedcentral.nih.gov:6720555', 'ftpubmed:oai:pubmedcentral.nih.gov:6889688', 'ftdoajarticles:oai:doaj.org_article:e16060828b60400c8603cd37cc9c8bca', 'ftdoajarticles:oai:doaj.org_article:36a225556c5a49b59def089a10a3279d', 'ftpubmed:oai:pubmedcentral.nih.gov:3933755', 'ftliverpoolstm:oai:archive.lstmed.ac.uk:7509', 'ftumanchesterpub:oai:pure.atira.dk:publications_33ff92cc-eed4-48f0-994c-1d0acd19f1b1', 'ftihswien:oai::5894', 'fthrcak:oai:hrcak.srce.hr:305985', 'ftdoajarticles:oai:doaj.org_article:26792694c774410fa08312683c886acb', 'ftpubmed:oai:pubmedcentral.nih.gov:7249676', 'ftfrontimediafig:oai:figshare.com:article_24277543', 'ftkingscollondon:oai:pure.atira.dk:publications_61e4ab0e-4f28-4d5d-8892-ff443575e192', 'ftpubmed:oai:pubmedcentral.nih.gov:7791849', 'ftunivmilanobic:oai:boa.unimib.it:10281_17214', 'ftunivgeneve:oai:unige.ch:aou:unige:155232', 'ftlinnaeusuniv:oai:DiVA.org:lnu-40549', 'ftuniaarhuspubl:oai:pure.atira.dk:publications_c056e602-53da-4e83-b6c2-e824ed1fad77', 'ftkingscollondon:oai:pure.atira.dk:publications_33739829-bd87-4d41-aefa-a2682b49261f', 'ftunivbrescia:oai:iris.unibs.it:11379_539015', 'ftunivmoliseiris:oai:iris.unimol.it:11695_477', 'ftunivsplit:oai:repozitorij.svkst.unist.hr:forenzikast_383', 'ftsydanskunivpub:oai:sdu.dk:publications_5fe40505-6d15-48d8-a337-8a4b619715a9', 'ftuabarcelonapb:oai:ddd.uab.cat:289634', 'ftupompeufabra:oai:repositori.upf.edu:10230_49193', 'fthrcak:oai:hrcak.srce.hr:246902', 'ftkingscollondon:oai:pure.atira.dk:publications_7639c966-fbe8-40b8-a325-b2e0ef05c1eb', 'ftcopenhagenunip:oai:pure.atira.dk:publications_ad997fd8-6115-47bf-aeba-71be699f3876', 'ftdnbreiheo:1250067170', 'ftunivgenova:oai:iris.unige.it:11567_503755', 'ftunivrijeka:oai:www.unirepository.svkri.uniri.hr:fthm_2708', 'ftunivrijeka:oai:www.unirepository.svkri.uniri.hr:fthm_3186', 'ftuwarwick:oai:wrap.warwick.ac.uk:146855', 'ftunivzuerich:oai:www.zora.uzh.ch:124548', 'ftiesbelgrad:oai:ebooks.ien.bg.ac.rs:115', 'ftdoajarticles:oai:doaj.org_article:9ca531890bfb427aa611cda3a2e33f51', 'ftpubmed:oai:pubmedcentral.nih.gov:7721354', 'ftvuamstcris:oai:research.vu.nl:publications_b8285cbe-722e-4f6f-b330-ec080e36b8f0', 'ftlondoneconom:oai:eprints.lse.ac.uk:116626', 'ftvuamsterumc:oai:pure.atira.dk:publications_05a186a1-525e-4360-85df-e8d088513ba5', 'ftvuamsterumc:oai:pure.atira.dk:publications_68587b22-f052-4021-ba9c-bafee1b35498', 'ftworldbank:oai:openknowledge.worldbank.org:10986_30579', 'ftglasgowcucris:oai:researchonline.gcu.ac.uk:publications_920c5054-23ff-4a67-ba8d-058a6a413fc5', 'ftnulzagrebzir:oai:zir.nsk.hr:fthm_2708', 'ftnulzagrebzir:oai:zir.nsk.hr:fthm_3186', 'ftnulzagrebzir:oai:zir.nsk.hr:foi_442', 'ftdoajarticles:oai:doaj.org_article:5bf847ecd95046399d35d251c2e96ab7', 'ftdoajarticles:oai:doaj.org_article:e7ac765c353c4cb28b645bafecf3f137', 'oai:doaj.org_article:9ca531890bfb427aa611cda3a2e33f51', 'oai:doaj.org_article:78d8cf2c62c6480eafa3c6b132418c86', 'oai:doaj.org_article:26792694c774410fa08312683c886acb', 'ftlitinstagrecon:oai:elaba:11675971', 'ftpubmed:oai:pubmedcentral.nih.gov:8356263', 'ftpubmed:oai:pubmedcentral.nih.gov:7798200', 'ftpubmed:oai:pubmedcentral.nih.gov:6418058', 'ftzenodo:oai:zenodo.org:7533130', 'ftzenodo:oai:zenodo.org:6683292', 'fthrcak:oai:hrcak.srce.hr:244498', 'ftunivhongkonghu:oai:hub.hku.hk:10722_87806', 'ftdoajarticles:oai:doaj.org_article:25d15b75e8874c7fa5f32662e476caf9', 'ftdoajarticles:oai:doaj.org_article:453b9faf9aa74ebbb23fe2c796485514', 'ftdoajarticles:oai:doaj.org_article:459f202aac0342c2ae503e16f12bce90', 'ftpubmed:oai:pubmedcentral.nih.gov:7231414', 'ftunivfreiburg:oai:freidok.uni-freiburg.de:154085', 'ftpubmed:oai:pubmedcentral.nih.gov:6925899', 'ftunivmaribor:oai:dk.um.si:IzpisGradiva.php?id=67004', 'ftiesbelgrad:oai:ebooks.ien.bg.ac.rs:356', 'ftpubmed:oai:pubmedcentral.nih.gov:6451281', 'ftmdpi:oai:mdpi.com:_1660-4601_19_15_9515_', 'ftuniveastangl:oai:ueaeprints.uea.ac.uk:61475', 'ftnulzagrebzir:oai:zir.nsk.hr:pravo_2876', 'ftiesbelgrad:oai:ebooks.ien.bg.ac.rs:238', 'oai:hrcak.srce.hr:23346', 'oai:hrcak.srce.hr:23005', 'ftjnepaljo:oai:ojs.pkp.sfu.ca:article_2434', 'ftubristolcris:oai:research-information.bris.ac.uk:publications_651775d8-7ee6-436c-ad29-0dab5252df3c', 'ftuniaarhuspubl:oai:pure.atira.dk:publications_6c0494b3-d369-4c19-9bbc-54834abd6d95', 'oai:doaj.org_article:b9dd420ea5f14cf9b67fed9754b57048', 'ftvuamsterumc:oai:pure.atira.dk:publications_eedd93f1-76f9-4d7b-a572-446dacbdc9ed', 'oai:doaj.org_article:453b9faf9aa74ebbb23fe2c796485514', 'ftunivbrescia:oai:iris.unibs.it:11379_503691', 'ftpubmed:oai:pubmedcentral.nih.gov:10293907', 'oai:revues.org:revus_1060', 'ftdoajarticles:oai:doaj.org_article:f2aa7a59ae6241d380fa088455f596e6', 'ftdoajarticles:oai:doaj.org_article:728ec30c13804eac99a0d4999d26f8d6', 'ftdoajarticles:oai:doaj.org_article:43ad06da6431404eb2bbbcbce5774ec5', 'ftdoajarticles:oai:doaj.org_article:05b7aadba8d34aa48204516ded9e20dd', 'ftdoajarticles:oai:doaj.org_article:c519986b58ab4a11be171975d5415cab', 'ftccsdartic:oai:HAL:hal-03691657v1', 'oai:hrcak.srce.hr:19672', 'ftdoajarticles:oai:doaj.org_article:6bf5928a8b2942259fad89ac075e0649', 'ftdoajarticles:oai:doaj.org_article:ca1e7faddd3a4029aeb7c14f8b22aa66', 'ftdoajarticles:oai:doaj.org_article:d4ad8cc55f254374a8b772b18e5943f8', 'ftdoajarticles:oai:doaj.org_article:ff3b08fc39144a38a14621323673e9e6', 'fthighwire:oai:open-archive.highwire.org:jech:78_1_61', 'ftdoajarticles:oai:doaj.org_article:31eab59e7f4d4a6baffa663cc5685c0d', 'ftdoajarticles:oai:doaj.org_article:8369fdd2df1d45149f1d9c8d7a017968', 'ftdoajarticles:oai:doaj.org_article:6df2a7a8b1c94a4c9223c3c9f9823033', 'ftdoajarticles:oai:doaj.org_article:4eb73630c4a84f2391e45f3248532bc7', 'ftdoajarticles:oai:doaj.org_article:7c4919f5c98f49b3abe2837fb4898ce2', 'ftpensoft:10.3897_ese.2022.e95247', 'ftunivzagrebmsr:oai:medlib.mef.hr:553', 'ftbiomed:oai:biomedcentral.com:s12909-014-0277-y', 'oai:hrcak.srce.hr:20480', 'oai:doaj.org_article:93fa8cb5d99f42d980be69cdbadfc07d', 'oai:doaj.org_article:4eb73630c4a84f2391e45f3248532bc7', 'ftdoajarticles:oai:doaj.org_article:7a692845a9424463a76043636a5aa1db', 'ftangliruskinfig:oai:figshare.com:article_30071859', 'ftangliruskinfig:oai:figshare.com:article_30071856', 'ftdoajarticles:oai:doaj.org_article:441242d7bf9542bea056868961cac762', 'ftdoajarticles:oai:doaj.org_article:4a56d18e88ee46ea91428146037e4692', 'ftdoajarticles:oai:doaj.org_article:24367a74268147acac4e47cea97ae70e', 'ftdoajarticles:oai:doaj.org_article:6a605dfe9461456abfa2f9e2f4500fae', 'ftbiomed:oai:biomedcentral.com:s12916-015-0476-3', '10.4000_revus.1060', '10.3406_chime.1993.1893', '10.4000_revus.93', 'oai:HAL:hal-05300284v1', 'oai:HAL:hal-05044988v1', 'ftnulzagrebzir:oai:zir.nsk.hr:fdmz_917', 'ftmdpi:oai:mdpi.com:_2227-9032_14_6_735_', 'ftunivosijek:oai:repozitorij.unios.hr:fdmz_917', 'ftunivalencia:oai:roderic.uv.es:10550_119462', 'ftunivmalmoe:oai:DiVA.org:mau-67033', 'ftuppsalauniv:oai:DiVA.org:uu-536601', 'fthrcak:oai:hrcak.srce.hr:329259', 'ftdoajarticles:oai:doaj.org_article:dfd362bb54704a6f91d6af61453f0325', 'ftagderuniv:oai:uia.brage.unit.no:11250_2989662', 'ftdoajarticles:oai:doaj.org_article:ea0865f07546424db8fa54139c05909e', 'ftdnbreiheo:123161756X', 'ftdnbreiheo:1245268635', 'fthrcak:oai:hrcak.srce.hr:20480', 'ftdoajarticles:oai:doaj.org_article:93fa8cb5d99f42d980be69cdbadfc07d', 'ftdoajarticles:oai:doaj.org_article:b9dd420ea5f14cf9b67fed9754b57048', 'ftcsic:oai:digital.csic.es:10261_403762', 'ftdnbreiheo:1208012568', 'ftdnbreiheo:1276937911', 'ftdoajarticles:oai:doaj.org_article:c30c559c93994b4e8f722fc1fd867678', 'fthrcak:oai:hrcak.srce.hr:38309', 'fthrcak:oai:hrcak.srce.hr:47886', 'ftid14132:oai:lirias2repo.kuleuven.be:123456789_676637', 'ftihswien:oai:irihs.ihs.ac.at:5894', 'ftbritmuseumfig:oai:figshare.com:article_30071856', 'ftbritmuseumfig:oai:figshare.com:article_30071859', 'ftcardiffmetufig:oai:figshare.com:article_30071856', 'ftcardiffmetufig:oai:figshare.com:article_30071859', 'ftfrontimediafig:oai:figshare.com:article_22597705', 'fthrcak:oai:hrcak.srce.hr:315400', 'ftid14132:oai:lirias2repo.kuleuven.be:20.500.12942_717523', 'ftinraparis:oai:HAL:hal-05300284v1', 'ftlincolnunivfig:oai:figshare.com:article_30071856', 'ftlincolnunivfig:oai:figshare.com:article_30071859', 'ftopenunivfig:oai:figshare.com:article_30071856', 'ftopenunivfig:oai:figshare.com:article_30071859', 'ftoskarbordeaux:oai:oskar-bordeaux.fr:20.500.12278_207735', 'ftarxivpreprints:oai:arXiv.org:2302.06655', 'ftcdlib:oai:escholarship.org:ark:_13030_qt4nm2w7b9', 'ftgeorgetownuniv:oai:repository.library.georgetown.edu:10822_962729', 'ftid14148:oai:pubfactory.com:_journals_11192_86_1_article-p227.xml', 'ftuniaucklandfig:oai:figshare.com:article_30071856', 'ftuniaucklandfig:oai:figshare.com:article_30071859', 'ftunivbathspafig:oai:figshare.com:article_30071859', 'ftunivbathspafig:oai:figshare.com:article_30071856', 'ftunivlimericfig:oai:figshare.com:article_30071859', 'ftunivlimericfig:oai:figshare.com:article_30071856', 'ftvivofig:oai:figshare.com:article_30071859', 'ftvivofig:oai:figshare.com:article_30071856', 'ftdoajarticles:oai:doaj.org_article:0e6360e78a3c48d99c0f901a05dca04a', 'ftdoajarticles:oai:doaj.org_article:15c474ee5a014402b080e2600d99ad2e', 'ftfolkehelseins:oai:fhi.brage.unit.no:11250_2420564', 'ftdoajarticles:oai:doaj.org_article:fc52b043a9fb4174b1bc067b9c95e03e', 'ftdoajarticles:oai:doaj.org_article:d45ad091a574447a83998c4d833e38d7', 'ftlenus:oai:www.lenus.ie:10147_644011', 'ftlondoneconom:oai:researchonline.lse.ac.uk:118814', 'ftndcdu:oai:generic.eprints.org:14234', 'ftumanchesterpub:oai:pure.atira.dk:publications_6eec9730-fcf8-4386-b79d-f11d81465fd8', 'ftuniaarhuspubl:oai:pure.atira.dk:publications_bc864434-71fe-4fa4-b741-3630311ae919', 'ftuniaarhuspubl:oai:pure.atira.dk:openaire_5b1ed7a4-0ef9-41a4-a725-894d42ff50ac', 'ftuniaarhuspubl:oai:pure.atira.dk:openaire_bc864434-71fe-4fa4-b741-3630311ae919', 'ftuniaarhuspubl:oai:pure.atira.dk:publications_5b1ed7a4-0ef9-41a4-a725-894d42ff50ac', 'ftunivleiden:oai:scholarlypublications.universiteitleiden.nl:item_3206719', 'ftunivmilanoair:oai:air.unimi.it:2434_808163', 'ftunivmilanoair:oai:air.unimi.it:2434_727506', 'ftunivnewcastnsw:uon:49041', 'ftunivsplit:oai:repozitorij.svkst.unist.hr:mefst_2942', 'ftunivsplit:oai:repozitorij.svkst.unist.hr:mefst_2947', 'ftunivstirling:oai:dspace.stir.ac.uk:1893_12985', 'ftunnottinghamrr:oai:nottingham-repository.worktribe.com:46170155', 'ftdublininstt:oai:arrow.tudublin.ie:scschcomart-1109', 'ftgriffithuniv:oai:research-repository.griffith.edu.au:10072_33555', 'ftkingscollondon:oai:kclpure.kcl.ac.uk:publications_4582a4de-6744-4d1d-9021-28cffba5a4fa', 'ftkingscollondon:oai:kclpure.kcl.ac.uk:publications_7639c966-fbe8-40b8-a325-b2e0ef05c1eb', 'ftmdpi:oai:mdpi.com:_2227-9032_13_16_1959_', 'ftuniljubljanaff:oai:ojs.revije.ff.uni-lj.si:article_20994', 'ftchalmersuniv:oai:research.chalmers.se:547318', 'fthrcak:oai:hrcak.srce.hr:325041', 'ftunibolognairis:oai:cris.unibo.it:11585_1051901', 'ftid14132:oai:lirias2repo.kuleuven.be:123456789_186665', 'ftgriffithuniv:oai:research-repository.griffith.edu.au:10072_26145', 'ftkentuniv:oai:kar.kent.ac.uk:24630', 'ftkingscollondon:oai:kclpure.kcl.ac.uk:publications_33739829-bd87-4d41-aefa-a2682b49261f', 'ftuniaarhuspubl:oai:pure.atira.dk:publications_f0f71c90-f833-11dd-8f9a-000ea68e967b', 'ftid14132:oai:lirias2repo.kuleuven.be:20.500.12942_722639', 'fthrcak:oai:hrcak.srce.hr:41340', 'fthrcak:oai:hrcak.srce.hr:59287', 'ftjnepaljo:oai:nepjol.info:article_2434', 'ftvilniusuniv:oai:vu.lt:elaba:229697589', 'ftutrentoiris:oai:iris.unitn.it:11572_373548', 'ftvuamstcris:oai:research.vu.nl:publications_bde919a7-1da3-4a9a-a4be-43a310b77d5f', 'ftvuamsterumc:oai:pure.atira.dk:publications_1866bb23-9ec2-47a0-a0b3-714b6ec6fed0', 'fthrcak:oai:hrcak.srce.hr:22798', 'fthrcak:oai:hrcak.srce.hr:125365']</t>
+  </si>
+  <si>
+    <t>['oai:doaj.org_article:3bea225666a941d1936b8aaa632a2506', 'oai:doaj.org_article:a53604f6bac94598abc986a43da29def']</t>
+  </si>
+  <si>
+    <t>['oai:doaj.org_article:23f23dbdb6e94ab2b02dd73fb6dc3a8e']</t>
+  </si>
+  <si>
     <t>['oai:doaj.org_article:a8b9a0376409419ea80ef2c17656ff96', 'oai:doaj.org_article:c79d7d362e9d4fe6aff08e4d3f038c56', 'oai:doaj.org_article:86ff9fffdbee4ff280c1ea4cdda4523c', 'oai:doaj.org_article:3f4db05102be4433849790e42df16311', 'oai:doaj.org_article:303453c1ded943dcac8807523b90f0f3', 'ftunivjaumeirep:oai:repositori.uji.es:10234_35660', 'ftunivjaumeirep:oai:repositori.uji.es:10234_42961', 'ftunivjaumeirep:oai:repositori.uji.es:10234_2625', 'ftunivjaumeirep:oai:repositori.uji.es:10234_204629', 'ftunivjaumeirep:oai:repositori.uji.es:10234_2701', 'ftunivjaumeirep:oai:repositori.uji.es:10234_3054', 'ftunivjaumeirep:oai:repositori.uji.es:10234_2719', 'ftunivjaumeirep:oai:repositori.uji.es:10234_2724', 'ftunivjaumeirep:oai:repositori.uji.es:10234_2729', 'ftunivjaumeirep:oai:repositori.uji.es:10234_2638', 'ftunivjaumeirep:oai:repositori.uji.es:10234_2660', 'ftunivjaumeirep:oai:repositori.uji.es:10234_2662', 'ftunivjaumeirep:oai:repositori.uji.es:10234_2663', 'ftunivjaumeirep:oai:repositori.uji.es:10234_2696', 'ftunivjaumeirep:oai:repositori.uji.es:10234_2708', 'ftunivjaumeirep:oai:repositori.uji.es:10234_704547', 'ftunivjaumeirep:oai:repositori.uji.es:10234_204863', 'ftunivgranada:oai:digibug.ugr.es:10481_100755', 'ftcentralamerjol:oai:ojs.pkp.sfu.ca:article_579', 'ftcentralamerjol:oai:ojs.pkp.sfu.ca:article_580', 'ftunivjaumeirep:oai:repositori.uji.es:10234_168480', 'ftunivjaumeirep:oai:repositori.uji.es:10234_166124', 'ftunivjaumeirep:oai:repositori.uji.es:10234_174379', 'ftunivjaumeirep:oai:repositori.uji.es:10234_175271', 'ftunivjaumeirep:oai:repositori.uji.es:10234_180073', 'ftunivjaumeirep:oai:repositori.uji.es:10234_185493', 'ftunivjaumeirep:oai:repositori.uji.es:10234_710156', 'oai:recyt.fecyt.es:article_81357', 'oai:doaj.org_article:404e6da0ba844fcb8918ffa8e624b55d', 'oai:doaj.org_article:eef5367f5a5441539ab4085a3fd12472', 'ftunivrosarioojs:oai:revistas.urosario.edu.co:article_2965', 'ftunivjaumeirep:oai:repositori.uji.es:10234_2725', 'ftunivjaumeirep:oai:repositori.uji.es:10234_2718', 'ftunivjaumeirep:oai:repositori.uji.es:10234_2636', 'ftunivjaumeirep:oai:repositori.uji.es:10234_3793', 'ftunivjaumeirep:oai:repositori.uji.es:10234_2627', 'ftunivjaumeirep:oai:repositori.uji.es:10234_2637', 'ftunivjaumeirep:oai:repositori.uji.es:10234_2628', 'ftunivjaumeirep:oai:repositori.uji.es:10234_2667', 'ftunivjaumeirep:oai:repositori.uji.es:10234_2664', 'ftunivjaumeirep:oai:repositori.uji.es:10234_2697', 'oai:doaj.org_article:d230ca9049304e0ab675aad6dcd1a5d7']</t>
   </si>
   <si>
+    <t>['ftsetonhalluniv:oai:scholarship.shu.edu:columbus-balboreview1933-1000', 'ftsetonhalluniv:oai:scholarship.shu.edu:columbus-balboreview1934-1001', 'ftsetonhallunil:oai:scholarship.shu.edu:columbus-balboreview1934-1001', 'ftsetonhallunil:oai:scholarship.shu.edu:columbus-balboreview1933-1000']</t>
+  </si>
+  <si>
     <t>['ftsetonhalluniv:oai:scholarship.shu.edu:columbus-balboreview1937-1001', 'ftsetonhalluniv:oai:scholarship.shu.edu:columbus-balboreview1935-1000', 'ftsetonhalluniv:oai:scholarship.shu.edu:columbus-balboreview1935-1001', 'ftsetonhalluniv:oai:scholarship.shu.edu:columbus-balboreview1937-1000', 'ftsetonhallunil:oai:scholarship.shu.edu:columbus-balboreview1935-1000', 'ftsetonhallunil:oai:scholarship.shu.edu:columbus-balboreview1937-1000']</t>
   </si>
   <si>
-    <t>['oai:doaj.org_article:3bea225666a941d1936b8aaa632a2506', 'oai:doaj.org_article:a53604f6bac94598abc986a43da29def']</t>
-  </si>
-  <si>
-    <t>['oai:doaj.org_article:23f23dbdb6e94ab2b02dd73fb6dc3a8e']</t>
-  </si>
-  <si>
-    <t>['ftsetonhalluniv:oai:scholarship.shu.edu:columbus-balboreview1933-1000', 'ftsetonhalluniv:oai:scholarship.shu.edu:columbus-balboreview1934-1001', 'ftsetonhallunil:oai:scholarship.shu.edu:columbus-balboreview1934-1001', 'ftsetonhallunil:oai:scholarship.shu.edu:columbus-balboreview1933-1000']</t>
+    <t>['oai:doaj.org_article:d9e01b9b0e9640749308d1929ab0d03b']</t>
+  </si>
+  <si>
+    <t>['oai:doaj.org_article:5de491285e8448cbbcac7abd701ee5b8']</t>
   </si>
   <si>
     <t>['oai:doaj.org_article:04f394ba950a41c5853022e361c61710', 'oai:doaj.org_article:3d60faab63a84ce2ac5d77a85e668b9f', 'oai:doaj.org_article:dc3aad928ad34bb2a41d3b4b04f0356e', 'oai:doaj.org_article:30691df957474b22aac9f8d352284b30', 'oai:doaj.org_article:e0b9af4568bb4458b74814fc78c2ce8d', 'oai:doaj.org_article:c63ddb68d86e4247996c2f36d125cd06', 'oai:doaj.org_article:e834b5612fc545c3ac3d205dc4e9c9f9', 'oai:doaj.org_article:377f6c256ec64fea93696440cee425e3', 'oai:doaj.org_article:66555908ed0e43228749e5ee8abf0aec', 'oai:doaj.org_article:804bdb9dcb94416485c4bba8bccff697', 'oai:doaj.org_article:1b499491173542b99741ed4f7160ce48', 'oai:doaj.org_article:8c540b520806428bb9c999f5654d3e3b', 'oai:doaj.org_article:039e7b5454cb4babafee3057845299db', 'oai:doaj.org_article:6803af582fe240d0b1efb3755c313e00', 'oai:doaj.org_article:5da9da14ad284e52a7d1d6b51ec205c1', 'oai:doaj.org_article:4bb655992a3241ea8197c74e3329c172', 'oai:doaj.org_article:8208e1253a7b49598c4d353ae8173848', 'oai:doaj.org_article:49cee080158942a2950bc00d1eff9010', 'oai:doaj.org_article:3c3b3486b3b240239c477d9a39365509', 'oai:doaj.org_article:ff05e1e2d0324d85b410e644a8fc2c09', 'oai:doaj.org_article:4bf1f061af004554867086b966b355e8', 'oai:doaj.org_article:1f35d0d353334da0b74d970a16e0339b', 'oai:doaj.org_article:325c2a5f09784c85af684074005c2625', 'oai:doaj.org_article:85e117a2ff7a4bba80f62a463d8e79bc', 'oai:doaj.org_article:7394e97101cb4f30973dc8102cbedea6', 'oai:doaj.org_article:2bfe073cc2404d629a95cf4a8fcbc6f7', 'oai:doaj.org_article:0c93c24f1a9444c28cd871e031ea198d', 'oai:doaj.org_article:8be65954801b40f0a41748bb6779fa32']</t>
   </si>
   <si>
+    <t>['oai:doaj.org_article:8609798aee2748f69109f29d263e04cd']</t>
+  </si>
+  <si>
+    <t>['oai:doaj.org_article:274e49e26ee445f8a7c161bdd2d278a2']</t>
+  </si>
+  <si>
+    <t>['oai:doaj.org_article:eee1f8f5f1a24d6da581ca388d6004ac']</t>
+  </si>
+  <si>
+    <t>['oai:doaj.org_article:e4f61c01ef974a729524d01a512e2336']</t>
+  </si>
+  <si>
+    <t>['oai:doaj.org_article:708f01c1d44146faa783be8c2ba0a30c', 'oai:doaj.org_article:50ed3d5d3032409e9224d3878bdd40b5']</t>
+  </si>
+  <si>
+    <t>['oai:doaj.org_article:87e727ff303a4c8087aed69b07c18dd8', 'oai:doaj.org_article:18651150c99240d3a837c6b3ac0dff28']</t>
+  </si>
+  <si>
+    <t>['oai:doaj.org_article:4a9339c77489420380e2f7865c3fb5f3', 'oai:doaj.org_article:fd0581815dc24cf2886785b831b927c1']</t>
+  </si>
+  <si>
     <t>['oai:doaj.org_article:77812275590a45c49d757837467fd8c8', 'oai:doaj.org_article:eea2bf287b7744b2b651b640f15de911', 'oai:doaj.org_article:05d215c42bfc41d39836fc538a60b04f', 'oai:doaj.org_article:378a9983864f4ed58d2120babb5a9109', 'oai:doaj.org_article:e2f82f8445194f85ad7543818a52365f', 'oai:doaj.org_article:1b1d9b2caad343d0a689b0e214f85c3d', 'oai:doaj.org_article:9bb62667cc05418db1d1e36ab285118a', 'oai:doaj.org_article:ae0b47efb6264db0a2fed0418427cc72', 'oai:doaj.org_article:bd667cd198be4ddb86f5ed8d5e7f353d', 'oai:doaj.org_article:a9657924710b42fc84fab917d1d5a6c1', 'oai:doaj.org_article:206c620edaff4cd4a1a44724ed6646cc', 'oai:doaj.org_article:6b00dbd57118443983a838b554de695e', 'oai:doaj.org_article:3e0b8b21c6e647b183d2222e19473f92', 'oai:doaj.org_article:23a5288bc1764147bb075fe85b7ed1f1', 'oai:doaj.org_article:509bb8b3ece44fd8a96a2f528faa1785', 'oai:doaj.org_article:ab18fa6fa9064e38a6fb1379a566ff35', 'oai:doaj.org_article:1998b1f08a3d4a80a320eb5a86dc05fa', 'oai:doaj.org_article:d9b8dc6e7723435eb4048dd97826388a', 'oai:doaj.org_article:4027b2977472448b95c44c4fef9086a7', 'oai:doaj.org_article:d1481f3993694f0b973e887d71475353', 'oai:doaj.org_article:106a1e5c8c41488787a00cc3f684b207', 'oai:doaj.org_article:50d99656b7684350b145cd48f35635ac', 'oai:doaj.org_article:d8f8465a360548aaa8831aecae6a7825', 'oai:doaj.org_article:e6ac09e814814793b5aa7189c2a7c5be', 'oai:doaj.org_article:0d8a9c854d274f9b8fa4295d3993f8c5', 'oai:doaj.org_article:1402aa67678149628071fe462ce04eb9', 'oai:doaj.org_article:54d25f38c10e4388a9550e58180df956', 'oai:doaj.org_article:76940fe3c3244c20a934bd20a76658f0', 'oai:doaj.org_article:06de260d4a2b489f94528f28b762733a', 'oai:doaj.org_article:3351f41af4b543dfacfa6dda4006066b', 'oai:doaj.org_article:cb8a8493a5a44670b81ae75e74e1838f', 'oai:doaj.org_article:fe10ebcb2ec94fa88042c871c471d105', 'oai:doaj.org_article:ba021b522a474f47bd862ab3e767d259', 'oai:doaj.org_article:3c12f77776104db6a62c1e8be251ab54', 'oai:doaj.org_article:73914873bd7b473b93f933ea6408b90c', 'oai:doaj.org_article:aae6e516edf54f11bd3d74bb6c3b1d31', 'oai:doaj.org_article:8c8d3ca3601b44de829a47e922dcfaaa', 'oai:doaj.org_article:fb7b7bb9cb6547f582b6fcdf406c9c7c', 'oai:doaj.org_article:b385083af9384863b8b5ebce8832f001', 'oai:doaj.org_article:c5bd0d802ce2446da369ddd33f77465e', 'oai:doaj.org_article:c7e220e275e240f1973f9c754476317d', 'oai:doaj.org_article:207f3b979df7494b9ae19c6469afe20a', 'oai:doaj.org_article:8dc7353138754ed99ff09a69276d6667', 'oai:doaj.org_article:6feac8f7797242e181c4e820706bb132', 'oai:doaj.org_article:80dbd0fff6b64982b4867f60b5ba0a06', 'oai:doaj.org_article:ab5c4bba9e3f4534b5f54d67191c7f72', 'oai:doaj.org_article:ad33a5cf15184eb881e596a3d2580fb9', 'oai:doaj.org_article:4b60aec4fa1549cba994c24436064b18', 'oai:doaj.org_article:ddec1ee9ea7841a0bac89c0f4443340e', 'oai:doaj.org_article:6371d78f84b741a0bee46fe6cec6d433', 'oai:doaj.org_article:8360af30f02d49d2aac2f7b8475031a6', 'oai:doaj.org_article:687a5a53fa254cca890f1516f6550c6c', 'oai:doaj.org_article:7a76224f011e4598adb4fe02ce1c1b19', 'oai:doaj.org_article:e7259a8171cd42b2adb2360d7afee9f5', 'oai:doaj.org_article:de5258f0918a48a7aa106ae98185a64b']</t>
   </si>
   <si>
-    <t>['oai:doaj.org_article:d9e01b9b0e9640749308d1929ab0d03b']</t>
-  </si>
-  <si>
-    <t>['oai:doaj.org_article:5de491285e8448cbbcac7abd701ee5b8']</t>
+    <t>['oai:doaj.org_article:8744be6e8ca7434297a0ce5ab8d96c36', 'oai:doaj.org_article:293cbc10dd3d409ea3b9a77a842dc669', 'oai:doaj.org_article:1371ff51fbee4b54aa17a5b8d6882da2', 'oai:doaj.org_article:ee72ab34aedc46769621f5d0e263cb9f', 'oai:doaj.org_article:ab2b09b2d66e4c8687dd3c8c30cb1b36', 'oai:doaj.org_article:3528146e42c04766a6dcb6efb65f7e53']</t>
+  </si>
+  <si>
+    <t>['10670_1.jqseeq']</t>
+  </si>
+  <si>
+    <t>['oai:recyt.fecyt.es:article_79043', 'oai:doaj.org_article:22f5842817674a7c9df6ab6dcda3d90b']</t>
+  </si>
+  <si>
+    <t>['10670_1.ctj6r9']</t>
+  </si>
+  <si>
+    <t>['oai:doaj.org_article:ab61c21e633a4a1c9971e95b1390c716', 'oai:doaj.org_article:68fb96c84ace499aaa4d74479a1a09b0', 'oai:doaj.org_article:ea0dd166f88545a488935a2bc1906b76', 'oai:doaj.org_article:5ffbd6b9eea94013b1fd06677afd44aa']</t>
+  </si>
+  <si>
+    <t>['oai:recyt.fecyt.es:article_79039', 'oai:doaj.org_article:c79dc0626fcd46b3a15eedad2e792e5b']</t>
+  </si>
+  <si>
+    <t>['oai:doaj.org_article:ebb4d100f442405096d13379cad2f4fa', 'oai:doaj.org_article:3c96d54a609d4d22b14a03b5a59c5394', 'oai:doaj.org_article:ca47bfd5204e48a8b9ce653e3372a61d', 'oai:doaj.org_article:94c4e79de602496285b5263e61d6b4e6', 'oai:doaj.org_article:99486388e9b24c5883d7d02ca95da316', 'oai:doaj.org_article:0940abbd0e754bedbd6d9da9d9d383b0', 'oai:doaj.org_article:6de894331cae4e27991675e7dba43554', 'oai:doaj.org_article:e316e97b397c4d88b33ca6c3f5f13a27', 'oai:doaj.org_article:fcac4cb9f1d84dceba044247e275a0f5', 'oai:doaj.org_article:164417ec4e634850be8971dcaf787084', 'oai:doaj.org_article:427c53b3cee442cabf4d7d0a63059c22', 'oai:doaj.org_article:98c2b2eae427498bbeb4f8fe1c79dc78', 'oai:doaj.org_article:8450d710d098454f8ef1190c89f1844c', 'oai:doaj.org_article:5d52873aac224ee58fe218dc75bafc8b', 'oai:doaj.org_article:74f2450349e1418b8e1e4e3df062805f', 'oai:doaj.org_article:a1695cf42eb640bf9367a5feaf1de0ef', 'oai:doaj.org_article:1a1e17eb44934863883c089ed21fd356', 'oai:doaj.org_article:23cb33e1e56149aaae6c8b6d1464d7bc', 'oai:doaj.org_article:1cf4ae944f6549969a7cdec7b3db985f', 'oai:doaj.org_article:bb84febb3d0b46779c67c06ea5a40289', 'oai:doaj.org_article:b3fc6b1965bd43fa9a44fdcc8feee57f', 'oai:doaj.org_article:d80cf6faa4dd446eba8e423f681f490a', 'oai:doaj.org_article:48b037d38b3149a4aec60531a8aed680', 'oai:doaj.org_article:6a88d0f8633848fcae29bff773fe5ca2', 'oai:doaj.org_article:5c14cb1dee334a2682000504523dcc54', 'oai:doaj.org_article:8d81513ed1bf4e27b3880834b7a111db', 'oai:doaj.org_article:d47470f88e3c477c9e0659b17a267c59', 'oai:doaj.org_article:b55881384daa4b88a6c6f754cb014568', 'oai:doaj.org_article:9a205e0b6ae14d8398af29e3a2d22ce7', 'oai:doaj.org_article:6bb0db779f1a4b5cb53998be55a2219d', 'oai:doaj.org_article:3803368831ef459aa14f273474c68a9d', 'oai:doaj.org_article:7f7c4305eea84b81819cfbec329acd57', 'oai:doaj.org_article:873ab8741aab48aa99b69d2ffdc5493c', 'oai:doaj.org_article:e0bc00006ebd49ad86320f0ddf6697d4', 'oai:doaj.org_article:df67577b7c134909840fd823170afe20', 'oai:doaj.org_article:6bfedde04fbd4a4e84c744afdb13e028', 'oai:doaj.org_article:23bd2170dac64435b7ad1ff654f714fc', 'oai:doaj.org_article:e196151d6e464ebcac7f4e6590d806de', 'oai:doaj.org_article:43dc1be1fcdd4488b91aba3cc90b297f', 'oai:doaj.org_article:8f266f9e9a634e5f85f9a0fc507b79a1', 'oai:doaj.org_article:1dbb5e0e492d42bb95e8d5b2a3c78610', 'oai:doaj.org_article:93af869cec454f37863c62b35d028dc2', 'oai:doaj.org_article:5609fc3d409b4b04b549d475d598526b', 'oai:doaj.org_article:5a4c6db695764319b727c9b2f2d27ae2', 'oai:doaj.org_article:c4d257e60edb47a28bbd0c58b88dcf23', 'oai:doaj.org_article:b52f1ed6421941929427265e7280b2ff', 'oai:doaj.org_article:443e19e0a08c43c29eded7e8b49392b4', 'oai:doaj.org_article:b397763365254d7d950f54a8e2932ba2', 'oai:doaj.org_article:2c558cc84c4148508b7c2874e0171524']</t>
+  </si>
+  <si>
+    <t>['10670_1.jb2q1v']</t>
+  </si>
+  <si>
+    <t>['10670_1.pqqo8q']</t>
+  </si>
+  <si>
+    <t>['oai:doaj.org_article:53b052908fe947d4a62b7e6a575525ea']</t>
+  </si>
+  <si>
+    <t>['ftuninsanjuanijs:oai:ojs.pkp.sfu.ca:article_807']</t>
+  </si>
+  <si>
+    <t>['oai:doaj.org_article:074fd2d89f0b4dc4b45eb307257a92b5', 'oai:doaj.org_article:5862c0a6730d43eba07453e769ccfa07', 'oai:doaj.org_article:dbef64a8bbeb49579cedf1cd6e93409a', 'oai:doaj.org_article:13ef6ad7e2984c07ac9adc0756703818', 'oai:doaj.org_article:7fbaec7737e743bcb6cad1163e2d4ee8', 'oai:doaj.org_article:302701027ecd4428a41fb50764dfad13', 'oai:doaj.org_article:69644e8ddfd2463db1941ce62853668e', 'oai:doaj.org_article:8a7a26003b0c4026b33f38f72b3ccd87', 'oai:doaj.org_article:594aa2b1c75f4e7d9fa6d0f1dcecac78', 'oai:doaj.org_article:cc873957cd9048918e8ea9566a5d7753', 'oai:doaj.org_article:e740f0a323f94b6889714eccefe0947f', 'oai:doaj.org_article:02afea1dfad540049a21de2f4e83021a', 'ftjmcys:oai:ojs2.www.medicinaclinicaysocial.org:article_40', 'ftjrpi:oai:ojs2.rpi.isri.cu:article_64', 'ftunivbiobioojs:oai:ojs.revistas.ubiobio.cl:article_5491', 'oai:recyt.fecyt.es:article_70727', 'oai:recyt.fecyt.es:article_88530', 'oai:recyt.fecyt.es:article_70836', 'oai:recyt.fecyt.es:article_70534', 'oai:recyt.fecyt.es:article_70512', 'oai:recyt.fecyt.es:article_70782', 'oai:recyt.fecyt.es:article_88548', 'oai:doaj.org_article:dfaa16778bd44b949b07543c87969ae3', 'oai:doaj.org_article:f75510227ad74603878d67689146ace0', 'oai:doaj.org_article:dd17e68e2a454efc90c3c308f8305f71', 'oai:ojs.revistas.ucm.es:article_60136', 'oai:doaj.org_article:20ee5bd9f2f14d258cc9f689f9f74401', 'oai:doaj.org_article:0437056da8e54d9683c63f847b994ab7', 'oai:doaj.org_article:459c788026c44b6e9eb2ca9368dce8e0', 'oai:doaj.org_article:4accaf83c0bd408ca970bf8fd404bdc1', 'oai:doaj.org_article:ea69f9d9a7024c9a828e5cf883b83ae4', 'oai:doaj.org_article:7b5c7a146a39416480ab93b231174b0f', 'oai:doaj.org_article:fce0cacfb6b349be8fbb817aa4fbefc3', 'oai:doaj.org_article:bcb317ab77684f38b6cf69a044d47459', 'oai:doaj.org_article:436be46a95b2419689b21f9c89815c7b', 'ftjrpi:oai:ojs2.rpi.isri.cu:article_146', 'oai:ojs.pkp.sfu.ca:article_70512', 'oai:ojs.pkp.sfu.ca:article_70534']</t>
+  </si>
+  <si>
+    <t>['oai:ojs.revistas.ucm.es:article_39794', 'oai:doaj.org_article:a37672d69fe34744a542971abc86c3d4', 'oai:doaj.org_article:df02fe3e1aa6446ca817c94a523375dc', 'oai:doaj.org_article:5ef9827768cd458ca07655b7bd586df7']</t>
+  </si>
+  <si>
+    <t>['10670_1.3escy8', 'oai:doaj.org_article:1b419ab9d7ef4010a42a3e1bfdd584a2', 'oai:doaj.org_article:ec57d0594dff446a96fc804ae9b64096', 'oai:doaj.org_article:4bcfc68d324e40ba910895ff9eeb53f9', 'oai:doaj.org_article:442376731f824e95b65d1352a65adf7b', 'oai:doaj.org_article:bcd42ba830724dfd838a0b5c419fa7b7', 'oai:doaj.org_article:7de645c700cb4497ace55cbc98808dae', 'ftdialnet:oai:dialnet.unirioja.es:ART0000845821', 'oai:doaj.org_article:e64cd19f007c459596d4810fe87fec75', 'oai:doaj.org_article:5514e80790c149a4a0e8d9d396b63b21', 'oai:doaj.org_article:9233de44f0cb4db1ba9be1564546da96']</t>
   </si>
   <si>
     <t>['oai:doaj.org_article:88a94414096a488cb30545129adfef3e', 'oai:doaj.org_article:d36725507166438fb4a735273e1f3863', 'oai:doaj.org_article:3743943233174041b0117c237b43a1a3', 'oai:doaj.org_article:16483b8940464114a63dfec744f0ef96', 'oai:doaj.org_article:0fcf34f1fa36491eb16b90b52c37f72c', 'oai:doaj.org_article:82798346b0ac4c229f9d293fa0b1d25a', 'oai:doaj.org_article:13206c44732e47b99b048314025fd439', 'oai:doaj.org_article:7a9e69c2e6ce46399d09c73e9cc3f0f1', 'oai:doaj.org_article:81b88fc1cf904529a4b4b6608a8c9827', 'oai:doaj.org_article:9244c00a0dad49f3809dbeff1b485738', 'oai:doaj.org_article:05f6d30a68fb49f8afc737a0a52a387c', 'oai:doaj.org_article:1135e07cabd54a4db0fc59f711d2bc21', 'oai:doaj.org_article:7dffa10d4d204e96b55d90c219d64229', 'oai:doaj.org_article:747bd200d458406694eed12eaff2bc56', 'oai:doaj.org_article:7086e53c9d6749c7b8d6d9d0eaee1bc8', 'oai:doaj.org_article:1b379e41f4c24d60814c12848a99d057', 'oai:doaj.org_article:e53ea09abfa248fdafc9d35155c2bac6', 'oai:doaj.org_article:db702b5249204f32841452416f7bb643', 'oai:doaj.org_article:dda875a9dca14ae69bf9a4f935e849e9', 'oai:doaj.org_article:4f45ce9eb5a944258c4ce5a52acac551', 'oai:doaj.org_article:1d6b0cf06d404235ba5df00354194a9a', 'oai:doaj.org_article:9dcda57f581143c5af813e284b85b140', 'oai:doaj.org_article:5648fc25e336454bb6beedaa248563b2', 'oai:doaj.org_article:66525c4e8a1b480aa4406adb41d7af94', 'oai:doaj.org_article:e8739bad619046fdaeb5f78dd01734b1', 'oai:doaj.org_article:d33cbc8c90fd4b1c977ffb0043a1505f', 'oai:doaj.org_article:d549c7384f1b41b3aee628903b14ef60', 'oai:doaj.org_article:eb070fb1e7b34862816aec536435eb1e', 'oai:doaj.org_article:a7d6a34ea7e84d7fad69886f6c20ae28', 'oai:doaj.org_article:a430f10e499a4db0aae005cf6e9ffc55', 'oai:doaj.org_article:4b977a5ea12c4fedbf6f6ceb9ebb1725', 'oai:doaj.org_article:41b8881e79d04c649e69c22965695ad8', 'oai:doaj.org_article:5750780956744c1ba8e094459ca99ed1', 'oai:doaj.org_article:8fabfc07bc4c40f9a9041897e5dfc615', 'oai:doaj.org_article:af587458574d4fd89da857c45ce19880', 'oai:doaj.org_article:953c5ed684ff470c8d5dc962cb8f6611', 'oai:doaj.org_article:9890f42fc9454b0fa429fb0c3a8f7c6f', 'oai:doaj.org_article:034a8a22a6994d8d9a6251e3ed596de7', 'oai:doaj.org_article:d607a904792b44138c7041dd3c6c92fa', 'oai:doaj.org_article:c17b669995f240bcbdf1c77659169f27', 'oai:doaj.org_article:97d82e4a73404fb8b97ddaf0aebd8a58', 'oai:doaj.org_article:d8d10a671baf4b30a8c477053eb3432b', 'oai:doaj.org_article:229f0ea00b7e4c8d86385559a40abbfc', 'oai:doaj.org_article:a01cfa61a6854719bb693c75e84002c4', 'oai:doaj.org_article:a8ec48aa710945ff8e4df1ed5b2f1b37', 'oai:doaj.org_article:6afcfcc54d084d0f86074ce4b76f6cf9', 'oai:doaj.org_article:3858949010214ff8bd5d964d5a57c4fe', 'oai:doaj.org_article:d19fae3f6b61475089dc25216154e5c7', 'oai:doaj.org_article:0ada59ee270b4e4dad6c29fbbe5a5d5a', 'oai:doaj.org_article:262dd7884f174dc99a101fe9a4d7d4f2', 'oai:doaj.org_article:9620f59b2a9a42028b75aea1f048358f', 'oai:doaj.org_article:6f6f685609af414585b0575519079612', 'oai:doaj.org_article:8432d9e491d64a91ad93a1e204f14cc8', 'oai:doaj.org_article:6a2c0ffcfe9240398a2605afa530e15f', 'oai:doaj.org_article:bd63816ac1a541bab8f0390a4e45938d', 'oai:doaj.org_article:9b82ee161c744b7996dad78f27d9a3fa', 'oai:doaj.org_article:71e3db7daefc4e23bf0427276a4ab4d2', 'oai:doaj.org_article:d3ab275ba6a1473aa3a6c0e2cc5d3d5f', 'oai:doaj.org_article:d3a0df0a924e4db7a6219548e7934374', 'oai:doaj.org_article:eeeb754bcaa84216bf433fbd93b5d094', 'oai:doaj.org_article:e011e8031cdc48d2bc4c15d93f8b466b', 'oai:doaj.org_article:38dbe6012fd946e5b8d6939df3435411', 'oai:doaj.org_article:f796980a99e142079ac090628ad62421', 'oai:doaj.org_article:e55abf4995a74d31ad5e7e04f4ec7152', 'oai:doaj.org_article:0774efb62f9942ec9bd4281a597e42fa', 'oai:doaj.org_article:9e9ef59615e7407c839f04f0fb86b0ac', 'oai:doaj.org_article:9937f594b9404fc591747c8e21df41cb', 'oai:doaj.org_article:5d25b69fd2744f8aa20eac22fb7007da', 'oai:doaj.org_article:295e0f71bac5463aad7f515aa27e2b35', 'oai:doaj.org_article:cd0eed3062b343ad99dbdf144057c220', 'oai:doaj.org_article:078889f11ad646fe9ec3e67d99bea258', 'oai:doaj.org_article:dd18ef9f9c224d019fa2bda829537cc5', 'oai:doaj.org_article:938f335feae84be1b1e0aa8a3a3f99bf', 'oai:doaj.org_article:fb24463ff1e743379398d0c7cb89baf7', 'oai:doaj.org_article:048da4a3e5f94c9a87260b155bb613db', 'oai:doaj.org_article:34c427195e124c04bf692669f7c8ad69', 'oai:doaj.org_article:f5878d5943ce4073bf6c1e72a00a874e', 'oai:doaj.org_article:ef4fc3b27e4c441abb9d5f095f4e7306', 'oai:doaj.org_article:001f3d1f71304beab2b543e17d9c6c1f', 'oai:doaj.org_article:f553e06727344951ad4247c5a23e0e1d', 'oai:doaj.org_article:e80d4f5c7c464a459cb8aabab77c5819', 'oai:doaj.org_article:ff79e43ea77840f7ad277fc16e3e3e5d', 'oai:doaj.org_article:1bc6e7a7d6c04a7295992fed8af50c7d', 'oai:doaj.org_article:91c419390c3346c68a11a67f24e258f2', 'oai:doaj.org_article:c7e815db7bae403484b6ef4e6763ead0', 'oai:doaj.org_article:11d56a530dee483688a13cab68557484', 'oai:doaj.org_article:a184d1e25ebe40c7b633f1a6630155d5', 'oai:doaj.org_article:4b84e47b12724107a0e50a61324f5864', 'oai:doaj.org_article:7dd89ad833e645358f17a4cc6147d30a', 'oai:doaj.org_article:a2f263075c7d4415826a38eab4fe53ab', 'oai:doaj.org_article:16cce3b84b83474ebdd2a4cd9fcfe257', 'oai:doaj.org_article:ec9ae874a2f2450aa0d9a3a4b0619d7e', 'oai:doaj.org_article:dce87ec7a3ae42fd962a85c7eda7141f', 'oai:doaj.org_article:f170d524c55b41bb9f738ca69c22c474', 'oai:doaj.org_article:6641d41bf0d14613987b03d889eab04a', 'oai:doaj.org_article:1cfd1906084b40acb13b1d9420721fcb', 'oai:doaj.org_article:8f1d0b8b2b1d43bbb42a4bc8ebe772d8', 'oai:doaj.org_article:fbe3334547f74a9da60f37091ec8df7c', 'oai:doaj.org_article:b768ddd0dc8c44678b495933dd3af5c3', 'oai:doaj.org_article:9534c5a3474242eb86061e8babd895fe', 'oai:doaj.org_article:3b9c76b012604934baf284bc8d66932c', 'oai:doaj.org_article:081f5f856ffe402387cc51212c100ef7', 'oai:doaj.org_article:bc6305f68ea94a16a70b75d663ef60fc', 'oai:doaj.org_article:71f76e37f77a4e64bdb4fb0ed7a3ed93', '10670_1.atg0r0', 'oai:doaj.org_article:3984eeaf73b54f038059eed2c9d57e8f', 'oai:doaj.org_article:55938f95671c4aa6aa24df0cbcaaf7c4', 'oai:doaj.org_article:fe39f7bdeef44149998a699e7934c626', 'oai:doaj.org_article:59fe43e2d0594230981e404708a27e0e', 'oai:doaj.org_article:d4f62528104d4ab9b77c3809ed56985c', 'oai:doaj.org_article:4cb7a172aa754f2e9c31a42466623aa1', 'oai:doaj.org_article:83673def41db460cab811db4066e9026', 'oai:doaj.org_article:25e9859888714ab9a4b2d2e888c03d0d', 'oai:doaj.org_article:27307a91970a4d99b2bd1413983b652a', 'oai:doaj.org_article:c8e5ab027a1a45db924824e0ce32b3d5', 'oai:doaj.org_article:e5c6d1b576c742a4ad2413fd5203bcaa', 'oai:doaj.org_article:56a2d617411c42c3a8b5ad8d9041c600', 'oai:doaj.org_article:2f298dd2f4eb4c27b139531a4536d74c', 'oai:doaj.org_article:95a0fe8bcd0047829c94981e72465fcf', 'oai:doaj.org_article:51d0c2c077664dcbb97013186f776ad9', 'oai:doaj.org_article:4e8797950fe14f04979ee97766f3db40', 'oai:doaj.org_article:89ab84ff7c194e96b94c27c0bf98369f', 'oai:doaj.org_article:3bb32e12d83f498fb0b7d2d4a3516588', 'oai:doaj.org_article:8275dd7e328a4e4d8fe039d4c196c2c1', 'oai:doaj.org_article:8ddd0ff4b11a49e5bbd4dc09dd8a2b19', 'oai:doaj.org_article:50f12159832c4f2fbe1958a0675132e2', 'oai:doaj.org_article:ef16883b635a4197a901892d7e16fc77', 'oai:doaj.org_article:2c0e9aca4f7e4f40bd50fd0edf72d5a0', 'oai:doaj.org_article:9b23bcbf3c7643b3b56ac22689b066c1', 'oai:doaj.org_article:17c39f1f947640e1b1134db2c5b77070', 'oai:doaj.org_article:d97ebb8ac61d48b8b381f00a04dfa0ca', 'oai:doaj.org_article:bde422f470f94e4cbe3a69c208af608c', 'oai:doaj.org_article:a5da409780ff4a87b495c1b8de4a0847', 'oai:doaj.org_article:218eda3993824080b7225d984b501cc1', 'oai:doaj.org_article:ba7773997e77472490e81793b8b7cb93', 'oai:doaj.org_article:91f87ea8162c46fcb0f46db5bfb9e7ab', 'oai:doaj.org_article:a83d70a64d634353a1be4bb961b907f0', 'oai:doaj.org_article:9ddaf5616c9d4603822403d45c80cac1', 'oai:doaj.org_article:9f68309105f2475caeb6d1ccad6a8edd', 'oai:doaj.org_article:39532c323cf04211b27e16643a49c9cc', 'oai:doaj.org_article:537f34c245564a978e4f5e1869bef58b', 'oai:doaj.org_article:bf945514afec43ce84bc9df6c2aea4d1', 'oai:doaj.org_article:6ff07c601af64649900a53c4c119b049', 'oai:doaj.org_article:6f4d858540ce438fb247a4c1eb9c8ef4', 'oai:doaj.org_article:58963fcc75254ac08b4331847b3e14ac', 'oai:doaj.org_article:479f825c11f74977aeee3f95b30788ec', 'oai:doaj.org_article:7bb72ff9dfa34de39e1d38aa4272b095', 'oai:doaj.org_article:59889a719bd940139a069c699bab1894', 'oai:doaj.org_article:b328133ee2a2460aab7c5663d35faedb', 'oai:doaj.org_article:4957ab2ef9354f11ad6f1f4e5631e2ab', 'oai:doaj.org_article:8a79d73e5a1a43bfb6c8af279373ffcb', 'oai:doaj.org_article:a9a70a51c3ab466dab597d92861793cc', 'oai:doaj.org_article:58bb514d968049e1b237a9d1646dc46d', 'oai:doaj.org_article:ae2c60fe72b0441b92985e6e9de3bb93', 'oai:doaj.org_article:c02aa395287a4749b8d3ac6299cd263b', 'oai:doaj.org_article:097540058bc44c9dbb738b90fefff7dc', 'oai:doaj.org_article:861ba14fd772480998fa1ce138a3d9e8', 'oai:doaj.org_article:338f7ea6de9a42ed965d3c300b2c9104', 'oai:doaj.org_article:bde111a7e25a4aaf94b07254b2e9d73f', 'oai:doaj.org_article:4d9166f2033a44d488eeac06355f4f9f', 'oai:doaj.org_article:bf11ccbdcf354331ae12499696aab5a9', 'oai:doaj.org_article:883d0578cae2461fa1adcbed8f01463b', 'oai:doaj.org_article:5c230f2e8c634d24ac9979ac419429a7', 'oai:doaj.org_article:003bf92e9f964a0390ae4e0fd41a7d8a', 'oai:doaj.org_article:7f4753b333e54f3faf8f2368619254dd', 'oai:doaj.org_article:9de56127996b41e1923dd742e764f566', 'oai:doaj.org_article:1f1ef2f540a24b9996feeee57e0610ab', 'oai:doaj.org_article:6260d9cbf6f44325995b9212058350a9', 'oai:doaj.org_article:5e22c1b718774358afd9bcf1edc994f4', 'oai:doaj.org_article:715f096ec05f41b9bf92bfabe1c911fe', 'oai:doaj.org_article:4bee7cbc3210401c8312706ee5246c71', 'oai:doaj.org_article:d71c6ab75dc2420ab0ec2d8d82a294e7', 'oai:doaj.org_article:7afc76accb334b3da4087798ed183b46']</t>
   </si>
   <si>
-    <t>['oai:doaj.org_article:ebb4d100f442405096d13379cad2f4fa', 'oai:doaj.org_article:3c96d54a609d4d22b14a03b5a59c5394', 'oai:doaj.org_article:ca47bfd5204e48a8b9ce653e3372a61d', 'oai:doaj.org_article:94c4e79de602496285b5263e61d6b4e6', 'oai:doaj.org_article:99486388e9b24c5883d7d02ca95da316', 'oai:doaj.org_article:0940abbd0e754bedbd6d9da9d9d383b0', 'oai:doaj.org_article:6de894331cae4e27991675e7dba43554', 'oai:doaj.org_article:e316e97b397c4d88b33ca6c3f5f13a27', 'oai:doaj.org_article:fcac4cb9f1d84dceba044247e275a0f5', 'oai:doaj.org_article:164417ec4e634850be8971dcaf787084', 'oai:doaj.org_article:427c53b3cee442cabf4d7d0a63059c22', 'oai:doaj.org_article:98c2b2eae427498bbeb4f8fe1c79dc78', 'oai:doaj.org_article:8450d710d098454f8ef1190c89f1844c', 'oai:doaj.org_article:5d52873aac224ee58fe218dc75bafc8b', 'oai:doaj.org_article:74f2450349e1418b8e1e4e3df062805f', 'oai:doaj.org_article:a1695cf42eb640bf9367a5feaf1de0ef', 'oai:doaj.org_article:1a1e17eb44934863883c089ed21fd356', 'oai:doaj.org_article:23cb33e1e56149aaae6c8b6d1464d7bc', 'oai:doaj.org_article:1cf4ae944f6549969a7cdec7b3db985f', 'oai:doaj.org_article:bb84febb3d0b46779c67c06ea5a40289', 'oai:doaj.org_article:b3fc6b1965bd43fa9a44fdcc8feee57f', 'oai:doaj.org_article:d80cf6faa4dd446eba8e423f681f490a', 'oai:doaj.org_article:48b037d38b3149a4aec60531a8aed680', 'oai:doaj.org_article:6a88d0f8633848fcae29bff773fe5ca2', 'oai:doaj.org_article:5c14cb1dee334a2682000504523dcc54', 'oai:doaj.org_article:8d81513ed1bf4e27b3880834b7a111db', 'oai:doaj.org_article:d47470f88e3c477c9e0659b17a267c59', 'oai:doaj.org_article:b55881384daa4b88a6c6f754cb014568', 'oai:doaj.org_article:9a205e0b6ae14d8398af29e3a2d22ce7', 'oai:doaj.org_article:6bb0db779f1a4b5cb53998be55a2219d', 'oai:doaj.org_article:3803368831ef459aa14f273474c68a9d', 'oai:doaj.org_article:7f7c4305eea84b81819cfbec329acd57', 'oai:doaj.org_article:873ab8741aab48aa99b69d2ffdc5493c', 'oai:doaj.org_article:e0bc00006ebd49ad86320f0ddf6697d4', 'oai:doaj.org_article:df67577b7c134909840fd823170afe20', 'oai:doaj.org_article:6bfedde04fbd4a4e84c744afdb13e028', 'oai:doaj.org_article:23bd2170dac64435b7ad1ff654f714fc', 'oai:doaj.org_article:e196151d6e464ebcac7f4e6590d806de', 'oai:doaj.org_article:43dc1be1fcdd4488b91aba3cc90b297f', 'oai:doaj.org_article:8f266f9e9a634e5f85f9a0fc507b79a1', 'oai:doaj.org_article:1dbb5e0e492d42bb95e8d5b2a3c78610', 'oai:doaj.org_article:93af869cec454f37863c62b35d028dc2', 'oai:doaj.org_article:5609fc3d409b4b04b549d475d598526b', 'oai:doaj.org_article:5a4c6db695764319b727c9b2f2d27ae2', 'oai:doaj.org_article:c4d257e60edb47a28bbd0c58b88dcf23', 'oai:doaj.org_article:b52f1ed6421941929427265e7280b2ff', 'oai:doaj.org_article:443e19e0a08c43c29eded7e8b49392b4', 'oai:doaj.org_article:b397763365254d7d950f54a8e2932ba2', 'oai:doaj.org_article:2c558cc84c4148508b7c2874e0171524']</t>
-  </si>
-  <si>
-    <t>['oai:doaj.org_article:8609798aee2748f69109f29d263e04cd']</t>
-  </si>
-  <si>
-    <t>['oai:doaj.org_article:274e49e26ee445f8a7c161bdd2d278a2']</t>
-  </si>
-  <si>
-    <t>['oai:doaj.org_article:eee1f8f5f1a24d6da581ca388d6004ac']</t>
-  </si>
-  <si>
-    <t>['oai:doaj.org_article:e4f61c01ef974a729524d01a512e2336']</t>
-  </si>
-  <si>
-    <t>['oai:doaj.org_article:708f01c1d44146faa783be8c2ba0a30c', 'oai:doaj.org_article:50ed3d5d3032409e9224d3878bdd40b5']</t>
-  </si>
-  <si>
-    <t>['oai:doaj.org_article:87e727ff303a4c8087aed69b07c18dd8', 'oai:doaj.org_article:18651150c99240d3a837c6b3ac0dff28']</t>
-  </si>
-  <si>
-    <t>['oai:doaj.org_article:4a9339c77489420380e2f7865c3fb5f3', 'oai:doaj.org_article:fd0581815dc24cf2886785b831b927c1']</t>
-  </si>
-  <si>
-    <t>['10670_1.jqseeq']</t>
-  </si>
-  <si>
-    <t>['oai:doaj.org_article:8744be6e8ca7434297a0ce5ab8d96c36', 'oai:doaj.org_article:293cbc10dd3d409ea3b9a77a842dc669', 'oai:doaj.org_article:1371ff51fbee4b54aa17a5b8d6882da2', 'oai:doaj.org_article:ee72ab34aedc46769621f5d0e263cb9f', 'oai:doaj.org_article:ab2b09b2d66e4c8687dd3c8c30cb1b36', 'oai:doaj.org_article:3528146e42c04766a6dcb6efb65f7e53']</t>
-  </si>
-  <si>
-    <t>['oai:recyt.fecyt.es:article_79043', 'oai:doaj.org_article:22f5842817674a7c9df6ab6dcda3d90b']</t>
-  </si>
-  <si>
-    <t>['10670_1.ctj6r9']</t>
-  </si>
-  <si>
-    <t>['oai:doaj.org_article:ab61c21e633a4a1c9971e95b1390c716', 'oai:doaj.org_article:68fb96c84ace499aaa4d74479a1a09b0', 'oai:doaj.org_article:ea0dd166f88545a488935a2bc1906b76', 'oai:doaj.org_article:5ffbd6b9eea94013b1fd06677afd44aa']</t>
-  </si>
-  <si>
-    <t>['oai:recyt.fecyt.es:article_79039', 'oai:doaj.org_article:c79dc0626fcd46b3a15eedad2e792e5b']</t>
-  </si>
-  <si>
-    <t>['10670_1.3escy8', 'oai:doaj.org_article:1b419ab9d7ef4010a42a3e1bfdd584a2', 'oai:doaj.org_article:ec57d0594dff446a96fc804ae9b64096', 'oai:doaj.org_article:4bcfc68d324e40ba910895ff9eeb53f9', 'oai:doaj.org_article:442376731f824e95b65d1352a65adf7b', 'oai:doaj.org_article:bcd42ba830724dfd838a0b5c419fa7b7', 'oai:doaj.org_article:7de645c700cb4497ace55cbc98808dae', 'ftdialnet:oai:dialnet.unirioja.es:ART0000845821', 'oai:doaj.org_article:e64cd19f007c459596d4810fe87fec75', 'oai:doaj.org_article:5514e80790c149a4a0e8d9d396b63b21', 'oai:doaj.org_article:9233de44f0cb4db1ba9be1564546da96']</t>
-  </si>
-  <si>
-    <t>['10670_1.jb2q1v']</t>
-  </si>
-  <si>
-    <t>['10670_1.pqqo8q']</t>
-  </si>
-  <si>
-    <t>['oai:doaj.org_article:53b052908fe947d4a62b7e6a575525ea']</t>
-  </si>
-  <si>
-    <t>['ftuninsanjuanijs:oai:ojs.pkp.sfu.ca:article_807']</t>
-  </si>
-  <si>
-    <t>['oai:doaj.org_article:074fd2d89f0b4dc4b45eb307257a92b5', 'oai:doaj.org_article:5862c0a6730d43eba07453e769ccfa07', 'oai:doaj.org_article:dbef64a8bbeb49579cedf1cd6e93409a', 'oai:doaj.org_article:13ef6ad7e2984c07ac9adc0756703818', 'oai:doaj.org_article:7fbaec7737e743bcb6cad1163e2d4ee8', 'oai:doaj.org_article:302701027ecd4428a41fb50764dfad13', 'oai:doaj.org_article:69644e8ddfd2463db1941ce62853668e', 'oai:doaj.org_article:8a7a26003b0c4026b33f38f72b3ccd87', 'oai:doaj.org_article:594aa2b1c75f4e7d9fa6d0f1dcecac78', 'oai:doaj.org_article:cc873957cd9048918e8ea9566a5d7753', 'oai:doaj.org_article:e740f0a323f94b6889714eccefe0947f', 'oai:doaj.org_article:02afea1dfad540049a21de2f4e83021a', 'ftjmcys:oai:ojs2.www.medicinaclinicaysocial.org:article_40', 'ftjrpi:oai:ojs2.rpi.isri.cu:article_64', 'ftunivbiobioojs:oai:ojs.revistas.ubiobio.cl:article_5491', 'oai:recyt.fecyt.es:article_70727', 'oai:recyt.fecyt.es:article_88530', 'oai:recyt.fecyt.es:article_70836', 'oai:recyt.fecyt.es:article_70534', 'oai:recyt.fecyt.es:article_70512', 'oai:recyt.fecyt.es:article_70782', 'oai:recyt.fecyt.es:article_88548', 'oai:doaj.org_article:dfaa16778bd44b949b07543c87969ae3', 'oai:doaj.org_article:f75510227ad74603878d67689146ace0', 'oai:doaj.org_article:dd17e68e2a454efc90c3c308f8305f71', 'oai:ojs.revistas.ucm.es:article_60136', 'oai:doaj.org_article:20ee5bd9f2f14d258cc9f689f9f74401', 'oai:doaj.org_article:0437056da8e54d9683c63f847b994ab7', 'oai:doaj.org_article:459c788026c44b6e9eb2ca9368dce8e0', 'oai:doaj.org_article:4accaf83c0bd408ca970bf8fd404bdc1', 'oai:doaj.org_article:ea69f9d9a7024c9a828e5cf883b83ae4', 'oai:doaj.org_article:7b5c7a146a39416480ab93b231174b0f', 'oai:doaj.org_article:fce0cacfb6b349be8fbb817aa4fbefc3', 'oai:doaj.org_article:bcb317ab77684f38b6cf69a044d47459', 'oai:doaj.org_article:436be46a95b2419689b21f9c89815c7b', 'ftjrpi:oai:ojs2.rpi.isri.cu:article_146', 'oai:ojs.pkp.sfu.ca:article_70512', 'oai:ojs.pkp.sfu.ca:article_70534']</t>
-  </si>
-  <si>
-    <t>['oai:ojs.revistas.ucm.es:article_39794', 'oai:doaj.org_article:a37672d69fe34744a542971abc86c3d4', 'oai:doaj.org_article:df02fe3e1aa6446ca817c94a523375dc', 'oai:doaj.org_article:5ef9827768cd458ca07655b7bd586df7']</t>
-  </si>
-  <si>
-    <t>['oai:doaj.org_article:8369fdd2df1d45149f1d9c8d7a017968', 'oai:doaj.org_article:6df2a7a8b1c94a4c9223c3c9f9823033', 'ftkingscollondon:oai:pure.atira.dk:publications_4582a4de-6744-4d1d-9021-28cffba5a4fa', 'ftunivgeneve:oai:unige.ch:unige:155232', 'ftinserm:oai:HAL:hal-03691657v1', 'ftoslouniv:oai:www.duo.uio.no:10852_93886', 'ftpubmed:oai:pubmedcentral.nih.gov:9010705', 'ftriip:oai:HAL:hal-03691657v1', 'ftpubmed:oai:pubmedcentral.nih.gov:9432753', 'ftpubmed:oai:pubmedcentral.nih.gov:4073248', 'ftworldbank:oai:openknowledge.worldbank.org:10986_34814', 'ftworldbank:oai:openknowledge.worldbank.org:10986_34926', 'oai:journals.um.si:article_97', 'oai:doaj.org_article:07c100a6ce324817b377171803c4855c', 'oai:doaj.org_article:5e6e2148c23c49a895791f48e61e0f85', 'ftunivliverpool:oai:livrepository.liverpool.ac.uk:3025011', 'ftpubmed:oai:pubmedcentral.nih.gov:9367745', 'ftdoajarticles:oai:doaj.org_article:95551ebe180740758115cd881e9ac8b7', 'ftdoajarticles:oai:doaj.org_article:c140614342044ce4bbde4a30eaac9bf0', 'ftleedsuniv:oai:eprints.whiterose.ac.uk:104170', 'ftunivessex:oai:repository.essex.ac.uk:33461', 'ftpubmed:oai:pubmedcentral.nih.gov:4593291', 'ftunivliverpool:oai:livrepository.liverpool.ac.uk:3154321', 'ftleedsuniv:oai:eprints.whiterose.ac.uk:185808', 'ftcovenantuniv:oai:generic.eprints.org:5719', 'ftdoajarticles:oai:doaj.org_article:3a88852d88af4eb6aa73cbcffaf685f1', 'ftdoajarticles:oai:doaj.org_article:fc6357040ca64fc984ecc96e77c19246', 'ftunivleuven:oai:lirias.kuleuven.be:123456789_186665', 'ftceon:oai:depot.ceon.pl:123456789_956', 'ftphilpapers:oai:philpapers.org_rec_BROPEI-3', 'fthrcak:oai:hrcak.srce.hr:23346', 'fthrcak:oai:hrcak.srce.hr:183381', 'ftpubmed:oai:pubmedcentral.nih.gov:9475410', 'ftpubmed:oai:pubmedcentral.nih.gov:6720555', 'ftpubmed:oai:pubmedcentral.nih.gov:6889688', 'ftdoajarticles:oai:doaj.org_article:e16060828b60400c8603cd37cc9c8bca', 'ftdoajarticles:oai:doaj.org_article:36a225556c5a49b59def089a10a3279d', 'ftpubmed:oai:pubmedcentral.nih.gov:3933755', 'ftliverpoolstm:oai:archive.lstmed.ac.uk:7509', 'ftumanchesterpub:oai:pure.atira.dk:publications_33ff92cc-eed4-48f0-994c-1d0acd19f1b1', 'ftihswien:oai::5894', 'fthrcak:oai:hrcak.srce.hr:305985', 'ftdoajarticles:oai:doaj.org_article:26792694c774410fa08312683c886acb', 'ftpubmed:oai:pubmedcentral.nih.gov:7249676', 'ftfrontimediafig:oai:figshare.com:article_24277543', 'ftkingscollondon:oai:pure.atira.dk:publications_61e4ab0e-4f28-4d5d-8892-ff443575e192', 'ftpubmed:oai:pubmedcentral.nih.gov:7791849', 'ftunivmilanobic:oai:boa.unimib.it:10281_17214', 'ftunivgeneve:oai:unige.ch:aou:unige:155232', 'ftlinnaeusuniv:oai:DiVA.org:lnu-40549', 'ftuniaarhuspubl:oai:pure.atira.dk:publications_c056e602-53da-4e83-b6c2-e824ed1fad77', 'ftkingscollondon:oai:pure.atira.dk:publications_33739829-bd87-4d41-aefa-a2682b49261f', 'ftunivbrescia:oai:iris.unibs.it:11379_539015', 'ftunivmoliseiris:oai:iris.unimol.it:11695_477', 'ftunivsplit:oai:repozitorij.svkst.unist.hr:forenzikast_383', 'ftsydanskunivpub:oai:sdu.dk:publications_5fe40505-6d15-48d8-a337-8a4b619715a9', 'ftuabarcelonapb:oai:ddd.uab.cat:289634', 'ftupompeufabra:oai:repositori.upf.edu:10230_49193', 'fthrcak:oai:hrcak.srce.hr:246902', 'ftkingscollondon:oai:pure.atira.dk:publications_7639c966-fbe8-40b8-a325-b2e0ef05c1eb', 'ftcopenhagenunip:oai:pure.atira.dk:publications_ad997fd8-6115-47bf-aeba-71be699f3876', 'ftdnbreiheo:1250067170', 'ftunivgenova:oai:iris.unige.it:11567_503755', 'ftunivrijeka:oai:www.unirepository.svkri.uniri.hr:fthm_2708', 'ftunivrijeka:oai:www.unirepository.svkri.uniri.hr:fthm_3186', 'ftuwarwick:oai:wrap.warwick.ac.uk:146855', 'ftunivzuerich:oai:www.zora.uzh.ch:124548', 'ftiesbelgrad:oai:ebooks.ien.bg.ac.rs:115', 'ftdoajarticles:oai:doaj.org_article:9ca531890bfb427aa611cda3a2e33f51', 'ftpubmed:oai:pubmedcentral.nih.gov:7721354', 'ftvuamstcris:oai:research.vu.nl:publications_b8285cbe-722e-4f6f-b330-ec080e36b8f0', 'ftlondoneconom:oai:eprints.lse.ac.uk:116626', 'ftvuamsterumc:oai:pure.atira.dk:publications_05a186a1-525e-4360-85df-e8d088513ba5', 'ftvuamsterumc:oai:pure.atira.dk:publications_68587b22-f052-4021-ba9c-bafee1b35498', 'ftworldbank:oai:openknowledge.worldbank.org:10986_30579', 'ftglasgowcucris:oai:researchonline.gcu.ac.uk:publications_920c5054-23ff-4a67-ba8d-058a6a413fc5', 'ftnulzagrebzir:oai:zir.nsk.hr:fthm_2708', 'ftnulzagrebzir:oai:zir.nsk.hr:fthm_3186', 'ftnulzagrebzir:oai:zir.nsk.hr:foi_442', 'ftdoajarticles:oai:doaj.org_article:5bf847ecd95046399d35d251c2e96ab7', 'ftdoajarticles:oai:doaj.org_article:e7ac765c353c4cb28b645bafecf3f137', 'oai:doaj.org_article:9ca531890bfb427aa611cda3a2e33f51', 'oai:doaj.org_article:78d8cf2c62c6480eafa3c6b132418c86', 'oai:doaj.org_article:26792694c774410fa08312683c886acb', 'ftlitinstagrecon:oai:elaba:11675971', 'ftpubmed:oai:pubmedcentral.nih.gov:8356263', 'ftpubmed:oai:pubmedcentral.nih.gov:7798200', 'ftpubmed:oai:pubmedcentral.nih.gov:6418058', 'ftzenodo:oai:zenodo.org:7533130', 'ftzenodo:oai:zenodo.org:6683292', 'fthrcak:oai:hrcak.srce.hr:244498', 'ftunivhongkonghu:oai:hub.hku.hk:10722_87806', 'ftdoajarticles:oai:doaj.org_article:25d15b75e8874c7fa5f32662e476caf9', 'ftdoajarticles:oai:doaj.org_article:453b9faf9aa74ebbb23fe2c796485514', 'ftdoajarticles:oai:doaj.org_article:459f202aac0342c2ae503e16f12bce90', 'ftpubmed:oai:pubmedcentral.nih.gov:7231414', 'ftunivfreiburg:oai:freidok.uni-freiburg.de:154085', 'ftpubmed:oai:pubmedcentral.nih.gov:6925899', 'ftunivmaribor:oai:dk.um.si:IzpisGradiva.php?id=67004', 'ftiesbelgrad:oai:ebooks.ien.bg.ac.rs:356', 'ftpubmed:oai:pubmedcentral.nih.gov:6451281', 'ftmdpi:oai:mdpi.com:_1660-4601_19_15_9515_', 'ftuniveastangl:oai:ueaeprints.uea.ac.uk:61475', 'ftnulzagrebzir:oai:zir.nsk.hr:pravo_2876', 'ftiesbelgrad:oai:ebooks.ien.bg.ac.rs:238', 'oai:hrcak.srce.hr:23346', 'oai:hrcak.srce.hr:23005', 'ftjnepaljo:oai:ojs.pkp.sfu.ca:article_2434', 'ftubristolcris:oai:research-information.bris.ac.uk:publications_651775d8-7ee6-436c-ad29-0dab5252df3c', 'ftuniaarhuspubl:oai:pure.atira.dk:publications_6c0494b3-d369-4c19-9bbc-54834abd6d95', 'oai:doaj.org_article:b9dd420ea5f14cf9b67fed9754b57048', 'ftvuamsterumc:oai:pure.atira.dk:publications_eedd93f1-76f9-4d7b-a572-446dacbdc9ed', 'oai:doaj.org_article:453b9faf9aa74ebbb23fe2c796485514', 'ftunivbrescia:oai:iris.unibs.it:11379_503691', 'ftpubmed:oai:pubmedcentral.nih.gov:10293907', 'oai:revues.org:revus_1060', 'ftdoajarticles:oai:doaj.org_article:f2aa7a59ae6241d380fa088455f596e6', 'ftdoajarticles:oai:doaj.org_article:728ec30c13804eac99a0d4999d26f8d6', 'ftdoajarticles:oai:doaj.org_article:43ad06da6431404eb2bbbcbce5774ec5', 'ftdoajarticles:oai:doaj.org_article:05b7aadba8d34aa48204516ded9e20dd', 'ftdoajarticles:oai:doaj.org_article:c519986b58ab4a11be171975d5415cab', 'ftccsdartic:oai:HAL:hal-03691657v1', 'oai:hrcak.srce.hr:19672', 'ftdoajarticles:oai:doaj.org_article:6bf5928a8b2942259fad89ac075e0649', 'ftdoajarticles:oai:doaj.org_article:ca1e7faddd3a4029aeb7c14f8b22aa66', 'ftdoajarticles:oai:doaj.org_article:d4ad8cc55f254374a8b772b18e5943f8', 'ftdoajarticles:oai:doaj.org_article:ff3b08fc39144a38a14621323673e9e6', 'fthighwire:oai:open-archive.highwire.org:jech:78_1_61', 'ftdoajarticles:oai:doaj.org_article:31eab59e7f4d4a6baffa663cc5685c0d', 'ftdoajarticles:oai:doaj.org_article:8369fdd2df1d45149f1d9c8d7a017968', 'ftdoajarticles:oai:doaj.org_article:6df2a7a8b1c94a4c9223c3c9f9823033', 'ftdoajarticles:oai:doaj.org_article:4eb73630c4a84f2391e45f3248532bc7', 'ftdoajarticles:oai:doaj.org_article:7c4919f5c98f49b3abe2837fb4898ce2', 'fthrcak:oai:hrcak.srce.hr:22798', 'ftpensoft:10.3897_ese.2022.e95247', 'fthrcak:oai:hrcak.srce.hr:337619', 'fthrcak:oai:hrcak.srce.hr:125365', 'ftunivzagrebmsr:oai:medlib.mef.hr:553', 'ftbiomed:oai:biomedcentral.com:s12909-014-0277-y', 'oai:hrcak.srce.hr:20480', 'oai:doaj.org_article:93fa8cb5d99f42d980be69cdbadfc07d', 'oai:doaj.org_article:4eb73630c4a84f2391e45f3248532bc7', 'ftdoajarticles:oai:doaj.org_article:7a692845a9424463a76043636a5aa1db', 'ftangliruskinfig:oai:figshare.com:article_30071859', 'ftangliruskinfig:oai:figshare.com:article_30071856', 'ftdoajarticles:oai:doaj.org_article:441242d7bf9542bea056868961cac762', 'ftdoajarticles:oai:doaj.org_article:4a56d18e88ee46ea91428146037e4692', 'ftdoajarticles:oai:doaj.org_article:24367a74268147acac4e47cea97ae70e', 'ftdoajarticles:oai:doaj.org_article:6a605dfe9461456abfa2f9e2f4500fae', 'ftbiomed:oai:biomedcentral.com:s12916-015-0476-3', '10.4000_revus.1060', '10.3406_chime.1993.1893', '10.4000_revus.93', 'oai:HAL:hal-05300284v1', 'oai:HAL:hal-05044988v1', 'ftnulzagrebzir:oai:zir.nsk.hr:fdmz_917', 'ftmdpi:oai:mdpi.com:_2227-9032_14_6_735_', 'ftunivosijek:oai:repozitorij.unios.hr:fdmz_917', 'ftunivalencia:oai:roderic.uv.es:10550_119462', 'ftunivmalmoe:oai:DiVA.org:mau-67033', 'ftuppsalauniv:oai:DiVA.org:uu-536601', 'fthrcak:oai:hrcak.srce.hr:329259', 'ftdoajarticles:oai:doaj.org_article:dfd362bb54704a6f91d6af61453f0325', 'ftagderuniv:oai:uia.brage.unit.no:11250_2989662', 'ftdoajarticles:oai:doaj.org_article:ea0865f07546424db8fa54139c05909e', 'ftdnbreiheo:123161756X', 'ftdnbreiheo:1245268635', 'fthrcak:oai:hrcak.srce.hr:20480', 'ftdoajarticles:oai:doaj.org_article:93fa8cb5d99f42d980be69cdbadfc07d', 'ftdoajarticles:oai:doaj.org_article:b9dd420ea5f14cf9b67fed9754b57048', 'ftcsic:oai:digital.csic.es:10261_403762', 'ftdnbreiheo:1208012568', 'ftdnbreiheo:1276937911', 'ftdoajarticles:oai:doaj.org_article:c30c559c93994b4e8f722fc1fd867678', 'fthrcak:oai:hrcak.srce.hr:38309', 'fthrcak:oai:hrcak.srce.hr:47886', 'ftid14132:oai:lirias2repo.kuleuven.be:123456789_676637', 'ftihswien:oai:irihs.ihs.ac.at:5894', 'ftbritmuseumfig:oai:figshare.com:article_30071856', 'ftbritmuseumfig:oai:figshare.com:article_30071859', 'ftcardiffmetufig:oai:figshare.com:article_30071856', 'ftcardiffmetufig:oai:figshare.com:article_30071859', 'ftfrontimediafig:oai:figshare.com:article_22597705', 'fthrcak:oai:hrcak.srce.hr:315400', 'ftid14132:oai:lirias2repo.kuleuven.be:20.500.12942_717523', 'ftinraparis:oai:HAL:hal-05300284v1', 'ftlincolnunivfig:oai:figshare.com:article_30071856', 'ftlincolnunivfig:oai:figshare.com:article_30071859', 'ftopenunivfig:oai:figshare.com:article_30071856', 'ftopenunivfig:oai:figshare.com:article_30071859', 'ftoskarbordeaux:oai:oskar-bordeaux.fr:20.500.12278_207735', 'ftarxivpreprints:oai:arXiv.org:2302.06655', 'ftcdlib:oai:escholarship.org:ark:_13030_qt4nm2w7b9', 'ftgeorgetownuniv:oai:repository.library.georgetown.edu:10822_962729', 'ftid14148:oai:pubfactory.com:_journals_11192_86_1_article-p227.xml', 'ftuniaucklandfig:oai:figshare.com:article_30071856', 'ftuniaucklandfig:oai:figshare.com:article_30071859', 'ftunivbathspafig:oai:figshare.com:article_30071859', 'ftunivbathspafig:oai:figshare.com:article_30071856', 'ftunivlimericfig:oai:figshare.com:article_30071859', 'ftunivlimericfig:oai:figshare.com:article_30071856', 'ftvivofig:oai:figshare.com:article_30071859', 'ftvivofig:oai:figshare.com:article_30071856', 'ftdoajarticles:oai:doaj.org_article:0e6360e78a3c48d99c0f901a05dca04a', 'ftdoajarticles:oai:doaj.org_article:15c474ee5a014402b080e2600d99ad2e', 'ftfolkehelseins:oai:fhi.brage.unit.no:11250_2420564', 'ftdoajarticles:oai:doaj.org_article:fc52b043a9fb4174b1bc067b9c95e03e', 'ftdoajarticles:oai:doaj.org_article:d45ad091a574447a83998c4d833e38d7', 'ftlenus:oai:www.lenus.ie:10147_644011', 'ftlondoneconom:oai:researchonline.lse.ac.uk:118814', 'ftndcdu:oai:generic.eprints.org:14234', 'ftumanchesterpub:oai:pure.atira.dk:publications_6eec9730-fcf8-4386-b79d-f11d81465fd8', 'ftuniaarhuspubl:oai:pure.atira.dk:publications_bc864434-71fe-4fa4-b741-3630311ae919', 'ftuniaarhuspubl:oai:pure.atira.dk:openaire_5b1ed7a4-0ef9-41a4-a725-894d42ff50ac', 'ftuniaarhuspubl:oai:pure.atira.dk:openaire_bc864434-71fe-4fa4-b741-3630311ae919', 'ftuniaarhuspubl:oai:pure.atira.dk:publications_5b1ed7a4-0ef9-41a4-a725-894d42ff50ac', 'ftunivleiden:oai:scholarlypublications.universiteitleiden.nl:item_3206719', 'ftunivmilanoair:oai:air.unimi.it:2434_808163', 'ftunivmilanoair:oai:air.unimi.it:2434_727506', 'ftunivnewcastnsw:uon:49041', 'ftunivsplit:oai:repozitorij.svkst.unist.hr:mefst_2942', 'ftunivsplit:oai:repozitorij.svkst.unist.hr:mefst_2947', 'ftunivstirling:oai:dspace.stir.ac.uk:1893_12985', 'ftunnottinghamrr:oai:nottingham-repository.worktribe.com:46170155', 'ftdublininstt:oai:arrow.tudublin.ie:scschcomart-1109', 'ftgriffithuniv:oai:research-repository.griffith.edu.au:10072_33555', 'ftkingscollondon:oai:kclpure.kcl.ac.uk:publications_4582a4de-6744-4d1d-9021-28cffba5a4fa', 'ftkingscollondon:oai:kclpure.kcl.ac.uk:publications_7639c966-fbe8-40b8-a325-b2e0ef05c1eb', 'ftmdpi:oai:mdpi.com:_2227-9032_13_16_1959_', 'ftuniljubljanaff:oai:ojs.revije.ff.uni-lj.si:article_20994', 'ftchalmersuniv:oai:research.chalmers.se:547318', 'fthrcak:oai:hrcak.srce.hr:325041', 'ftunibolognairis:oai:cris.unibo.it:11585_1051901', 'ftid14132:oai:lirias2repo.kuleuven.be:123456789_186665', 'ftgriffithuniv:oai:research-repository.griffith.edu.au:10072_26145', 'ftkentuniv:oai:kar.kent.ac.uk:24630', 'ftkingscollondon:oai:kclpure.kcl.ac.uk:publications_33739829-bd87-4d41-aefa-a2682b49261f', 'ftuniaarhuspubl:oai:pure.atira.dk:publications_f0f71c90-f833-11dd-8f9a-000ea68e967b', 'ftid14132:oai:lirias2repo.kuleuven.be:20.500.12942_722639', 'fthrcak:oai:hrcak.srce.hr:41340', 'fthrcak:oai:hrcak.srce.hr:59287', 'ftjnepaljo:oai:nepjol.info:article_2434', 'ftvilniusuniv:oai:vu.lt:elaba:229697589', 'ftutrentoiris:oai:iris.unitn.it:11572_373548', 'ftvuamstcris:oai:research.vu.nl:publications_bde919a7-1da3-4a9a-a4be-43a310b77d5f']</t>
+    <t>['oai:doaj.org_article:0191cd91a97b4a0686895c5f7006ed40']</t>
+  </si>
+  <si>
+    <t>['ftjcpu:oai:https:__cuaderno.pucmm.edu.do_index.php_index_oai:article_100', 'ftjcpu:oai:https:__cuaderno.pucmm.edu.do_index.php_index_oai:article_146', 'ftjcpu:oai:https:__cuaderno.pucmm.edu.do_index.php_index_oai:article_124', 'ftjcpu:oai:https:__cuaderno.pucmm.edu.do_index.php_index_oai:article_71', 'ftjcpu:oai:https:__cuaderno.pucmm.edu.do_index.php_index_oai:article_61', 'oai:doaj.org_article:a4135be585e2471985d61500f16c71bf', 'oai:doaj.org_article:830b9ac384d7451eb64d44e004752722', 'oai:doaj.org_article:dec29c416d5d4b4d910d46135922c640', 'oai:doaj.org_article:3d4154b526674a409d52cfecebece7dd', 'oai:doaj.org_article:4ef566e798d140cca229bd7292958c30', 'ftjcpu:oai:https:__cuaderno.pucmm.edu.do_index.php_index_oai:article_177']</t>
+  </si>
+  <si>
+    <t>['oai:doaj.org_article:e34ac171cdc74bf3b017970146374f53', 'oai:doaj.org_article:de16933c60d14675a2d94df4cebfedb9', 'oai:doaj.org_article:0a26f6763a584825b733bd205e1c92a4', 'oai:doaj.org_article:befb7058620c4edf953dfff2aac8549f', 'oai:doaj.org_article:383af1c363144fecb3bb54ea80fb4bae', 'oai:doaj.org_article:19c0deab49fb49bc87165c73efd5411c', 'oai:doaj.org_article:9514e6a98b2046988f09d4ff5aec7117', 'oai:doaj.org_article:374f9d642500453d8af28351bded1b71', 'oai:doaj.org_article:db81c127d50c4247be57b8d71db89375', 'oai:doaj.org_article:fcd1431029144ced80fe2ae6c6d7617f', 'oai:doaj.org_article:705be56885834bdbab9336b4a871c4bb', 'oai:doaj.org_article:f35c13141b974d94976cec6ee03fcc6c', 'oai:doaj.org_article:bb41b816838a4aeba5125ecc97501b05', 'oai:doaj.org_article:51ecbf73a3114c4faa36d632b7ad2c83', 'oai:doaj.org_article:a5466205319f4407957a8d56c6d69e81', 'oai:doaj.org_article:8ab6b327c5d847ab8797aee5adf88105', 'oai:doaj.org_article:280e4fd10d2c4730b93b51f7bbbeaf5e', 'oai:doaj.org_article:433ec20a2121424ba210a9ca4e5d9fdb', 'oai:doaj.org_article:4621b68dcdab4cd68aeac7f31a40cf36', 'oai:doaj.org_article:73f67127439a4b9b88fe15ee151b403b', 'oai:doaj.org_article:4c33a9e5676c463fb935c994ff5b9c40', 'oai:doaj.org_article:b796c3d5a05c4b4f8f1322cbf4db5d0b', 'oai:doaj.org_article:12f587b2c4cb49e4af3965e9fec6d4b2', 'oai:doaj.org_article:59057bf10c5948b888a36dbe0d765bb8', 'oai:doaj.org_article:ff1c3a513e754709919cac73e3cb8ca3', 'oai:doaj.org_article:caa39227f06a4d4fab4b8817bc97f533', 'oai:doaj.org_article:0a56169ae3544d519aa80543f5cd9223', 'oai:doaj.org_article:de5220e3306f446c8d474431631eb8af', 'oai:doaj.org_article:8823d97aa1874e20991a1c7ade4de3dc', 'oai:doaj.org_article:b2ac799c785f4a52b01f4c10d7f769a2', 'oai:doaj.org_article:579c37e0d9604285810c13d18654060b', 'oai:doaj.org_article:0230526f0014444ba92cd87f6eb94f19', 'oai:doaj.org_article:e115ef77a69c4d7c98b4617a182d7cb5', 'oai:doaj.org_article:83c773342a7a4f31a37c4d96a4fc585d', 'oai:doaj.org_article:1e182742a41b46da8bcd8a16d0a539e7', 'oai:doaj.org_article:05846ff848f44d218e45e42d5553cd4a', 'oai:doaj.org_article:e855acb3a5cf4b019ed4a2a5442180dc', 'oai:doaj.org_article:1448b7c4b71b420890193c00d74ab496', 'oai:doaj.org_article:2b20ee59f7ce4c39ba1a59a9f8852615', 'oai:doaj.org_article:b4e413d6eed349c8a7d95577e283f13c', 'oai:doaj.org_article:ad0e85df7c3c402d8b54685cc5f9eefc', 'oai:doaj.org_article:271f07f363bb4b7cb3771983a54d1a4f', 'oai:doaj.org_article:bbdd888fd13c4eda8efe67cbbcd975b8', 'oai:doaj.org_article:8a3458cef9434ab4828e4c45519d5568', '10670_1.yc3wd6', '10670_1.11thzf', '10670_1.6pvua5']</t>
   </si>
   <si>
     <t>['oai:doaj.org_article:cdd658ca4462486c97cb4ec1e2ee6423', 'oai:doaj.org_article:5606034b3afc46828939e99c0bbb46a4', 'oai:doaj.org_article:27617759475a429f9b1eae239a0ff5c2', 'oai:doaj.org_article:0c565c5a52574c01a6f86b8e7b0701d6', 'oai:doaj.org_article:38a01cf412cc482392b3660673966fd2', 'oai:doaj.org_article:6b11b824a76744d2a39dda4ceea688a6', 'oai:doaj.org_article:658d28a067e5440387fd556bb90e412b', 'oai:doaj.org_article:bf2409b581aa4be89d60a08fd612dfb6', 'oai:doaj.org_article:cdb3fc6e813146e894cc32aca254a124', 'oai:doaj.org_article:e81008a3ff4b4a5594506bdbd95d5c4d', 'oai:doaj.org_article:f3a6b8bd8cff48b0a37196da7ea85049', 'oai:doaj.org_article:1d40ccefee7c4fc48d7c17b9bdcbf976', 'oai:doaj.org_article:9cfd551eb37d4c5ea4c16f23b1620bad', 'oai:doaj.org_article:e821fcd6b4c44db09c64bd71c6c860cd', 'oai:doaj.org_article:7cbea5954bdc4f57bf12c35b0bae22ec', 'oai:doaj.org_article:227b979412ec48f5a87ca2f22f264ac0', 'oai:doaj.org_article:841a785d161e45c6968fe43969b3ce1c', 'oai:doaj.org_article:7b63080630b34b1f9373684cdf41ca0e', 'oai:doaj.org_article:cb5afba7ccd242e0b39c9cde0299167f', 'oai:doaj.org_article:6fe33a3c0177440e92f53d64358cab79', 'oai:doaj.org_article:389bb336f6414aad9f02547adec47349', 'oai:doaj.org_article:cd201430a5834ff18ed388de3259f3ee', 'oai:doaj.org_article:45d68f72f63d4f73aedd765e6ab75a8c', 'oai:doaj.org_article:5ec59706f65242c6891ae90bf3ffe979', 'oai:doaj.org_article:cec5e234dc7f44fbb6c82bc1f0feff8b', 'oai:doaj.org_article:aa9689cd64ce4fe48681ed802ec99dc6', 'oai:doaj.org_article:54b9d48846bd427ebd218a675b47f732', 'oai:doaj.org_article:e4177c689c284ef98570efadbf252901', 'oai:doaj.org_article:f5bdabb55e6743e3877497ba5360ecc4', 'oai:doaj.org_article:d26df96420464cf0b422c39824899d02', 'oai:doaj.org_article:5facd0e377884ae2b06ce506b0bd08bf', 'oai:doaj.org_article:2a80a0cac6c0492fbd74d9522af9d265', 'oai:doaj.org_article:b014446d04f04acf8c6ca279577ecf97', 'oai:doaj.org_article:335e2b60fc7c42e98635b419a39f9b0f', 'oai:doaj.org_article:384c6b903867425bbf8c62325a185721', 'oai:doaj.org_article:49d491df73444b9e9bb94066875e0923', 'oai:doaj.org_article:1b805a0d92484973bfa67f3ec64bb84f', 'oai:doaj.org_article:91f9d8317f2248f5ba561a7cca3e335f', 'oai:doaj.org_article:691d7fb19cdf408aa382b18956f52491', 'oai:doaj.org_article:c6336d848a1c40299b7a46416239fa14', 'oai:doaj.org_article:8761298ab49f4a86957f9f405b6289d3', 'oai:doaj.org_article:1ec93112ebd64a38a8ddc47603dada40', 'oai:doaj.org_article:59cc891845f94a648391e011ff726359', 'oai:doaj.org_article:504725adc14a4e5685cf4d5cf1b624b2', 'oai:doaj.org_article:61b71c447a4842b0bbfb6bd82e314c75', 'oai:doaj.org_article:90c62464794942668c92e9a1695eaecb', 'oai:doaj.org_article:67bad78a07604ffea635f7747f6b4471', 'oai:doaj.org_article:46f2ba5534144f4cb56396028b53d75d', 'oai:doaj.org_article:4a84cd1834284f70a25d7b7ad81f0ccc', 'oai:doaj.org_article:5131330f50e54789b67898422537c5c9', 'oai:doaj.org_article:c64551cdd4c84800bf62ce4293c53c08', 'oai:doaj.org_article:47d489ee373f44bba218605beb4e5fed', 'oai:doaj.org_article:f0bf52b902814ec7b39d8bd056564068', 'oai:doaj.org_article:b0a8d203162b4b91a8602736c70cb3ff', 'oai:doaj.org_article:b752214df67b4dd3b2e8d5e5cf744e79', 'oai:doaj.org_article:f4d8a3f185cf474b8ef1f03e7933d95b', 'oai:doaj.org_article:f40a81d4f4264c75ad24d9c0bbc3468e']</t>
   </si>
   <si>
-    <t>['ftjcpu:oai:https:__cuaderno.pucmm.edu.do_index.php_index_oai:article_100', 'ftjcpu:oai:https:__cuaderno.pucmm.edu.do_index.php_index_oai:article_146', 'ftjcpu:oai:https:__cuaderno.pucmm.edu.do_index.php_index_oai:article_124', 'ftjcpu:oai:https:__cuaderno.pucmm.edu.do_index.php_index_oai:article_71', 'ftjcpu:oai:https:__cuaderno.pucmm.edu.do_index.php_index_oai:article_61', 'oai:doaj.org_article:a4135be585e2471985d61500f16c71bf', 'oai:doaj.org_article:830b9ac384d7451eb64d44e004752722', 'oai:doaj.org_article:dec29c416d5d4b4d910d46135922c640', 'oai:doaj.org_article:3d4154b526674a409d52cfecebece7dd', 'oai:doaj.org_article:4ef566e798d140cca229bd7292958c30', 'ftjcpu:oai:https:__cuaderno.pucmm.edu.do_index.php_index_oai:article_177']</t>
-  </si>
-  <si>
-    <t>['oai:doaj.org_article:0191cd91a97b4a0686895c5f7006ed40']</t>
-  </si>
-  <si>
-    <t>['oai:doaj.org_article:e34ac171cdc74bf3b017970146374f53', 'oai:doaj.org_article:de16933c60d14675a2d94df4cebfedb9', 'oai:doaj.org_article:0a26f6763a584825b733bd205e1c92a4', 'oai:doaj.org_article:befb7058620c4edf953dfff2aac8549f', 'oai:doaj.org_article:383af1c363144fecb3bb54ea80fb4bae', 'oai:doaj.org_article:19c0deab49fb49bc87165c73efd5411c', 'oai:doaj.org_article:9514e6a98b2046988f09d4ff5aec7117', 'oai:doaj.org_article:374f9d642500453d8af28351bded1b71', 'oai:doaj.org_article:db81c127d50c4247be57b8d71db89375', 'oai:doaj.org_article:fcd1431029144ced80fe2ae6c6d7617f', 'oai:doaj.org_article:705be56885834bdbab9336b4a871c4bb', 'oai:doaj.org_article:f35c13141b974d94976cec6ee03fcc6c', 'oai:doaj.org_article:bb41b816838a4aeba5125ecc97501b05', 'oai:doaj.org_article:51ecbf73a3114c4faa36d632b7ad2c83', 'oai:doaj.org_article:a5466205319f4407957a8d56c6d69e81', 'oai:doaj.org_article:8ab6b327c5d847ab8797aee5adf88105', 'oai:doaj.org_article:280e4fd10d2c4730b93b51f7bbbeaf5e', 'oai:doaj.org_article:433ec20a2121424ba210a9ca4e5d9fdb', 'oai:doaj.org_article:4621b68dcdab4cd68aeac7f31a40cf36', 'oai:doaj.org_article:73f67127439a4b9b88fe15ee151b403b', 'oai:doaj.org_article:4c33a9e5676c463fb935c994ff5b9c40', 'oai:doaj.org_article:b796c3d5a05c4b4f8f1322cbf4db5d0b', 'oai:doaj.org_article:12f587b2c4cb49e4af3965e9fec6d4b2', 'oai:doaj.org_article:59057bf10c5948b888a36dbe0d765bb8', 'oai:doaj.org_article:ff1c3a513e754709919cac73e3cb8ca3', 'oai:doaj.org_article:caa39227f06a4d4fab4b8817bc97f533', 'oai:doaj.org_article:0a56169ae3544d519aa80543f5cd9223', 'oai:doaj.org_article:de5220e3306f446c8d474431631eb8af', 'oai:doaj.org_article:8823d97aa1874e20991a1c7ade4de3dc', 'oai:doaj.org_article:b2ac799c785f4a52b01f4c10d7f769a2', 'oai:doaj.org_article:579c37e0d9604285810c13d18654060b', 'oai:doaj.org_article:0230526f0014444ba92cd87f6eb94f19', 'oai:doaj.org_article:e115ef77a69c4d7c98b4617a182d7cb5', 'oai:doaj.org_article:83c773342a7a4f31a37c4d96a4fc585d', 'oai:doaj.org_article:1e182742a41b46da8bcd8a16d0a539e7', 'oai:doaj.org_article:05846ff848f44d218e45e42d5553cd4a', 'oai:doaj.org_article:e855acb3a5cf4b019ed4a2a5442180dc', 'oai:doaj.org_article:1448b7c4b71b420890193c00d74ab496', 'oai:doaj.org_article:2b20ee59f7ce4c39ba1a59a9f8852615', 'oai:doaj.org_article:b4e413d6eed349c8a7d95577e283f13c', 'oai:doaj.org_article:ad0e85df7c3c402d8b54685cc5f9eefc', 'oai:doaj.org_article:271f07f363bb4b7cb3771983a54d1a4f', 'oai:doaj.org_article:bbdd888fd13c4eda8efe67cbbcd975b8', 'oai:doaj.org_article:8a3458cef9434ab4828e4c45519d5568', '10670_1.yc3wd6', '10670_1.11thzf', '10670_1.6pvua5']</t>
+    <t>['10670_1.wxohe9']</t>
+  </si>
+  <si>
+    <t>['ftuniillesbalear:enginy:Enginy_2009v01p004']</t>
+  </si>
+  <si>
+    <t>['ftjohrm:oai:ojs2.journal.ohrm.bba.md:article_99', 'ftjohrm:oai:ojs2.journal.ohrm.bba.md:article_693', 'ftjohrm:oai:ojs2.journal.ohrm.bba.md:article_80', 'ftjohrm:oai:ojs2.journal.ohrm.bba.md:article_692', 'ftjohrm:oai:ojs2.journal.ohrm.bba.md:article_131']</t>
+  </si>
+  <si>
+    <t>['ftjohrm:oai:ojs2.journal.ohrm.bba.md:article_344']</t>
+  </si>
+  <si>
+    <t>['oai:doaj.org_article:1daba098677b430a8eb98a900c21c02f']</t>
+  </si>
+  <si>
+    <t>['oai:doaj.org_article:421c4cd2d7aa46dbb59b791d017754da', 'oai:doaj.org_article:31d00ff305f74cc9b72e6aba596b4d74', 'oai:doaj.org_article:21116222458542efadf1319e00409f9b', 'oai:doaj.org_article:20319b634e1f490a85445c40fd9fe810', 'oai:doaj.org_article:cab3b47aa82a4ce0a7f16510decacf65', 'oai:doaj.org_article:a696f9de796c4fafbd070b990aba405e', 'oai:doaj.org_article:efec42e3590d4948aecec6dfdca6ffc0', 'oai:doaj.org_article:2858b96b0578458fa957328b5634b1a8', 'oai:doaj.org_article:aaae9a55995e4c48ae965563d3242ccd', 'oai:doaj.org_article:b4a61156b7e541c1beff02072d633e1d', 'oai:doaj.org_article:bd00151e1d3d4b249ff465961e91eab3', 'oai:doaj.org_article:10d07bb8cc594fc997986fbf070bfef9', 'oai:doaj.org_article:cf642840ab264945a3382059ec6ab20d', 'oai:doaj.org_article:e3f5b68281a845d596e5d741452d6b8e', 'oai:doaj.org_article:e9a8cae380ef4acb85d0d5559dd2cff9', 'oai:doaj.org_article:f884c3e66b8f4761a84102ef9f32059c', 'oai:doaj.org_article:eae176da7854401091d3449dae088c18', 'oai:doaj.org_article:3864f92a29994b57b41e5eab654e77d4', 'oai:doaj.org_article:799c19945f7f4f3c98c04c9230205bc7', 'oai:doaj.org_article:43a228d215754c859e2641d05fac9ccc', 'oai:doaj.org_article:13d23d6bf19841f5a13d793978fa7726']</t>
   </si>
   <si>
     <t>['oai:doaj.org_article:8a3458cef9434ab4828e4c45519d5568', 'oai:doaj.org_article:271f07f363bb4b7cb3771983a54d1a4f', 'oai:doaj.org_article:ad0e85df7c3c402d8b54685cc5f9eefc', 'oai:doaj.org_article:b4e413d6eed349c8a7d95577e283f13c', 'oai:doaj.org_article:83c773342a7a4f31a37c4d96a4fc585d', 'oai:doaj.org_article:1448b7c4b71b420890193c00d74ab496', 'oai:doaj.org_article:1e182742a41b46da8bcd8a16d0a539e7', 'oai:doaj.org_article:e855acb3a5cf4b019ed4a2a5442180dc', 'oai:doaj.org_article:de5220e3306f446c8d474431631eb8af', 'oai:doaj.org_article:59057bf10c5948b888a36dbe0d765bb8', 'oai:doaj.org_article:fbe044e08b2045c0b96414a3c666d7d2', 'oai:doaj.org_article:059efc09b87845daa26b74a4fe667268', 'oai:doaj.org_article:9931f39beecd42da95e4bc4ca0b58e59', 'oai:doaj.org_article:71dc932e2d81484394890c1e76871ed7', 'ftjroentgen:oai:roentgen.pt:article_105', 'ftjroentgen:oai:roentgen.pt:article_117', 'ftjroentgen:oai:roentgen.pt:article_156', 'oai:doaj.org_article:9514e6a98b2046988f09d4ff5aec7117', 'oai:doaj.org_article:383af1c363144fecb3bb54ea80fb4bae', 'oai:doaj.org_article:befb7058620c4edf953dfff2aac8549f', 'oai:doaj.org_article:0a26f6763a584825b733bd205e1c92a4', 'oai:doaj.org_article:e34ac171cdc74bf3b017970146374f53', 'oai:doaj.org_article:73f67127439a4b9b88fe15ee151b403b', 'oai:doaj.org_article:433ec20a2121424ba210a9ca4e5d9fdb', 'oai:doaj.org_article:4c33a9e5676c463fb935c994ff5b9c40', 'oai:doaj.org_article:280e4fd10d2c4730b93b51f7bbbeaf5e', 'oai:doaj.org_article:a5466205319f4407957a8d56c6d69e81', 'oai:doaj.org_article:51ecbf73a3114c4faa36d632b7ad2c83', 'oai:doaj.org_article:bb41b816838a4aeba5125ecc97501b05', 'oai:doaj.org_article:f35c13141b974d94976cec6ee03fcc6c', 'oai:doaj.org_article:4621b68dcdab4cd68aeac7f31a40cf36', 'oai:doaj.org_article:ff1c3a513e754709919cac73e3cb8ca3', 'oai:doaj.org_article:db81c127d50c4247be57b8d71db89375', 'oai:doaj.org_article:19c0deab49fb49bc87165c73efd5411c', 'oai:doaj.org_article:de16933c60d14675a2d94df4cebfedb9', 'ftjroentgen:oai:roentgen.pt:article_94', 'oai:doaj.org_article:b796c3d5a05c4b4f8f1322cbf4db5d0b', 'oai:doaj.org_article:d91dff1c30e3428eb306560372dcc3d5', 'oai:doaj.org_article:dd502b25947f4da980bad7e320669fa1', 'oai:doaj.org_article:ef6d3d253ba1492c891097e47c2adca3', 'oai:doaj.org_article:3a888f252bfa48a3802dfc66ada7e308', 'oai:doaj.org_article:bc95b62ffa7b46bfb4510dc2532aceb3', 'oai:doaj.org_article:d890a1a3cbdb43639472c47a16cf1835', 'oai:doaj.org_article:d1b20c5010464ff2b7f612dabfb05bc3', 'oai:doaj.org_article:b10ac6b437e94a4a8b1aceaaf2e4375a', 'oai:doaj.org_article:a04dce0595f148aea3e950e697a3d5e3', 'oai:doaj.org_article:de810166d5424e12b10208243c9c782f', 'oai:doaj.org_article:a621dc02fb584169a1b2f749a3d4ec14', 'oai:doaj.org_article:e0d4edff802d49e2935dfff2a074750c', 'oai:doaj.org_article:76e1533ccada4e01bf552add95cb6966', 'oai:doaj.org_article:207c1bfbd4d04c9a8e8f7ee6403fd680', 'oai:doaj.org_article:8cab8ae2d10e4ac68345fd52ca0b5980', 'oai:doaj.org_article:c45a894ab3374b1cb181b4db1a1061b4', 'oai:doaj.org_article:7a3d1e9f002c4a28af9032917a6ea020', 'oai:doaj.org_article:99db4a30a23148feb2fa2d84e56c813a', 'oai:doaj.org_article:c5508e630dbc44fa898fe9ec522f1a08', 'oai:doaj.org_article:60100a962c084924b552e7ffc4e69cc6', 'oai:doaj.org_article:e7248b00b4484bef87588826e3cf27a2', 'oai:doaj.org_article:70e00010f43c493b985a2458a20f2595', 'oai:doaj.org_article:6f1845d23c2a460fa5bfb60d7bc41487', 'oai:doaj.org_article:bdc08f20f1594a80a6a47d9a9e076b1b', 'oai:doaj.org_article:58631a0f8f6943a69696f61246da93a8', 'oai:doaj.org_article:4fc8fd9a28c74e269c75573498bd1d88', 'oai:doaj.org_article:d6d0b84a372542c0b4f2db9a392aec96', 'oai:doaj.org_article:3a6a33456ba7486e8ea505e458d777de', 'oai:doaj.org_article:b552a9adc60d4f38b959199737770c92']</t>
   </si>
   <si>
-    <t>['oai:doaj.org_article:421c4cd2d7aa46dbb59b791d017754da', 'oai:doaj.org_article:31d00ff305f74cc9b72e6aba596b4d74', 'oai:doaj.org_article:21116222458542efadf1319e00409f9b', 'oai:doaj.org_article:20319b634e1f490a85445c40fd9fe810', 'oai:doaj.org_article:cab3b47aa82a4ce0a7f16510decacf65', 'oai:doaj.org_article:a696f9de796c4fafbd070b990aba405e', 'oai:doaj.org_article:efec42e3590d4948aecec6dfdca6ffc0', 'oai:doaj.org_article:2858b96b0578458fa957328b5634b1a8', 'oai:doaj.org_article:aaae9a55995e4c48ae965563d3242ccd', 'oai:doaj.org_article:b4a61156b7e541c1beff02072d633e1d', 'oai:doaj.org_article:bd00151e1d3d4b249ff465961e91eab3', 'oai:doaj.org_article:10d07bb8cc594fc997986fbf070bfef9', 'oai:doaj.org_article:cf642840ab264945a3382059ec6ab20d', 'oai:doaj.org_article:e3f5b68281a845d596e5d741452d6b8e', 'oai:doaj.org_article:e9a8cae380ef4acb85d0d5559dd2cff9', 'oai:doaj.org_article:f884c3e66b8f4761a84102ef9f32059c', 'oai:doaj.org_article:eae176da7854401091d3449dae088c18', 'oai:doaj.org_article:3864f92a29994b57b41e5eab654e77d4', 'oai:doaj.org_article:799c19945f7f4f3c98c04c9230205bc7', 'oai:doaj.org_article:43a228d215754c859e2641d05fac9ccc', 'oai:doaj.org_article:13d23d6bf19841f5a13d793978fa7726']</t>
-  </si>
-  <si>
-    <t>['10670_1.wxohe9']</t>
-  </si>
-  <si>
-    <t>['ftuniillesbalear:enginy:Enginy_2009v01p004']</t>
-  </si>
-  <si>
-    <t>['ftjohrm:oai:ojs2.journal.ohrm.bba.md:article_344']</t>
-  </si>
-  <si>
-    <t>['ftjohrm:oai:ojs2.journal.ohrm.bba.md:article_99', 'ftjohrm:oai:ojs2.journal.ohrm.bba.md:article_693', 'ftjohrm:oai:ojs2.journal.ohrm.bba.md:article_80', 'ftjohrm:oai:ojs2.journal.ohrm.bba.md:article_692', 'ftjohrm:oai:ojs2.journal.ohrm.bba.md:article_131']</t>
-  </si>
-  <si>
-    <t>['oai:doaj.org_article:1daba098677b430a8eb98a900c21c02f']</t>
-  </si>
-  <si>
     <t>['oai:doaj.org_article:f43b114ab0a04a85be9730214b176b1d', 'oai:doaj.org_article:2982de13c42b4ef4870f22e49b1b13d9']</t>
   </si>
   <si>
+    <t>['oai:doaj.org_article:37bead80957b41a0bc6a0db04d0b9616', 'oai:doaj.org_article:4eae2e31fb3b47a89ce20b328eb163ef', 'oai:doaj.org_article:515cf90291fa44438c2f76da0547ad89', 'oai:doaj.org_article:f481db39f2484bbd9db908ccbb847690', 'oai:doaj.org_article:744c47d57727418bb4aee05a3b61aa07', 'oai:doaj.org_article:b777a2711e704df4a4fed1a5b8fda435', 'oai:doaj.org_article:4fd0d45cc8b14b1c95804d0a74ade599', 'oai:doaj.org_article:91d1719ce1d74d8fb7b953a55e98d804']</t>
+  </si>
+  <si>
+    <t>['oai:doaj.org_article:c27616f69162484497ddaf92f8f35b6f']</t>
+  </si>
+  <si>
     <t>['oai:doaj.org_article:24a9ad5e32c143278e11186fee515993', 'oai:doaj.org_article:f617055f50234301b515b727fa72161e', 'oai:doaj.org_article:5d600afebc5740719f47fa056ab7cc87', 'oai:doaj.org_article:2442da7a8cd141d084e5e6906c08d621', 'oai:doaj.org_article:19761bba44704421958ed63895d94065', 'oai:doaj.org_article:38dae9b1412c4ddca2d6f4a1933a8a68', 'oai:doaj.org_article:0b7ab60f23504085bd6933efc2cab1e2', 'oai:doaj.org_article:050406cc5cdd41d386a0b8d385b0b31c', 'oai:doaj.org_article:8ea105dc8e694f728fde11128712e8fe', 'oai:doaj.org_article:157d5b651eab4c4ba661925d3853a5e7', 'oai:doaj.org_article:eaf85d24f2cd4b98b4bd1c6ff6b3d058', 'oai:doaj.org_article:1f51f4cd1cf14cb78e27d3517c13f3fd', 'oai:doaj.org_article:77477682930141ae89636428158b9b0a', 'oai:doaj.org_article:817deb9dbd54451d9ff109f27165f2d0', 'oai:doaj.org_article:95e4b25cb4e5413ba2d355cd1b44f9a4', 'oai:doaj.org_article:09dbbe43f81b4bf48493dfc512440b65', 'oai:doaj.org_article:e2e22c0255f3404fa280e1743af7d1c4', 'oai:doaj.org_article:85d6357c1f0545d3be9abd4fbee2a717', 'oai:doaj.org_article:4ceb5e654be34c4c90caa132be232cbd', 'oai:doaj.org_article:f5621813d05d4336a1402ee209507006', 'oai:doaj.org_article:d1d05391e13d4dfb90f6fa76285bc427', 'oai:doaj.org_article:a1efa67ae1aa426092baa29bf66733bf', 'oai:doaj.org_article:120d41b0a12045f89c92e95db9ea7d66']</t>
   </si>
   <si>
-    <t>['oai:doaj.org_article:37bead80957b41a0bc6a0db04d0b9616', 'oai:doaj.org_article:4eae2e31fb3b47a89ce20b328eb163ef', 'oai:doaj.org_article:515cf90291fa44438c2f76da0547ad89', 'oai:doaj.org_article:f481db39f2484bbd9db908ccbb847690', 'oai:doaj.org_article:744c47d57727418bb4aee05a3b61aa07', 'oai:doaj.org_article:b777a2711e704df4a4fed1a5b8fda435', 'oai:doaj.org_article:4fd0d45cc8b14b1c95804d0a74ade599', 'oai:doaj.org_article:91d1719ce1d74d8fb7b953a55e98d804']</t>
-  </si>
-  <si>
-    <t>['oai:doaj.org_article:c27616f69162484497ddaf92f8f35b6f']</t>
-  </si>
-  <si>
     <t>['10670_1.nez6tt']</t>
   </si>
   <si>
+    <t>['ftdnbreiheo:1097589641']</t>
+  </si>
+  <si>
+    <t>['oai:doaj.org_article:4dc6058543154732858ab4b3eba6af57', 'oai:doaj.org_article:18575623b883449f9d2b0ffea80791a0', 'oai:doaj.org_article:6ce83a7701754b6aae35828fdc0f71fb', 'oai:doaj.org_article:b3e02da5c3a9449697b1bea7a3799ca1', 'oai:doaj.org_article:ba65108177404c94ae2e3a2d0c8721c3']</t>
+  </si>
+  <si>
+    <t>['oai:doaj.org_article:0d9ff90e90c447d3a6f4a787ddb7cb05']</t>
+  </si>
+  <si>
+    <t>['http:__hdl.handle.net_2078.1_119262']</t>
+  </si>
+  <si>
+    <t>['50|openedition_::d834fb5dbaecc0e47b25a0bf0833429c']</t>
+  </si>
+  <si>
+    <t>['10670_1.in385q']</t>
+  </si>
+  <si>
     <t>['oai:doaj.org_article:394fb79dcfc447379c078479dae8b244', 'oai:doaj.org_article:d737dd500a1d49fda708e701a86c62e3', 'oai:doaj.org_article:2542d22601e1484784a941c63506ff78', 'oai:doaj.org_article:41b56d6878de448299e358c745074bb4', 'oai:doaj.org_article:33a20393bd7149b3954a85c0e0c5b5f8', 'oai:doaj.org_article:351e604153a044f5bfa756bb37272e42', 'oai:doaj.org_article:1eb425511e2848748f24ec6626f9b999', 'oai:doaj.org_article:77d669b324c347db88e0f48a7615f20e', 'oai:doaj.org_article:827fcb23b10a4812a8683ea6fb9f0b69', 'oai:doaj.org_article:241475824c454134b93966662bb8f237', 'oai:doaj.org_article:ca8a83f2d3af46108ea2049396b26f74', 'oai:doaj.org_article:8e44053be7c642dda82d8b2662bd1555', 'oai:doaj.org_article:424b81e12ccd4846b4abb3d8c7a948e4', 'oai:doaj.org_article:5a9319c81aba47a8a08319e908eae005', 'oai:doaj.org_article:c494d851381d4743b5eb802f32336352', 'oai:doaj.org_article:57d0a55663be45d19ceccc6f87288f48', 'oai:doaj.org_article:5bd52a8cd7b842f6b35cd1e8de9b8160', 'oai:doaj.org_article:99a5159250a14881a124ef4ba8a23aa6', 'oai:doaj.org_article:2fe7d6ea959b4db5867e180ddb5462c7', 'ftunivesantacat:oai:ojs.revistas.udesc.br:article_20854', 'ftunivesantacat:oai:ojs.revistas.udesc.br:article_20841', 'oai:doaj.org_article:b34a922295fd473f9a8eccbe2d948c9c', 'oai:doaj.org_article:50b6a29ec7b44efb8996bf629dd33c30', 'oai:doaj.org_article:d0ddcf06ecc944edb93289b1857c1bc4', 'oai:doaj.org_article:194a4a9e481943e09ca1d5055e28455a', 'oai:doaj.org_article:10c8f483294948a6947c0b984c202b6a']</t>
   </si>
   <si>
-    <t>['oai:doaj.org_article:4dc6058543154732858ab4b3eba6af57', 'oai:doaj.org_article:18575623b883449f9d2b0ffea80791a0', 'oai:doaj.org_article:6ce83a7701754b6aae35828fdc0f71fb', 'oai:doaj.org_article:b3e02da5c3a9449697b1bea7a3799ca1', 'oai:doaj.org_article:ba65108177404c94ae2e3a2d0c8721c3']</t>
-  </si>
-  <si>
-    <t>['oai:doaj.org_article:8369fdd2df1d45149f1d9c8d7a017968', 'oai:doaj.org_article:6df2a7a8b1c94a4c9223c3c9f9823033', 'ftkingscollondon:oai:pure.atira.dk:publications_4582a4de-6744-4d1d-9021-28cffba5a4fa', 'ftunivgeneve:oai:unige.ch:unige:155232', 'ftinserm:oai:HAL:hal-03691657v1', 'ftoslouniv:oai:www.duo.uio.no:10852_93886', 'ftpubmed:oai:pubmedcentral.nih.gov:9010705', 'ftriip:oai:HAL:hal-03691657v1', 'ftpubmed:oai:pubmedcentral.nih.gov:9432753', 'ftpubmed:oai:pubmedcentral.nih.gov:4073248', 'ftworldbank:oai:openknowledge.worldbank.org:10986_34814', 'ftworldbank:oai:openknowledge.worldbank.org:10986_34926', 'oai:journals.um.si:article_97', 'oai:doaj.org_article:07c100a6ce324817b377171803c4855c', 'oai:doaj.org_article:5e6e2148c23c49a895791f48e61e0f85', 'ftunivliverpool:oai:livrepository.liverpool.ac.uk:3025011', 'ftpubmed:oai:pubmedcentral.nih.gov:9367745', 'ftdoajarticles:oai:doaj.org_article:95551ebe180740758115cd881e9ac8b7', 'ftdoajarticles:oai:doaj.org_article:c140614342044ce4bbde4a30eaac9bf0', 'ftleedsuniv:oai:eprints.whiterose.ac.uk:104170', 'ftunivessex:oai:repository.essex.ac.uk:33461', 'ftpubmed:oai:pubmedcentral.nih.gov:4593291', 'ftunivliverpool:oai:livrepository.liverpool.ac.uk:3154321', 'ftleedsuniv:oai:eprints.whiterose.ac.uk:185808', 'ftcovenantuniv:oai:generic.eprints.org:5719', 'ftdoajarticles:oai:doaj.org_article:3a88852d88af4eb6aa73cbcffaf685f1', 'ftdoajarticles:oai:doaj.org_article:fc6357040ca64fc984ecc96e77c19246', 'ftunivleuven:oai:lirias.kuleuven.be:123456789_186665', 'ftceon:oai:depot.ceon.pl:123456789_956', 'ftphilpapers:oai:philpapers.org_rec_BROPEI-3', 'fthrcak:oai:hrcak.srce.hr:23346', 'fthrcak:oai:hrcak.srce.hr:183381', 'ftpubmed:oai:pubmedcentral.nih.gov:9475410', 'ftpubmed:oai:pubmedcentral.nih.gov:6720555', 'ftpubmed:oai:pubmedcentral.nih.gov:6889688', 'ftdoajarticles:oai:doaj.org_article:e16060828b60400c8603cd37cc9c8bca', 'ftdoajarticles:oai:doaj.org_article:36a225556c5a49b59def089a10a3279d', 'ftpubmed:oai:pubmedcentral.nih.gov:3933755', 'ftliverpoolstm:oai:archive.lstmed.ac.uk:7509', 'ftumanchesterpub:oai:pure.atira.dk:publications_33ff92cc-eed4-48f0-994c-1d0acd19f1b1', 'ftihswien:oai::5894', 'fthrcak:oai:hrcak.srce.hr:305985', 'ftdoajarticles:oai:doaj.org_article:26792694c774410fa08312683c886acb', 'ftpubmed:oai:pubmedcentral.nih.gov:7249676', 'ftfrontimediafig:oai:figshare.com:article_24277543', 'ftkingscollondon:oai:pure.atira.dk:publications_61e4ab0e-4f28-4d5d-8892-ff443575e192', 'ftpubmed:oai:pubmedcentral.nih.gov:7791849', 'ftunivmilanobic:oai:boa.unimib.it:10281_17214', 'ftunivgeneve:oai:unige.ch:aou:unige:155232', 'ftlinnaeusuniv:oai:DiVA.org:lnu-40549', 'ftuniaarhuspubl:oai:pure.atira.dk:publications_c056e602-53da-4e83-b6c2-e824ed1fad77', 'ftkingscollondon:oai:pure.atira.dk:publications_33739829-bd87-4d41-aefa-a2682b49261f', 'ftunivbrescia:oai:iris.unibs.it:11379_539015', 'ftunivmoliseiris:oai:iris.unimol.it:11695_477', 'ftunivsplit:oai:repozitorij.svkst.unist.hr:forenzikast_383', 'ftsydanskunivpub:oai:sdu.dk:publications_5fe40505-6d15-48d8-a337-8a4b619715a9', 'ftuabarcelonapb:oai:ddd.uab.cat:289634', 'ftupompeufabra:oai:repositori.upf.edu:10230_49193', 'fthrcak:oai:hrcak.srce.hr:246902', 'ftkingscollondon:oai:pure.atira.dk:publications_7639c966-fbe8-40b8-a325-b2e0ef05c1eb', 'ftcopenhagenunip:oai:pure.atira.dk:publications_ad997fd8-6115-47bf-aeba-71be699f3876', 'ftdnbreiheo:1250067170', 'ftunivgenova:oai:iris.unige.it:11567_503755', 'ftunivrijeka:oai:www.unirepository.svkri.uniri.hr:fthm_2708', 'ftunivrijeka:oai:www.unirepository.svkri.uniri.hr:fthm_3186', 'ftuwarwick:oai:wrap.warwick.ac.uk:146855', 'ftunivzuerich:oai:www.zora.uzh.ch:124548', 'ftiesbelgrad:oai:ebooks.ien.bg.ac.rs:115', 'ftdoajarticles:oai:doaj.org_article:9ca531890bfb427aa611cda3a2e33f51', 'ftpubmed:oai:pubmedcentral.nih.gov:7721354', 'ftvuamstcris:oai:research.vu.nl:publications_b8285cbe-722e-4f6f-b330-ec080e36b8f0', 'ftlondoneconom:oai:eprints.lse.ac.uk:116626', 'ftvuamsterumc:oai:pure.atira.dk:publications_05a186a1-525e-4360-85df-e8d088513ba5', 'ftvuamsterumc:oai:pure.atira.dk:publications_68587b22-f052-4021-ba9c-bafee1b35498', 'ftworldbank:oai:openknowledge.worldbank.org:10986_30579', 'ftglasgowcucris:oai:researchonline.gcu.ac.uk:publications_920c5054-23ff-4a67-ba8d-058a6a413fc5', 'ftnulzagrebzir:oai:zir.nsk.hr:fthm_2708', 'ftnulzagrebzir:oai:zir.nsk.hr:fthm_3186', 'ftnulzagrebzir:oai:zir.nsk.hr:foi_442', 'ftdoajarticles:oai:doaj.org_article:5bf847ecd95046399d35d251c2e96ab7', 'ftdoajarticles:oai:doaj.org_article:e7ac765c353c4cb28b645bafecf3f137', 'oai:doaj.org_article:9ca531890bfb427aa611cda3a2e33f51', 'oai:doaj.org_article:78d8cf2c62c6480eafa3c6b132418c86', 'oai:doaj.org_article:26792694c774410fa08312683c886acb', 'ftlitinstagrecon:oai:elaba:11675971', 'ftpubmed:oai:pubmedcentral.nih.gov:8356263', 'ftpubmed:oai:pubmedcentral.nih.gov:7798200', 'ftpubmed:oai:pubmedcentral.nih.gov:6418058', 'ftzenodo:oai:zenodo.org:7533130', 'ftzenodo:oai:zenodo.org:6683292', 'fthrcak:oai:hrcak.srce.hr:244498', 'ftunivhongkonghu:oai:hub.hku.hk:10722_87806', 'ftdoajarticles:oai:doaj.org_article:25d15b75e8874c7fa5f32662e476caf9', 'ftdoajarticles:oai:doaj.org_article:453b9faf9aa74ebbb23fe2c796485514', 'ftdoajarticles:oai:doaj.org_article:459f202aac0342c2ae503e16f12bce90', 'ftpubmed:oai:pubmedcentral.nih.gov:7231414', 'ftunivfreiburg:oai:freidok.uni-freiburg.de:154085', 'ftpubmed:oai:pubmedcentral.nih.gov:6925899', 'ftunivmaribor:oai:dk.um.si:IzpisGradiva.php?id=67004', 'ftiesbelgrad:oai:ebooks.ien.bg.ac.rs:356', 'ftpubmed:oai:pubmedcentral.nih.gov:6451281', 'ftmdpi:oai:mdpi.com:_1660-4601_19_15_9515_', 'ftuniveastangl:oai:ueaeprints.uea.ac.uk:61475', 'ftnulzagrebzir:oai:zir.nsk.hr:pravo_2876', 'ftiesbelgrad:oai:ebooks.ien.bg.ac.rs:238', 'oai:hrcak.srce.hr:23346', 'oai:hrcak.srce.hr:23005', 'ftjnepaljo:oai:ojs.pkp.sfu.ca:article_2434', 'ftubristolcris:oai:research-information.bris.ac.uk:publications_651775d8-7ee6-436c-ad29-0dab5252df3c', 'ftuniaarhuspubl:oai:pure.atira.dk:publications_6c0494b3-d369-4c19-9bbc-54834abd6d95', 'oai:doaj.org_article:b9dd420ea5f14cf9b67fed9754b57048', 'ftvuamsterumc:oai:pure.atira.dk:publications_eedd93f1-76f9-4d7b-a572-446dacbdc9ed', 'oai:doaj.org_article:453b9faf9aa74ebbb23fe2c796485514', 'ftunivbrescia:oai:iris.unibs.it:11379_503691', 'ftpubmed:oai:pubmedcentral.nih.gov:10293907', 'oai:revues.org:revus_1060', 'ftdoajarticles:oai:doaj.org_article:f2aa7a59ae6241d380fa088455f596e6', 'ftdoajarticles:oai:doaj.org_article:728ec30c13804eac99a0d4999d26f8d6', 'ftdoajarticles:oai:doaj.org_article:43ad06da6431404eb2bbbcbce5774ec5', 'ftdoajarticles:oai:doaj.org_article:05b7aadba8d34aa48204516ded9e20dd', 'ftdoajarticles:oai:doaj.org_article:c519986b58ab4a11be171975d5415cab', 'ftccsdartic:oai:HAL:hal-03691657v1', 'oai:hrcak.srce.hr:19672', 'ftdoajarticles:oai:doaj.org_article:6bf5928a8b2942259fad89ac075e0649', 'ftdoajarticles:oai:doaj.org_article:ca1e7faddd3a4029aeb7c14f8b22aa66', 'ftdoajarticles:oai:doaj.org_article:d4ad8cc55f254374a8b772b18e5943f8', 'ftdoajarticles:oai:doaj.org_article:ff3b08fc39144a38a14621323673e9e6', 'fthighwire:oai:open-archive.highwire.org:jech:78_1_61', 'ftdoajarticles:oai:doaj.org_article:31eab59e7f4d4a6baffa663cc5685c0d', 'ftdoajarticles:oai:doaj.org_article:8369fdd2df1d45149f1d9c8d7a017968', 'ftdoajarticles:oai:doaj.org_article:6df2a7a8b1c94a4c9223c3c9f9823033', 'ftdoajarticles:oai:doaj.org_article:4eb73630c4a84f2391e45f3248532bc7', 'ftdoajarticles:oai:doaj.org_article:7c4919f5c98f49b3abe2837fb4898ce2', 'ftpensoft:10.3897_ese.2022.e95247', 'ftunivzagrebmsr:oai:medlib.mef.hr:553', 'ftbiomed:oai:biomedcentral.com:s12909-014-0277-y', 'oai:hrcak.srce.hr:20480', 'oai:doaj.org_article:93fa8cb5d99f42d980be69cdbadfc07d', 'oai:doaj.org_article:4eb73630c4a84f2391e45f3248532bc7', 'ftdoajarticles:oai:doaj.org_article:7a692845a9424463a76043636a5aa1db', 'ftangliruskinfig:oai:figshare.com:article_30071859', 'ftangliruskinfig:oai:figshare.com:article_30071856', 'ftdoajarticles:oai:doaj.org_article:441242d7bf9542bea056868961cac762', 'ftdoajarticles:oai:doaj.org_article:4a56d18e88ee46ea91428146037e4692', 'ftdoajarticles:oai:doaj.org_article:24367a74268147acac4e47cea97ae70e', 'ftdoajarticles:oai:doaj.org_article:6a605dfe9461456abfa2f9e2f4500fae', 'ftbiomed:oai:biomedcentral.com:s12916-015-0476-3', '10.4000_revus.1060', '10.3406_chime.1993.1893', '10.4000_revus.93', 'oai:HAL:hal-05300284v1', 'oai:HAL:hal-05044988v1', 'ftnulzagrebzir:oai:zir.nsk.hr:fdmz_917', 'ftmdpi:oai:mdpi.com:_2227-9032_14_6_735_', 'ftunivosijek:oai:repozitorij.unios.hr:fdmz_917', 'ftunivalencia:oai:roderic.uv.es:10550_119462', 'ftunivmalmoe:oai:DiVA.org:mau-67033', 'ftuppsalauniv:oai:DiVA.org:uu-536601', 'fthrcak:oai:hrcak.srce.hr:329259', 'ftdoajarticles:oai:doaj.org_article:dfd362bb54704a6f91d6af61453f0325', 'ftagderuniv:oai:uia.brage.unit.no:11250_2989662', 'ftdoajarticles:oai:doaj.org_article:ea0865f07546424db8fa54139c05909e', 'ftdnbreiheo:123161756X', 'ftdnbreiheo:1245268635', 'fthrcak:oai:hrcak.srce.hr:20480', 'ftdoajarticles:oai:doaj.org_article:93fa8cb5d99f42d980be69cdbadfc07d', 'ftdoajarticles:oai:doaj.org_article:b9dd420ea5f14cf9b67fed9754b57048', 'ftcsic:oai:digital.csic.es:10261_403762', 'ftdnbreiheo:1208012568', 'ftdnbreiheo:1276937911', 'ftdoajarticles:oai:doaj.org_article:c30c559c93994b4e8f722fc1fd867678', 'fthrcak:oai:hrcak.srce.hr:38309', 'fthrcak:oai:hrcak.srce.hr:47886', 'ftid14132:oai:lirias2repo.kuleuven.be:123456789_676637', 'ftihswien:oai:irihs.ihs.ac.at:5894', 'ftbritmuseumfig:oai:figshare.com:article_30071856', 'ftbritmuseumfig:oai:figshare.com:article_30071859', 'ftcardiffmetufig:oai:figshare.com:article_30071856', 'ftcardiffmetufig:oai:figshare.com:article_30071859', 'ftfrontimediafig:oai:figshare.com:article_22597705', 'fthrcak:oai:hrcak.srce.hr:315400', 'ftid14132:oai:lirias2repo.kuleuven.be:20.500.12942_717523', 'ftinraparis:oai:HAL:hal-05300284v1', 'ftlincolnunivfig:oai:figshare.com:article_30071856', 'ftlincolnunivfig:oai:figshare.com:article_30071859', 'ftopenunivfig:oai:figshare.com:article_30071856', 'ftopenunivfig:oai:figshare.com:article_30071859', 'ftoskarbordeaux:oai:oskar-bordeaux.fr:20.500.12278_207735', 'ftarxivpreprints:oai:arXiv.org:2302.06655', 'ftcdlib:oai:escholarship.org:ark:_13030_qt4nm2w7b9', 'ftgeorgetownuniv:oai:repository.library.georgetown.edu:10822_962729', 'ftid14148:oai:pubfactory.com:_journals_11192_86_1_article-p227.xml', 'ftuniaucklandfig:oai:figshare.com:article_30071856', 'ftuniaucklandfig:oai:figshare.com:article_30071859', 'ftunivbathspafig:oai:figshare.com:article_30071859', 'ftunivbathspafig:oai:figshare.com:article_30071856', 'ftunivlimericfig:oai:figshare.com:article_30071859', 'ftunivlimericfig:oai:figshare.com:article_30071856', 'ftvivofig:oai:figshare.com:article_30071859', 'ftvivofig:oai:figshare.com:article_30071856', 'ftdoajarticles:oai:doaj.org_article:0e6360e78a3c48d99c0f901a05dca04a', 'ftdoajarticles:oai:doaj.org_article:15c474ee5a014402b080e2600d99ad2e', 'ftfolkehelseins:oai:fhi.brage.unit.no:11250_2420564', 'ftdoajarticles:oai:doaj.org_article:fc52b043a9fb4174b1bc067b9c95e03e', 'ftdoajarticles:oai:doaj.org_article:d45ad091a574447a83998c4d833e38d7', 'ftlenus:oai:www.lenus.ie:10147_644011', 'ftlondoneconom:oai:researchonline.lse.ac.uk:118814', 'ftndcdu:oai:generic.eprints.org:14234', 'ftumanchesterpub:oai:pure.atira.dk:publications_6eec9730-fcf8-4386-b79d-f11d81465fd8', 'ftuniaarhuspubl:oai:pure.atira.dk:publications_bc864434-71fe-4fa4-b741-3630311ae919', 'ftuniaarhuspubl:oai:pure.atira.dk:openaire_5b1ed7a4-0ef9-41a4-a725-894d42ff50ac', 'ftuniaarhuspubl:oai:pure.atira.dk:openaire_bc864434-71fe-4fa4-b741-3630311ae919', 'ftuniaarhuspubl:oai:pure.atira.dk:publications_5b1ed7a4-0ef9-41a4-a725-894d42ff50ac', 'ftunivleiden:oai:scholarlypublications.universiteitleiden.nl:item_3206719', 'ftunivmilanoair:oai:air.unimi.it:2434_808163', 'ftunivmilanoair:oai:air.unimi.it:2434_727506', 'ftunivnewcastnsw:uon:49041', 'ftunivsplit:oai:repozitorij.svkst.unist.hr:mefst_2942', 'ftunivsplit:oai:repozitorij.svkst.unist.hr:mefst_2947', 'ftunivstirling:oai:dspace.stir.ac.uk:1893_12985', 'ftunnottinghamrr:oai:nottingham-repository.worktribe.com:46170155', 'ftdublininstt:oai:arrow.tudublin.ie:scschcomart-1109', 'ftgriffithuniv:oai:research-repository.griffith.edu.au:10072_33555', 'ftkingscollondon:oai:kclpure.kcl.ac.uk:publications_4582a4de-6744-4d1d-9021-28cffba5a4fa', 'ftkingscollondon:oai:kclpure.kcl.ac.uk:publications_7639c966-fbe8-40b8-a325-b2e0ef05c1eb', 'ftmdpi:oai:mdpi.com:_2227-9032_13_16_1959_', 'ftuniljubljanaff:oai:ojs.revije.ff.uni-lj.si:article_20994', 'ftchalmersuniv:oai:research.chalmers.se:547318', 'fthrcak:oai:hrcak.srce.hr:325041', 'ftunibolognairis:oai:cris.unibo.it:11585_1051901', 'ftid14132:oai:lirias2repo.kuleuven.be:123456789_186665', 'ftgriffithuniv:oai:research-repository.griffith.edu.au:10072_26145', 'ftkentuniv:oai:kar.kent.ac.uk:24630', 'ftkingscollondon:oai:kclpure.kcl.ac.uk:publications_33739829-bd87-4d41-aefa-a2682b49261f', 'ftuniaarhuspubl:oai:pure.atira.dk:publications_f0f71c90-f833-11dd-8f9a-000ea68e967b', 'ftid14132:oai:lirias2repo.kuleuven.be:20.500.12942_722639', 'fthrcak:oai:hrcak.srce.hr:41340', 'fthrcak:oai:hrcak.srce.hr:59287', 'ftjnepaljo:oai:nepjol.info:article_2434', 'ftvilniusuniv:oai:vu.lt:elaba:229697589', 'ftutrentoiris:oai:iris.unitn.it:11572_373548', 'ftvuamstcris:oai:research.vu.nl:publications_bde919a7-1da3-4a9a-a4be-43a310b77d5f', 'ftvuamsterumc:oai:pure.atira.dk:publications_1866bb23-9ec2-47a0-a0b3-714b6ec6fed0', 'fthrcak:oai:hrcak.srce.hr:22798', 'fthrcak:oai:hrcak.srce.hr:125365']</t>
-  </si>
-  <si>
-    <t>['ftdnbreiheo:1097589641']</t>
-  </si>
-  <si>
-    <t>['oai:doaj.org_article:0d9ff90e90c447d3a6f4a787ddb7cb05']</t>
-  </si>
-  <si>
-    <t>['http:__hdl.handle.net_2078.1_119262']</t>
-  </si>
-  <si>
-    <t>['50|openedition_::d834fb5dbaecc0e47b25a0bf0833429c']</t>
-  </si>
-  <si>
-    <t>['10670_1.in385q']</t>
-  </si>
-  <si>
     <t>['ftgeorgetownuniv:oai:repository.library.georgetown.edu:10822_558209']</t>
   </si>
   <si>
@@ -2221,21 +2221,21 @@
     <t>['oai:doaj.org_article:04e5388efbfa45a784ca2cb797f98918']</t>
   </si>
   <si>
+    <t>['10670_1.peq140']</t>
+  </si>
+  <si>
+    <t>['ftunivdenverir:oai:digitalcommons.du.edu:dlr-4758']</t>
+  </si>
+  <si>
     <t>['ftunivdenverir:oai:digitalcommons.du.edu:dlr-5167']</t>
   </si>
   <si>
-    <t>['ftunivdenverir:oai:digitalcommons.du.edu:dlr-4758']</t>
-  </si>
-  <si>
-    <t>['10670_1.peq140']</t>
+    <t>['oai:doaj.org_article:cd459b75c3e1474580895227e7d86d24', 'oai:doaj.org_article:8f4f086a3a234f68bdd68884d55c54c3']</t>
   </si>
   <si>
     <t>['oai:doaj.org_article:eab97e4532f84b54b7145610b87f6f39']</t>
   </si>
   <si>
-    <t>['oai:doaj.org_article:cd459b75c3e1474580895227e7d86d24', 'oai:doaj.org_article:8f4f086a3a234f68bdd68884d55c54c3']</t>
-  </si>
-  <si>
     <t>['oai:doaj.org_article:9fcf52f3760640e38649281302836cef']</t>
   </si>
   <si>
@@ -2266,27 +2266,30 @@
     <t>['oai:doaj.org_article:e98f78992cf54209aa978cb3f5025261', 'oai:doaj.org_article:215e42e3f43844448fee9cee7d3222d5']</t>
   </si>
   <si>
+    <t>['oai:doaj.org_article:a0a7e7ee0a404bb6b72f9f84ce7a1ff0', 'oai:doaj.org_article:c56e2c3686d346bb996d85281a2a2e9d', 'oai:doaj.org_article:45d80404109146f59d1e7c3f2de13115', 'oai:doaj.org_article:133469bd32d0463ea61600d1d4cfdef3', 'oai:doaj.org_article:67ad3928a4bb4cebb6e901c1a5115937', 'oai:doaj.org_article:c98d09c5c48646a68a3fe8bf1077e11a', 'oai:doaj.org_article:2f45eb20df9145d0af7017afb6b33d93', 'oai:doaj.org_article:003f37acb7c147c29e8d9a1736d9d233', 'oai:doaj.org_article:4f11aba51af1494e87b49bf7bd325c37', 'oai:doaj.org_article:a4a66fa5a828461bad45a971f13b15ee', 'oai:doaj.org_article:36b9d09ecae6425b854c2e3018cbf1cc', 'oai:doaj.org_article:37c1af01820d44598e870b90174da082', 'oai:doaj.org_article:ed5cc6f6841d4cf0b850535137e79ace', 'oai:doaj.org_article:f04d34034b1a4850a316784674a1849d', 'oai:doaj.org_article:3990b25371bc44dba617c89e585b4193', 'oai:doaj.org_article:35cbc2ae76ca4e719277cce6d3ae71c1', 'ftunivbunghatta:oai:ejurnal.bunghatta.ac.id:article_14871', 'oai:doaj.org_article:638deac6af33432cade7a98325322386', 'oai:doaj.org_article:365bd45391424be38c6b89484167840e', 'oai:doaj.org_article:c8ab45ab1fce424b9ffa309b2f284a98', 'oai:doaj.org_article:ace2d55d80754233ac28cd92d9a5086c', 'ftdonboscouniojs:oai:ojs.pkp.sfu.ca:article_2998', 'ftunpalangkaraya:oai:ojs.e-journal.upr.ac.id:article_1706', 'ftdialnet:oai:dialnet.unirioja.es:ART0001218145', 'ftdoajarticles:oai:doaj.org_article:ace2d55d80754233ac28cd92d9a5086c', 'oai:doaj.org_article:1fc5205f80734394b40031c9729bb940', 'oai:doaj.org_article:6b2956bacc114e4f925933d9701ed397', 'oai:doaj.org_article:dec3090d8537473a8399ddc15d5238a9', 'oai:doaj.org_article:5caac12c0b2e4a5493b9695b64923ebd', 'oai:doaj.org_article:9f64064a62404e509c2989372ca555ff', 'oai:doaj.org_article:49e8a85742574f77a71fabc818e5c50f', 'oai:doaj.org_article:0032dc4826b84569b43ced6b69898f67', 'oai:doaj.org_article:a81dd0b7333546f08f8d81b17080afd8', 'oai:doaj.org_article:194d55e706994d549d881711badad929', 'oai:doaj.org_article:dc7aa4328a044e0986ad83e8777e0e7c', 'oai:doaj.org_article:60c00a676ae84963ab57ea908186c4a9', 'oai:doaj.org_article:c1b74ecee4d34ec7bc7ba88cdce8e903', 'oai:doaj.org_article:9b384ea115b94b2b998c46f119669829', 'oai:doaj.org_article:dc7d92a70386470aa381a265bef0d861', 'oai:doaj.org_article:a220e0d7cb24486cafbf669eb5027496', 'oai:doaj.org_article:361b751016f24b9a943c7c251aabf42d', 'oai:doaj.org_article:b2cf1d23dab54beb89938f632c6ae257', 'oai:doaj.org_article:e285a5f363684692bfe5f74a72c83c67', 'oai:doaj.org_article:52ca27beca03463085e288b442240355', 'oai:doaj.org_article:117f8b6fea9449b8875e43ffc4e255b6', 'oai:doaj.org_article:334761f2d24e40148e90684ec35aa158', 'oai:doaj.org_article:cb6f18cab8c842d6a2f8b21134f2e5d9', 'oai:doaj.org_article:283ef6292d3149d1893ed6aaa85b0b79', 'oai:doaj.org_article:d7b4e3b5aae64ee0bee53b56e4857fdd', 'oai:doaj.org_article:ab177ac327764869a739e25a54174fcd', 'oai:doaj.org_article:bc0cc83d03a9460295c1ec182a30060d', 'oai:doaj.org_article:b13041922e8b4b8f8882d786fa3cffb4', 'oai:doaj.org_article:614218708fa649059287dc44991d7ea2', 'oai:doaj.org_article:b10031cda1e24eac91d06c3ae770ec90', 'oai:doaj.org_article:93a9dd7850744d1b81d48f41ecc9efb1', 'oai:doaj.org_article:e4f8a9a9817d424a8ca17b73c457aefb', 'oai:doaj.org_article:0108d356e2b94128b69947ca7c89a57d', 'oai:doaj.org_article:7b1a406325904fdab0a6023284e8476a', 'oai:doaj.org_article:9a9eded027cd422caddc37dfea2e2fe9', 'oai:doaj.org_article:7c6ac46198c04fde91051a24d54e76a9', 'oai:doaj.org_article:5aee9bcac1ac4c56b5ad2a18be73cd86', 'oai:doaj.org_article:9c037f1f82434bd98440a9f28108bf56', 'oai:doaj.org_article:338c834230364162ab43d4e209cd6ce4', 'oai:doaj.org_article:9680880b05c942578ad7e2740fbb0d14', 'oai:doaj.org_article:0aa1e1545e034b99bf603d8a4911b1f1', 'oai:doaj.org_article:da498036f312453eb0aa8fe20775f7b3', 'oai:doaj.org_article:c805eac58af8439499334d48510690f8', 'oai:doaj.org_article:1ff63501fb2146c0a22d14dd129ed9d7', 'oai:doaj.org_article:d9d2916c2663483ba5355cfc3bacaaff', 'oai:doaj.org_article:9f8adf4f52e5497c8148201efb423b79', 'oai:doaj.org_article:a62b50b2114e44a0bd6818f6b7f8decc', 'oai:doaj.org_article:0e4947551aab41d597ead1c45a6ea4fc', 'oai:doaj.org_article:8f3ce3db1fa645d0951ca9ad630e50fb', 'oai:doaj.org_article:34c9e131a43f415b8e5a541b4f4f7bd6', 'oai:doaj.org_article:ac62c63256fd4f63963c3042bf765dda', 'oai:doaj.org_article:8b6422cbc31e4cb09b9259d712fa96d9', 'oai:doaj.org_article:89b436953c4040e0bebfe09c647ff548', 'oai:doaj.org_article:dfde21a9b72e4726904c5ea95f1e512c', 'oai:doaj.org_article:4d1ee7c1dcd044a1898a09526f885549', 'oai:doaj.org_article:63302284750f41dfb7d143702c748c9f', 'oai:doaj.org_article:e8e5fe854b1e424c830f64c40e25feae', 'ftunitroemsoe:oai:ojs.pkp.sfu.ca:article_203', 'ftunitroemsoe:oai:ojs.pkp.sfu.ca:article_356', 'oai:doaj.org_article:df6e0a07a7664edea1a5243fce60ca39', 'oai:doaj.org_article:1f9cb53951044ab78daa6809646952d2', 'oai:doaj.org_article:40442ab44d664f43b14e09e6e87b5259', 'oai:doaj.org_article:aeac92bec70c41c39d296e2fb2d676b5', 'oai:doaj.org_article:3d0a52df204d48499ec45765e73cfee5', 'oai:doaj.org_article:10484a02ac5e40359b99a9873215fafa', 'oai:doaj.org_article:8140b965f9904c4ca145932278831ad3', 'oai:doaj.org_article:7cd5934f28004862a0244b6e9cfece5d', 'oai:doaj.org_article:70ae0644d8dd4522a332bf1b40f320a6']</t>
+  </si>
+  <si>
     <t>['oai:doaj.org_article:536535ced38b4f00a2ccbb321364997c', 'oai:doaj.org_article:5b0c3fe299b644d7a92ff161bb8006b5', 'oai:doaj.org_article:ed913527a0424d3895fa51c1c91b68a0']</t>
   </si>
   <si>
+    <t>['oai:doaj.org_article:6811d4c2838a4621b6530e9da489fe6c']</t>
+  </si>
+  <si>
+    <t>['oai:doaj.org_article:249aae56537c48bf9cc24ed179396985']</t>
+  </si>
+  <si>
+    <t>['10670_1.rfng8i']</t>
+  </si>
+  <si>
+    <t>['10670_1.2jkgrg']</t>
+  </si>
+  <si>
+    <t>['oai:doaj.org_article:fdee90777c7d472e82b78c377c8cf575']</t>
+  </si>
+  <si>
     <t>['oai:doaj.org_article:9e61790bf7a34bbf9c20fd2dd810bb0f', 'oai:doaj.org_article:5aee96edf7a74853b1660015f8466577', 'oai:doaj.org_article:62a0862019644964bebc35c2d3e8f62f', 'oai:doaj.org_article:dac9d5b4a0224ccbbec56e026878c660', 'oai:doaj.org_article:74887ffbbd69498bb3164d41972972dd', 'oai:doaj.org_article:4d01aff4a0ee4b048baf6618e74efe7a', 'oai:doaj.org_article:d755bcd7ccc043809fe60d71c3beb4a3', 'oai:doaj.org_article:a1b7b5fc9dbe4c6db268c15b38708bad', 'oai:doaj.org_article:0d77130b104247f1b15c3a487377f52e', 'oai:doaj.org_article:ac701bfb724e4db3a6ed53017e9dedd8', 'oai:doaj.org_article:b35680667552486086ee8969b2291ddd', 'oai:doaj.org_article:d1ccaca78f6a4448b473956c6eab309e', 'oai:doaj.org_article:482499b02e56462f96df8f8e4b0fe3c5', 'oai:doaj.org_article:3eb2a8e8a06b49398229ba40807977dd', 'oai:doaj.org_article:365fc3ae2fd047d5a57c214257c3433b', 'oai:doaj.org_article:ebc368b6d1174d0c970b959f643a80e2', 'oai:doaj.org_article:abc1801c9d0f417097c27ffa7e20b81c', 'oai:doaj.org_article:bb7bcf0d21634ce49f4a511caeaabfcb', 'oai:doaj.org_article:b45fb30fab734952867f560eb710118e', 'oai:doaj.org_article:6dfe0cb599814493a53ab0ba4e6ccbf7', 'oai:doaj.org_article:218e1989e1db456984c22d0fe990185a', 'oai:doaj.org_article:6021198189474e98bc7cf40dcaf16889', 'oai:doaj.org_article:6b9269790f2f4271b86dc5a55f13b059', 'oai:doaj.org_article:d208fe666ca44804a44ef126090976c0', 'oai:doaj.org_article:4b106f775c004ca89d69e972cd65d288', 'oai:doaj.org_article:c30ab83776044d08aa9fa896283cfa53', 'oai:doaj.org_article:cf0fe489e34a495db8c4910817dfb52b', 'oai:doaj.org_article:edd7fac458844451827c122b42d97c96', 'oai:doaj.org_article:456a14e9d7574c1f82379e5c64a88fde', 'oai:doaj.org_article:569fa964ade04d3eb540271ec8a9fbf1', 'oai:doaj.org_article:0e640e2f871649149a81b5fa9506a51c', 'oai:doaj.org_article:6e27dab0d828487186cce707e85e1e8b', 'oai:doaj.org_article:9edde67f260647e78f0d9bafff8c5c41', 'oai:doaj.org_article:4ecd67a6eaba439db40725d7ea194eb1', 'oai:doaj.org_article:8abafec3771a4408b2fc1ac551fda82e', 'oai:doaj.org_article:99d4200c67444f2fbde95fb7c1683561', 'oai:doaj.org_article:2c0e8e615d924dec899f55665597575f', 'oai:doaj.org_article:105962765c9c47878702a5b22c384b94']</t>
   </si>
   <si>
-    <t>['oai:doaj.org_article:6811d4c2838a4621b6530e9da489fe6c']</t>
-  </si>
-  <si>
-    <t>['oai:doaj.org_article:249aae56537c48bf9cc24ed179396985']</t>
-  </si>
-  <si>
-    <t>['10670_1.rfng8i']</t>
-  </si>
-  <si>
-    <t>['10670_1.2jkgrg']</t>
-  </si>
-  <si>
-    <t>['oai:doaj.org_article:fdee90777c7d472e82b78c377c8cf575']</t>
-  </si>
-  <si>
     <t>['oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_138', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_146', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_162', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_171', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_179', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_187', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_495', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_198', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_207', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_221', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_228', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_20', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_27', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_31', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_38', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_61', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_395', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_68', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_75', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_413', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_428', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_431', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_433', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_84', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_436', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_437', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_438', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_247', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_264', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_270', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_279', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_286', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_292', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_316', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_323', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_330', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_336', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_342', 'oai:doaj.org_article:1792a076a0ee40fdbb73a181813ed468', 'oai:doaj.org_article:7cd0c881bd7948589b5b40ad69a3702d', 'oai:doaj.org_article:aea461eacbe84320968ac48992b34097', 'oai:doaj.org_article:c9e4e44a7db2457b93b9db8e5d12a755', 'oai:doaj.org_article:664bb71f60704f3c9cf56547e0065382', 'oai:doaj.org_article:608ad2d9787843a9bed7ec3bb11bb270', 'oai:doaj.org_article:7bd9761c35464193a2a2aec4920725fe', 'ftdoajarticles:oai:doaj.org_article:ac10dc3b948e4705ac3170cd64b3d330', 'ftdoajarticles:oai:doaj.org_article:4e599f4ff9c94502bc71f872c9d8f4f3', 'ftdoajarticles:oai:doaj.org_article:9975669891b04703a2adca2c65427527', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_154', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_216', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_386', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_408', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_424', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_426', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_427', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_429', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_434', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_435', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_111', 'oai:ojs2.ojs.westeurope.cloudapp.azure.com:article_305', 'ftjpakistanp:oai:ojs2.journal.psc.edu.pk:article_70', 'ftjpakistanp:oai:ojs2.journal.psc.edu.pk:article_89', 'ftsubhamburgojs:oai:ojs.journals.sub.uni-hamburg.de:article_2080', 'ftsubhamburgojs:oai:ojs.journals.sub.uni-hamburg.de:article_2079', 'ftdoajarticles:oai:doaj.org_article:608ad2d9787843a9bed7ec3bb11bb270', 'ftdoajarticles:oai:doaj.org_article:7bd9761c35464193a2a2aec4920725fe', 'ftunivlampungfk:oai:ojs.journal.eng.unila.ac.id:article_311', 'ftdoajarticles:oai:doaj.org_article:367af575bb8d4b42a787269cdc066e19', 'ftdoajarticles:oai:doaj.org_article:5de13c8b07b54403a026201e3ebb2fab', 'ftdoajarticles:oai:doaj.org_article:1635f11ddeb84a03aaf65a5f82fe4fcc', 'ftjpakistanp:oai:ojs2.journal.psc.edu.pk:article_27', 'ftjbnzsee:oai:bulletin.nzsee.org.nz:article_547', 'ftunizagrebsrceo:oai:ojs.pkp.sfu.ca:article_16363', 'ftyayasandpiopm:oai:ojs2.publisher.yayasandpi.or.id:article_1607', 'ftupompeufabra:oai:repositori.upf.edu:10230_53755', 'ftworldbank:oai:openknowledge.worldbank.org:10986_41447', 'oai:doaj.org_article:350afecf3fb34e5097fcf721268c416b', 'oai:doaj.org_article:ff03fd84bd36447c948733737f23dcf6', 'ftuniljubljanaff:oai:ojs.revije.ff.uni-lj.si:article_19345', 'ftdergipark2ojs:oai:dergipark.org.tr:article_285209', 'ftdergipark2ojs:oai:dergipark.org.tr:article_284465', 'ftdergipark2ojs:oai:dergipark.org.tr:article_285666', 'ftdergipark2ojs:oai:dergipark.org.tr:article_284470', 'ftdergipark2ojs:oai:dergipark.org.tr:article_326881']</t>
   </si>
   <si>
@@ -2308,33 +2311,30 @@
     <t>['oai:doaj.org_article:fe75f207c7824cecb373672ccc2eb0ac', 'oai:doaj.org_article:536b1da4406b4a77a9515b353c2679c4']</t>
   </si>
   <si>
+    <t>['oai:doaj.org_article:228e38734d1c4904b555b3064eaab75c']</t>
+  </si>
+  <si>
+    <t>['oai:doaj.org_article:9059fa29d809486d842c4e37257384b5']</t>
+  </si>
+  <si>
+    <t>['ftdoajarticles:oai:doaj.org_article:aba29d5f8d404060a949771cb149fb23', 'oai:doaj.org_article:aba29d5f8d404060a949771cb149fb23']</t>
+  </si>
+  <si>
+    <t>['oai:doaj.org_article:3034348d8b1341caadaa7ae30caba7e6', 'oai:doaj.org_article:4db2797852154ce2bc21f12d5a301340', 'oai:doaj.org_article:f2c90fff12314a24b4c70f0bcf1963ce', 'oai:doaj.org_article:2de7f0e591124e4fbea1160457bb5427', 'oai:doaj.org_article:714b54a9d9fa4ade80cf066919e0bf01', 'oai:doaj.org_article:5eaaeb78b38240779a7338058e2e2b8f']</t>
+  </si>
+  <si>
+    <t>['oai:doaj.org_article:1f6606c0e8cf45feb3a364d897d74b6f', 'oai:doaj.org_article:ace550010ead4e1180f9d762f5e2698b']</t>
+  </si>
+  <si>
+    <t>['oai:doaj.org_article:f6a795e9faee4e2697953b73701fa691', 'oai:doaj.org_article:fcb478c5561d42d292beb1c8e23ae53c']</t>
+  </si>
+  <si>
+    <t>['oai:doaj.org_article:11ad5e1fb1e741a5bc88a01254eb8167']</t>
+  </si>
+  <si>
     <t>['oai:doaj.org_article:2bcfb5054ed54f45879ba733a9131745', 'oai:doaj.org_article:c8938b5e8e19497e9c42546ac5d00afd', 'oai:doaj.org_article:9efbd3ce37424e12944607b4235b7279', 'oai:doaj.org_article:163e244bff444f04b3150f05f0380961', 'oai:doaj.org_article:6dd713ee5ae04c8a8b626aa8ee2fb0c4', 'oai:doaj.org_article:b94c6f806214460c942ac6f409a8f40c', 'oai:doaj.org_article:9085e1e82bcf492686bd958da8252fc1', 'oai:doaj.org_article:8f0969821b50405c88953ab6fe8d7f74', 'oai:doaj.org_article:e38616c2c2f746559d0900e126e02354', 'oai:doaj.org_article:adefd23fe76d4587a13469e40d439319', 'oai:doaj.org_article:7572ce653fa04fb4a114feb5ded2be9a', 'oai:doaj.org_article:628994db665e46789891f43dabca75cb', 'oai:doaj.org_article:c5196f45e32f4822a3c70eccef9cea07', 'oai:doaj.org_article:c8da047c68b94058aacabd5d5105674e', 'oai:doaj.org_article:0acb3114bee645088e4e6afc310bbddc', 'oai:doaj.org_article:c89fb6742c4441aa978e524af285f168', 'oai:doaj.org_article:7ac8e7de0a274343a1189c84a264916b', 'oai:doaj.org_article:4af431ba965a4fc49547400bd6af6dff', 'oai:doaj.org_article:f2ccfce2cc824ae2aa812cecebda4d02', 'oai:doaj.org_article:81641a39d5f74ea2ae3006e47adcedcd', 'oai:doaj.org_article:45fb4b643c374b2d90c13e83ace77d54', 'oai:doaj.org_article:e6fcde49381f4b81bc1d9104850155ca', 'oai:doaj.org_article:1d8e4bcee7e846b683aaeb185084196c', 'oai:doaj.org_article:34240a09e52344169950135547471352', 'oai:doaj.org_article:773280d7a3fc4d27b7cd03bb5df0ee34', 'oai:doaj.org_article:7f1838ce836449b5ab25ce98cc6fc883', 'oai:doaj.org_article:6597338ba5cf41c4be1cdd115c587b17', 'oai:doaj.org_article:9004966f9bc44f6797540da364ca5820', 'oai:doaj.org_article:bbe8ce9bc88a45468a5cf7c31173cd45', 'oai:doaj.org_article:9366961d1f554fb592409ea3cc8d7612', 'oai:doaj.org_article:f595adf7f4c1408997e0fe4fdb9d0a05', 'oai:doaj.org_article:9defacdc4c0749f4a3cdfed5e7c3bf68', 'oai:doaj.org_article:9408e28337e04524a4ffb29db747a2d5', 'oai:doaj.org_article:e5b906ee3b2b4b259847a023f10cd997', 'oai:doaj.org_article:a4717b47245243b4a958819db5940f62', 'oai:doaj.org_article:d38d14907606490c888971c27def9323', 'oai:doaj.org_article:8c68a48fd41b4c7b87f029a2e51e0ae4', 'oai:doaj.org_article:6bb1e50bd7de4cc3b7c793dd8a89a9ab', 'oai:doaj.org_article:1b33f4e5c0a047db97f02ff842f20c20', 'oai:doaj.org_article:5200f29f54bb4136a5110e1ccc2b4421', 'oai:doaj.org_article:3620181cbe82412cb2e1ad1988b260f0', 'oai:doaj.org_article:365f4d07b9274c1eaf5e26634aed6c38', 'oai:doaj.org_article:2c979c207a384834a8219c686ceeb5dd', 'oai:doaj.org_article:49314cce6fba42b9b9dfde6cddd63500', 'oai:doaj.org_article:922064f763d0498c869de3cdd20a7337', 'oai:doaj.org_article:7170fefa27f54a3c9cbac749c800a994', 'oai:doaj.org_article:5b41f8319d6b43f2829bcd5d06ad754f', 'oai:doaj.org_article:75acccada39347189b6de2871efc3d90', 'oai:doaj.org_article:f1644022284147e28f6cd68e0ba8b37d', 'oai:doaj.org_article:7253ff2d839940148c85493aed113e4e', 'oai:doaj.org_article:bb831a0a8c7749e5a074a7654e4584cd', 'oai:doaj.org_article:d0e83711428f4ed192536f3da915c285']</t>
   </si>
   <si>
-    <t>['oai:doaj.org_article:228e38734d1c4904b555b3064eaab75c']</t>
-  </si>
-  <si>
-    <t>['oai:doaj.org_article:9059fa29d809486d842c4e37257384b5']</t>
-  </si>
-  <si>
-    <t>['oai:doaj.org_article:a0a7e7ee0a404bb6b72f9f84ce7a1ff0', 'oai:doaj.org_article:c56e2c3686d346bb996d85281a2a2e9d', 'oai:doaj.org_article:45d80404109146f59d1e7c3f2de13115', 'oai:doaj.org_article:133469bd32d0463ea61600d1d4cfdef3', 'oai:doaj.org_article:67ad3928a4bb4cebb6e901c1a5115937', 'oai:doaj.org_article:c98d09c5c48646a68a3fe8bf1077e11a', 'oai:doaj.org_article:2f45eb20df9145d0af7017afb6b33d93', 'oai:doaj.org_article:003f37acb7c147c29e8d9a1736d9d233', 'oai:doaj.org_article:4f11aba51af1494e87b49bf7bd325c37', 'oai:doaj.org_article:a4a66fa5a828461bad45a971f13b15ee', 'oai:doaj.org_article:36b9d09ecae6425b854c2e3018cbf1cc', 'oai:doaj.org_article:37c1af01820d44598e870b90174da082', 'oai:doaj.org_article:ed5cc6f6841d4cf0b850535137e79ace', 'oai:doaj.org_article:f04d34034b1a4850a316784674a1849d', 'oai:doaj.org_article:3990b25371bc44dba617c89e585b4193', 'oai:doaj.org_article:35cbc2ae76ca4e719277cce6d3ae71c1', 'ftunivbunghatta:oai:ejurnal.bunghatta.ac.id:article_14871', 'oai:doaj.org_article:638deac6af33432cade7a98325322386', 'oai:doaj.org_article:365bd45391424be38c6b89484167840e', 'oai:doaj.org_article:c8ab45ab1fce424b9ffa309b2f284a98', 'oai:doaj.org_article:ace2d55d80754233ac28cd92d9a5086c', 'ftdonboscouniojs:oai:ojs.pkp.sfu.ca:article_2998', 'ftunpalangkaraya:oai:ojs.e-journal.upr.ac.id:article_1706', 'ftdialnet:oai:dialnet.unirioja.es:ART0001218145', 'ftdoajarticles:oai:doaj.org_article:ace2d55d80754233ac28cd92d9a5086c', 'oai:doaj.org_article:1fc5205f80734394b40031c9729bb940', 'oai:doaj.org_article:6b2956bacc114e4f925933d9701ed397', 'oai:doaj.org_article:dec3090d8537473a8399ddc15d5238a9', 'oai:doaj.org_article:5caac12c0b2e4a5493b9695b64923ebd', 'oai:doaj.org_article:9f64064a62404e509c2989372ca555ff', 'oai:doaj.org_article:49e8a85742574f77a71fabc818e5c50f', 'oai:doaj.org_article:0032dc4826b84569b43ced6b69898f67', 'oai:doaj.org_article:a81dd0b7333546f08f8d81b17080afd8', 'oai:doaj.org_article:194d55e706994d549d881711badad929', 'oai:doaj.org_article:dc7aa4328a044e0986ad83e8777e0e7c', 'oai:doaj.org_article:60c00a676ae84963ab57ea908186c4a9', 'oai:doaj.org_article:c1b74ecee4d34ec7bc7ba88cdce8e903', 'oai:doaj.org_article:9b384ea115b94b2b998c46f119669829', 'oai:doaj.org_article:dc7d92a70386470aa381a265bef0d861', 'oai:doaj.org_article:a220e0d7cb24486cafbf669eb5027496', 'oai:doaj.org_article:361b751016f24b9a943c7c251aabf42d', 'oai:doaj.org_article:b2cf1d23dab54beb89938f632c6ae257', 'oai:doaj.org_article:e285a5f363684692bfe5f74a72c83c67', 'oai:doaj.org_article:52ca27beca03463085e288b442240355', 'oai:doaj.org_article:117f8b6fea9449b8875e43ffc4e255b6', 'oai:doaj.org_article:334761f2d24e40148e90684ec35aa158', 'oai:doaj.org_article:cb6f18cab8c842d6a2f8b21134f2e5d9', 'oai:doaj.org_article:283ef6292d3149d1893ed6aaa85b0b79', 'oai:doaj.org_article:d7b4e3b5aae64ee0bee53b56e4857fdd', 'oai:doaj.org_article:ab177ac327764869a739e25a54174fcd', 'oai:doaj.org_article:bc0cc83d03a9460295c1ec182a30060d', 'oai:doaj.org_article:b13041922e8b4b8f8882d786fa3cffb4', 'oai:doaj.org_article:614218708fa649059287dc44991d7ea2', 'oai:doaj.org_article:b10031cda1e24eac91d06c3ae770ec90', 'oai:doaj.org_article:93a9dd7850744d1b81d48f41ecc9efb1', 'oai:doaj.org_article:e4f8a9a9817d424a8ca17b73c457aefb', 'oai:doaj.org_article:0108d356e2b94128b69947ca7c89a57d', 'oai:doaj.org_article:7b1a406325904fdab0a6023284e8476a', 'oai:doaj.org_article:9a9eded027cd422caddc37dfea2e2fe9', 'oai:doaj.org_article:7c6ac46198c04fde91051a24d54e76a9', 'oai:doaj.org_article:5aee9bcac1ac4c56b5ad2a18be73cd86', 'oai:doaj.org_article:9c037f1f82434bd98440a9f28108bf56', 'oai:doaj.org_article:338c834230364162ab43d4e209cd6ce4', 'oai:doaj.org_article:9680880b05c942578ad7e2740fbb0d14', 'oai:doaj.org_article:0aa1e1545e034b99bf603d8a4911b1f1', 'oai:doaj.org_article:da498036f312453eb0aa8fe20775f7b3', 'oai:doaj.org_article:c805eac58af8439499334d48510690f8', 'oai:doaj.org_article:1ff63501fb2146c0a22d14dd129ed9d7', 'oai:doaj.org_article:d9d2916c2663483ba5355cfc3bacaaff', 'oai:doaj.org_article:9f8adf4f52e5497c8148201efb423b79', 'oai:doaj.org_article:a62b50b2114e44a0bd6818f6b7f8decc', 'oai:doaj.org_article:0e4947551aab41d597ead1c45a6ea4fc', 'oai:doaj.org_article:8f3ce3db1fa645d0951ca9ad630e50fb', 'oai:doaj.org_article:34c9e131a43f415b8e5a541b4f4f7bd6', 'oai:doaj.org_article:ac62c63256fd4f63963c3042bf765dda', 'oai:doaj.org_article:8b6422cbc31e4cb09b9259d712fa96d9', 'oai:doaj.org_article:89b436953c4040e0bebfe09c647ff548', 'oai:doaj.org_article:dfde21a9b72e4726904c5ea95f1e512c', 'oai:doaj.org_article:4d1ee7c1dcd044a1898a09526f885549', 'oai:doaj.org_article:63302284750f41dfb7d143702c748c9f', 'oai:doaj.org_article:e8e5fe854b1e424c830f64c40e25feae', 'ftunitroemsoe:oai:ojs.pkp.sfu.ca:article_203', 'ftunitroemsoe:oai:ojs.pkp.sfu.ca:article_356', 'oai:doaj.org_article:df6e0a07a7664edea1a5243fce60ca39', 'oai:doaj.org_article:1f9cb53951044ab78daa6809646952d2', 'oai:doaj.org_article:40442ab44d664f43b14e09e6e87b5259', 'oai:doaj.org_article:aeac92bec70c41c39d296e2fb2d676b5', 'oai:doaj.org_article:3d0a52df204d48499ec45765e73cfee5', 'oai:doaj.org_article:10484a02ac5e40359b99a9873215fafa', 'oai:doaj.org_article:8140b965f9904c4ca145932278831ad3', 'oai:doaj.org_article:7cd5934f28004862a0244b6e9cfece5d', 'oai:doaj.org_article:70ae0644d8dd4522a332bf1b40f320a6']</t>
-  </si>
-  <si>
-    <t>['ftdoajarticles:oai:doaj.org_article:aba29d5f8d404060a949771cb149fb23', 'oai:doaj.org_article:aba29d5f8d404060a949771cb149fb23']</t>
-  </si>
-  <si>
-    <t>['oai:doaj.org_article:3034348d8b1341caadaa7ae30caba7e6', 'oai:doaj.org_article:4db2797852154ce2bc21f12d5a301340', 'oai:doaj.org_article:f2c90fff12314a24b4c70f0bcf1963ce', 'oai:doaj.org_article:2de7f0e591124e4fbea1160457bb5427', 'oai:doaj.org_article:714b54a9d9fa4ade80cf066919e0bf01', 'oai:doaj.org_article:5eaaeb78b38240779a7338058e2e2b8f']</t>
-  </si>
-  <si>
-    <t>['oai:doaj.org_article:1f6606c0e8cf45feb3a364d897d74b6f', 'oai:doaj.org_article:ace550010ead4e1180f9d762f5e2698b']</t>
-  </si>
-  <si>
-    <t>['oai:doaj.org_article:f6a795e9faee4e2697953b73701fa691', 'oai:doaj.org_article:fcb478c5561d42d292beb1c8e23ae53c']</t>
-  </si>
-  <si>
-    <t>['oai:doaj.org_article:11ad5e1fb1e741a5bc88a01254eb8167']</t>
-  </si>
-  <si>
     <t>['oai:doaj.org_article:ae3f2df7db82482d8114a61f9eb2b020']</t>
   </si>
   <si>
@@ -2392,18 +2392,18 @@
     <t>['oai:doaj.org_article:c93cf49b65c94d769fdc28a039215261', 'oai:doaj.org_article:c1e9f6e2e4ad4ba786e42ad04d94f565', 'oai:doaj.org_article:790576e440bc40bca0e8c008fd3087fe', 'oai:doaj.org_article:3ac1c2a4b78d4fa5869f2c9aecac0358', 'oai:doaj.org_article:52ec4d87888c41fc83b0cf729e5115e0', 'oai:doaj.org_article:5140a20d19d0428b8908dcd5e12e606a', 'oai:doaj.org_article:1d2433236838477984e925015fac91ce', 'oai:doaj.org_article:1c5fa13b6357404fb3c96f164dcb9778', 'oai:doaj.org_article:e3d80d0944114c909f31331182207dc3', 'oai:doaj.org_article:bda2e78d73f84ea7a03e4f25b4cf9394', 'oai:doaj.org_article:0d633a1a49624a40b2830bd3511b6375', 'oai:doaj.org_article:b80b33fd15a545f0b7bf6cd4f3aca443', 'oai:doaj.org_article:8298fdb3bd8d45f1874280875293f5aa', 'oai:doaj.org_article:1b1424affe254556957c5cd500cfbd17', 'oai:doaj.org_article:d78c75d74d564b97a36c497d3aa7111b', 'oai:doaj.org_article:3b50967284e94a2294676def016f202a', 'oai:doaj.org_article:2627ce9df68c4d2b8e2ad9e4d840d27a', 'oai:doaj.org_article:5c068989d9a649ff8cce0481ffc35f2d', 'oai:doaj.org_article:323696607b034ab1a236895d97493b83', 'oai:doaj.org_article:8b81dbc2713d48a58488e3b5bf7576d3', 'oai:doaj.org_article:fa23aa42a60a455387f1ca856e1ef0c9', 'oai:doaj.org_article:65667fb2602149529a8bc551f36e353c', 'oai:doaj.org_article:6d46c07a123f4da2aa53a0a035b5c25a', 'oai:doaj.org_article:41998f92ae0c4dbab7eaf78a74acab42', 'oai:doaj.org_article:c7b93dabeffe4e63bedcbaa8a5a773b8', 'oai:doaj.org_article:dad366c7eeb24c4f8e9119d2df78caaf', 'oai:doaj.org_article:b079e11280144ac5b61bdfbd22ef25ff', 'oai:doaj.org_article:a2a90202d3bc4f68b4ac8b4522e24553', 'oai:doaj.org_article:5d204d3222054e06b19d8fd3033e64b9', 'oai:doaj.org_article:3309df36e4b44371be57c50c6a274fbd', 'oai:doaj.org_article:f4d0dedfa2da4b1aa84517778468bbf4', 'oai:doaj.org_article:e34067a3cb934579a36d977ff44b4fc5', 'oai:doaj.org_article:8e2e4afb36e449d2b3cf7ba649e2c923', 'ftjwtt:oai:oai.mirtr.elpub.ru:article_875', 'ftjmedsovet:oai:oai.medsovet.elpub.ru:article_236', 'ftjmedsovet:oai:oai.medsovet.elpub.ru:article_350', 'ftjmedsovet:oai:oai.medsovet.elpub.ru:article_535', 'ftdoajarticles:oai:doaj.org_article:17f49173f58040adbd01aac78d7441c4', 'ftdoajarticles:oai:doaj.org_article:52466a86fa7649e09d48223c2ea77c2c', 'ftdoajarticles:oai:doaj.org_article:323696607b034ab1a236895d97493b83', 'ftdoajarticles:oai:doaj.org_article:d49481d958974738a77632993039fc3e', 'ftdoajarticles:oai:doaj.org_article:e074bb54bab244efbee3df22535daadc', 'ftdoajarticles:oai:doaj.org_article:e8584363ef824b96b9841df12d25a91d', 'ftjisjaee:oai:oai.alternative.elpub.ru:article_707', 'ftjvoprstat:oai:oai.voprstat.elpub.ru:article_279', 'ftjwtt:oai:oai.mirtr.elpub.ru:article_1379', 'ftjtransplantolo:oai:oai.transplantologiya.elpub.ru:article_176', 'oai:doaj.org_article:38dfac40c39b4f3b96351f6d5e28595a', 'oai:doaj.org_article:62a07bff94af4a52aec750fef40c9949', 'oai:doaj.org_article:2bf6765ba1b142cfa76a54c8d5f67f8f', 'oai:doaj.org_article:5016a4f88ddb43ea80dfb5e0af75bc03', 'oai:doaj.org_article:a3c28aac7a284bf0b8b84503288eb87e', 'oai:doaj.org_article:0f44669e5866403ca33944037f055bd0', 'oai:doaj.org_article:aa0df0c43e574079a4b0be3ef937a1c3', 'oai:doaj.org_article:92cc529be18a4640863dff5f5ffb7d2b', 'oai:doaj.org_article:bcc48d99f7334afc956aa851d1a4e787', 'oai:doaj.org_article:582345c474c24ad4a36ac42f777c4a37', 'oai:doaj.org_article:8ccc47fe81284bf491535027ad27705d', 'oai:doaj.org_article:2c59ea3a68c7469f909b013fafda34d8', 'oai:doaj.org_article:da03c3efadb543b4a8abe565e44d5b72', 'oai:doaj.org_article:953bdd8717a6414c899a265cd4e5a86f', 'oai:doaj.org_article:842a5cffadbc45ea81ac6a46aa2b5fbf', 'oai:doaj.org_article:fb115085aff149979c619d8b604d80fb', 'oai:doaj.org_article:96d6b99fcebb4992bcd0504c11049433', 'oai:doaj.org_article:91af241141364816957f15b55c29c243', 'oai:doaj.org_article:2bc285e0dc214bfb8fdfc7bd48a30b6c', 'oai:doaj.org_article:6462f2ee074b4bbfa697957dc371a13c', 'oai:doaj.org_article:cd267172877841d79b50e638be2fcc67', 'oai:doaj.org_article:866410d327e4466b8b062eb735ce4d19', 'oai:doaj.org_article:aff84e5ee411425ca0810e4a5a6e4e47', 'oai:doaj.org_article:e9bcb2bfc5b044aebccaced25d7aa05b', 'oai:doaj.org_article:3ffa3a69116c451f9c2b45b2ba547f81', 'oai:doaj.org_article:4e966c3ab6ed47239d7e7fbb1a420e59', 'oai:doaj.org_article:cb034e1982864e818994c06c9f8b21f8', 'oai:doaj.org_article:574b83e7b40e40dc8382a6e40ce174e7', 'oai:doaj.org_article:7dbcc7d993224fddb8fbc441224cdcc7', 'oai:doaj.org_article:abc0780e064c41988305a486f945cbc4', 'ftdoajarticles:oai:doaj.org_article:4b48f661e0e24ab0ab14f911930534a4', 'ftdoajarticles:oai:doaj.org_article:72b78510069b427186739dbc0bfa25cc', 'ftdoajarticles:oai:doaj.org_article:405ddb688cca4439b42e53026bbcd4e7', 'ftdoajarticles:oai:doaj.org_article:3fe61ff157904a38913a39fda7bc11d2', 'ftdoajarticles:oai:doaj.org_article:788e7cd6c28d4a6a82bef0fa609c3a76', 'ftdoajarticles:oai:doaj.org_article:abc0780e064c41988305a486f945cbc4', 'oai:doaj.org_article:1862c416bcc64638aa696e3fdadb847f', 'oai:doaj.org_article:c17511389c674359a453f0798e2dedeb', 'oai:doaj.org_article:a9830120745a42bf928cae90482bcc87', 'oai:doaj.org_article:c4db41f39cde4e8987cb2209235ec200', 'oai:doaj.org_article:246112f6b5424647b8d8a76d5fb7fca2', 'oai:doaj.org_article:0beaea3b21994206a88b8e7fb4665974', 'oai:doaj.org_article:f4d7403601054ba1b9e15011c611135d', 'oai:doaj.org_article:c09567a7bcc1452e8abbcad316da6030', 'oai:doaj.org_article:4bbf5e893499403496901c05a7006276', 'oai:doaj.org_article:5f25943684ef4aadb1f08641860f1a4c', 'oai:doaj.org_article:54aa082424764bf5b3868dcf607b70d3', 'oai:doaj.org_article:d2844fc4a43746729ac6eff92223476d', 'ftjteos:oai:oai.ecna.elpub.ru:article_93', 'oai:doaj.org_article:a6bc4704fc00424f91e388993569a9a8', 'oai:doaj.org_article:3a991c04a05c4f6dacba13649a410e7a', 'oai:doaj.org_article:a7e53fcd50bb49de8c98f117c262f8d4', 'oai:doaj.org_article:582d27ffa68d4c089a914487770cc230', 'oai:doaj.org_article:51aca785bedd44e1a0772f9c3a4fd661', 'oai:doaj.org_article:2aeca103eb7d49b0a5887770e0d4d647', 'oai:doaj.org_article:65765864ff7c4b958bf91b7f38b660a5', 'oai:doaj.org_article:f86296b6850944c6ad5cf2ca9a3323ca', 'oai:doaj.org_article:fdcbaf0f04fe4cefa152d0b16ea683ec', 'oai:doaj.org_article:5b36eb2322474dd4819469675608385f', 'oai:doaj.org_article:ef4e33bf96bb41aba5243eaa3beaa001', 'oai:doaj.org_article:08153d2358b9421e9966568dd645b18b', 'oai:doaj.org_article:5e22178d5a7d4f6a9164c976bc2b4dc2', 'oai:doaj.org_article:81596ada19804187bdab893c05e6eecb', 'oai:doaj.org_article:35db9915e3ab4f33ad17b0f947faa2da', 'oai:doaj.org_article:96fa4f6d4ef548ad8abe3c2c601634cc', 'oai:doaj.org_article:07e06178835248d29c99576e91f44b06', 'oai:doaj.org_article:51bef8807c7240578ae43b9982131154', 'oai:doaj.org_article:80bff23243584fe09ec9000ad1b0a619', 'oai:doaj.org_article:d54066d2f4c841d8a8b1559678c09e4f', 'oai:doaj.org_article:3078b7edd6c04b8fad64b65bbacb0464', 'oai:doaj.org_article:23bac83bc6614617bc0bb6cfe046370b', 'oai:doaj.org_article:82859d82f76e4c9e8a19edfb27c2ead3', 'oai:doaj.org_article:db56016d56b04cacab5e039f27c79aa9', 'oai:doaj.org_article:c59d537281f74d8cb445b845ac7cd0d6', 'oai:doaj.org_article:d3e07d46fc9247cc897bee7ebd47e6e0', 'oai:doaj.org_article:43abf5305d454d1ca504ce8fa6b03e4a', 'oai:doaj.org_article:ee6eb009da0d49bbaa9ee16d7444fd55', 'oai:doaj.org_article:28e5715b6d394d3d8bb0e5e11994b684', 'oai:doaj.org_article:ab556d6abb364319a7d65fde6ab31d3c', 'oai:doaj.org_article:e03d257ab7e74243992271c86013eca9', 'oai:doaj.org_article:fd478b2d25d744528766bef353bc9477', 'oai:doaj.org_article:fd09443b15c74318a2e67c980d0005f5', 'oai:doaj.org_article:1d0bd0da47174686b1c7bb56279ce159', 'oai:doaj.org_article:cdefdb5b65184482bb6b239fc863d848', 'oai:doaj.org_article:5e66ff65f3c34f3ca24d02c5fcb32d99', 'oai:doaj.org_article:af11cb8ed4914daabfca8e9fd44bf423', 'oai:doaj.org_article:126b28de61484b0c8213d4ea87265fb6', 'oai:doaj.org_article:e6d39ac657074d939bddeae2df1b7f6e', 'oai:doaj.org_article:0d4ab7ec4d7949ec9ac7f98f51940955', 'oai:doaj.org_article:006ecbff77264b3eac8375ba2b8c8b36', 'ftdoajarticles:oai:doaj.org_article:91d08286f88e4cf8a566e35dc10f67aa', 'ftdoajarticles:oai:doaj.org_article:aec4f101e8a44be498b688302f4ff3a6', 'oai:doaj.org_article:5731fa2ecd10450db91a426042a5fbcd', 'oai:doaj.org_article:3120a808532f48d5b368183424f34661', 'oai:doaj.org_article:aeefee9a0b88495c9f4c83b593c05cf1', 'oai:doaj.org_article:ebdd2f745c6e4d96b94cd1e3a4dfe8ed', 'oai:doaj.org_article:528af4cc875d4aba82eb356b9bb87a04', 'oai:doaj.org_article:90cf84e956bd42fd87572ddc425f5bac', 'oai:doaj.org_article:eb4410d0236b4b51a32b2897ec05f63c', 'ftdoajarticles:oai:doaj.org_article:01886b297b36433dad8d3f4acdcc7449', 'ftdoajarticles:oai:doaj.org_article:1da2696048ec4cd69a16a8b781504790', 'ftdoajarticles:oai:doaj.org_article:cab50e4daf784e368d8ba68e97f77cf7']</t>
   </si>
   <si>
+    <t>['ftuabarcelonapb:oai:ddd.uab.cat:60050']</t>
+  </si>
+  <si>
+    <t>['10670_1.yp7164', 'oai:doaj.org_article:ae1270f7f41c44cc9513cf06622866c4']</t>
+  </si>
+  <si>
     <t>['ftdoajarticles:oai:doaj.org_article:68c87775c4aa4e4aaea5c632c5bd1a0a', 'ftunivcanter:oai:ir.canterbury.ac.nz:10092_14521']</t>
   </si>
   <si>
-    <t>['10670_1.yp7164', 'oai:doaj.org_article:ae1270f7f41c44cc9513cf06622866c4']</t>
-  </si>
-  <si>
     <t>['10670_1.f29usx']</t>
   </si>
   <si>
-    <t>['ftuabarcelonapb:oai:ddd.uab.cat:60050']</t>
-  </si>
-  <si>
     <t>['oai:doaj.org_article:917eed3113e04a4e9c21484b22af9fef']</t>
   </si>
   <si>
@@ -2440,6 +2440,9 @@
     <t>['oai:doaj.org_article:669e2954e59f471eb5b7229bd58d1c76']</t>
   </si>
   <si>
+    <t>['ftnordiccouncil:oai:DiVA.org:norden-4286', 'ftnordiccouncil:oai:DiVA.org:norden-4474', 'ftnordiccouncil:oai:DiVA.org:norden-4485', 'ftnordiccouncil:oai:DiVA.org:norden-5243', 'ftnordiccouncil:oai:DiVA.org:norden-4471', 'ftnordiccouncil:oai:DiVA.org:norden-4472', 'ftnordiccouncil:oai:DiVA.org:norden-4473', 'ftnordiccouncil:oai:DiVA.org:norden-4481', 'ftnordiccouncil:oai:DiVA.org:norden-4480', 'ftnordiccouncil:oai:DiVA.org:norden-4475', 'ftnordiccouncil:oai:DiVA.org:norden-4479', 'ftnordiccouncil:oai:DiVA.org:norden-4571', 'ftnordiccouncil:oai:DiVA.org:norden-4487', 'ftnordiccouncil:oai:DiVA.org:norden-4483', 'ftnordiccouncil:oai:DiVA.org:norden-4488', 'ftnordiccouncil:oai:DiVA.org:norden-4482', 'ftnordiccouncil:oai:DiVA.org:norden-4486', 'ftnordiccouncil:oai:DiVA.org:norden-4587', 'ftnordiccouncil:oai:DiVA.org:norden-4981', 'ftnordiccouncil:oai:DiVA.org:norden-4701']</t>
+  </si>
+  <si>
     <t>['oai:doaj.org_article:85158e74408042d3aa85f336f44851ac', 'ftdoajarticles:oai:doaj.org_article:85158e74408042d3aa85f336f44851ac']</t>
   </si>
   <si>
@@ -2449,15 +2452,12 @@
     <t>['10670_1.gsmx8f']</t>
   </si>
   <si>
+    <t>['ftjkoers:oai:ojs.pkp.sfu.ca:article_2026']</t>
+  </si>
+  <si>
     <t>['oai:doaj.org_article:beccd5309dfe4b6ebb4fcecc3bcf5688']</t>
   </si>
   <si>
-    <t>['ftjkoers:oai:ojs.pkp.sfu.ca:article_2026']</t>
-  </si>
-  <si>
-    <t>['ftnordiccouncil:oai:DiVA.org:norden-4286', 'ftnordiccouncil:oai:DiVA.org:norden-4474', 'ftnordiccouncil:oai:DiVA.org:norden-4485', 'ftnordiccouncil:oai:DiVA.org:norden-5243', 'ftnordiccouncil:oai:DiVA.org:norden-4471', 'ftnordiccouncil:oai:DiVA.org:norden-4472', 'ftnordiccouncil:oai:DiVA.org:norden-4473', 'ftnordiccouncil:oai:DiVA.org:norden-4481', 'ftnordiccouncil:oai:DiVA.org:norden-4480', 'ftnordiccouncil:oai:DiVA.org:norden-4475', 'ftnordiccouncil:oai:DiVA.org:norden-4479', 'ftnordiccouncil:oai:DiVA.org:norden-4571', 'ftnordiccouncil:oai:DiVA.org:norden-4487', 'ftnordiccouncil:oai:DiVA.org:norden-4483', 'ftnordiccouncil:oai:DiVA.org:norden-4488', 'ftnordiccouncil:oai:DiVA.org:norden-4482', 'ftnordiccouncil:oai:DiVA.org:norden-4486', 'ftnordiccouncil:oai:DiVA.org:norden-4587', 'ftnordiccouncil:oai:DiVA.org:norden-4981', 'ftnordiccouncil:oai:DiVA.org:norden-4701']</t>
-  </si>
-  <si>
     <t>['10670_1.f25jl8']</t>
   </si>
   <si>
@@ -2482,48 +2482,48 @@
     <t>['oai:doaj.org_article:5b44974c01754ac6a5dd5941aebb16b3']</t>
   </si>
   <si>
+    <t>['10670_1.1t5f4b', 'oai:doaj.org_article:aaff31ade7214f05a5b944c5bfc272b0']</t>
+  </si>
+  <si>
+    <t>['oai:doaj.org_article:9cf31f08a33349fba73151247ec463d4', 'oai:doaj.org_article:8979cad2937b4dbc856bb55ed67d820a']</t>
+  </si>
+  <si>
+    <t>['ftjbi:oai:ojs.pkp.sfu.ca:article_13041']</t>
+  </si>
+  <si>
     <t>['oai:doaj.org_article:7eafe54570c04ae594479b29927b0fd4', 'oai:doaj.org_article:0d08cfb3acb448648dd3fcc695f94c1d', 'oai:doaj.org_article:0344cfa59ba14780a0738628ba3d97d8', 'oai:doaj.org_article:4fe2c8c962f14c6d93faa872d484ac7f', 'oai:doaj.org_article:1c047dc4be564756869d3403c97ba3c1', 'oai:doaj.org_article:edd904fd36c84daa9d6efe54fa400fc6', 'oai:doaj.org_article:6596849cc3a342d396d80b6332a8dc62', 'oai:doaj.org_article:62d4c59b20fb4399b609d2c2da7f9771', 'oai:doaj.org_article:70cbd6d9c02649dc918ce8b6d8beee6a', 'oai:doaj.org_article:73bf06d05340448491ceb2be9eb95d0e', 'oai:doaj.org_article:07eca03403714b41be66e4c057ef911b', 'oai:doaj.org_article:1b08d68356a94683bd18576327b609f9', 'oai:doaj.org_article:47320b25a1004aeab6fc4dd328125d46', 'oai:doaj.org_article:61bae87e8d2d47959e3e8219496277fd', 'oai:doaj.org_article:3e520722d9674a3097831943ec62a2b7', 'ftjijcto:oai:ojs.ijcto.org:article_327', 'oai:doaj.org_article:5a48f052fbaf472899568b3f9b9d4a4e', 'oai:doaj.org_article:5c2c2056e01b4bcbb3c3863ac2436ccc', 'oai:doaj.org_article:240db0ddaefd4d66b1d7d44aa5298b9b', 'oai:doaj.org_article:90d8985faa2e4fa6ae94a99c0482faf9', 'ftenpresspublojs:oai:ojs.systems.enpress-publisher.com:article_548', 'ftjijcto:oai:ojs.ijcto.org:article_572', 'ftjijcto:oai:ojs.ijcto.org:article_573', 'ftdoajarticles:oai:doaj.org_article:cec3214b372144ea81deaaab983a0c5c', 'oai:doaj.org_article:6b566d726be5413f9f8bac5e66f6f6ec', 'oai:doaj.org_article:0bf630cea78a4a05b8d4748abacaf12a', 'oai:doaj.org_article:1ed0294fbe4646cea6653c565f35f59e', 'oai:doaj.org_article:9e1a7e98603845418d3c20baf72e0d4b', 'oai:doaj.org_article:34aa50c6f48441b38274013cf19a5d6c', 'oai:doaj.org_article:386ff117b8df4f27b33b682750eda9d4', 'oai:doaj.org_article:1e73969f949b47b58d095726eb89eb66', 'oai:doaj.org_article:b9a3b9a4f4b94842a6ce465df19e18de', 'oai:doaj.org_article:baf8351d4ebe42d3a793522ac11b5a9c', 'oai:doaj.org_article:81571d82fc9e4bf6ac96e2a7313ac4a9', 'oai:doaj.org_article:5afe532554a544d386b925c9bfb1ce03', 'oai:doaj.org_article:74f70c32053443f2b5a72e6e5693511b', 'oai:doaj.org_article:7b79d5c9c18d4d7eaec5473f16ddddc0', 'oai:doaj.org_article:3bef8ed8ca944a48845d10c23cc60427', 'oai:doaj.org_article:596ff87efa444471b7405551448cfef5', 'oai:doaj.org_article:5fb859b9b5784ec08ff4046dbe4525ab', 'oai:doaj.org_article:821472d79b904fb98152f03060d694ae', 'oai:doaj.org_article:38238863f0814e248143923d911218e8', 'oai:doaj.org_article:def57812631742b6823f6da3ee0a444b', 'oai:doaj.org_article:f589a8f67f924623b6ad72eb84cff82f', 'oai:doaj.org_article:2a3a35d535a44653823923d5f4eda70b', 'oai:doaj.org_article:dbb3b43178214cdda97c64a4e8755474', 'oai:doaj.org_article:8a3eeaad28b34f0595f4b8a4b90b5963', 'ftjijcto:oai:ojs.ijcto.org:article_231', 'oai:doaj.org_article:aef66fb737f342cbb2028ec77c5957cf', 'oai:doaj.org_article:ff8e2b55c6fe4ed197d0dc77770fa272', 'oai:doaj.org_article:54efec4fb0fe46629f434aab0963da6f', 'oai:doaj.org_article:4120725e9f674ec8bae6c1fbe2284389', 'oai:doaj.org_article:e8a024371cba45e6b848bacd7db121a3', 'oai:doaj.org_article:9accd1b7a3b14848b23cf6d7e7b2e623', 'oai:doaj.org_article:c748ee4ee33d40b1a1ac9baacbb97ff1', 'oai:doaj.org_article:ba8d847abff24a3a9dd6c644fb39287d', 'oai:doaj.org_article:65d8ed8e3c3044c1b7bab18864daa57d', 'oai:doaj.org_article:c0ae88bd831540efac96e66f017ba302', 'oai:doaj.org_article:06a63bb3abbe4de5843c81a13b9a56f4', 'oai:doaj.org_article:5a2028b5498248c9930f92143cab8c5c', 'oai:doaj.org_article:d95a18b6c8554f428d9deb4c39bbaa30', 'oai:doaj.org_article:62591bc2d5e140fca30f118f02d3b64b', 'oai:doaj.org_article:fa8d4c8e89a444619ff272f8e97d1759', 'oai:doaj.org_article:10775c81d8674bbc83cfef4f6e77e9eb', 'oai:doaj.org_article:2430a53c4e244378bf64c110c39da543', 'oai:doaj.org_article:f32a25d83d2c473199d1cd3a060df221', 'oai:doaj.org_article:073ab6230d8743679afc0462be9cfd59', 'oai:doaj.org_article:d4c0edca19a3453cb1b149a69ccd1a42', 'oai:doaj.org_article:80f22a1f0e764a3898e0fc482ab607fb', 'oai:doaj.org_article:4581ea5ead4047ed9d0538c579835ebc', 'oai:doaj.org_article:79554f075bac42f3aa15b4d68b855345', 'oai:doaj.org_article:90fa5741a1c34428a14f24943371e10c', 'oai:doaj.org_article:9b3fdba4318c4dc086ba0656856c9fc9']</t>
   </si>
   <si>
-    <t>['10670_1.1t5f4b', 'oai:doaj.org_article:aaff31ade7214f05a5b944c5bfc272b0']</t>
-  </si>
-  <si>
-    <t>['ftjbi:oai:ojs.pkp.sfu.ca:article_13041']</t>
-  </si>
-  <si>
-    <t>['oai:doaj.org_article:9cf31f08a33349fba73151247ec463d4', 'oai:doaj.org_article:8979cad2937b4dbc856bb55ed67d820a']</t>
-  </si>
-  <si>
     <t>['oai:doaj.org_article:583c5a162ce34ca88d0f6b8cc5b46b15', 'oai:doaj.org_article:979435d533834a79849a5c88cc59c690', 'oai:doaj.org_article:38ece7641fc14475b67d433c0482f34c', 'oai:doaj.org_article:55133b2292bd40a498d6f29bc2c6e293']</t>
   </si>
   <si>
     <t>['ftrootspressojs:oai:ojs2.rootspress.org:article_458', 'ftrootspressojs:oai:ojs2.rootspress.org:article_316', 'ftrootspressojs:oai:ojs2.rootspress.org:article_484', 'oai:doaj.org_article:a4dbd47a0d2c42d59f42bf74db56d98c', 'ftunivprahaojs:oai:www.ojs.cuni.cz:article_3863', 'oai:doaj.org_article:24e358efd89341e4be697638899885a9', 'oai:doaj.org_article:06c5cdb94917458fa77217b297e13047', 'oai:doaj.org_article:069c7961e74a49bcbb12a365b7d4e597', 'oai:doaj.org_article:cfed9436ff1d4ce19da09d02b284ece7', 'oai:doaj.org_article:5f6efa85fa254b419adb0be332933356', 'oai:doaj.org_article:fbb705a5c91d4fe9b2b3973c377cdf62', 'oai:doaj.org_article:f7168e9caec64fe7b481d404509bf02f', 'oai:doaj.org_article:b8617ec3123048a6bcf43355e4b5f1ca', 'oai:doaj.org_article:da685fa5dbb84b2398c0a49168537a2c', 'oai:doaj.org_article:5f6517c9bc504ef3b4c953c9a4a7b73e', 'oai:doaj.org_article:9c471cdd7f4545f484eb47f0875408ba']</t>
   </si>
   <si>
+    <t>['ftopenresearchl:oai:biblioboard.com:f4aad77a-eeed-415a-981c-0a3e3d9a3490', 'ftopenresearchl:oai:biblioboard.com:742d42b7-5325-4dbe-bb6a-ae50194152f9']</t>
+  </si>
+  <si>
+    <t>['ftdoajarticles:oai:doaj.org_article:c89a8b2078924cb68ceb13548b4155aa']</t>
+  </si>
+  <si>
+    <t>['ftindrastraojs:oai:ojs2.ojs.indrastra.com:article_217']</t>
+  </si>
+  <si>
+    <t>['ftindrastraojs:oai:ojs2.ojs.indrastra.com:article_223']</t>
+  </si>
+  <si>
+    <t>['oai:doaj.org_article:d37d29ed683f4c9b841618e93c54fbfe', 'oai:doaj.org_article:2ecce9b8fcbf4f58aec465615c6a52b2']</t>
+  </si>
+  <si>
+    <t>['ftdoajarticles:oai:doaj.org_article:7aaf59c82fab44008ed6bb973281e9d0']</t>
+  </si>
+  <si>
+    <t>['oai:doaj.org_article:647e751ec38b4f83894d8cb982ead1de', 'oai:doaj.org_article:5a357f7faf6f4c4ca4833d0017c2ad74', 'oai:doaj.org_article:b90d9c6ded0343139ec85f56ad2d631e', 'oai:doaj.org_article:d960d38126af438483e1cde185d31706', 'oai:doaj.org_article:f68f2b05460b43ab929c15326e28fcfa', 'oai:doaj.org_article:cd35ba2f9c734182bc6744ac12872103', 'oai:doaj.org_article:bc84bd3b589d4ed491a1bafa60dab3c9', 'oai:doaj.org_article:bca5e055f4d14afa96d0182c28c4bdc2', 'oai:doaj.org_article:82139ce88d2a4347b21a35c445701e04', 'oai:doaj.org_article:3c354819b58c470baa68ccd3de4d6296', 'ftdoajarticles:oai:doaj.org_article:6e37b7e578d44f36a4e7268b0da94e23', 'oai:doaj.org_article:2a1769709d2e4f61b02652596d0d2599', 'oai:doaj.org_article:de3b335e3ab94136b91f2b57d73f6000', 'oai:doaj.org_article:68453a085acb4a93988fe9729fe70cdf', 'oai:doaj.org_article:5a51c2cc8e444bd4b16509f662d91939', 'oai:doaj.org_article:dea2b84d6d844263a7327bc685db62dc', 'oai:doaj.org_article:c746199bd3414a6a9735eb1ebd5d7f7c', 'oai:doaj.org_article:8a3682a058b94df683154ef171c813d3', 'oai:doaj.org_article:31ff182fbe2a40d7b57c9f0562c223b9', 'oai:doaj.org_article:13a39351e84d49cdba7309568ccc5855', 'oai:doaj.org_article:0ac7a9e0326c4d5f888b784639643e4e', 'oai:doaj.org_article:92fecbc7411a4ee3bb81746903b8a465', 'oai:doaj.org_article:7196f024ca1e4017884702f0a1c6c33d', 'oai:doaj.org_article:e4ec8c7b1c6a4f799072eb6129a9e8bd', 'oai:doaj.org_article:f58f32b702f34000922a87256f2dff05', 'oai:doaj.org_article:2dc44d7d16cd4f569d5c2f883dc3773b', 'oai:doaj.org_article:2e28e8e29dfd4552b236d8427c58a4e2', 'oai:doaj.org_article:ca8ddfc7c7fb4ae4b24ab689169bb148', 'oai:doaj.org_article:14c21f2a8bf54840a3f98bf65ed4f9ef', 'oai:doaj.org_article:32be4cab7d584f0e83c49f7837b9bb4a', 'oai:doaj.org_article:fd4d4a73ab494edfb9ba207522e2924e', 'oai:doaj.org_article:3449065f736f4cde97584d3531d027a9', 'oai:doaj.org_article:2059b14ee73043829aabe2b1a8392657', 'oai:doaj.org_article:94b9b93183c8430a8316884916406ef1', 'oai:doaj.org_article:284dcaaedede40259de5294cfeac29ab', 'oai:doaj.org_article:bb993f6811d5406a9234e587169f099d', 'oai:doaj.org_article:04917963167145ee906304d1688ac39f', 'oai:doaj.org_article:795da3bfdd8d4a22bf512d00acfe288a', 'oai:doaj.org_article:79db5fa83afc4a008e948bf0579e46b7', 'oai:doaj.org_article:2d9b042f9b9d488e9fc120586b122501', 'oai:doaj.org_article:35c50c34cedc449f8668109fb6046bfd', 'oai:doaj.org_article:60791f5a829a446ca580766dbe47afab', 'ftustellenboscho:oai:www.journals.ac.za_oai:article_2117', 'ftjtmfv:oai:ojs.tmfv.com.ua:article_2358', 'ftmedicalunivojs:oai:ojs.pkp.sfu.ca:article_8365', 'ftmedicalunivojs:oai:ojs.pkp.sfu.ca:article_8366', 'oai:doaj.org_article:36bbb6425d144445bb916c46881948b4', 'oai:doaj.org_article:cc08399bb45342dc8b5f8a87cb3c7e4e', 'oai:doaj.org_article:f5fa736d5eb7425590a5460726511f7a', 'oai:doaj.org_article:1b7eb1ac73884e8d86d1ce7e755bf3df', 'oai:doaj.org_article:9c6ab87cc0e748538c94c1a17fc98e4e', 'oai:doaj.org_article:0fc03bfb27b14ab29fe5066c0dd602e1', 'oai:doaj.org_article:3422c51860c5409b9a24de1f6e1b438c', 'oai:doaj.org_article:001fe4ce9003420094a5dbc0a3b7a81d', 'oai:doaj.org_article:d19ae682ed914f3797eafcae4ebdf2b9', 'oai:doaj.org_article:81177508ef494ba6b66fa82624a4ce41', 'oai:doaj.org_article:99981dccf6fe4ede81c280d0db0332d2', 'oai:doaj.org_article:8cdcc20fa19242149d6fc5ffc20361fe', 'oai:doaj.org_article:3e811d0851f44640b3ddb73a580e9d25', 'oai:doaj.org_article:159a6a76018a4d5396fc9c18c9e1b01e', 'oai:doaj.org_article:a646f9a4b7bd474788a6306f930122c3', 'oai:doaj.org_article:69f1fbb72447405c8443a52f81b9f0ac', 'oai:doaj.org_article:cea704a90c76433dbdf39a449173a1c2', 'oai:doaj.org_article:16a6fbb0dd224a51b0fbd396f4f47505', 'oai:doaj.org_article:9dc4da6a3ef04314b67f46fd7208a5b3', 'oai:doaj.org_article:62c85e1241cb4d19abf5b39e471ae751', 'oai:doaj.org_article:edc877522c564228aa73bb16bcc6d50b', 'oai:doaj.org_article:46491807cebf4d3aaaf2b4cbeaf8a13b', 'oai:doaj.org_article:eaf39afeb7e94c72bf6dd7a090c296e6', 'oai:doaj.org_article:a98e356a0258469abd5b68f037a9afa3', 'ftdoajarticles:oai:doaj.org_article:af060298195442f6a01fd35316192139', 'oai:doaj.org_article:70dee4881ef547faa0e7e75fbb7c2591', 'ftopenedition:oai:hypotheses.org:anthrodes_1106', 'oai:bibliotekanauki.pl:783288', 'oai:doaj.org_article:715272136c2d4785825461d1b9e99ae8', 'oai:doaj.org_article:aa5f283cbd704a34bd4e9773e342c3c4', 'oai:doaj.org_article:0aa6bda49a1849d683d9c55db48875a5', 'oai:doaj.org_article:b312124b67d34430b3b7e4b5da143dfc', 'oai:doaj.org_article:6d49b179df254ec894c2a8871eb7fcd9', 'oai:doaj.org_article:0872c5ce452a4878a78a8d6e386f9938', 'oai:doaj.org_article:2cd60f5ad679456886156517101703be', 'oai:doaj.org_article:fbf1ab9738724154a123719fe0766a4c', 'oai:doaj.org_article:5357d28645184a60994f047386281395', 'oai:doaj.org_article:005c4d26d97c4ac086a6b8851c61bb50', 'oai:doaj.org_article:83ffd1b401eb49e5bc71a4d6b763e886', 'oai:doaj.org_article:f32a9bf1d76c40b3adc7afe516102451', 'oai:doaj.org_article:e6f1ceca9bad43fe83afc0bbe9040e30', 'oai:doaj.org_article:cdc8216b7ff246509f966278dd9f9c40', 'oai:doaj.org_article:2a4edd9aaa9f430c86a181c2684985b9', 'oai:doaj.org_article:31e3d7382d564ad39528511458ba5990', 'oai:doaj.org_article:80c6252e603a4bd1b45673fbd887ef64', 'oai:doaj.org_article:d7a19f45b026418ba66250c798f7e8d8', 'oai:doaj.org_article:be936a5f6c4341bdb7d4cc04a7b0c5d4', 'oai:doaj.org_article:4dc9e91e536d4bbc86709a5caf52cbed', 'oai:doaj.org_article:4f74c966ca1140029ec8b3310d570444', 'oai:doaj.org_article:b80fe9476a3d48b8976724309f733740', 'oai:doaj.org_article:771f4a896eb74ded94e6e664647ff864', 'oai:doaj.org_article:77b70b6dc5d7461c9bb4a1c03d387a55', 'oai:doaj.org_article:aa48eba9c82a474587e17829f0112c44', 'ftunivalcalaojs:oai:ojs.erevistas.publicaciones.uah.es:article_2856', 'oai:doaj.org_article:a4c714298c444cc39ed666a60c3eba6e']</t>
+  </si>
+  <si>
     <t>['oai:doaj.org_article:5d5056cf5d68420790de582dd243159e', 'oai:doaj.org_article:766870ee39ed48fa9d73f1343b831fde', 'oai:doaj.org_article:4b57e26e3b304ceba260229aabe3baf0', 'oai:doaj.org_article:7cf943e18160432091c5fbb18b266cb9', 'oai:doaj.org_article:3049324d3b4c40aea82a2eafba9374c5', 'oai:doaj.org_article:1c2e6942a45145099a7280b912db31d3', 'oai:doaj.org_article:622c9f0fafbe4a1d89d7a8800305edba', 'oai:doaj.org_article:c710bbf6a3be452d8e2d23370709492e', 'oai:doaj.org_article:b22c09155de54e29a455a33ab89e61f0', 'oai:doaj.org_article:84fd8806d3594e27977ac59c624fc69e', 'oai:doaj.org_article:abcfc57c8c2b495ba8f59b865d1413ab', 'oai:doaj.org_article:9b9fa640eb124cc782e3b23baa00195c', 'oai:doaj.org_article:217b0f89825442c48755f2145279e4f1', 'oai:doaj.org_article:086d7187ec9e4ff986917a1c7c16224d', 'oai:doaj.org_article:0162ae817cd3425992ff0216932cd9e6', 'oai:doaj.org_article:359ea4969f0249639c0f672be171bb20', 'oai:doaj.org_article:1a422b3c17a54110ad4469e9e947975a', 'oai:doaj.org_article:5133592954bf4083a603222d1074a978', 'oai:doaj.org_article:418a06c0005843028e0b0f9da86a3d58', 'oai:doaj.org_article:1a4430b8fa7c428c94514645d331e3b9', 'oai:doaj.org_article:b5c97ace93374fffa8753bf1d4d31075', 'oai:doaj.org_article:01eb4f2ae40d4305bfafeee8768d6e64', 'oai:doaj.org_article:f6c7790b7c0c469099f0e1ffba51cb18', 'oai:doaj.org_article:8ebd3a305ac24cf8889998ddf0ca0c6e', 'oai:doaj.org_article:6473791487fb4537a57c991919aae10e', 'oai:doaj.org_article:ec822191b8654607bba3c6a96d5a6d63', 'oai:doaj.org_article:a7463ad046a744eb9add32167e42bb4d', 'oai:doaj.org_article:b9cf1a4d59da46f5a88349469ecec666', 'oai:doaj.org_article:6a124e55367444c3b46354ddd72fe5df', 'oai:doaj.org_article:b34c8571a1af45aebb47df01b19b196f', 'oai:doaj.org_article:8a70b3f66d7c48fa921cd400d5168cd9', 'oai:doaj.org_article:1f4ba179dfc545568634b961d9e40bef', 'oai:doaj.org_article:d27693aba8ed4fcdb07de2cd2e183fbc', 'oai:doaj.org_article:93688aa04f6c4bf08ae3f102087559b1', 'oai:doaj.org_article:07bcdf34856d48f6aee395cff62b02bc', 'oai:doaj.org_article:d7305cd663a345debe1f59656d97d828', 'oai:doaj.org_article:d4a234cc4f724c45ad099738743c47fe', 'oai:doaj.org_article:95b48659002041acb104623fd46e936e', 'oai:doaj.org_article:ec6eabf5de364e5a8580f9c357c82497', 'oai:doaj.org_article:8be63c231063490bbf5a8d0c94273a20', 'oai:doaj.org_article:e871f295d18d42f192f8ae4966ed40dc', 'oai:doaj.org_article:d114c7a3393d47f8b3c0ce5b29872fe9', 'oai:doaj.org_article:e206951f02b1418796682564f139160e', 'oai:doaj.org_article:3c2d6938cc844c03890796832b17da9b', 'oai:doaj.org_article:996efd22c13042b9afa4530e490525a3', 'oai:doaj.org_article:e55ef5b471ea4c43a794a3c06e89fd43', 'ftuaustralchile:oai:revistas.uach.cl:article_4290', 'ftuaustralchile:oai:revistas.uach.cl:article_4275', 'ftuaustralchile:oai:revistas.uach.cl:article_4267', 'ftuaustralchile:oai:revistas.uach.cl:article_4268', 'ftuaustralchile:oai:revistas.uach.cl:article_4297', 'ftuaustralchile:oai:revistas.uach.cl:article_4281', 'ftdoajarticles:oai:doaj.org_article:6ed2918a355d4f7aade9e5218269607c', 'ftdialnet:oai:dialnet.unirioja.es:ART0000921196', 'ftdialnet:oai:dialnet.unirioja.es:ART0001305861', 'ftdoajarticles:oai:doaj.org_article:32d28b4497a14f7faea64ba6ceaf60a5', 'ftunivhabanaojs:oai:revistas.uh.cu:article_6403', 'ftunibueairesfsc:oai:ojs.pkp.sfu.ca:article_9328', 'ftunipnargentina:oai:ojs2.portalrevistas.unipe.edu.ar:article_243', 'ftunisantotomasc:oai:repository.usta.edu.co:11634_63469', 'ftdialnet:oai:dialnet.unirioja.es:ART0000729950', 'ftdialnet:oai:dialnet.unirioja.es:ART0000729952', 'ftdialnet:oai:dialnet.unirioja.es:ART0000729937', 'ftdialnet:oai:dialnet.unirioja.es:ART0000729983', 'ftdialnet:oai:dialnet.unirioja.es:ART0000730121', 'ftdialnet:oai:dialnet.unirioja.es:ART0000730123', 'ftdialnet:oai:dialnet.unirioja.es:ART0000730042', 'ftdialnet:oai:dialnet.unirioja.es:ART0000730080', 'ftdialnet:oai:dialnet.unirioja.es:ART0000730074', 'ftjpolired:oai:polired.upm.es:article_5162', 'oai:doaj.org_article:185b0a584ae442c7a2111438653071c4', 'oai:doaj.org_article:f7b3d225a6e849c0b50304f32a156365', 'oai:doaj.org_article:95b956c8ce1748ecbe9637d0427eb164', 'oai:doaj.org_article:aa23e61934004fdd8b9765657a317935', 'oai:doaj.org_article:762e71747a614d26b1090be2b708d70c', 'oai:doaj.org_article:e12e02c27ff8400fb731c90cf1305730', 'oai:doaj.org_article:1c57408756214981b79d4b9a6ca11c81', 'oai:doaj.org_article:53ac7df34c8a4408bb1922ee1d0e4f7b', 'oai:doaj.org_article:8c59866e8fce4e8b8453aabf39ad1645', 'oai:doaj.org_article:19600af252f145249f1754eabdbd0e16', 'oai:doaj.org_article:e6b629455046466ba290f31829518047', 'oai:doaj.org_article:02b0b85d96834f4693db34860fdb7f48', 'oai:doaj.org_article:c34f8d8eff414f0c870cebbb958de00d', 'oai:doaj.org_article:2006e20c4f25487e958cd0247164d033', 'oai:doaj.org_article:22810ab1756f4e80b73f23a83bedf562', 'oai:doaj.org_article:efa01032d3e0472797b0ebae3918ead1', 'oai:doaj.org_article:09b48d4a61af4f80be840bb09c34b1fb', 'oai:doaj.org_article:9359e2edf4df447f95e39734ab140fed', 'oai:doaj.org_article:bf5c61a493db43da8d3f04d417d1ccef', 'oai:doaj.org_article:74edeb9315a04c2a95593e14ae86eb37', 'oai:doaj.org_article:772b3e9bdf094a4baf4b9ca64ca61d62', 'oai:doaj.org_article:7b2716dd2af94ef9babf1f4653c37c64', 'oai:doaj.org_article:28d4e8b26d934ecc9741f3d139761d6f', 'oai:doaj.org_article:c171ee795ff34d90933828f89cb8243f', 'oai:doaj.org_article:d886fd6f432a479eafb6cdf8c309a28c', 'oai:doaj.org_article:c87febd7472941ed9ea4a5c0b246c1c4', 'oai:doaj.org_article:db04eff42a944552b47e16f3b08489ca', 'oai:doaj.org_article:87ff0ca31d174ad3a7360a385934e559', 'oai:doaj.org_article:e93a050e636541a7ad3b81bf63387fc8', 'oai:doaj.org_article:89306865c96c413291a70def091a44e6', 'oai:doaj.org_article:0f6b7687646d4582b53fc7ed5e759107', 'oai:doaj.org_article:d449f74305df4d7eb3d7ffad9ca2e360', 'oai:doaj.org_article:01d9558f531a4266a4bf5b4c8ab61f7c', 'oai:doaj.org_article:3e68e3b1d2de4d35a952b6524f431b1f', 'oai:doaj.org_article:ad6ef0e0a25d4ec09f52af64cfa46a15', 'oai:doaj.org_article:ded696723217429ebd9af45f4d62343d', 'oai:doaj.org_article:bd35719767744c4285199ecf97568e1d', 'oai:doaj.org_article:35a9f5aa42304bbcbacb85f700eb511e', 'oai:doaj.org_article:5ce6c0a24ad0479f89fa4b53330c55ad', 'oai:doaj.org_article:46ec0ed09ca5469aac8b08b1e80f027b', 'oai:doaj.org_article:2390de6baa6d4985bfe401460581ea41', 'oai:doaj.org_article:ec8581dcbfd741f8af5c02e4b7c40f48', 'oai:doaj.org_article:ea32966a77864ff8b5b8adfe7b8e9194', 'oai:doaj.org_article:bd0f6fa94a91451ead057754948b415f', 'oai:doaj.org_article:49e16c5e40914a189e792724afee5ff4', 'oai:doaj.org_article:44f435a4213049f0b4f337b9ece81f09', 'oai:doaj.org_article:5ac11cbcb27d4175b51f64407039ebcc', 'oai:doaj.org_article:25c327a2dfc34dedb5fc55b19461ac5b', 'oai:doaj.org_article:ac6ff68c7e1548a98bd008561212cde3', 'oai:doaj.org_article:9b1f23808aa24b0aa994fa8840882282', 'oai:doaj.org_article:2d46d2bf48834ebdab56128cf9fec99c', 'oai:doaj.org_article:15917d030e054d19b8287a18bef622bf', 'oai:doaj.org_article:20e9e257c5fb4634b8e48a532d894c85', 'oai:doaj.org_article:e902ee73df004de1b2c9dce0f6a0f1b6', 'oai:doaj.org_article:d5d24f81305f46869c8716cc2e944f2b', 'oai:doaj.org_article:7e4455d45f5d431a9119be9fa222a75b', 'oai:doaj.org_article:cbde907af7734213aea402ca31dd1692', 'oai:doaj.org_article:bf9782f8713b461db2c5589bc71456a1', 'oai:doaj.org_article:71de6b8127a64ab3afabd67c08a2df2b', 'oai:doaj.org_article:3d7818bb3a5a444cba475c2d044df19d', 'oai:doaj.org_article:3c73737294164e8e91631e3f723446fa', 'oai:doaj.org_article:b4f1c34bd4664a668baec7b6044a26ad', 'oai:doaj.org_article:043401a737214de498c783fbb827e626', 'oai:doaj.org_article:02c8b1429493414c90b65cec1a6d335a', 'oai:doaj.org_article:49e2a03f9d52479c98d1b874db828782', 'oai:doaj.org_article:36d81fc3b26b4169b560b94bc15d5356', 'oai:doaj.org_article:562ce960317049f5811fbe615a5b1bd3', 'oai:doaj.org_article:91fdd50c56174613a0853bd087176965', 'oai:doaj.org_article:f180b2cb69374dd1a8d5666919b037b3', 'oai:doaj.org_article:e1093e9ccf264b099c1bc8ab329eb431', 'oai:doaj.org_article:acf1ceeb97694326809224e3b935ab14', 'oai:doaj.org_article:4803286a22a04fc3a9a335f5c228fd33', 'oai:doaj.org_article:626608b9a7254875920e4f86c955d2d6', 'oai:doaj.org_article:4e669b0c341d4c03affb9beca788f50a', 'oai:doaj.org_article:2160211302674ff396b82d67aba8c9ae', 'oai:doaj.org_article:089e8cbbbe9045b6b9f24ac1a5cafb9c', 'oai:doaj.org_article:0336fdf67a22460c81c15488032f0d2d', 'oai:doaj.org_article:8d041d813b2d40fe8921c69316d805e7', 'oai:doaj.org_article:0fed744452dc4191be8fae55a647af1f', 'oai:doaj.org_article:9f164b98c0b040fabc8f439d5a20e5a2', 'oai:doaj.org_article:2b942b93406746e58a14b815f4438614', 'oai:doaj.org_article:cb157af3170a464a8c63f576c90a0b4d', 'oai:doaj.org_article:0d8038883bf34a37bef5887b31c2031c', 'oai:doaj.org_article:411112e7b8dd4092a4b34f847bccb332', 'oai:doaj.org_article:8990965c71164704883eb01c803522f2', 'oai:doaj.org_article:ed966dc72acf472e9fc70a8f5b0df6fe', 'oai:doaj.org_article:029d972cf3724eff9b701311a0cacc3a', 'oai:doaj.org_article:5038fb3edb774f40bc73c03bff3a8984', 'oai:doaj.org_article:afaf2d55419a400d83b2d12271a1313d', 'oai:doaj.org_article:144aec701ca940b18c6913aa06b9edf2', 'oai:doaj.org_article:e3a476e6b86246e0bbb06fd639eb6847', 'oai:doaj.org_article:60ad6e052de54e2ca1c0192f347cdb11', 'oai:doaj.org_article:f3f14a55bdcd49ce8da90879a0a7a601', 'oai:doaj.org_article:c3420e1cb9774c29b162b6a587730475', 'oai:doaj.org_article:91d28639682b4059b7e2201614c82fbd', 'oai:doaj.org_article:27da7bac3b4d46b6933a3b9a4813be57', 'oai:doaj.org_article:b7bbfb14c0b747c0b7e5698aa790e75b', 'oai:doaj.org_article:6f7c552ac8ff436a93f7bd42a79d6604', 'oai:doaj.org_article:5b0fa2ebe4384617b980600057822605', 'oai:doaj.org_article:68b4fc0ba13546b1bb8f5a89c439a132', 'oai:doaj.org_article:a6bbfb9560194fde81b5b947fa429b60', 'oai:doaj.org_article:8c302242a3c44113b8f054d255ea030b', 'oai:doaj.org_article:94c128f7b0cf45fcbcc967829c9ce4ca', 'oai:doaj.org_article:82325bc608b945fa80139aeda90f9f28', 'oai:doaj.org_article:5a5f5445125a4af2a21107aade9ca80a', 'oai:doaj.org_article:211a430eb8294fb9865b1b404ea8b6f9', 'oai:doaj.org_article:8d6cfaece8eb44278a274744dfa07706', 'oai:doaj.org_article:e42f09fcab304d3ab0102b24fdee7caf', 'oai:doaj.org_article:18092b0a466346fcac193b9e5bb8e2c7', 'oai:doaj.org_article:91f50fbf0c6e4167babe8d8b188346f0', 'oai:doaj.org_article:12876601b48b44438dd43cc814ba6e63', 'oai:doaj.org_article:97576082e4484b38805e9dccba4cefe0', 'oai:doaj.org_article:122d63dd061e40eba661e2991e2a8c4a', 'oai:doaj.org_article:41e1c1e19dbb4a3791e75e530cf2aa75', 'oai:doaj.org_article:5964ddc115214274a14a45a0d5437ecf', 'oai:doaj.org_article:dc5ecbe1b861479a92ecca6678277dc5', 'oai:doaj.org_article:ea5e611020824750a8fb4db0d8b99f79', 'oai:doaj.org_article:9ac60ce9ca6c4f4780bf3ede82f3844b', 'oai:doaj.org_article:7b5a451554f641bf9625f675ec4b5ce0', 'oai:doaj.org_article:477e764309104ef1a8627a81ec2ee784', 'oai:doaj.org_article:1e88ccb3fb234c4f9bff25b2e5116931', 'oai:doaj.org_article:664b72d3bf804f76a48b8aa0e16799b5', 'oai:doaj.org_article:d1125130c7f644ec900b5a3d2bfc29d3', 'oai:doaj.org_article:c43efae2bcc94b19a39d6de9dad245e7', 'oai:doaj.org_article:1d359fc6559d48ada31718260dbea5b1', 'oai:doaj.org_article:a88a81d68c6649109129f49022b1657c', 'oai:doaj.org_article:290be4d698104b928ac44c5ab543652f', 'oai:doaj.org_article:d83f112c987d44f2826c4c209801c2ab', 'oai:doaj.org_article:067f8a1bf806418db2c9aabaa90cd19e', 'oai:doaj.org_article:5f37d2e8312a417793c6f8888ea28dc3', 'oai:doaj.org_article:b3b3507a641b4b4fa0194b06d28a3dbf', 'oai:doaj.org_article:68dc90a6eb4f430d8ac552e45e8e4925', 'oai:doaj.org_article:294aae4ec3974149881290f581bd7e91', 'oai:doaj.org_article:0eea240e40654b6e9aaa06438afb378c', 'oai:doaj.org_article:3826ba79d4234d84a0bb48925101226c', 'oai:doaj.org_article:f1211c90b51d42beb5635dd0f836dddf', 'oai:doaj.org_article:c58015816bbb481f8d79daa4afc323ee', 'oai:doaj.org_article:2658853d89df4bbca88fd706242189ea', 'oai:doaj.org_article:520a57bfed534d609dbff1da481e714c', 'oai:doaj.org_article:9e7f66bca7ed4f059880032f0d45cd47', 'oai:doaj.org_article:6d4772096a8c4047aeb1211fdca7e305', 'oai:doaj.org_article:e828e7135a8f438bb3cd874734734c24', 'oai:doaj.org_article:8990c2c8970a4ba7b26cb25cd4ce2a1c', 'oai:doaj.org_article:fc3a0c0d177745349f0c711b2ffa0df9', 'oai:doaj.org_article:a72ba97ecd5c4ab68d6720f4e09eddc7', 'oai:doaj.org_article:8e55a17cbaaa4065babb0908e3fbfce3', 'oai:doaj.org_article:5961237b270745b09ce35904bc14bc2c', 'oai:doaj.org_article:87bef739b92d47c9b6b37a559199fc77', 'oai:doaj.org_article:f5fd13a4e67742d9970d7288b703a181', 'oai:doaj.org_article:8c14c72825bb44e5ae67f6330abb840e', 'oai:doaj.org_article:b302c11184fc44418c84e882a7503810', 'oai:doaj.org_article:cbbfa62debc346dfae565186f4349b6a', 'oai:doaj.org_article:a7d1ce035bd54be2808bafa85e1042bf', 'oai:doaj.org_article:87f33dfc7c5241748e133e4f74b5e441', 'oai:doaj.org_article:980a8d26b76c489abc4b8f9a164ec030', 'oai:doaj.org_article:c56da288ca6941a0ae8452b6ea5aaf6e', 'oai:doaj.org_article:94b3d8a5076b45a585e34e5863fa7a39', 'oai:doaj.org_article:804ada6a7846497f9efee013b8bf2c05', 'oai:doaj.org_article:4772fcbe37ea4331b224ba818c9b43cd', 'oai:doaj.org_article:6c34376ba57f46a0b993ada6369d5e8a', 'oai:doaj.org_article:e6d3f565a3ee41a6970f2f858d18780b', 'oai:doaj.org_article:012b3f9586f8495c8b9db883fe7e4996', 'oai:doaj.org_article:eef922dddc8341f684be45cdccc4cb02', 'oai:doaj.org_article:a22c02865ebf4b649406bcfd975fbb9e', 'oai:doaj.org_article:b63077a51c714bc9b27c234bd997f378', 'oai:doaj.org_article:5ae1fdea875e49288a0d715c749498fc', 'oai:doaj.org_article:d3256eb9cd57417ba84a47a1c3e7cd37', 'oai:doaj.org_article:ee41ed2d387a4cb58fa7d6373f4b7694', 'oai:doaj.org_article:ecc66b3eae48466c80f6c62ca69ec45d', 'oai:doaj.org_article:9d67d2f99fd343859eccd0582047a364', 'oai:doaj.org_article:bfebdd83b6974e339695be63f6d464ef', 'oai:doaj.org_article:5eaad9d09f66420ca6d6914040aa6626', 'oai:doaj.org_article:ddd47ac30efe4de38435862e9abc6114', 'oai:doaj.org_article:dd6f5047a7974b69a02639d63191dde8', 'oai:doaj.org_article:087e3904d20448ad962460ca699df7c1', 'oai:doaj.org_article:f38ea298e2a4429a90eba9fb433a4d7a', 'oai:doaj.org_article:75e56bd4c2774f58b65b547b8f55a805', 'oai:doaj.org_article:b4ad4cb83b30495390d94be7d804644d', 'oai:doaj.org_article:8778b362c8b44bf08d00935dec3280c2', 'oai:doaj.org_article:1b43feef98d4425f8e0e02508cd5b741', 'ftcentralamerjol:oai:ojs.pkp.sfu.ca:article_632', 'oai:doaj.org_article:4ee517d6afc046359e95236ec7a002eb', 'ftdoajarticles:oai:doaj.org_article:418fb411a774427692b499729702cbec', 'oai:doaj.org_article:3d234ada20f94ada835854eaefec043e', 'oai:doaj.org_article:67c049aa99a24f7588a26c5d8a8d61fd', 'oai:doaj.org_article:dc8cc13d5fb847949722d0ad7a414a5a', 'oai:doaj.org_article:758038fec1f2470d8d0c2a7d7f6e955c', 'oai:doaj.org_article:de4dd3d1fd734cdf8f2e4ac11dbb7bc1', 'oai:doaj.org_article:9bed76d1a7684e9dad4205111577acef', 'oai:doaj.org_article:63cdc788aaca426b8d95773fc77b40d0', 'oai:doaj.org_article:0ccf297d73d941ad95595618498277af', 'oai:doaj.org_article:7722c73b2250442c84ccbbf805844d6b', 'oai:doaj.org_article:fb8319dde552442abd91139d864743c1', 'oai:doaj.org_article:19b57661e9f34c2f8eafa41ef4c5cb88', 'oai:doaj.org_article:66f5af2678374a0ab55132cb29d4156e', 'oai:doaj.org_article:0dbaa598b11d47359aea5b4e57770a66', 'oai:doaj.org_article:b6855b3d317441bd83dd8f8166a48dfa', 'oai:doaj.org_article:52bd37a1d74149adbe9ba7ecc183ad1a', 'oai:doaj.org_article:d5ae4b42aa084adaadaffe333e363b6c', 'oai:doaj.org_article:4c823bdfcea549049922bc7c417fb321', 'oai:doaj.org_article:8b89325ed11c43978500b164a60e8a5f', 'oai:doaj.org_article:5cfb1bf68cf44cb3b56ccaafba660774', 'oai:doaj.org_article:93ba461dffd742c9bd2479d736b8878d', 'oai:doaj.org_article:e745d6a3a9cf4f91a2f1db5c170aae9d', 'oai:doaj.org_article:117f52155411420e8ac3cf197cd96d83', 'oai:doaj.org_article:962b135e39454e2eb37de33a4805659c', 'oai:doaj.org_article:8a2ebd6fd61b41e4902825999db1c5b9', 'oai:doaj.org_article:04e252a9c2154384a329d042012995ee', 'oai:doaj.org_article:0194c12b281445749b5717a775466c82', 'oai:doaj.org_article:eb704eaea71c4f0eb4aedca6eb9065db', 'oai:doaj.org_article:16b959017fae4adbaf26b31557d2acbb', 'oai:doaj.org_article:7b3dae20d9a84053821510249defdf30', 'oai:doaj.org_article:9eba19123f1241e3bea161d942ed298c', 'oai:doaj.org_article:da3ec523235c4a09971eade45b07efa8', 'oai:doaj.org_article:aba50b04e35745dc9be3cf74b451be01', 'oai:doaj.org_article:8ef42d7a015642ff84502d87691df35a', 'oai:doaj.org_article:179296f21d374e4b9d6b560391df3428', 'oai:doaj.org_article:836c0116dfeb46248f7709e56cab24f3', 'oai:doaj.org_article:6f604a8fb1144b0aa34b1143bffdbe79', 'oai:doaj.org_article:3944655d1ad44fb5a05d27afb0056174', 'oai:doaj.org_article:c4812c28a18243829194e149cc240f3d', 'oai:doaj.org_article:e823cf8442924a9db1ba46effc5c3617', 'oai:doaj.org_article:bd6a57fa1b5640e3939d77252b44f0d4', 'oai:doaj.org_article:3bb04c955aec4d90a3e832e04aac1847', 'oai:doaj.org_article:cba60cc77cbc4f7fa6409ceda127b024', 'oai:doaj.org_article:7acc122e92554acd9f4b7ae7a930ed10', 'oai:doaj.org_article:365fcaab1f714d379df2f65986bfbef6', 'oai:doaj.org_article:b3e29ffd37df43d8a9694e5466827a1e', 'oai:doaj.org_article:9186cc0837874b448128f1b5e27133c2', 'oai:doaj.org_article:595172e891704220a6f7b04e361c4185', 'oai:doaj.org_article:b4c71c424a1d4e2d924882a3febd62a0', 'oai:doaj.org_article:4e056ecc084348a3bac84c14671a6dae', 'oai:doaj.org_article:aa878d36f172426aaae35a8d431911d3', 'oai:doaj.org_article:c353cc42193640f98f31f368e9ac7eb3', 'oai:doaj.org_article:33e5300ddc604b9ca26392b088467272', 'oai:doaj.org_article:274aabc8cba845c9b8a71add548adc74', 'oai:doaj.org_article:8e6574e1e4414524a5e7540455094342', 'oai:doaj.org_article:5c939e580e8943e9a7aa1e61ad7802fd', 'oai:doaj.org_article:440f3784f5fa4e14ad81d4591e4e2d2b', 'oai:doaj.org_article:c49fd51e29d94ce19d177efe0dffee5a', 'oai:doaj.org_article:956322be63944b36a2abcb8522af7782', 'oai:doaj.org_article:de39203009ce4b05b5b8c6d107236d61', 'oai:doaj.org_article:19c3e0b8c4624f279c02d8cf8c396dbc', 'oai:doaj.org_article:3ab25684766149cca2bf1fbaf1fb474b', 'oai:doaj.org_article:3613d302c5164c939b80ac10fa6e6a54', 'oai:doaj.org_article:ecf75c59a5704ff1b38007f7fed85127', 'oai:doaj.org_article:79658327a11e41c48cfc7455c5c870b8', 'oai:doaj.org_article:93dda03b695044afba45bba41fe2131d', 'oai:doaj.org_article:db43670ac73c42479ed2c5913bdca36d', 'oai:doaj.org_article:2fbb01fbd32c4d159e6d6dd1ebd365e3', 'oai:doaj.org_article:36e8fe27f2694d39a7e5c967c5a338f3', 'oai:doaj.org_article:64e6206edc894ff5af0d5dad35302fcf', 'oai:doaj.org_article:28bf9aa563b64e95bf1ecf7e1fe52d5c', 'oai:doaj.org_article:5182764004374a05bf2ce480223c8c7f', 'oai:doaj.org_article:60f1f73a2b5e4617b3c27fbb3b4da65a', 'oai:doaj.org_article:7586dd5b2d1144e7a56b6a94697361a7', 'oai:doaj.org_article:6d23104e9115432e97aad646b53bd00c', 'oai:doaj.org_article:e412e5f0eeea432fac780aba7b40709f', 'oai:doaj.org_article:f6eab3bb8ebf461cbf1d32df1e6ef716', 'oai:doaj.org_article:dac7ee5888c04851b71871c6c03267a1', 'oai:doaj.org_article:f7358036d55c41ecb6986811a2c7fa91', 'oai:doaj.org_article:12b5339d17eb40129a1eef8bf708e69b', 'oai:doaj.org_article:5362f95caf3b4a44a4d69479b21b1f75', 'oai:doaj.org_article:4f58757a3ba04a4d8143169770f37a08', 'oai:doaj.org_article:35bc270fff404bce8db7d2c2a3049f4d', 'oai:doaj.org_article:b0062baa711b44c2a5c7571bbcb13c18', 'oai:doaj.org_article:502bf8d9567d43edb9e8be69be37a1aa', 'oai:doaj.org_article:69f3a84eec4147d3843d9bae9e4ba5a8', 'oai:doaj.org_article:8d9e546a8ea94a48af7ff6bcf17d109b', 'oai:doaj.org_article:197967ea0cda475ab1a6aa635cc7858b', 'oai:doaj.org_article:5a0e0e0bcd3e42fda8fc5f1607330ae4', 'oai:doaj.org_article:afd5befe40a843909514944001fde1db', 'oai:doaj.org_article:5d17b3dbf9c9454fbe9bcd43de679e42', 'oai:doaj.org_article:5255604080b14f41b122e7484a362a18', 'oai:doaj.org_article:d0658808159e43fdac842e847886d05a', 'oai:doaj.org_article:a1f2239f94814b2499ad3ab222eb6849', 'oai:doaj.org_article:68d9cbcd3318477da5d09a528ba4f01c', 'oai:doaj.org_article:4f8900222bca48b9bf025e0e9b165e1f', 'oai:doaj.org_article:6d85ebe20ced480e8eb43919d95f5927', 'oai:doaj.org_article:662cc82726874169b6d2bc18a1ab808d', 'oai:doaj.org_article:244bb8d20b224f0690643689a7792e3a', 'oai:doaj.org_article:bda4e75f118844d3bc7ad9e8c9b29134', 'oai:doaj.org_article:0c5ee04cfe17477a887cc2a454c27f2c', 'oai:doaj.org_article:25bef38cfc5a4df397b6bb231cbfe6a7', 'oai:doaj.org_article:343f92691525417585cb1dedcee971c3', 'ftuningsarmiento:oai:ojs2.revistas.ungs.edu.ar:article_372', 'oai:doaj.org_article:3f09f4b6dfd54fa98772fb53e22fe89e', 'oai:doaj.org_article:0882fa1ad0964480884c204e49d786d6', 'oai:doaj.org_article:b66cf92fda8c4c079f4e77b61ca8afcb', 'oai:doaj.org_article:e53ef78216c0498ebb969f6fd6b6608c', 'oai:doaj.org_article:ecd773e9e26d47669b42322227611df7', 'oai:doaj.org_article:29f5a2c356174ac981d352e24b70bd03', 'oai:doaj.org_article:2fb81bf7e671415d9f5f6a13e2d7554d', 'oai:doaj.org_article:4698e519c39248fcb48fabf47558e055', 'oai:doaj.org_article:e2d00fa7ca37427cb4416dc956e13cf2', 'oai:doaj.org_article:f00b366ecd8f47398c138d14ea7e543d', 'oai:doaj.org_article:f1cc86440da74179bd123730b66760d5', 'oai:doaj.org_article:2b284db6bea342ebb8dafbe160a2f366', 'oai:doaj.org_article:85c17851eef5493291468ae9a930506f', 'oai:doaj.org_article:b86b6c8c6751434586bb82de6a5c00dc', 'oai:doaj.org_article:1cc59c1499f84081b8042c002253c16f', 'oai:doaj.org_article:c3ddac9cec4c4d78810a6d2e6f290af1', 'oai:doaj.org_article:534fd23de4d04159a93dcb1ef3489a9b', 'oai:doaj.org_article:c33278c83688469c9126e55a57e6d467', 'oai:doaj.org_article:c20785c404b740d48fa8ec832a1210d1', 'oai:doaj.org_article:e2bcb938204b473c881486eea172b772', 'oai:doaj.org_article:ea8dfcf8d1aa45b1b450dfb997660f11', 'oai:doaj.org_article:eb6c164cb22d459db083022f8f25486b', 'oai:doaj.org_article:3f033d72e3eb454d90baf3a5ae130f58', 'ftuaustralchile:oai:revistas.uach.cl:article_4260', 'ftuaustralchile:oai:revistas.uach.cl:article_4282', '10.4000_conflits.1506']</t>
   </si>
   <si>
-    <t>['ftdoajarticles:oai:doaj.org_article:c89a8b2078924cb68ceb13548b4155aa']</t>
-  </si>
-  <si>
-    <t>['ftindrastraojs:oai:ojs2.ojs.indrastra.com:article_217']</t>
-  </si>
-  <si>
-    <t>['ftindrastraojs:oai:ojs2.ojs.indrastra.com:article_223']</t>
-  </si>
-  <si>
-    <t>['oai:doaj.org_article:d37d29ed683f4c9b841618e93c54fbfe', 'oai:doaj.org_article:2ecce9b8fcbf4f58aec465615c6a52b2']</t>
-  </si>
-  <si>
-    <t>['ftdoajarticles:oai:doaj.org_article:7aaf59c82fab44008ed6bb973281e9d0']</t>
-  </si>
-  <si>
-    <t>['ftopenresearchl:oai:biblioboard.com:f4aad77a-eeed-415a-981c-0a3e3d9a3490', 'ftopenresearchl:oai:biblioboard.com:742d42b7-5325-4dbe-bb6a-ae50194152f9']</t>
-  </si>
-  <si>
-    <t>['oai:doaj.org_article:647e751ec38b4f83894d8cb982ead1de', 'oai:doaj.org_article:5a357f7faf6f4c4ca4833d0017c2ad74', 'oai:doaj.org_article:b90d9c6ded0343139ec85f56ad2d631e', 'oai:doaj.org_article:d960d38126af438483e1cde185d31706', 'oai:doaj.org_article:f68f2b05460b43ab929c15326e28fcfa', 'oai:doaj.org_article:cd35ba2f9c734182bc6744ac12872103', 'oai:doaj.org_article:bc84bd3b589d4ed491a1bafa60dab3c9', 'oai:doaj.org_article:bca5e055f4d14afa96d0182c28c4bdc2', 'oai:doaj.org_article:82139ce88d2a4347b21a35c445701e04', 'oai:doaj.org_article:3c354819b58c470baa68ccd3de4d6296', 'ftdoajarticles:oai:doaj.org_article:6e37b7e578d44f36a4e7268b0da94e23', 'oai:doaj.org_article:2a1769709d2e4f61b02652596d0d2599', 'oai:doaj.org_article:de3b335e3ab94136b91f2b57d73f6000', 'oai:doaj.org_article:68453a085acb4a93988fe9729fe70cdf', 'oai:doaj.org_article:5a51c2cc8e444bd4b16509f662d91939', 'oai:doaj.org_article:dea2b84d6d844263a7327bc685db62dc', 'oai:doaj.org_article:c746199bd3414a6a9735eb1ebd5d7f7c', 'oai:doaj.org_article:8a3682a058b94df683154ef171c813d3', 'oai:doaj.org_article:31ff182fbe2a40d7b57c9f0562c223b9', 'oai:doaj.org_article:13a39351e84d49cdba7309568ccc5855', 'oai:doaj.org_article:0ac7a9e0326c4d5f888b784639643e4e', 'oai:doaj.org_article:92fecbc7411a4ee3bb81746903b8a465', 'oai:doaj.org_article:7196f024ca1e4017884702f0a1c6c33d', 'oai:doaj.org_article:e4ec8c7b1c6a4f799072eb6129a9e8bd', 'oai:doaj.org_article:f58f32b702f34000922a87256f2dff05', 'oai:doaj.org_article:2dc44d7d16cd4f569d5c2f883dc3773b', 'oai:doaj.org_article:2e28e8e29dfd4552b236d8427c58a4e2', 'oai:doaj.org_article:ca8ddfc7c7fb4ae4b24ab689169bb148', 'oai:doaj.org_article:14c21f2a8bf54840a3f98bf65ed4f9ef', 'oai:doaj.org_article:32be4cab7d584f0e83c49f7837b9bb4a', 'oai:doaj.org_article:fd4d4a73ab494edfb9ba207522e2924e', 'oai:doaj.org_article:3449065f736f4cde97584d3531d027a9', 'oai:doaj.org_article:2059b14ee73043829aabe2b1a8392657', 'oai:doaj.org_article:94b9b93183c8430a8316884916406ef1', 'oai:doaj.org_article:284dcaaedede40259de5294cfeac29ab', 'oai:doaj.org_article:bb993f6811d5406a9234e587169f099d', 'oai:doaj.org_article:04917963167145ee906304d1688ac39f', 'oai:doaj.org_article:795da3bfdd8d4a22bf512d00acfe288a', 'oai:doaj.org_article:79db5fa83afc4a008e948bf0579e46b7', 'oai:doaj.org_article:2d9b042f9b9d488e9fc120586b122501', 'oai:doaj.org_article:35c50c34cedc449f8668109fb6046bfd', 'oai:doaj.org_article:60791f5a829a446ca580766dbe47afab', 'ftustellenboscho:oai:www.journals.ac.za_oai:article_2117', 'ftjtmfv:oai:ojs.tmfv.com.ua:article_2358', 'ftmedicalunivojs:oai:ojs.pkp.sfu.ca:article_8365', 'ftmedicalunivojs:oai:ojs.pkp.sfu.ca:article_8366', 'oai:doaj.org_article:36bbb6425d144445bb916c46881948b4', 'oai:doaj.org_article:cc08399bb45342dc8b5f8a87cb3c7e4e', 'oai:doaj.org_article:f5fa736d5eb7425590a5460726511f7a', 'oai:doaj.org_article:1b7eb1ac73884e8d86d1ce7e755bf3df', 'oai:doaj.org_article:9c6ab87cc0e748538c94c1a17fc98e4e', 'oai:doaj.org_article:0fc03bfb27b14ab29fe5066c0dd602e1', 'oai:doaj.org_article:3422c51860c5409b9a24de1f6e1b438c', 'oai:doaj.org_article:001fe4ce9003420094a5dbc0a3b7a81d', 'oai:doaj.org_article:d19ae682ed914f3797eafcae4ebdf2b9', 'oai:doaj.org_article:81177508ef494ba6b66fa82624a4ce41', 'oai:doaj.org_article:99981dccf6fe4ede81c280d0db0332d2', 'oai:doaj.org_article:8cdcc20fa19242149d6fc5ffc20361fe', 'oai:doaj.org_article:3e811d0851f44640b3ddb73a580e9d25', 'oai:doaj.org_article:159a6a76018a4d5396fc9c18c9e1b01e', 'oai:doaj.org_article:a646f9a4b7bd474788a6306f930122c3', 'oai:doaj.org_article:69f1fbb72447405c8443a52f81b9f0ac', 'oai:doaj.org_article:cea704a90c76433dbdf39a449173a1c2', 'oai:doaj.org_article:16a6fbb0dd224a51b0fbd396f4f47505', 'oai:doaj.org_article:9dc4da6a3ef04314b67f46fd7208a5b3', 'oai:doaj.org_article:62c85e1241cb4d19abf5b39e471ae751', 'oai:doaj.org_article:edc877522c564228aa73bb16bcc6d50b', 'oai:doaj.org_article:46491807cebf4d3aaaf2b4cbeaf8a13b', 'oai:doaj.org_article:eaf39afeb7e94c72bf6dd7a090c296e6', 'oai:doaj.org_article:a98e356a0258469abd5b68f037a9afa3', 'ftdoajarticles:oai:doaj.org_article:af060298195442f6a01fd35316192139', 'oai:doaj.org_article:70dee4881ef547faa0e7e75fbb7c2591', 'ftopenedition:oai:hypotheses.org:anthrodes_1106', 'oai:bibliotekanauki.pl:783288', 'oai:doaj.org_article:715272136c2d4785825461d1b9e99ae8', 'oai:doaj.org_article:aa5f283cbd704a34bd4e9773e342c3c4', 'oai:doaj.org_article:0aa6bda49a1849d683d9c55db48875a5', 'oai:doaj.org_article:b312124b67d34430b3b7e4b5da143dfc', 'oai:doaj.org_article:6d49b179df254ec894c2a8871eb7fcd9', 'oai:doaj.org_article:0872c5ce452a4878a78a8d6e386f9938', 'oai:doaj.org_article:2cd60f5ad679456886156517101703be', 'oai:doaj.org_article:fbf1ab9738724154a123719fe0766a4c', 'oai:doaj.org_article:5357d28645184a60994f047386281395', 'oai:doaj.org_article:005c4d26d97c4ac086a6b8851c61bb50', 'oai:doaj.org_article:83ffd1b401eb49e5bc71a4d6b763e886', 'oai:doaj.org_article:f32a9bf1d76c40b3adc7afe516102451', 'oai:doaj.org_article:e6f1ceca9bad43fe83afc0bbe9040e30', 'oai:doaj.org_article:cdc8216b7ff246509f966278dd9f9c40', 'oai:doaj.org_article:2a4edd9aaa9f430c86a181c2684985b9', 'oai:doaj.org_article:31e3d7382d564ad39528511458ba5990', 'oai:doaj.org_article:80c6252e603a4bd1b45673fbd887ef64', 'oai:doaj.org_article:d7a19f45b026418ba66250c798f7e8d8', 'oai:doaj.org_article:be936a5f6c4341bdb7d4cc04a7b0c5d4', 'oai:doaj.org_article:4dc9e91e536d4bbc86709a5caf52cbed', 'oai:doaj.org_article:4f74c966ca1140029ec8b3310d570444', 'oai:doaj.org_article:b80fe9476a3d48b8976724309f733740', 'oai:doaj.org_article:771f4a896eb74ded94e6e664647ff864', 'oai:doaj.org_article:77b70b6dc5d7461c9bb4a1c03d387a55', 'oai:doaj.org_article:aa48eba9c82a474587e17829f0112c44', 'ftunivalcalaojs:oai:ojs.erevistas.publicaciones.uah.es:article_2856', 'oai:doaj.org_article:a4c714298c444cc39ed666a60c3eba6e']</t>
-  </si>
-  <si>
     <t>['oai:doaj.org_article:388c6c18d25c4b7baace79c491fe03a6', 'oai:doaj.org_article:080f2a8080fd43e19aed1a79ce0b72c0', 'oai:doaj.org_article:700481b135264b019ea8087374f5cc50', 'oai:doaj.org_article:df19b53bdf684b6784616f377fd66d4e', 'oai:doaj.org_article:7e86ce719a5b456ebc2a4b0d75048802', 'oai:doaj.org_article:931370d1d14f453bbc69a75d33389066', 'oai:doaj.org_article:88a2bdd36a184e94be4f45d2f68ecf97', 'oai:doaj.org_article:4f5e7d5d427b4af2bd92b693f41fa72b', 'oai:doaj.org_article:f58dc25de3824a79a389e87c3267ae29', 'oai:doaj.org_article:7b87db325f834acbaefb3063124eb638', 'oai:doaj.org_article:e5520f184d214a18acdac27ad89a8b6b', 'oai:doaj.org_article:1ecdaae54cc84da8a88fae54da8341cb', 'oai:doaj.org_article:bc04ee1d3f7a431eba26520f74bb15f9', 'oai:doaj.org_article:8edae6fdcc314376969651a7d31bea8d', 'oai:doaj.org_article:1fe290d7772f49e787d22b05c3af6008', 'oai:doaj.org_article:8e716510fe2d45c9981c3b4c4ac2ad75', 'oai:doaj.org_article:4e758fc8bb4d4e39b06259fb68311362', 'oai:doaj.org_article:d07602431b8e45749827718c0e8103b1', 'oai:doaj.org_article:989e8bc4c841453d9d666d6312d40486', 'oai:doaj.org_article:ca7918f8327f4b64b79749b122443451', 'oai:doaj.org_article:3bd2d41b468044e9bf895d4dc46b93dc', 'oai:doaj.org_article:44583f66a6b446feb5b2a942ed662c95', 'oai:doaj.org_article:29d84e177bee438f86c34891560f0650', 'oai:doaj.org_article:18d167ef016b41789102b6ebdeaa0561', 'oai:doaj.org_article:a6e478ba2db04d28b4a9617ba59eaaec', 'oai:doaj.org_article:eefe8f89d51d435ca4229117ff00a806', 'oai:doaj.org_article:e88b6dd91a6649fda438eb6b58cd1cc6', 'oai:doaj.org_article:7cf00f36ddd447859e76f8810a97681a', 'ftdoajarticles:oai:doaj.org_article:41996086b31a4cd88368172068f54640', 'ftdoajarticles:oai:doaj.org_article:a9cdf398733d48728e334c88b2c3a38f', 'ftdoajarticles:oai:doaj.org_article:6e82dbc43e774402a5138e902b5b8cfe', 'ftdoajarticles:oai:doaj.org_article:ac59c43e9d4b470eb8112fa430eeec74', 'ftopenedition:oai:hypotheses.org:europeresist_2364', 'ftdoajarticles:oai:doaj.org_article:7cb802f391404816a2285f92189312ff', 'ftdoajarticles:oai:doaj.org_article:3b2177e6bc0849d393ecb0074b860932', 'ftdoajarticles:oai:doaj.org_article:3d016403f72f40379405a8b68744fd2a', 'ftdoajarticles:oai:doaj.org_article:248f966658d94d60857ee4ceefa75f48', 'ftjbangladeshjo:oai:banglajol:article_2391', 'ftjbangladeshjo:oai:banglajol:article_1704', 'ftjbjbms:oai:ojs2.www.bjbms.org:article_2367', 'ftdoajarticles:oai:doaj.org_article:f413ef74e05741e0ae9d8680a7a6b73a', 'ftvilniusunivojs:oai:ojs.www4063.vu.lt:article_1092', 'ftjnepaljo:oai:ojs.pkp.sfu.ca:article_8231', 'ftjnepaljo:oai:ojs.pkp.sfu.ca:article_7612', 'ftopenedition:oai:hypotheses.org:europeresist_2236', 'ftuniljubljanaff:oai:ojs.revije.ff.uni-lj.si:article_8627', 'ftunivarizonaojs:oai:journals.uair.arizona.edu:article_12495', 'ftunivarizonaojs:oai:journals.uair.arizona.edu:article_14622', 'ftunivarizonaojs:oai:journals.uair.arizona.edu:article_15841', 'ftunivarizonaojs:oai:journals.uair.arizona.edu:article_15894', 'ftunivarizonaojs:oai:journals.uair.arizona.edu:article_15918', 'ftunivarizonaojs:oai:journals.uair.arizona.edu:article_15929', 'ftunivbrasilojs:oai:ojs.pkp.sfu.ca:article_21547', 'ftunivarizonaojs:oai:journals.uair.arizona.edu:article_15907', 'ftunivarizonaojs:oai:journals.uair.arizona.edu:article_15933', 'ftunivbrasilojs:oai:ojs.pkp.sfu.ca:article_21523', 'ftmedicalunivojs:oai:ojs.pkp.sfu.ca:article_10130', 'ftopenjournalsnl:oai:ojs.www.openjournals.localhost:article_6731', 'oai:doaj.org_article:17137b7f26c749ed99434b399fcb7bfc', 'oai:doaj.org_article:b234139d55b9495a9d4cd485a1b4578f', 'oai:doaj.org_article:e26e20e7d1ff4705bcb8924c0ae73363', 'oai:doaj.org_article:e35648da528c4d278d2134f15942e06c', 'oai:doaj.org_article:4daab25d8c8c42198296b0f1ccf1032e', 'oai:doaj.org_article:da68caefd6d4468ba4947cad8b108ffb', 'oai:doaj.org_article:87242454d8694765af88ae50d362bdad', 'oai:doaj.org_article:f9d812a49b2b4db0a6bbc325b556d558', 'oai:doaj.org_article:70695d958bc144e3adbd1226594346b5', 'oai:doaj.org_article:4daaf0191c0f49399859f52275da8aeb', 'oai:doaj.org_article:60fb5fa6743147fd8c3e0b387a40370e', 'oai:doaj.org_article:5281c1a62c04458481a08c11e4cb321c', 'oai:doaj.org_article:090407d61bfb469883ff7e1299592287', 'oai:doaj.org_article:e76d1f9a0d4f40dc830464195be767b8', 'oai:doaj.org_article:b5122843ff304bc38a0234a5678e1285', 'oai:doaj.org_article:b79aae7355f54588b6cceb8335ba9968', 'oai:doaj.org_article:f5b29cb35b8049d7929aaf3ea9a09c43', 'oai:doaj.org_article:b5aae4fa50f7429f8419267e4e260451', 'oai:doaj.org_article:33846973cb624fb2b40be73c66d6e3e6', 'oai:doaj.org_article:8881be70936640bea2df694b9e01f0ec', 'oai:doaj.org_article:4221eb6c2aa24dbd8ed2c66df370dd82', 'oai:doaj.org_article:1cbf95b800c542e7a3a52ff4ab43ac97', 'oai:doaj.org_article:3ecc1c14ee774741bd88a24b4c32e6cb', 'oai:doaj.org_article:d8dafc4adc514898b0ffb0449c797356', 'oai:doaj.org_article:bb5ada99d57241d7abe0152efbe1a89a', 'oai:doaj.org_article:978e5f50d8f843bba2f77d17a7d2eecb', 'oai:doaj.org_article:5e014d40bb4c4b2eabcb1f4a28664522', 'oai:doaj.org_article:8a08113300c246e0b03bd6fe356122d1', 'oai:doaj.org_article:aad494c538ee41619b7b6f4c67a211c5', 'oai:doaj.org_article:367ba5c2b6d24c6c94b3aec3535bd2ce', 'oai:doaj.org_article:d22f2923083a4be1b045c6f612a92162', 'oai:doaj.org_article:205b988d72dd47eca4566d4b52e33091', 'oai:doaj.org_article:05ef717f3ecb49dabb104ee3fdd59dcb', 'oai:doaj.org_article:d77c3a97f5544b2b8cf705b48545d23b', 'oai:doaj.org_article:5f2bfa14c40d4e7b84d876027b94fbea', 'oai:doaj.org_article:e34952ad2a2c48feb3633eada4696443', 'oai:doaj.org_article:749d305b713d4968be2b68acc92ad92e', 'oai:doaj.org_article:28f2c9c74ccb4c13a54ab6c233828839', 'oai:doaj.org_article:ac82872416084f07b2167367aa6bc355', 'oai:doaj.org_article:a954cabd489a4f9abab94945b6fda36f', 'oai:doaj.org_article:9a436f89a3174ed9b674d2787b230d56', 'oai:doaj.org_article:cd328c9ad1be4fa1acee0c2d71e0507e', 'oai:doaj.org_article:76949f64deaa49a3945b91cc1dc5d567', 'oai:doaj.org_article:ed8912b2eefb4333b666d60a4ef5d8a5', 'ftjbjbms:oai:ojs2.www.bjbms.org:article_3505', 'ftdoajarticles:oai:doaj.org_article:daa54afb551040519076c64705b42e64', 'ftdoajarticles:oai:doaj.org_article:ebe51b9c73204756b58f14f2eb22939f', 'oai:doaj.org_article:9fcf35d63b7e4ff59cb48446e7beaf21', 'oai:doaj.org_article:5ad01ac00efb4f8bb593b61dbcde333d', 'oai:doaj.org_article:ad3129c27dbb4554946913f49611b3d5', 'oai:doaj.org_article:ad918e6e5d4d467bb6d29704853250a0', 'ft4scienceojs:oai:journals.4science.ge:article_966', 'ftunivbrasilojs:oai:ojs.pkp.sfu.ca:article_21536', 'ftunivbrasilojs:oai:ojs.pkp.sfu.ca:article_21561', 'ftunivbrasilojs:oai:ojs.pkp.sfu.ca:article_21573', 'ftunivbrasilojs:oai:ojs.pkp.sfu.ca:article_21682', 'ftunivbrasilojs:oai:ojs.pkp.sfu.ca:article_21734', 'ftunivbrasilojs:oai:ojs.pkp.sfu.ca:article_21662', 'oai:doaj.org_article:8525cf4572cc4093b4ea57e8ab1e6c99', 'ftunivarizonaojs:oai:journals.uair.arizona.edu:article_15864', 'ftunivarizonaojs:oai:journals.uair.arizona.edu:article_15849', 'ftunivarizonaojs:oai:journals.uair.arizona.edu:article_15889', 'ftunivarizonaojs:oai:journals.uair.arizona.edu:article_15923', 'ftunivbrasilojs:oai:ojs.pkp.sfu.ca:article_21497', 'ftunivbrasilojs:oai:ojs.pkp.sfu.ca:article_21510', 'oai:doaj.org_article:2b8a7b99b53544aa9d47a5df8a27c40a', 'oai:doaj.org_article:a619b8c038b644d296aa0a4fe772fafd', 'oai:doaj.org_article:30d1778577f544919372c599d4000227', 'oai:doaj.org_article:df61f8f7243d49cf8ba902d2d3d18cde', 'oai:doaj.org_article:e90428b3d3f3487c800c850af0c3bceb', 'oai:doaj.org_article:337c97ada16f496092a4901cc0e9729d', 'oai:doaj.org_article:073a9cdb7be04abf84b3bbfda5de01d5', 'oai:doaj.org_article:054c7cc44c844d018ba129ad075beaab', 'oai:doaj.org_article:2f162be24ddf415c91ddfad9cf9eef2a', 'oai:doaj.org_article:876cac78741543388c71595776843c49', 'oai:doaj.org_article:408df9acf604482f944273b241a315f1', 'oai:doaj.org_article:73c8e96557ff40e7acf169108121bc16', 'oai:doaj.org_article:1b41fecef4d344d69567e5ac97e23268', 'oai:doaj.org_article:b393d75b32ad42df9f21bcd3624131f7', 'oai:doaj.org_article:84576af274394a5fa380498ea885bf58', 'oai:doaj.org_article:84649bb092a6423ebafb53eba0713634', 'oai:doaj.org_article:f5cf186b20184844b5e1638b695ecd10', 'oai:doaj.org_article:dca31e387c0e425ba8afbaf0def679a6', 'oai:doaj.org_article:6a5a252263e34ee19f047bf74d209da7', 'oai:doaj.org_article:e88310a5ce574b44a6b9e9bad8b94e41', 'oai:doaj.org_article:1ef032c10c1f49e0950e7c67604c4124', 'oai:doaj.org_article:a8558f4724514a418c595b01db8afeee', 'oai:doaj.org_article:e1701fc000854c6a866c2fcf2e474af3', 'oai:doaj.org_article:d8a39adbf2b0470e997a8fdf9399c2e5', 'oai:doaj.org_article:7d4d1acc9012406ea65ecdbda4ab5ffb', 'oai:doaj.org_article:d2fdba5cd1424156aee5de5c427ce078', 'oai:doaj.org_article:8c906b640dfa46d387999722be9efa1a', 'oai:doaj.org_article:152e07c68b394f889658389a333564a6', 'ftopenedition:oai:hypotheses.org:europeresist_1930', 'oai:doaj.org_article:ad4c72dd81754c6e9106ec7a2ff69fa2', 'oai:doaj.org_article:9bcc4e401dc547f8bb2002d23def9d99', 'oai:doaj.org_article:edd879c1899f46d6b48631955293bd64', 'oai:doaj.org_article:218a787b1c944bd7a064a6cc3b558134', 'oai:doaj.org_article:b025426a95d84b92aea28b8b7030d3d9', 'oai:doaj.org_article:88b99b0062a54c49b47c83fb63f89ab6', 'oai:doaj.org_article:74fd98166a324ff6b24d2a7c6a2ce7ae', 'oai:doaj.org_article:30ae66f8904a44a3bb63c28dd21cf63e', 'oai:doaj.org_article:82395f57eeb6474291d43ac046753dc0', 'oai:doaj.org_article:ad7f64bc56e74b71a50c0b8581fe1856', 'oai:doaj.org_article:c024d13aba55444daf02066e68f80e13', 'ftopenedition:oai:hypotheses.org:europeresist_2226', 'ftopenedition:oai:hypotheses.org:europeresist_2455', 'ftopenedition:oai:hypotheses.org:europeresist_2409', 'ftopenedition:oai:hypotheses.org:europeresist_2199', 'oai:doaj.org_article:585b2fbd2ac54096bba665b579d2eec9', 'oai:doaj.org_article:d0fa92e18a224142a291879b919e7646', 'oai:doaj.org_article:32cdd68e02e448cbadd101d1ee98a302', 'oai:doaj.org_article:13050f1c336940edaf9491c631b8f523', 'oai:doaj.org_article:8668f4bc26594185971576d5798b3f9a', 'oai:doaj.org_article:5dbcf701e38041118a59bcaa5716d9d2', 'oai:doaj.org_article:75b8f3c67e9047b7a0be83e8124f8d0d', 'oai:doaj.org_article:29710aca410e4a789c27593421995074', 'oai:doaj.org_article:1a6db556c66341e9870f2bdd2508f1c3', 'oai:doaj.org_article:642fcb9086ad43f295a19344f9cef19a', 'oai:doaj.org_article:7ae600c7454e4eecac8691dcf5c8369a', 'oai:doaj.org_article:94ff22e8e2334e7bab5a552d00ea0e9e', 'ftopenedition:oai:hypotheses.org:gtw_20441', 'oai:doaj.org_article:96b3aa3fdbd34b4bb65dc8610713e0df', 'oai:doaj.org_article:b9906a6705d6411b859bd4a2c57a17cf', 'oai:doaj.org_article:6e9eb19ae6da4ee48b37388e38a70cf2', 'oai:doaj.org_article:6292eb32c1fe4690b8a56dc5e1e62e55', 'oai:doaj.org_article:3ce4802d292341acbbbd583c241bf8c7', 'oai:doaj.org_article:de3bbfd06033422aae1edaaa2ebc34da', 'oai:doaj.org_article:7941cfc61555495b8d90541f2ce98034', 'oai:doaj.org_article:04f0230b0a0c4e54a26674b5b820301e', 'oai:doaj.org_article:f22ae6b526b24d19a226879b87018d6a', 'ftdoajarticles:oai:doaj.org_article:f9a7cde6a2f64d44bd255225a934ad63', 'oai:doaj.org_article:bb16f81d5071415585bd83bfe42873b0', 'oai:doaj.org_article:793fb6b420894c3cbd81a54168b5a46a', 'oai:doaj.org_article:ee75abfc8c72440aba532b77750df20e', 'oai:doaj.org_article:e3bc4054eaf34606931fb6060a356378', 'oai:doaj.org_article:d70365bfede54617887c9860c6e00a7a']</t>
   </si>
   <si>
@@ -2542,27 +2542,27 @@
     <t>['socio', 'edu']</t>
   </si>
   <si>
+    <t>['psy', 'lang']</t>
+  </si>
+  <si>
+    <t>['relig', 'litt']</t>
+  </si>
+  <si>
     <t>['lang', 'art']</t>
   </si>
   <si>
-    <t>['psy', 'lang']</t>
-  </si>
-  <si>
-    <t>['relig', 'litt']</t>
-  </si>
-  <si>
     <t>['anthro-se', 'hist']</t>
   </si>
   <si>
+    <t>['scipo', 'droit']</t>
+  </si>
+  <si>
+    <t>['envir']</t>
+  </si>
+  <si>
     <t>['hisphilso', 'hist']</t>
   </si>
   <si>
-    <t>['scipo', 'droit']</t>
-  </si>
-  <si>
-    <t>['envir']</t>
-  </si>
-  <si>
     <t>['relig', 'anthro-se']</t>
   </si>
   <si>
@@ -2581,18 +2581,18 @@
     <t>['scipo', 'eco']</t>
   </si>
   <si>
+    <t>['lang', 'psy']</t>
+  </si>
+  <si>
+    <t>['lang', 'edu']</t>
+  </si>
+  <si>
+    <t>['phil', 'socio']</t>
+  </si>
+  <si>
     <t>['demo', 'socio']</t>
   </si>
   <si>
-    <t>['lang', 'edu']</t>
-  </si>
-  <si>
-    <t>['lang', 'psy']</t>
-  </si>
-  <si>
-    <t>['phil', 'socio']</t>
-  </si>
-  <si>
     <t>['phil', 'edu']</t>
   </si>
   <si>
@@ -2629,18 +2629,18 @@
     <t>['lang', 'musiq']</t>
   </si>
   <si>
+    <t>['scipo', 'hisphilso']</t>
+  </si>
+  <si>
+    <t>['scipo', 'socio']</t>
+  </si>
+  <si>
+    <t>['psy', 'edu']</t>
+  </si>
+  <si>
     <t>['hist', 'droit']</t>
   </si>
   <si>
-    <t>['scipo', 'socio']</t>
-  </si>
-  <si>
-    <t>['scipo', 'hisphilso']</t>
-  </si>
-  <si>
-    <t>['psy', 'edu']</t>
-  </si>
-  <si>
     <t>['scipo', 'edu']</t>
   </si>
   <si>
@@ -2659,6 +2659,9 @@
     <t>['socio', 'psy']</t>
   </si>
   <si>
+    <t>['psy', 'socio', 'demo', 'eco']</t>
+  </si>
+  <si>
     <t>['anthro-se', 'lang']</t>
   </si>
   <si>
@@ -2671,9 +2674,6 @@
     <t>['lang', 'info']</t>
   </si>
   <si>
-    <t>['psy', 'socio', 'demo', 'eco']</t>
-  </si>
-  <si>
     <t>['lang', 'demo']</t>
   </si>
   <si>
@@ -2710,33 +2710,33 @@
     <t>['hist', 'phil']</t>
   </si>
   <si>
+    <t>['lang', 'hist']</t>
+  </si>
+  <si>
     <t>['anthro-se', 'relig']</t>
   </si>
   <si>
-    <t>['lang', 'hist']</t>
-  </si>
-  <si>
     <t>['art']</t>
   </si>
   <si>
+    <t>['lang', 'socio']</t>
+  </si>
+  <si>
     <t>['scipo', 'phil']</t>
   </si>
   <si>
     <t>['lang', 'anthro-se']</t>
   </si>
   <si>
-    <t>['lang', 'socio']</t>
-  </si>
-  <si>
     <t>['psy', 'anthro-se']</t>
   </si>
   <si>
+    <t>['edu', 'anthro-se']</t>
+  </si>
+  <si>
     <t>['phil', 'lang']</t>
   </si>
   <si>
-    <t>['edu', 'anthro-se']</t>
-  </si>
-  <si>
     <t>['musiq', 'edu']</t>
   </si>
   <si>
@@ -2749,15 +2749,15 @@
     <t>['socio', 'scipo']</t>
   </si>
   <si>
+    <t>['hist', 'litt']</t>
+  </si>
+  <si>
     <t>['scipo', 'demo']</t>
   </si>
   <si>
     <t>['art', 'hisphilso']</t>
   </si>
   <si>
-    <t>['hist', 'litt']</t>
-  </si>
-  <si>
     <t>['edu', 'scipo']</t>
   </si>
   <si>
@@ -2779,12 +2779,12 @@
     <t>['musiq']</t>
   </si>
   <si>
+    <t>['art', 'litt']</t>
+  </si>
+  <si>
     <t>['edu', 'droit']</t>
   </si>
   <si>
-    <t>['art', 'litt']</t>
-  </si>
-  <si>
     <t>['hist', 'scipo']</t>
   </si>
   <si>
@@ -2797,24 +2797,24 @@
     <t>['socio', 'hist']</t>
   </si>
   <si>
+    <t>['lang', 'scipo']</t>
+  </si>
+  <si>
+    <t>['socio', 'envir']</t>
+  </si>
+  <si>
+    <t>['litt', 'art']</t>
+  </si>
+  <si>
+    <t>['lang', 'archi']</t>
+  </si>
+  <si>
+    <t>['archi', 'hist']</t>
+  </si>
+  <si>
     <t>['demo', 'envir', 'stat', 'geo', 'socio', 'psy', 'edu', 'anthro-se', 'lang', 'archeo', 'phil', 'droit', 'genre', 'litt', 'art', 'hisphilso', 'manag', 'info', 'archi', 'relig', 'hist', 'scipo']</t>
   </si>
   <si>
-    <t>['lang', 'scipo']</t>
-  </si>
-  <si>
-    <t>['lang', 'archi']</t>
-  </si>
-  <si>
-    <t>['socio', 'envir']</t>
-  </si>
-  <si>
-    <t>['litt', 'art']</t>
-  </si>
-  <si>
-    <t>['archi', 'hist']</t>
-  </si>
-  <si>
     <t>['psy', 'socio']</t>
   </si>
   <si>
@@ -2824,60 +2824,60 @@
     <t>['litt', 'info', 'geo', 'archeo']</t>
   </si>
   <si>
+    <t>['droit', 'info']</t>
+  </si>
+  <si>
     <t>['envir', 'archi', 'lang', 'socio', 'litt', 'demo', 'scipo', 'hisphilso', 'phil', 'hist']</t>
   </si>
   <si>
+    <t>['litt', 'lang', 'info', 'manag', 'museo', 'art']</t>
+  </si>
+  <si>
     <t>['phil', 'art']</t>
   </si>
   <si>
-    <t>['litt', 'lang', 'info', 'manag', 'museo', 'art']</t>
-  </si>
-  <si>
-    <t>['droit', 'info']</t>
+    <t>['hist', 'litt', 'anthro-se']</t>
   </si>
   <si>
     <t>['relig', 'musiq']</t>
   </si>
   <si>
-    <t>['hist', 'litt', 'anthro-se']</t>
-  </si>
-  <si>
     <t>['info', 'demo']</t>
   </si>
   <si>
+    <t>['hist', 'phil', 'socio']</t>
+  </si>
+  <si>
+    <t>['hist', 'hisphilso', 'phil']</t>
+  </si>
+  <si>
     <t>['geo', 'hisphilso']</t>
   </si>
   <si>
-    <t>['hist', 'phil', 'socio']</t>
-  </si>
-  <si>
-    <t>['hist', 'hisphilso', 'phil']</t>
-  </si>
-  <si>
     <t>['hist', 'phil', 'litt', 'info']</t>
   </si>
   <si>
     <t>['musiq', 'lang', 'psy']</t>
   </si>
   <si>
+    <t>['musiq', 'art']</t>
+  </si>
+  <si>
+    <t>['hist', 'envir']</t>
+  </si>
+  <si>
+    <t>['scipo', 'anthro-se']</t>
+  </si>
+  <si>
+    <t>['archeo', 'phil', 'droit', 'hist', 'eco']</t>
+  </si>
+  <si>
+    <t>['archeo', 'archi']</t>
+  </si>
+  <si>
     <t>['phil', 'anthro-se', 'hist', 'hisphilso', 'scipo', 'art', 'demo']</t>
   </si>
   <si>
-    <t>['musiq', 'art']</t>
-  </si>
-  <si>
-    <t>['hist', 'envir']</t>
-  </si>
-  <si>
-    <t>['archeo', 'phil', 'droit', 'hist', 'eco']</t>
-  </si>
-  <si>
-    <t>['scipo', 'anthro-se']</t>
-  </si>
-  <si>
-    <t>['archeo', 'archi']</t>
-  </si>
-  <si>
     <t>['edu', 'hist', 'lang', 'phil', 'eco']</t>
   </si>
   <si>
@@ -2896,12 +2896,12 @@
     <t>['envir', 'info']</t>
   </si>
   <si>
+    <t>['geo', 'archeo', 'hist']</t>
+  </si>
+  <si>
     <t>['geo', 'hist', 'art', 'museo', 'archeo']</t>
   </si>
   <si>
-    <t>['geo', 'archeo', 'hist']</t>
-  </si>
-  <si>
     <t>['anthro-se', 'art', 'hist', 'hisphilso', 'archeo', 'demo', 'droit']</t>
   </si>
   <si>
@@ -2980,84 +2980,87 @@
     <t>['droit', 'hist', 'scipo']</t>
   </si>
   <si>
+    <t>['relig', 'museo', 'musiq', 'demo', 'litt', 'geo', 'eco', 'hist', 'anthro-se', 'envir', 'psy', 'hisphilso', 'genre', 'scipo', 'lang', 'class', 'info', 'anthro-bio', 'archi', 'art', 'stat', 'socio', 'manag', 'phil', 'edu', 'droit']</t>
+  </si>
+  <si>
+    <t>['hist', 'socio', 'phil', 'eco']</t>
+  </si>
+  <si>
     <t>['hist', 'phil', 'info', 'scipo', 'museo', 'archeo', 'eco', 'litt']</t>
   </si>
   <si>
-    <t>['hist', 'socio', 'phil', 'eco']</t>
-  </si>
-  <si>
     <t>['info']</t>
   </si>
   <si>
+    <t>['relig', 'museo', 'musiq', 'demo', 'litt', 'geo', 'eco', 'hist', 'anthro-se', 'envir', 'psy', 'hisphilso', 'genre', 'scipo', 'lang', 'class', 'info', 'anthro-bio', 'archi', 'stat', 'art', 'socio', 'manag', 'phil', 'edu', 'droit']</t>
+  </si>
+  <si>
+    <t>['edu', 'socio']</t>
+  </si>
+  <si>
     <t>['scipo', 'droit', 'archeo', 'phil', 'lang', 'hist', 'edu', 'litt', 'archi', 'geo', 'demo', 'relig', 'anthro-se', 'envir', 'eco', 'musiq', 'art', 'socio', 'class', 'stat', 'info']</t>
   </si>
   <si>
     <t>['hist', 'phil', 'art']</t>
   </si>
   <si>
-    <t>['edu', 'socio']</t>
+    <t>['edu', 'lang']</t>
+  </si>
+  <si>
+    <t>['archeo', 'info']</t>
+  </si>
+  <si>
+    <t>['hist', 'phil', 'archeo', 'class', 'lang', 'art', 'info', 'litt', 'anthro-se', 'stat', 'hisphilso']</t>
+  </si>
+  <si>
+    <t>['stat', 'edu', 'socio', 'hist', 'phil']</t>
   </si>
   <si>
     <t>['hist', 'lang', 'anthro-se', 'phil']</t>
   </si>
   <si>
+    <t>['anthro-se', 'edu', 'socio', 'hist', 'phil', 'hisphilso', 'psy', 'lang']</t>
+  </si>
+  <si>
+    <t>['hist', 'phil', 'litt', 'lang']</t>
+  </si>
+  <si>
+    <t>['genre', 'hisphilso']</t>
+  </si>
+  <si>
+    <t>['edu', 'phil', 'litt']</t>
+  </si>
+  <si>
+    <t>['hist', 'scipo', 'phil', 'socio', 'stat', 'eco', 'manag', 'envir', 'musiq', 'info', 'litt', 'art', 'edu', 'class', 'anthro-se', 'lang']</t>
+  </si>
+  <si>
+    <t>['edu', 'phil', 'stat', 'eco', 'anthro-se', 'genre', 'scipo', 'droit', 'lang', 'hist']</t>
+  </si>
+  <si>
     <t>['hist', 'phil', 'edu', 'lang', 'socio', 'info', 'scipo', 'hisphilso', 'droit', 'genre', 'stat', 'psy', 'art', 'anthro-se', 'geo', 'litt', 'envir', 'archeo', 'class', 'manag']</t>
   </si>
   <si>
-    <t>['hist', 'phil', 'litt', 'lang']</t>
-  </si>
-  <si>
-    <t>['edu', 'lang']</t>
-  </si>
-  <si>
-    <t>['archeo', 'info']</t>
-  </si>
-  <si>
-    <t>['hist', 'phil', 'archeo', 'class', 'lang', 'art', 'info', 'litt', 'anthro-se', 'stat', 'hisphilso']</t>
-  </si>
-  <si>
-    <t>['stat', 'edu', 'socio', 'hist', 'phil']</t>
-  </si>
-  <si>
-    <t>['anthro-se', 'edu', 'socio', 'hist', 'phil', 'hisphilso', 'psy', 'lang']</t>
-  </si>
-  <si>
-    <t>['edu', 'phil', 'stat', 'eco', 'anthro-se', 'genre', 'scipo', 'droit', 'lang', 'hist']</t>
-  </si>
-  <si>
-    <t>['genre', 'hisphilso']</t>
-  </si>
-  <si>
-    <t>['edu', 'phil', 'litt']</t>
-  </si>
-  <si>
-    <t>['hist', 'scipo', 'phil', 'socio', 'stat', 'eco', 'manag', 'envir', 'musiq', 'info', 'litt', 'art', 'edu', 'class', 'anthro-se', 'lang']</t>
-  </si>
-  <si>
-    <t>['relig', 'museo', 'musiq', 'demo', 'litt', 'geo', 'eco', 'hist', 'anthro-se', 'envir', 'psy', 'hisphilso', 'genre', 'scipo', 'lang', 'class', 'info', 'anthro-bio', 'archi', 'art', 'stat', 'socio', 'manag', 'phil', 'edu', 'droit']</t>
+    <t>['edu', 'socio', 'lang', 'scipo', 'hist', 'litt', 'info', 'stat']</t>
+  </si>
+  <si>
+    <t>['phil', 'info', 'hist', 'edu', 'lang', 'socio', 'scipo', 'art', 'litt', 'geo']</t>
   </si>
   <si>
     <t>['stat', 'lang', 'scipo', 'archi', 'litt', 'edu', 'socio', 'anthro-se']</t>
   </si>
   <si>
-    <t>['edu', 'socio', 'lang', 'scipo', 'hist', 'litt', 'info', 'stat']</t>
-  </si>
-  <si>
-    <t>['phil', 'info', 'hist', 'edu', 'lang', 'socio', 'scipo', 'art', 'litt', 'geo']</t>
+    <t>['hist', 'phil', 'scipo']</t>
+  </si>
+  <si>
+    <t>['hist', 'phil', 'edu', 'lang']</t>
+  </si>
+  <si>
+    <t>['genre', 'info', 'hist', 'droit', 'class', 'phil', 'eco']</t>
   </si>
   <si>
     <t>['phil', 'hist', 'droit', 'hisphilso', 'info', 'edu', 'lang', 'socio', 'scipo', 'art', 'litt', 'geo']</t>
   </si>
   <si>
-    <t>['genre', 'info', 'hist', 'droit', 'class', 'phil', 'eco']</t>
-  </si>
-  <si>
-    <t>['hist', 'phil', 'scipo']</t>
-  </si>
-  <si>
-    <t>['hist', 'phil', 'edu', 'lang']</t>
-  </si>
-  <si>
     <t>['socio', 'lang', 'edu', 'hist', 'art']</t>
   </si>
   <si>
@@ -3067,33 +3070,30 @@
     <t>['info', 'droit']</t>
   </si>
   <si>
+    <t>['envir', 'geo']</t>
+  </si>
+  <si>
+    <t>['info', 'scipo', 'phil', 'archeo', 'edu']</t>
+  </si>
+  <si>
+    <t>['litt', 'hisphilso']</t>
+  </si>
+  <si>
+    <t>['phil', 'lang', 'art']</t>
+  </si>
+  <si>
     <t>['geo', 'manag', 'phil', 'hist', 'edu', 'socio', 'lang', 'info', 'scipo', 'litt', 'archeo', 'anthro-se']</t>
   </si>
   <si>
-    <t>['info', 'scipo', 'phil', 'archeo', 'edu']</t>
-  </si>
-  <si>
-    <t>['relig', 'museo', 'musiq', 'demo', 'litt', 'geo', 'eco', 'hist', 'anthro-se', 'envir', 'psy', 'hisphilso', 'genre', 'scipo', 'lang', 'class', 'info', 'anthro-bio', 'archi', 'stat', 'art', 'socio', 'manag', 'phil', 'edu', 'droit']</t>
-  </si>
-  <si>
-    <t>['envir', 'geo']</t>
-  </si>
-  <si>
-    <t>['litt', 'hisphilso']</t>
-  </si>
-  <si>
-    <t>['phil', 'lang', 'art']</t>
+    <t>['info', 'psy']</t>
+  </si>
+  <si>
+    <t>['droit', 'phil']</t>
   </si>
   <si>
     <t>['droit', 'eco']</t>
   </si>
   <si>
-    <t>['droit', 'phil']</t>
-  </si>
-  <si>
-    <t>['info', 'psy']</t>
-  </si>
-  <si>
     <t>['class', 'hist', 'phil']</t>
   </si>
   <si>
@@ -3106,15 +3106,18 @@
     <t>['info', 'socio', 'droit', 'art', 'phil', 'archeo', 'hist']</t>
   </si>
   <si>
+    <t>['scipo', 'phil', 'hist', 'lang', 'relig', 'info', 'stat', 'art', 'manag', 'litt', 'edu', 'hisphilso', 'psy', 'envir', 'eco', 'droit', 'socio', 'museo']</t>
+  </si>
+  <si>
+    <t>['archi', 'hisphilso', 'art']</t>
+  </si>
+  <si>
+    <t>['litt', 'socio', 'hist', 'phil']</t>
+  </si>
+  <si>
     <t>['hist', 'socio', 'art', 'musiq', 'litt', 'info', 'phil', 'archeo', 'stat', 'eco', 'lang', 'class', 'scipo', 'edu', 'psy']</t>
   </si>
   <si>
-    <t>['archi', 'hisphilso', 'art']</t>
-  </si>
-  <si>
-    <t>['litt', 'socio', 'hist', 'phil']</t>
-  </si>
-  <si>
     <t>['relig', 'musiq', 'demo', 'litt', 'geo', 'eco', 'hist', 'anthro-se', 'envir', 'psy', 'hisphilso', 'genre', 'scipo', 'lang', 'class', 'archi', 'info', 'anthro-bio', 'art', 'stat', 'socio', 'manag', 'phil', 'edu', 'droit', 'archeo']</t>
   </si>
   <si>
@@ -3130,27 +3133,24 @@
     <t>['droit', 'envir', 'hist', 'phil']</t>
   </si>
   <si>
+    <t>['socio', 'anthro-se', 'hist', 'scipo']</t>
+  </si>
+  <si>
+    <t>['hist', 'phil', 'litt', 'scipo', 'genre', 'info', 'eco']</t>
+  </si>
+  <si>
+    <t>['edu', 'lang', 'info', 'litt']</t>
+  </si>
+  <si>
+    <t>['edu', 'lang', 'socio']</t>
+  </si>
+  <si>
+    <t>['socio', 'psy', 'musiq', 'hist']</t>
+  </si>
+  <si>
     <t>['hist', 'lang', 'litt', 'socio', 'info', 'phil', 'scipo', 'psy', 'hisphilso', 'musiq', 'art']</t>
   </si>
   <si>
-    <t>['scipo', 'phil', 'hist', 'lang', 'relig', 'info', 'stat', 'art', 'manag', 'litt', 'edu', 'hisphilso', 'psy', 'envir', 'eco', 'droit', 'socio', 'museo']</t>
-  </si>
-  <si>
-    <t>['socio', 'anthro-se', 'hist', 'scipo']</t>
-  </si>
-  <si>
-    <t>['hist', 'phil', 'litt', 'scipo', 'genre', 'info', 'eco']</t>
-  </si>
-  <si>
-    <t>['edu', 'lang', 'info', 'litt']</t>
-  </si>
-  <si>
-    <t>['edu', 'lang', 'socio']</t>
-  </si>
-  <si>
-    <t>['socio', 'psy', 'musiq', 'hist']</t>
-  </si>
-  <si>
     <t>['socio', 'edu', 'lang', 'hist', 'phil', 'eco', 'litt']</t>
   </si>
   <si>
@@ -3181,12 +3181,12 @@
     <t>['hist', 'phil', 'scipo', 'demo', 'stat', 'info', 'litt', 'lang', 'manag', 'edu', 'hisphilso', 'art', 'socio', 'museo', 'droit', 'eco', 'psy', 'relig', 'anthro-se', 'envir', 'geo']</t>
   </si>
   <si>
+    <t>['art', 'hist']</t>
+  </si>
+  <si>
     <t>['genre', 'litt', 'anthro-se', 'edu', 'info']</t>
   </si>
   <si>
-    <t>['art', 'hist']</t>
-  </si>
-  <si>
     <t>['anthro-se', 'archeo']</t>
   </si>
   <si>
@@ -3208,12 +3208,12 @@
     <t>['edu', 'hist']</t>
   </si>
   <si>
+    <t>['scipo', 'demo', 'eco', 'socio']</t>
+  </si>
+  <si>
     <t>['hist', 'phil', 'litt']</t>
   </si>
   <si>
-    <t>['scipo', 'demo', 'eco', 'socio']</t>
-  </si>
-  <si>
     <t>['art', 'info']</t>
   </si>
   <si>
@@ -3229,33 +3229,33 @@
     <t>['anthro-se', 'hist', 'socio', 'edu']</t>
   </si>
   <si>
+    <t>['hist', 'lang', 'class', 'edu', 'phil', 'litt', 'eco']</t>
+  </si>
+  <si>
     <t>['info', 'droit', 'hist', 'phil', 'manag', 'relig', 'archeo', 'art', 'envir', 'lang', 'scipo', 'eco', 'geo', 'litt', 'socio', 'edu', 'psy']</t>
   </si>
   <si>
-    <t>['hist', 'lang', 'class', 'edu', 'phil', 'litt', 'eco']</t>
-  </si>
-  <si>
     <t>['info', 'edu', 'psy']</t>
   </si>
   <si>
     <t>['hist', 'phil', 'scipo', 'litt', 'hisphilso', 'envir', 'anthro-se', 'eco', 'lang', 'psy', 'socio', 'info', 'droit', 'archeo', 'geo']</t>
   </si>
   <si>
+    <t>['phil', 'hist', 'psy', 'socio']</t>
+  </si>
+  <si>
+    <t>['hist', 'scipo', 'phil']</t>
+  </si>
+  <si>
+    <t>['hist', 'relig']</t>
+  </si>
+  <si>
+    <t>['info', 'lang', 'hist', 'genre', 'litt', 'phil', 'scipo', 'relig', 'manag', 'archi', 'socio', 'stat', 'edu', 'archeo', 'art', 'geo', 'droit', 'eco', 'hisphilso', 'anthro-se']</t>
+  </si>
+  <si>
     <t>['relig', 'museo', 'musiq', 'litt', 'eco', 'geo', 'hist', 'anthro-se', 'envir', 'hisphilso', 'psy', 'genre', 'scipo', 'lang', 'class', 'info', 'archi', 'art', 'stat', 'socio', 'manag', 'phil', 'edu', 'droit', 'archeo']</t>
   </si>
   <si>
-    <t>['phil', 'hist', 'psy', 'socio']</t>
-  </si>
-  <si>
-    <t>['hist', 'scipo', 'phil']</t>
-  </si>
-  <si>
-    <t>['hist', 'relig']</t>
-  </si>
-  <si>
-    <t>['info', 'lang', 'hist', 'genre', 'litt', 'phil', 'scipo', 'relig', 'manag', 'archi', 'socio', 'stat', 'edu', 'archeo', 'art', 'geo', 'droit', 'eco', 'hisphilso', 'anthro-se']</t>
-  </si>
-  <si>
     <t>['edu', 'socio', 'hist', 'phil', 'droit', 'hisphilso', 'relig', 'info', 'archi', 'art', 'anthro-se', 'lang', 'stat', 'scipo', 'musiq', 'litt', 'manag', 'geo', 'archeo', 'class', 'museo', 'genre', 'psy']</t>
   </si>
   <si>
@@ -3268,12 +3268,12 @@
     <t>(JYU.Wisdom community)</t>
   </si>
   <si>
+    <t>(sous la dir. de)</t>
+  </si>
+  <si>
     <t>Networked Learning Editorial Collective, (NLEC)</t>
   </si>
   <si>
-    <t>(sous la dir. de)</t>
-  </si>
-  <si>
     <t>(pdf Formatında)</t>
   </si>
   <si>
@@ -3295,12 +3295,12 @@
     <t>(Coe, Charles H.)</t>
   </si>
   <si>
+    <t>Columbus-Balbo Review Editorial Board</t>
+  </si>
+  <si>
     <t>Columbus-Balbo Editorial Board</t>
   </si>
   <si>
-    <t>Columbus-Balbo Review Editorial Board</t>
-  </si>
-  <si>
     <t>Comité Editorial, Comité Editorial</t>
   </si>
   <si>
@@ -3322,12 +3322,12 @@
     <t>NOSOSCO, Editorial Group</t>
   </si>
   <si>
+    <t>Team, Editorial</t>
+  </si>
+  <si>
     <t>Editorial, Comité</t>
   </si>
   <si>
-    <t>Team, Editorial</t>
-  </si>
-  <si>
     <t>Author</t>
   </si>
   <si>
@@ -3337,12 +3337,12 @@
     <t>(Jyu.Wisdom Community)</t>
   </si>
   <si>
+    <t>(Sous La Dir. De)</t>
+  </si>
+  <si>
     <t>Networked Learning Editorial Collective, (Nlec)</t>
   </si>
   <si>
-    <t>(Sous La Dir. De)</t>
-  </si>
-  <si>
     <t>(Pdf Formatında)</t>
   </si>
   <si>
@@ -3379,30 +3379,30 @@
     <t>__-ovY2V8WJaJtQE9crlcID</t>
   </si>
   <si>
+    <t>__-IaGDaXcYTDnsBd3RzrgY</t>
+  </si>
+  <si>
+    <t>__-lON76W5CSnNMbkPAYezr</t>
+  </si>
+  <si>
     <t>__-jAvurCrgF1fPdAxeXxZc</t>
   </si>
   <si>
-    <t>__-IaGDaXcYTDnsBd3RzrgY</t>
-  </si>
-  <si>
-    <t>__-lON76W5CSnNMbkPAYezr</t>
-  </si>
-  <si>
     <t>__0T8inb4rnvx93h5vRc2Wz</t>
   </si>
   <si>
     <t>__1bKMVZRF2lGHXw5BAhc6F</t>
   </si>
   <si>
+    <t>__178mD65TgTNLB_U4mfAMi</t>
+  </si>
+  <si>
+    <t>__1aP0xuCfoRyhGZRbrpPcT</t>
+  </si>
+  <si>
     <t>__1RN_-bmxxkGhUlVjIxZF3</t>
   </si>
   <si>
-    <t>__178mD65TgTNLB_U4mfAMi</t>
-  </si>
-  <si>
-    <t>__1aP0xuCfoRyhGZRbrpPcT</t>
-  </si>
-  <si>
     <t>__200V7kjAxUieJXfJ7v_00</t>
   </si>
   <si>
@@ -3427,18 +3427,18 @@
     <t>__3VFsX0b-3JronnekwvOsC</t>
   </si>
   <si>
+    <t>__2hN9-HYOwtAYV8rEUm1tZ</t>
+  </si>
+  <si>
+    <t>__2s6KcJyR8Ug42-PftPEwK</t>
+  </si>
+  <si>
+    <t>__2vGBRrxTT1aDKdOtxprGA</t>
+  </si>
+  <si>
     <t>__2QiZDWERr5IDxOTxmwe_X</t>
   </si>
   <si>
-    <t>__2s6KcJyR8Ug42-PftPEwK</t>
-  </si>
-  <si>
-    <t>__2hN9-HYOwtAYV8rEUm1tZ</t>
-  </si>
-  <si>
-    <t>__2vGBRrxTT1aDKdOtxprGA</t>
-  </si>
-  <si>
     <t>__3_jse8IHzt0CU0dNALT6S</t>
   </si>
   <si>
@@ -3502,33 +3502,33 @@
     <t>__9htbkvHgpb_BupOqt4_bt</t>
   </si>
   <si>
+    <t>__A2PObfvhgd1RDg_NvM_A5</t>
+  </si>
+  <si>
+    <t>__AG14-pFQ-JF50KASNCVU8</t>
+  </si>
+  <si>
+    <t>__AZJfY1ACEit1ct4I0AMIn</t>
+  </si>
+  <si>
+    <t>__AfBBvrYreueEw-popoXhG</t>
+  </si>
+  <si>
     <t>__9uiaL2Kr6Uuw0yf_D42gg</t>
   </si>
   <si>
-    <t>__AG14-pFQ-JF50KASNCVU8</t>
-  </si>
-  <si>
-    <t>__A2PObfvhgd1RDg_NvM_A5</t>
-  </si>
-  <si>
-    <t>__AfBBvrYreueEw-popoXhG</t>
-  </si>
-  <si>
-    <t>__AZJfY1ACEit1ct4I0AMIn</t>
+    <t>__AqJW4n8fEFgGBusAOhOaM</t>
+  </si>
+  <si>
+    <t>__B48CvhswoxpjvcxokJy-w</t>
+  </si>
+  <si>
+    <t>__CbVn3NfZxz3EQAoem0Wmt</t>
   </si>
   <si>
     <t>__BM1GRdI2elucOvBAXbLuR</t>
   </si>
   <si>
-    <t>__AqJW4n8fEFgGBusAOhOaM</t>
-  </si>
-  <si>
-    <t>__B48CvhswoxpjvcxokJy-w</t>
-  </si>
-  <si>
-    <t>__CbVn3NfZxz3EQAoem0Wmt</t>
-  </si>
-  <si>
     <t>__C8pH9MO5Ey0d-FVGDxSJ9</t>
   </si>
   <si>
@@ -3544,15 +3544,15 @@
     <t>__DnXXLW1m6dfh9rHD7mIu4</t>
   </si>
   <si>
+    <t>__CbwQdx-gEWFktXcVYb8ME</t>
+  </si>
+  <si>
+    <t>__Dxuo_uNaUGg3mumbQFchm</t>
+  </si>
+  <si>
     <t>__Dp5Fssm0mw7OOLf5E7Ryo</t>
   </si>
   <si>
-    <t>__CbwQdx-gEWFktXcVYb8ME</t>
-  </si>
-  <si>
-    <t>__Dxuo_uNaUGg3mumbQFchm</t>
-  </si>
-  <si>
     <t>__ECN3GMEZfySqI0_19fsLI</t>
   </si>
   <si>
@@ -3565,6 +3565,9 @@
     <t>__EVanYtOCG9OmAx8tajr_1</t>
   </si>
   <si>
+    <t>__DpaWUjHZQMo7B_9GMMD1x</t>
+  </si>
+  <si>
     <t>__Ei0v0_SPsoHnPp66dBoX5</t>
   </si>
   <si>
@@ -3577,33 +3580,30 @@
     <t>__FYw0tp9QQzm2nmDDa5X_T</t>
   </si>
   <si>
+    <t>__HLjlO4VJyjm1jh6y4hlYX</t>
+  </si>
+  <si>
     <t>__FhCfRPCmfXALcusT0Rwkz</t>
   </si>
   <si>
-    <t>__HLjlO4VJyjm1jh6y4hlYX</t>
-  </si>
-  <si>
     <t>__GeJ0lOVILlQKFGngrsGqa</t>
   </si>
   <si>
     <t>__GulDaDah1yGGWLg-Cl8Yc</t>
   </si>
   <si>
+    <t>__HORV6k_x5UWJWiUb82kJc</t>
+  </si>
+  <si>
+    <t>__HSbUu5OJtG2xEhCrMQKfA</t>
+  </si>
+  <si>
+    <t>__ITOtyjwDyPLLbvvmW3Gv7</t>
+  </si>
+  <si>
     <t>__Gy6afOqA93AnbmqSNdcoi</t>
   </si>
   <si>
-    <t>__DpaWUjHZQMo7B_9GMMD1x</t>
-  </si>
-  <si>
-    <t>__HORV6k_x5UWJWiUb82kJc</t>
-  </si>
-  <si>
-    <t>__HSbUu5OJtG2xEhCrMQKfA</t>
-  </si>
-  <si>
-    <t>__ITOtyjwDyPLLbvvmW3Gv7</t>
-  </si>
-  <si>
     <t>__Ic3qvlSt2gMH81OUwECWq</t>
   </si>
   <si>
@@ -3625,12 +3625,12 @@
     <t>__JsUS-TJQq2MeqQOXz2j3e</t>
   </si>
   <si>
+    <t>__Kn_alAO1yru5IfyMnNh99</t>
+  </si>
+  <si>
     <t>__K8U1IzoCR_pny3OPWLsv5</t>
   </si>
   <si>
-    <t>__Kn_alAO1yru5IfyMnNh99</t>
-  </si>
-  <si>
     <t>__Kx2k4Pin1eTDdzQsDycZN</t>
   </si>
   <si>
@@ -3643,12 +3643,12 @@
     <t>__LGhy5C-maWz86sJiJheFr</t>
   </si>
   <si>
+    <t>__LUPdElLlsoUtrMgG91mGm</t>
+  </si>
+  <si>
     <t>__LlIeHSXS7_3jX0-67Odha</t>
   </si>
   <si>
-    <t>__LUPdElLlsoUtrMgG91mGm</t>
-  </si>
-  <si>
     <t>__MEvh03EPyCTDz8xEecDnx</t>
   </si>
   <si>
@@ -3658,12 +3658,12 @@
     <t>__NGAIH-p7bqNxmKzWRmt2Y</t>
   </si>
   <si>
+    <t>__Mrogc4RD17LLs3Y02qWE_</t>
+  </si>
+  <si>
     <t>__OHTo8WdCa2SUVHNshP2d7</t>
   </si>
   <si>
-    <t>__Mrogc4RD17LLs3Y02qWE_</t>
-  </si>
-  <si>
     <t>__OLQO9XSGl7fPa6u2zFhhk</t>
   </si>
   <si>
@@ -3676,12 +3676,12 @@
     <t>__Oar71J7VzZOSGkXrIjV9g</t>
   </si>
   <si>
+    <t>__P92IJiRexY6MZa_XDO4q9</t>
+  </si>
+  <si>
     <t>__OrVD1QaUTurw_uBpYfn3i</t>
   </si>
   <si>
-    <t>__P92IJiRexY6MZa_XDO4q9</t>
-  </si>
-  <si>
     <t>__Ov0QH6Msk9Rx9OHgWOqad</t>
   </si>
   <si>
@@ -3700,78 +3700,78 @@
     <t>__Q8PhgVa3HWHZSD_Ly4OUE</t>
   </si>
   <si>
+    <t>__QeFruFjrzHs13HokW34uj</t>
+  </si>
+  <si>
     <t>__QgIpF4Bx7R9jC4FTJpPk9</t>
   </si>
   <si>
-    <t>__QeFruFjrzHs13HokW34uj</t>
+    <t>__QgR8iwqzs3rDqSWqP3F3v</t>
+  </si>
+  <si>
+    <t>__Qu1fONElXe56Uh9jKGy-F</t>
+  </si>
+  <si>
+    <t>__RFMytckzphrKGMudij7Bq</t>
+  </si>
+  <si>
+    <t>__TNT-W-mv9St-M2Uak3uIF</t>
+  </si>
+  <si>
+    <t>__TdcjeXNyGclW3p7VT5XF0</t>
+  </si>
+  <si>
+    <t>__RkVJi0ud0MSVvXAPBM5DA</t>
   </si>
   <si>
     <t>__SZOBgZvjvLVFAapAPzH6U</t>
   </si>
   <si>
-    <t>__QgR8iwqzs3rDqSWqP3F3v</t>
-  </si>
-  <si>
-    <t>__Qu1fONElXe56Uh9jKGy-F</t>
-  </si>
-  <si>
-    <t>__RFMytckzphrKGMudij7Bq</t>
-  </si>
-  <si>
-    <t>__TNT-W-mv9St-M2Uak3uIF</t>
-  </si>
-  <si>
-    <t>__TdcjeXNyGclW3p7VT5XF0</t>
-  </si>
-  <si>
-    <t>__RkVJi0ud0MSVvXAPBM5DA</t>
-  </si>
-  <si>
     <t>__SZf06srOGN6ipqT-bjCi1</t>
   </si>
   <si>
+    <t>__TxdrgT53BW-loSXLmwiAq</t>
+  </si>
+  <si>
+    <t>__UbGcN4UZYc7E7MR8lVPcV</t>
+  </si>
+  <si>
     <t>__UNzIJsET6tqFmZ2gy4E-F</t>
   </si>
   <si>
+    <t>__VDgvCA8C36t0E9lW0Ts1Y</t>
+  </si>
+  <si>
     <t>__UVbtB5cR23nyRWFT6Kmwc</t>
   </si>
   <si>
-    <t>__VDgvCA8C36t0E9lW0Ts1Y</t>
-  </si>
-  <si>
     <t>__Uj4a6MJkMVA3-5dvllKXy</t>
   </si>
   <si>
-    <t>__TxdrgT53BW-loSXLmwiAq</t>
-  </si>
-  <si>
-    <t>__UbGcN4UZYc7E7MR8lVPcV</t>
+    <t>__W7uBVETJps2i_IeILgqAu</t>
   </si>
   <si>
     <t>__V3dmozoU47tI9vDmn_aA-</t>
   </si>
   <si>
-    <t>__W7uBVETJps2i_IeILgqAu</t>
+    <t>__VOv0Gcgfb-PePH-VpoO7L</t>
   </si>
   <si>
     <t>__V_mUpt8LAf63ToUNJ8PNt</t>
   </si>
   <si>
+    <t>__W0zT4Ty1bQRId4ZUIu5PG</t>
+  </si>
+  <si>
+    <t>__WRYhc3GUDKKCvw5kcE26N</t>
+  </si>
+  <si>
     <t>__WgNHjjpRu9DLjkxV6Nt8n</t>
   </si>
   <si>
-    <t>__VOv0Gcgfb-PePH-VpoO7L</t>
-  </si>
-  <si>
     <t>__Wivz2MO59csSfg2-6lK1_</t>
   </si>
   <si>
-    <t>__W0zT4Ty1bQRId4ZUIu5PG</t>
-  </si>
-  <si>
-    <t>__WRYhc3GUDKKCvw5kcE26N</t>
-  </si>
-  <si>
     <t>__WqRF4e7_-CD0jJkiROsSj</t>
   </si>
   <si>
@@ -3781,16 +3781,22 @@
     <t>__WzynEbgd4Ri30gpPICjVY</t>
   </si>
   <si>
+    <t>__XP9DwQUe77T6KwURNvPrk</t>
+  </si>
+  <si>
     <t>__Xj2DPaHj6hV4BHY2Ec22e</t>
   </si>
   <si>
     <t>__Xkd_6E5PZrJ8l89jCgN7Q</t>
   </si>
   <si>
+    <t>__XqVDulC-XxxUJ5kWXSIQe</t>
+  </si>
+  <si>
     <t>__XznlvUl9L_VqsAQlvQRkf</t>
   </si>
   <si>
-    <t>__XP9DwQUe77T6KwURNvPrk</t>
+    <t>__Yzbo3HUWcDRZVt9zT-hSI</t>
   </si>
   <si>
     <t>__YEe4aFlGtrkhy2FmOvYT9</t>
@@ -3799,9 +3805,6 @@
     <t>__YpcXkxW6w8_nxOISvLVZe</t>
   </si>
   <si>
-    <t>__XqVDulC-XxxUJ5kWXSIQe</t>
-  </si>
-  <si>
     <t>__YxMSeFSnqgw0etuzDOvRd</t>
   </si>
   <si>
@@ -3814,75 +3817,72 @@
     <t>___CerbA-G1PsJB6ghnZQvw</t>
   </si>
   <si>
+    <t>__bF_DyQNuGn_xt-ITEVWcs</t>
+  </si>
+  <si>
     <t>___imhkvXUPWbY68QBDDDLF</t>
   </si>
   <si>
-    <t>__Yzbo3HUWcDRZVt9zT-hSI</t>
+    <t>__ahmziCZoL9PgZykSRnGm6</t>
+  </si>
+  <si>
+    <t>__bTG6hwRuZBobUT3OhkyFj</t>
+  </si>
+  <si>
+    <t>__aKO2DeElk_vdhBAp3KiI7</t>
   </si>
   <si>
     <t>__a51naj8Kqmw6dp6Jn9a0P</t>
   </si>
   <si>
-    <t>__bTG6hwRuZBobUT3OhkyFj</t>
-  </si>
-  <si>
-    <t>__aKO2DeElk_vdhBAp3KiI7</t>
-  </si>
-  <si>
-    <t>__bF_DyQNuGn_xt-ITEVWcs</t>
-  </si>
-  <si>
-    <t>__ahmziCZoL9PgZykSRnGm6</t>
-  </si>
-  <si>
     <t>__ccXIVITvdOUSrnuMiZ1Vo</t>
   </si>
   <si>
+    <t>__dCr-t89-wbG2nDqFgsfXO</t>
+  </si>
+  <si>
+    <t>__dHPDOc00ELyzElDXsHgvw</t>
+  </si>
+  <si>
+    <t>__d_dDatuJH6CKOHnfSgYPZ</t>
+  </si>
+  <si>
+    <t>__dg31YoJaXBXYkiRuN5syE</t>
+  </si>
+  <si>
     <t>__bVMJ7bkpPPOe-daHWUMTT</t>
   </si>
   <si>
-    <t>__dHPDOc00ELyzElDXsHgvw</t>
-  </si>
-  <si>
-    <t>__dg31YoJaXBXYkiRuN5syE</t>
-  </si>
-  <si>
-    <t>__dCr-t89-wbG2nDqFgsfXO</t>
-  </si>
-  <si>
     <t>__dr_voH7wzl_QqOSpAGS4N</t>
   </si>
   <si>
     <t>__dLb5aR3ami9NyjRKre6vj</t>
   </si>
   <si>
-    <t>__d_dDatuJH6CKOHnfSgYPZ</t>
-  </si>
-  <si>
     <t>__egzUiNIzAXuO4ge3pk8vn</t>
   </si>
   <si>
     <t>__fmYrAYLEhTZ0mXcuMHwCB</t>
   </si>
   <si>
+    <t>__gZ6-iMF8vY_o0xO0MVBOh</t>
+  </si>
+  <si>
+    <t>__hw2al-QWx8Zspdi0LgH_5</t>
+  </si>
+  <si>
     <t>__h_dAfccEevtKI-NrElZ3L</t>
   </si>
   <si>
     <t>__gH8CG8DPJRr_PfxjY6UxQ</t>
   </si>
   <si>
+    <t>__i1IeYMHKvxkFPh2pAFkPm</t>
+  </si>
+  <si>
     <t>__gXWKmTu4krN6AJGA1dQ5t</t>
   </si>
   <si>
-    <t>__hw2al-QWx8Zspdi0LgH_5</t>
-  </si>
-  <si>
-    <t>__i1IeYMHKvxkFPh2pAFkPm</t>
-  </si>
-  <si>
-    <t>__gZ6-iMF8vY_o0xO0MVBOh</t>
-  </si>
-  <si>
     <t>__itY0q4WNl5aSlpxZaHsFK</t>
   </si>
   <si>
@@ -3901,177 +3901,177 @@
     <t>__jgqNOrlplDb0isCPKTWuT</t>
   </si>
   <si>
+    <t>__kGT23HKVmXyDP98rag-di</t>
+  </si>
+  <si>
     <t>__kNkjDYG9RMj07p7ZMhNjY</t>
   </si>
   <si>
+    <t>__jv7ZH-xA4i0-WKx1CBzhi</t>
+  </si>
+  <si>
     <t>__jiPf6-98fLFa3Lc-fBXtR</t>
   </si>
   <si>
-    <t>__jv7ZH-xA4i0-WKx1CBzhi</t>
-  </si>
-  <si>
-    <t>__kGT23HKVmXyDP98rag-di</t>
-  </si>
-  <si>
     <t>__kP7RRli7n7Xzm7E-C3Niq</t>
   </si>
   <si>
+    <t>__mIY6BlZQYUJAHI3s5mHnp</t>
+  </si>
+  <si>
     <t>__kUjO7cTPg50L02-K3KoBi</t>
   </si>
   <si>
+    <t>__mvSdXLQCXhi3rx_PETrXr</t>
+  </si>
+  <si>
+    <t>__n9_hXsIKe4Tz5gLpY98L1</t>
+  </si>
+  <si>
+    <t>__nF0oOEv6MhlZKEqpGHbyD</t>
+  </si>
+  <si>
+    <t>__lLNFDcrcyEHMqGV9XH_lE</t>
+  </si>
+  <si>
+    <t>__nDFrvg0ShX5f93_XwHyxs</t>
+  </si>
+  <si>
+    <t>__nTz2ygYD4klvezaJZYouE</t>
+  </si>
+  <si>
     <t>__n-wob8cuvkde1DuVpNwGq</t>
   </si>
   <si>
-    <t>__n9_hXsIKe4Tz5gLpY98L1</t>
-  </si>
-  <si>
-    <t>__mIY6BlZQYUJAHI3s5mHnp</t>
-  </si>
-  <si>
-    <t>__lLNFDcrcyEHMqGV9XH_lE</t>
-  </si>
-  <si>
-    <t>__nF0oOEv6MhlZKEqpGHbyD</t>
-  </si>
-  <si>
-    <t>__mvSdXLQCXhi3rx_PETrXr</t>
-  </si>
-  <si>
     <t>__ncOwSMlrvYFp1IWkc2q_J</t>
   </si>
   <si>
     <t>__nFKwGUcKPU2JMLHlWeh0C</t>
   </si>
   <si>
-    <t>__nDFrvg0ShX5f93_XwHyxs</t>
-  </si>
-  <si>
-    <t>__nTz2ygYD4klvezaJZYouE</t>
+    <t>__oK_PTO0q8Lej387o1hhXi</t>
+  </si>
+  <si>
+    <t>__ow8dZtHVDXkGVjkAgPXkE</t>
+  </si>
+  <si>
+    <t>__oSY4zD3SqwqXhObaprLYx</t>
   </si>
   <si>
     <t>__oFTuOshLLhf3ZCol9Kpkt</t>
   </si>
   <si>
-    <t>__ow8dZtHVDXkGVjkAgPXkE</t>
+    <t>__pI3PPwXB8Kn06wLhwlunu</t>
+  </si>
+  <si>
+    <t>__p3A4c4EM7-XooFagOhcqc</t>
   </si>
   <si>
     <t>__onA2Wg-dHoQiZze9Kj_YU</t>
   </si>
   <si>
-    <t>__p3A4c4EM7-XooFagOhcqc</t>
-  </si>
-  <si>
-    <t>__oSY4zD3SqwqXhObaprLYx</t>
-  </si>
-  <si>
-    <t>__oK_PTO0q8Lej387o1hhXi</t>
-  </si>
-  <si>
-    <t>__pI3PPwXB8Kn06wLhwlunu</t>
+    <t>__poJkIGGRiVzbFSbeUjSO2</t>
+  </si>
+  <si>
+    <t>__ppT1fDr8XVoXwy1j35jVH</t>
+  </si>
+  <si>
+    <t>__pQZGYKtX-7qMPyJmpQROZ</t>
   </si>
   <si>
     <t>__pfLWrSeTkzcVmJKyaS35b</t>
   </si>
   <si>
-    <t>__ppT1fDr8XVoXwy1j35jVH</t>
-  </si>
-  <si>
-    <t>__pQZGYKtX-7qMPyJmpQROZ</t>
-  </si>
-  <si>
     <t>__q27iar5JB21jMq5Xc2YE2</t>
   </si>
   <si>
-    <t>__poJkIGGRiVzbFSbeUjSO2</t>
+    <t>__qeddd0QVmKz20A8F83ixb</t>
+  </si>
+  <si>
+    <t>__qqW7UMhpG-T593Bq1kVXV</t>
   </si>
   <si>
     <t>__qSo3Y2dIkJzlSkXR9WAsQ</t>
   </si>
   <si>
-    <t>__qeddd0QVmKz20A8F83ixb</t>
+    <t>__rAwUj2_QMJJeqd1uCkN4l</t>
+  </si>
+  <si>
+    <t>__rv1q0OOH6_m6YqjNvVe8X</t>
   </si>
   <si>
     <t>__r6e_pmVwZYix5ydsQKDSI</t>
   </si>
   <si>
-    <t>__rAwUj2_QMJJeqd1uCkN4l</t>
-  </si>
-  <si>
-    <t>__rv1q0OOH6_m6YqjNvVe8X</t>
+    <t>__r_WFNR2xKffgQYN1NRRD6</t>
+  </si>
+  <si>
+    <t>__ryGDXscdXIJBJ9AKgVaaT</t>
+  </si>
+  <si>
+    <t>__rZE7YUektjET6kH1AytVq</t>
+  </si>
+  <si>
+    <t>__sZnXJGWR74k2YgvEVDw8B</t>
+  </si>
+  <si>
+    <t>__uJg4BmD5JgSNudl8wEhgU</t>
+  </si>
+  <si>
+    <t>__suzIMUmhb7zLGSmd0Hihh</t>
+  </si>
+  <si>
+    <t>__tEEcJ9RLnfM_tcwqQb-by</t>
+  </si>
+  <si>
+    <t>__upZT-qST585lMu8Ymww0H</t>
+  </si>
+  <si>
+    <t>__uWRpfIv6T0bwbLA-MO6r-</t>
   </si>
   <si>
     <t>__fHGkL0oVDFuSGGKataw9M</t>
   </si>
   <si>
-    <t>__qqW7UMhpG-T593Bq1kVXV</t>
-  </si>
-  <si>
-    <t>__r_WFNR2xKffgQYN1NRRD6</t>
-  </si>
-  <si>
-    <t>__ryGDXscdXIJBJ9AKgVaaT</t>
-  </si>
-  <si>
-    <t>__rZE7YUektjET6kH1AytVq</t>
-  </si>
-  <si>
-    <t>__suzIMUmhb7zLGSmd0Hihh</t>
-  </si>
-  <si>
-    <t>__sZnXJGWR74k2YgvEVDw8B</t>
-  </si>
-  <si>
-    <t>__uJg4BmD5JgSNudl8wEhgU</t>
-  </si>
-  <si>
-    <t>__uWRpfIv6T0bwbLA-MO6r-</t>
-  </si>
-  <si>
-    <t>__upZT-qST585lMu8Ymww0H</t>
-  </si>
-  <si>
-    <t>__tEEcJ9RLnfM_tcwqQb-by</t>
-  </si>
-  <si>
     <t>__vSKep5XTvdCXQJCTCWdc3</t>
   </si>
   <si>
     <t>__wqSvYLgW0BP-IBvsKfIae</t>
   </si>
   <si>
+    <t>__xKytadaP3ajf1U2penkJk</t>
+  </si>
+  <si>
     <t>__yQq9uFvZ7kWQHjo3eeOuG</t>
   </si>
   <si>
+    <t>__vYgqH32Brt3Em_CeKTqRL</t>
+  </si>
+  <si>
     <t>__yXSovz2hAXn66joh3k_q7</t>
   </si>
   <si>
-    <t>__vYgqH32Brt3Em_CeKTqRL</t>
-  </si>
-  <si>
-    <t>__xKytadaP3ajf1U2penkJk</t>
+    <t>__ykt8c6WgWgjo3EQ96JOZs</t>
   </si>
   <si>
     <t>__y8GBoX9CFLPqmmjC6UPvn</t>
   </si>
   <si>
-    <t>__ykt8c6WgWgjo3EQ96JOZs</t>
-  </si>
-  <si>
     <t>__zY4O-WZo453gfRWMT2x7O</t>
   </si>
   <si>
+    <t>__zoazg8A5mOVbcyWHZoKt-</t>
+  </si>
+  <si>
+    <t>__zLxzANwhm10j-yRDAhWjT</t>
+  </si>
+  <si>
+    <t>_colloque_de_l_association_des_mediateurs_des_institutions_de_sante_amis__E81SDFoIogYBS88d7sf60</t>
+  </si>
+  <si>
     <t>_autores_7yQRgKS-lpN32J8HyknD2</t>
   </si>
   <si>
-    <t>__zLxzANwhm10j-yRDAhWjT</t>
-  </si>
-  <si>
-    <t>_colloque_de_l_association_des_mediateurs_des_institutions_de_sante_amis__E81SDFoIogYBS88d7sf60</t>
-  </si>
-  <si>
-    <t>__zoazg8A5mOVbcyWHZoKt-</t>
-  </si>
-  <si>
     <t>_colloque_organise_par_la_vlaamse_vereniging_ombudsfunctie_van_alle_zorgvoorzieningen_vvovaz__UFJwNOdFE_uQ9Rwf8Bcjs</t>
   </si>
   <si>
@@ -4084,51 +4084,51 @@
     <t>__zpk70-Thf0H5oJsq7oLyf</t>
   </si>
   <si>
+    <t>_dans_le_cadre_du_certificat_interuniversitaire_en_ethique_des_soins_de_sante_organise_par_l_ucl_et_les_fundp_namur__NEq8M1P0Eoy2RnjP0_P7b</t>
+  </si>
+  <si>
+    <t>_con_uoldelul_chelati_dirar__KJ_a8l4_xFk6sLaTv0lTM</t>
+  </si>
+  <si>
+    <t>_conselho_editorial_85M0_6oeUB41Og92bwgxU</t>
+  </si>
+  <si>
+    <t>_editorial_team_kVNnqvNxcIvkoHBJqUGOq</t>
+  </si>
+  <si>
+    <t>_board_of_editors_jiUnHSND4Gj0jZkqvkDYF</t>
+  </si>
+  <si>
+    <t>_eds__KtmL8DKyOY9uIBynh3GYk</t>
+  </si>
+  <si>
+    <t>_em_open_rivers_em_editorial_staff_DiL3arLXI-FlAAz4n5vwG</t>
+  </si>
+  <si>
+    <t>_editorial_comments_XvpijJ7wprNMbYAOHhT7e</t>
+  </si>
+  <si>
+    <t>_en_collaboration_avec_baudin_a__4L4_FHKGmtzQil8QkK2y4</t>
+  </si>
+  <si>
     <t>_consejo_de_editores_de_la_revista_historias__bYwepZ4k-t7AF3PLi3RWn</t>
   </si>
   <si>
-    <t>_dans_le_cadre_du_certificat_interuniversitaire_en_ethique_des_soins_de_sante_organise_par_l_ucl_et_les_fundp_namur__NEq8M1P0Eoy2RnjP0_P7b</t>
-  </si>
-  <si>
-    <t>_con_uoldelul_chelati_dirar__KJ_a8l4_xFk6sLaTv0lTM</t>
-  </si>
-  <si>
-    <t>_conselho_editorial_85M0_6oeUB41Og92bwgxU</t>
-  </si>
-  <si>
-    <t>_editorial_team_kVNnqvNxcIvkoHBJqUGOq</t>
-  </si>
-  <si>
-    <t>_eds__KtmL8DKyOY9uIBynh3GYk</t>
-  </si>
-  <si>
-    <t>_en_collaboration_avec_baudin_a__4L4_FHKGmtzQil8QkK2y4</t>
-  </si>
-  <si>
-    <t>_em_open_rivers_em_editorial_staff_DiL3arLXI-FlAAz4n5vwG</t>
-  </si>
-  <si>
-    <t>_board_of_editors_jiUnHSND4Gj0jZkqvkDYF</t>
-  </si>
-  <si>
     <t>_expose_devant_le_conseil_d_entreprise_de_l_ucl__boV91YybohEjYjdsHNyee</t>
   </si>
   <si>
-    <t>_editorial_comments_XvpijJ7wprNMbYAOHhT7e</t>
+    <t>_en_collaboration_avec_personnes__4XJq4tk17PbVCF-PRoqdf</t>
   </si>
   <si>
     <t>_en_collaboration_avec_personnes__3l4w3MNlvm32nA0FvFgE5</t>
   </si>
   <si>
-    <t>_en_collaboration_avec_personnes__4XJq4tk17PbVCF-PRoqdf</t>
+    <t>_honorary_research_fellow_presso_l_istituto_di_storia_contemporanea_della_sodertorn_university_di_stoccolma_monica_quirico_J69S4o4KhgXeierZYy2NY</t>
   </si>
   <si>
     <t>_freedman__lb1UlOWru363okTr4t4vH</t>
   </si>
   <si>
-    <t>_honorary_research_fellow_presso_l_istituto_di_storia_contemporanea_della_sodertorn_university_di_stoccolma_monica_quirico_J69S4o4KhgXeierZYy2NY</t>
-  </si>
-  <si>
     <t>_ita_hrsg__vhKa-nvPC-jVoHPreXzir</t>
   </si>
   <si>
@@ -4144,54 +4144,54 @@
     <t>_n_n_member_of_working_group__myL3pzR2TeSBIyUzyOTPo</t>
   </si>
   <si>
+    <t>_relaciones_internacionales_equipo_editorial_ZJ-I9dFqsIs5Db9CYhT0n</t>
+  </si>
+  <si>
+    <t>_f__xBD5wLxNIlieOgnXiDTCf</t>
+  </si>
+  <si>
+    <t>_seminaire_organise_par_le_centre_du_cancer_et_d_hematologie_de_l_ucl__SptgSd4iSdb5UnsGz5gaw</t>
+  </si>
+  <si>
+    <t>_sous_la_dir_et_avec_une_intro_de__VN23DjOenbKbI-EdbluU5</t>
+  </si>
+  <si>
+    <t>_mp__LDGPjm8awiFWOMqjSMT7P</t>
+  </si>
+  <si>
+    <t>_sous_la_dir_de__HWpwhZOsnO_zlsNWFP3jH</t>
+  </si>
+  <si>
+    <t>_th_congress_of_the_rei_cretariae_romanae_fautores_3-Vi40SP09YfQbZQl1LJ5</t>
+  </si>
+  <si>
     <t>_nlec_networked_learning_editorial_collective_UlQk-Ai8VmzmpHnw94qfX</t>
   </si>
   <si>
-    <t>_relaciones_internacionales_equipo_editorial_ZJ-I9dFqsIs5Db9CYhT0n</t>
-  </si>
-  <si>
-    <t>_seminaire_organise_par_le_centre_du_cancer_et_d_hematologie_de_l_ucl__SptgSd4iSdb5UnsGz5gaw</t>
-  </si>
-  <si>
-    <t>_f__xBD5wLxNIlieOgnXiDTCf</t>
-  </si>
-  <si>
-    <t>_sous_la_dir_et_avec_une_intro_de__VN23DjOenbKbI-EdbluU5</t>
-  </si>
-  <si>
-    <t>_th_congress_of_the_rei_cretariae_romanae_fautores_3-Vi40SP09YfQbZQl1LJ5</t>
-  </si>
-  <si>
-    <t>_mp__LDGPjm8awiFWOMqjSMT7P</t>
-  </si>
-  <si>
-    <t>_sous_la_dir_de__HWpwhZOsnO_zlsNWFP3jH</t>
-  </si>
-  <si>
     <t>_pdf_formatinda__HYs2wNiunf1Nkkg6_U6xX</t>
   </si>
   <si>
     <t>_traducao_de_luciana_hamond__PSFD1mgUNNsCP8K6FSScc</t>
   </si>
   <si>
+    <t>_traducao_de_yuri_behr__9SsAnbKPFlB6ywIegZil9</t>
+  </si>
+  <si>
+    <t>_unikl_bmi__ipW3gO414Y1beUKzOJ86M</t>
+  </si>
+  <si>
+    <t>_twb_translators_without_borders_XeftCoWJ9sYZ9AoKL71gy</t>
+  </si>
+  <si>
+    <t>_varios_autores_R2tNjK-3GG5cRbwq7WO7M</t>
+  </si>
+  <si>
+    <t>_wg__gRcSMdwEj0cUm7ZNoGpoI</t>
+  </si>
+  <si>
     <t>_the_editors_RykkjpycJKoVK6JexMgQd</t>
   </si>
   <si>
-    <t>_traducao_de_yuri_behr__9SsAnbKPFlB6ywIegZil9</t>
-  </si>
-  <si>
-    <t>_unikl_bmi__ipW3gO414Y1beUKzOJ86M</t>
-  </si>
-  <si>
-    <t>_varios_autores_R2tNjK-3GG5cRbwq7WO7M</t>
-  </si>
-  <si>
-    <t>_twb_translators_without_borders_XeftCoWJ9sYZ9AoKL71gy</t>
-  </si>
-  <si>
-    <t>_wg__gRcSMdwEj0cUm7ZNoGpoI</t>
-  </si>
-  <si>
     <t>a_comissao_editorial_X6z0AY3C0HnJMgsLBrhTN</t>
   </si>
   <si>
@@ -4210,27 +4210,27 @@
     <t>agenda_estado_de_derecho_editorial_team_4gVs2GpiXuIE9rmJnoJ_B</t>
   </si>
   <si>
+    <t>_spelled_william_eden_in_mp_syllabus__urwM-kE7jU_aNSe_OiUn6</t>
+  </si>
+  <si>
     <t>ala_editorial_board_Nn4EQXjt5cy03X8ffe7R0</t>
   </si>
   <si>
     <t>ala_editors_VpPlb4gPeKZe6Prfck34d</t>
   </si>
   <si>
-    <t>_spelled_william_eden_in_mp_syllabus__urwM-kE7jU_aNSe_OiUn6</t>
-  </si>
-  <si>
     <t>albanie_tirana_1iq3mvZuNzo5JNg49Xp_B</t>
   </si>
   <si>
     <t>alexandra_esther_editors__Ixq56VVtkEU0lo7Efsnf6</t>
   </si>
   <si>
+    <t>_william_leete__lrDVAQhUEl9JR2dkvPbss</t>
+  </si>
+  <si>
     <t>aline_lara_galicia_uyFxLx9WJXm-fvrdiaabu</t>
   </si>
   <si>
-    <t>_william_leete__lrDVAQhUEl9JR2dkvPbss</t>
-  </si>
-  <si>
     <t>academies_editorial_board_loCcB_Qjm82DRjhi5Ynou</t>
   </si>
   <si>
@@ -4351,195 +4351,195 @@
     <t>cjal_editorial_board_I1H74QPTE2aGsj0T7B83a</t>
   </si>
   <si>
+    <t>a_marusic_rEjPQkkupEEbkkkGEu_oU</t>
+  </si>
+  <si>
+    <t>co_editors_co_editoras_bpPlmvDQtp_OvybeGO-fZ</t>
+  </si>
+  <si>
+    <t>co_editors_in_chief_jamie_pearce_Gv5c4MKP52JSymK4gxS0n</t>
+  </si>
+  <si>
     <t>cjs_editors_U1I7oiMEf4YobxQvMtqat</t>
   </si>
   <si>
-    <t>co_editors_co_editoras_bpPlmvDQtp_OvybeGO-fZ</t>
-  </si>
-  <si>
-    <t>co_editors_in_chief_jamie_pearce_Gv5c4MKP52JSymK4gxS0n</t>
-  </si>
-  <si>
     <t>coasts_editorial_office_qs6SBPqBORgK4RXemeZAI</t>
   </si>
   <si>
+    <t>coeditora_qFP-WfMhsWTkwkdGacj6c</t>
+  </si>
+  <si>
     <t>coeditor_ba7V6C-Ghl47Nq_6KzmBw</t>
   </si>
   <si>
-    <t>coeditora_qFP-WfMhsWTkwkdGacj6c</t>
+    <t>ana_marusic_Eh549tTojsl-sqgW0dIhT</t>
+  </si>
+  <si>
+    <t>comision_editorial_8BnvukwZy9u-6so0LH9ux</t>
+  </si>
+  <si>
+    <t>comissao_comissao_editorial_GE63IehJ7-69M-y8FJ5SH</t>
   </si>
   <si>
     <t>autores_varios_wQWgqpXnbVLMBbtxtJDZu</t>
   </si>
   <si>
+    <t>columbus_balbo_review_editorial_board_MJJHgTHfFX5l8j5-LrnAz</t>
+  </si>
+  <si>
     <t>columbus_balbo_editorial_board_DbWrbjR38kEgienDOyk-H</t>
   </si>
   <si>
-    <t>comision_editorial_8BnvukwZy9u-6so0LH9ux</t>
-  </si>
-  <si>
-    <t>comissao_comissao_editorial_GE63IehJ7-69M-y8FJ5SH</t>
-  </si>
-  <si>
-    <t>columbus_balbo_review_editorial_board_MJJHgTHfFX5l8j5-LrnAz</t>
+    <t>comissao_editorial_rbhe_LmeskWKasL0OI-4PAbxXi</t>
+  </si>
+  <si>
+    <t>comissao_editorial_rbhe_TbjaoQ8MlPBlVnnyvdPfc</t>
   </si>
   <si>
     <t>comissao_editorial_do_boletim_geografico_do_rio_grande_do_sul_XF4SX15yzGExvqoQqLRZt</t>
   </si>
   <si>
+    <t>comissao_editorial_rbhe_hdGAQTA3qnJWMKF4pt-MQ</t>
+  </si>
+  <si>
+    <t>comissao_editorial_rbhe_tKnxmoJ2HhDzO7Jlackpb</t>
+  </si>
+  <si>
+    <t>comissao_editorial_revista_horizontes_nedM26KnYZYh9KbtR_y8X</t>
+  </si>
+  <si>
+    <t>comitato_di_redazione_icc_icc_editorial_board_edited_by__MamzfCLhnBuMNHU50oVen</t>
+  </si>
+  <si>
+    <t>comitato_editoriale_HBXiq_rys0j78M59RQ9Cv</t>
+  </si>
+  <si>
+    <t>comite_comite_editorial_fM95p8EFfd9AJHA3Ve3zI</t>
+  </si>
+  <si>
+    <t>comite_editoral_tnyU32x-yYxwvLcLAYZ8F</t>
+  </si>
+  <si>
     <t>comissao_editorial_rbhe_9hZzNokYUlnNdA6T4QNyu</t>
   </si>
   <si>
-    <t>comissao_editorial_rbhe_LmeskWKasL0OI-4PAbxXi</t>
-  </si>
-  <si>
-    <t>comissao_editorial_rbhe_TbjaoQ8MlPBlVnnyvdPfc</t>
+    <t>comite_editorial_atoz_RvE3qVXREO2pZp4qii2DD</t>
+  </si>
+  <si>
+    <t>comite_editorial_cec_2mnGa06gxu_TuglAr8Dpz</t>
+  </si>
+  <si>
+    <t>comite_editorial_de_encrucijadas_KCP1q_tBrSKmtH0MhiZc6</t>
+  </si>
+  <si>
+    <t>comite_editorial_de_la_revista_de_artes_y_humanidades_unica_Sb-cjKKdQFAHkzScIxapA</t>
+  </si>
+  <si>
+    <t>comite_editorial_do_anuario_antropologico_TN_W0xKoMdk6jGo83dARq</t>
+  </si>
+  <si>
+    <t>comite_editorial_encrucijadas_m4_BGMhIvyhlNtSq9qZ3i</t>
+  </si>
+  <si>
+    <t>comissao_editorial_rbhe__TY5hQ_b9HEvGuIBjHnOJj</t>
+  </si>
+  <si>
+    <t>comite_editorial_revista_investigacion_y_postgrado_UTCSYYg7b12C1K89EKs3k</t>
+  </si>
+  <si>
+    <t>comite_editorial_revista_procesos_historicos_vIzarRfZU_ZKdB-uL5cpb</t>
+  </si>
+  <si>
+    <t>comite_editorial_revista_sociedad_y_economia_nwph-GoXSiOjVvPjEPRQD</t>
+  </si>
+  <si>
+    <t>comite_editorial_trazos_xEmnvlTkfWv29LJZ9ksei</t>
+  </si>
+  <si>
+    <t>consejo_editorial_8FjKE8lNzlLc6tJdg-FhI</t>
+  </si>
+  <si>
+    <t>consejo_editorial_consejo_editorial_sRpxaGtozOuVJumDlfIjg</t>
+  </si>
+  <si>
+    <t>comite_editorial_comite_editorial_FQsqpVJqW3jP1Q3VhcR5v</t>
   </si>
   <si>
     <t>comissao_editorial_B0xBSjMkfSw2jnlTRLi9o</t>
   </si>
   <si>
-    <t>comissao_editorial_rbhe__TY5hQ_b9HEvGuIBjHnOJj</t>
-  </si>
-  <si>
-    <t>comissao_editorial_rbhe_hdGAQTA3qnJWMKF4pt-MQ</t>
-  </si>
-  <si>
-    <t>comissao_editorial_rbhe_tKnxmoJ2HhDzO7Jlackpb</t>
-  </si>
-  <si>
-    <t>comissao_editorial_revista_horizontes_nedM26KnYZYh9KbtR_y8X</t>
-  </si>
-  <si>
-    <t>comitato_di_redazione_icc_icc_editorial_board_edited_by__MamzfCLhnBuMNHU50oVen</t>
-  </si>
-  <si>
-    <t>comitato_editoriale_HBXiq_rys0j78M59RQ9Cv</t>
-  </si>
-  <si>
-    <t>comite_comite_editorial_fM95p8EFfd9AJHA3Ve3zI</t>
-  </si>
-  <si>
-    <t>comite_editoral_tnyU32x-yYxwvLcLAYZ8F</t>
-  </si>
-  <si>
-    <t>comite_editorial_cec_2mnGa06gxu_TuglAr8Dpz</t>
-  </si>
-  <si>
-    <t>comite_editorial_atoz_RvE3qVXREO2pZp4qii2DD</t>
-  </si>
-  <si>
-    <t>comite_editorial_de_encrucijadas_KCP1q_tBrSKmtH0MhiZc6</t>
-  </si>
-  <si>
-    <t>comite_editorial_de_la_revista_de_artes_y_humanidades_unica_Sb-cjKKdQFAHkzScIxapA</t>
-  </si>
-  <si>
-    <t>comite_editorial_do_anuario_antropologico_TN_W0xKoMdk6jGo83dARq</t>
-  </si>
-  <si>
-    <t>comite_editorial_encrucijadas_m4_BGMhIvyhlNtSq9qZ3i</t>
-  </si>
-  <si>
-    <t>comite_editorial_comite_editorial_FQsqpVJqW3jP1Q3VhcR5v</t>
-  </si>
-  <si>
-    <t>comite_editorial_revista_investigacion_y_postgrado_UTCSYYg7b12C1K89EKs3k</t>
-  </si>
-  <si>
-    <t>comite_editorial_revista_procesos_historicos_vIzarRfZU_ZKdB-uL5cpb</t>
-  </si>
-  <si>
-    <t>comite_editorial_revista_sociedad_y_economia_nwph-GoXSiOjVvPjEPRQD</t>
-  </si>
-  <si>
-    <t>comite_editorial_trazos_xEmnvlTkfWv29LJZ9ksei</t>
-  </si>
-  <si>
-    <t>consejo_editorial_8FjKE8lNzlLc6tJdg-FhI</t>
-  </si>
-  <si>
-    <t>consejo_editorial_consejo_editorial_sRpxaGtozOuVJumDlfIjg</t>
-  </si>
-  <si>
-    <t>a_marusic_rEjPQkkupEEbkkkGEu_oU</t>
+    <t>conselho_editorail_AgoFeg_1RWIPqlwEMupka</t>
+  </si>
+  <si>
+    <t>consejo_editorial_cuaderno_de_pedagogia_universitaria_IUk5Uu-0PEaaW64G4r99H</t>
+  </si>
+  <si>
+    <t>conselho_editorial_WUcZheBXidwVF9WvE7T_L</t>
   </si>
   <si>
     <t>consejo_editorial_cuaderno_de_pedagogia_universitaria_3SqCnKpsRkK7zJOfS7z8Y</t>
   </si>
   <si>
-    <t>consejo_editorial_cuaderno_de_pedagogia_universitaria_IUk5Uu-0PEaaW64G4r99H</t>
-  </si>
-  <si>
-    <t>conselho_editorail_AgoFeg_1RWIPqlwEMupka</t>
-  </si>
-  <si>
-    <t>conselho_editorial_WUcZheBXidwVF9WvE7T_L</t>
+    <t>conselhoeditorial_vGpD57mzBKj8pkto2bYls</t>
+  </si>
+  <si>
+    <t>consell_editorial_R8FKn_ghst8IQEIZT1Aex</t>
+  </si>
+  <si>
+    <t>consiliul_editorial_gEJNpJO1nI1dHGpsgQ26r</t>
+  </si>
+  <si>
+    <t>consiliul_editorial_oh_rm_4ysA4aU6Fg_tc2Tw5CEqb</t>
+  </si>
+  <si>
+    <t>contracampo_editorial_7QBbHVdlRt9yrHhOPeRJD</t>
+  </si>
+  <si>
+    <t>conselho_editorial_sequencia_aTpRXemLMNjvfsPFyUEmo</t>
   </si>
   <si>
     <t>conselho_editorial_0M7amGVs-n55v8h8e0Ar9</t>
   </si>
   <si>
-    <t>conselho_editorial_sequencia_aTpRXemLMNjvfsPFyUEmo</t>
-  </si>
-  <si>
-    <t>conselhoeditorial_vGpD57mzBKj8pkto2bYls</t>
-  </si>
-  <si>
-    <t>consell_editorial_R8FKn_ghst8IQEIZT1Aex</t>
-  </si>
-  <si>
-    <t>consiliul_editorial_oh_rm_4ysA4aU6Fg_tc2Tw5CEqb</t>
-  </si>
-  <si>
-    <t>consiliul_editorial_gEJNpJO1nI1dHGpsgQ26r</t>
-  </si>
-  <si>
-    <t>contracampo_editorial_7QBbHVdlRt9yrHhOPeRJD</t>
-  </si>
-  <si>
     <t>corpo_editorial_nanduty_dLuaZXYPOc-hy3UDLjisU</t>
   </si>
   <si>
+    <t>cover_editorial_team_LnrigFFcH4JzhZUcdnZk5</t>
+  </si>
+  <si>
+    <t>cristina_hurtado_editora__o_e6V3iKxJVf_NXiYEuC5</t>
+  </si>
+  <si>
     <t>coordinacion_editorial_5LA8v_L9_bIP3jM-4na3U</t>
   </si>
   <si>
-    <t>cover_editorial_team_LnrigFFcH4JzhZUcdnZk5</t>
-  </si>
-  <si>
-    <t>cristina_hurtado_editora__o_e6V3iKxJVf_NXiYEuC5</t>
-  </si>
-  <si>
     <t>cuerpo_editorial_revista_criterio_libre_UB_398goUDB9ETXuY8ybM</t>
   </si>
   <si>
+    <t>de_l_amenagement_du_territoire_et_du_developpement_durable_ministere_de_l_equipement_FETX70BM-PACamvy9PmDB</t>
+  </si>
+  <si>
+    <t>dee_ann_vibbert_n2IYfCJdJhsf_QvWv45f6</t>
+  </si>
+  <si>
+    <t>data_editorial_office_Be639vdijo4l2KyRuHh2R</t>
+  </si>
+  <si>
+    <t>della_resistenza_e_della_societa_italiana_fra_le_due_guerre_carmelo_albanese_ha_conseguito_il_titolo_di_dottore_di_ricerca_in_storia_contemporanea_all_universita_di_firenze_con_una_tesi_sulla_lotta_politica_in_sicilia_in_eta_giolittiana_ideg_premio_spadolini_nuova_antologia_xviii_edizione_interessato_ai_temi_dell_antifascismo_yhp9rKwC6-2T-MOz4ZtAD</t>
+  </si>
+  <si>
+    <t>departement_de_pediatrie_dans_le_cadre_du_cours_post_universitaire_O2l80_OrXLYkiFyo8sQKH</t>
+  </si>
+  <si>
+    <t>devonshire_manuscript_editorial_group_EN_FsREIzN-WEozc1Neyh</t>
+  </si>
+  <si>
+    <t>dhlabeditor_kDZHm8NHulx_YLXSKZ3IV</t>
+  </si>
+  <si>
     <t>corpo_editorial_wFIb11fRHWCiWUzFs2T-V</t>
   </si>
   <si>
-    <t>data_editorial_office_Be639vdijo4l2KyRuHh2R</t>
-  </si>
-  <si>
-    <t>ana_marusic_Eh549tTojsl-sqgW0dIhT</t>
-  </si>
-  <si>
-    <t>de_l_amenagement_du_territoire_et_du_developpement_durable_ministere_de_l_equipement_FETX70BM-PACamvy9PmDB</t>
-  </si>
-  <si>
-    <t>dee_ann_vibbert_n2IYfCJdJhsf_QvWv45f6</t>
-  </si>
-  <si>
-    <t>della_resistenza_e_della_societa_italiana_fra_le_due_guerre_carmelo_albanese_ha_conseguito_il_titolo_di_dottore_di_ricerca_in_storia_contemporanea_all_universita_di_firenze_con_una_tesi_sulla_lotta_politica_in_sicilia_in_eta_giolittiana_ideg_premio_spadolini_nuova_antologia_xviii_edizione_interessato_ai_temi_dell_antifascismo_yhp9rKwC6-2T-MOz4ZtAD</t>
-  </si>
-  <si>
-    <t>departement_de_pediatrie_dans_le_cadre_du_cours_post_universitaire_O2l80_OrXLYkiFyo8sQKH</t>
-  </si>
-  <si>
-    <t>devonshire_manuscript_editorial_group_EN_FsREIzN-WEozc1Neyh</t>
-  </si>
-  <si>
-    <t>dhlabeditor_kDZHm8NHulx_YLXSKZ3IV</t>
-  </si>
-  <si>
     <t>diana_editors_marinova_J7uRxHIEgqUNcgH5Qrw3I</t>
   </si>
   <si>
@@ -4552,21 +4552,21 @@
     <t>diretrizes_para_autores_2AsxCyUFV8bW8TzDmfgi-</t>
   </si>
   <si>
+    <t>dont_equipe_medios__JaJqmWVZam2CXnEqQennH</t>
+  </si>
+  <si>
+    <t>dicta_editorial_board_K35WtYOGxxG5o2pl0G7q8</t>
+  </si>
+  <si>
     <t>dicta_editorial_board_1QFNllFxjxv2qJQ1oDx_7</t>
   </si>
   <si>
-    <t>dicta_editorial_board_K35WtYOGxxG5o2pl0G7q8</t>
-  </si>
-  <si>
-    <t>dont_equipe_medios__JaJqmWVZam2CXnEqQennH</t>
+    <t>dottore_di_ricerca_in_storia_contemporanea_per_l_universitat_autonoma_de_barcelona_e_l_universita_di_bologna_steven_forti_NTgl6tvJ7sh3fCwBscv-d</t>
   </si>
   <si>
     <t>e_autore_oltre_che_di_noti_studi_sulla_storia_della_sicilia_culminati_nel_best_seller_internazionale_storia_della_mafia_roma_giuseppe_carlo_marino_gia_ordinario_di_storia_contemporanea_nell_universita_di_palermo_S_qrihWi3IQei5LdU2Rl1</t>
   </si>
   <si>
-    <t>dottore_di_ricerca_in_storia_contemporanea_per_l_universitat_autonoma_de_barcelona_e_l_universita_di_bologna_steven_forti_NTgl6tvJ7sh3fCwBscv-d</t>
-  </si>
-  <si>
     <t>edinburgh_mat_editorial_collective_qEz3n5GvHrSd8oJ2N0qTO</t>
   </si>
   <si>
@@ -4597,27 +4597,30 @@
     <t>editores_da_albuquerque_revista_de_historia_dUoTEJPU8QlYzIr-KE55Y</t>
   </si>
   <si>
+    <t>editor_editor_ua6RlrPShI4aDybjLs8g1</t>
+  </si>
+  <si>
     <t>editores_da_sisyphus_79Rdkgty3pLCd_4ItoxRv</t>
   </si>
   <si>
+    <t>editores_de_albuquerque_zohWp6bS2keqxhOeno_59</t>
+  </si>
+  <si>
+    <t>editores_de_sisyphus_BjY9ye9f3HjH8oAvI-_WX</t>
+  </si>
+  <si>
+    <t>editores_de_territorios_fronteiras_-lvwjSgTXhT40R56zskWE</t>
+  </si>
+  <si>
+    <t>editores_editores_de_refime_TsgEevKXS0UdWC-nltqaX</t>
+  </si>
+  <si>
+    <t>editores_historia_mexicana_9sMnGo3tmjJqg9-4AT4Jj</t>
+  </si>
+  <si>
     <t>editores_de_albuquerque_revista_de_historia_22h2Yu_36FJZxDvyC_Z5x</t>
   </si>
   <si>
-    <t>editores_de_albuquerque_zohWp6bS2keqxhOeno_59</t>
-  </si>
-  <si>
-    <t>editores_de_sisyphus_BjY9ye9f3HjH8oAvI-_WX</t>
-  </si>
-  <si>
-    <t>editores_de_territorios_fronteiras_-lvwjSgTXhT40R56zskWE</t>
-  </si>
-  <si>
-    <t>editores_editores_de_refime_TsgEevKXS0UdWC-nltqaX</t>
-  </si>
-  <si>
-    <t>editores_historia_mexicana_9sMnGo3tmjJqg9-4AT4Jj</t>
-  </si>
-  <si>
     <t>editor_KdacIFAlcq5FLAbpEuux_</t>
   </si>
   <si>
@@ -4639,33 +4642,30 @@
     <t>editores_tematicos__ymenXR4DIW9AZMacFdQU</t>
   </si>
   <si>
+    <t>editores_vozes_e_dialogo_zIWU9rYmrrXcE9KUDWJLV</t>
+  </si>
+  <si>
+    <t>editori_riuniti_university_press_lorenzo_kamel_is_a_phd_candidate_at_alma_mater_studiorum_university_of_bologna_he_obtained_a_b_a_and_m_a_in_philosophy_from_la_sapienza_university_of_rome_and_a_m_a_in_social_sciences_at_the_hebrew_university_of_jerusalem_he_is_the_author_of_many_academic_articles_and_of_two_books_l_alternativa_roma_cYT3Z2xib6bgUGhKxNaSC</t>
+  </si>
+  <si>
+    <t>editoria_executiva_xxbniQ1g_23YniS6SM8SH</t>
+  </si>
+  <si>
+    <t>editoria_da_carta_internacional_Hl5HCbKqXZit8gks0kcr0</t>
+  </si>
+  <si>
+    <t>editoria_geral_y_tBv_eebCqxMGUsk07Tq</t>
+  </si>
+  <si>
+    <t>editoria_mlbvHxRjBTy4CWSoNKX5P</t>
+  </si>
+  <si>
+    <t>editoria_movimento_revista_de_educacao_0lLfqDjBWWjSx3rMlkdyz</t>
+  </si>
+  <si>
     <t>editores_interthesis_az6wznbwejO6dZwIV-c6G</t>
   </si>
   <si>
-    <t>editores_vozes_e_dialogo_zIWU9rYmrrXcE9KUDWJLV</t>
-  </si>
-  <si>
-    <t>editori_riuniti_university_press_lorenzo_kamel_is_a_phd_candidate_at_alma_mater_studiorum_university_of_bologna_he_obtained_a_b_a_and_m_a_in_philosophy_from_la_sapienza_university_of_rome_and_a_m_a_in_social_sciences_at_the_hebrew_university_of_jerusalem_he_is_the_author_of_many_academic_articles_and_of_two_books_l_alternativa_roma_cYT3Z2xib6bgUGhKxNaSC</t>
-  </si>
-  <si>
-    <t>editor_editor_ua6RlrPShI4aDybjLs8g1</t>
-  </si>
-  <si>
-    <t>editoria_executiva_xxbniQ1g_23YniS6SM8SH</t>
-  </si>
-  <si>
-    <t>editoria_da_carta_internacional_Hl5HCbKqXZit8gks0kcr0</t>
-  </si>
-  <si>
-    <t>editoria_geral_y_tBv_eebCqxMGUsk07Tq</t>
-  </si>
-  <si>
-    <t>editoria_mlbvHxRjBTy4CWSoNKX5P</t>
-  </si>
-  <si>
-    <t>editoria_movimento_revista_de_educacao_0lLfqDjBWWjSx3rMlkdyz</t>
-  </si>
-  <si>
     <t>editoria_rbpec_RIgmYILXP_cdkqPq-Mb9F</t>
   </si>
   <si>
@@ -4726,18 +4726,18 @@
     <t>editorial_article_wIz2mq6yiWM-y00oNf04o</t>
   </si>
   <si>
+    <t>editorial_catalana_PDsEGVlzKEPX9CyB2pCOL</t>
+  </si>
+  <si>
+    <t>editorial_comite_zA8Gjj_53JZQRQ-TcldEG</t>
+  </si>
+  <si>
     <t>editorial_collective_1KHKIzKNbq8AtGgavYkLO</t>
   </si>
   <si>
-    <t>editorial_comite_zA8Gjj_53JZQRQ-TcldEG</t>
-  </si>
-  <si>
     <t>editorial_comments_and_symposium_info_editorial_team_cCFkFZ8PMheSQMJKflhyG</t>
   </si>
   <si>
-    <t>editorial_catalana_PDsEGVlzKEPX9CyB2pCOL</t>
-  </si>
-  <si>
     <t>editorial_committee_of_the_anuario_antropologico_2t8ZurtwtuUOOpMK0UDbC</t>
   </si>
   <si>
@@ -4777,6 +4777,9 @@
     <t>editorial_information_and_table_of_contents_x3CWsI7Xez4SSvuQXoWme</t>
   </si>
   <si>
+    <t>editorial_group_nososco_jneaj2xaeRVHUnh_i1NaK</t>
+  </si>
+  <si>
     <t>editorial_journal_of_asean_studies_HLqRlBrgjooSraJsYlOf5</t>
   </si>
   <si>
@@ -4786,15 +4789,12 @@
     <t>editorial_neogranadina_RnQGrR2_JV7bNqaVMFBaT</t>
   </si>
   <si>
+    <t>editorial_office_FIPpK7_iuuQ2lkQnHw8KF</t>
+  </si>
+  <si>
     <t>editorial_nuevo_derecho_tvLIAQQEGa3IH4X5pnPyu</t>
   </si>
   <si>
-    <t>editorial_office_FIPpK7_iuuQ2lkQnHw8KF</t>
-  </si>
-  <si>
-    <t>editorial_group_nososco_jneaj2xaeRVHUnh_i1NaK</t>
-  </si>
-  <si>
     <t>editorial_papel_cosido_MR9h9RSWmFiB7M2gietRL</t>
   </si>
   <si>
@@ -4819,46 +4819,46 @@
     <t>editorial_revista_de_urbanismo_XOf2JjGQidAo7UzOtiiEi</t>
   </si>
   <si>
+    <t>editorial_revista_palobra_EunLstwio28_BEVLcYhpW</t>
+  </si>
+  <si>
+    <t>editorial_rppi_tNJlf3XITEEiJEI7L3o4D</t>
+  </si>
+  <si>
+    <t>editorial_staff_OXAyUp6W21vJg8qfbOA9g</t>
+  </si>
+  <si>
     <t>editorial_office_R0jDpcMPUWWJrVUNW7HN_</t>
   </si>
   <si>
-    <t>editorial_revista_palobra_EunLstwio28_BEVLcYhpW</t>
-  </si>
-  <si>
-    <t>editorial_staff_OXAyUp6W21vJg8qfbOA9g</t>
-  </si>
-  <si>
-    <t>editorial_rppi_tNJlf3XITEEiJEI7L3o4D</t>
-  </si>
-  <si>
     <t>editorial_staff_cover_5k5erVq9ao2G7BRHPEwAH</t>
   </si>
   <si>
     <t>editorial_staff_g8sSom_aZmnZOZ88Ds8pQ</t>
   </si>
   <si>
+    <t>editorial_staff_at_elangdell_press_4X-sFAdIRS7zGYnXsKX3U</t>
+  </si>
+  <si>
+    <t>editorial_team_diabetes_mellitus_r3P4fpzz_3EIYFbomlBWN</t>
+  </si>
+  <si>
+    <t>editorial_team_indrastra_global_HVaNp6VIhlF2uG1yOqm7K</t>
+  </si>
+  <si>
+    <t>editorial_team_indrastra_global_RZ99C4A6c7KFG6PBD8J2s</t>
+  </si>
+  <si>
+    <t>editorial_team_jppfa_cfRywELbDC4MHhJ08-LyU</t>
+  </si>
+  <si>
+    <t>editorial_team_militaria_1GBLs1q4OzaRsCkG1ve-S</t>
+  </si>
+  <si>
+    <t>editorial_team_P_R--ZhOnpRyMnUwEKa9d</t>
+  </si>
+  <si>
     <t>comite_editorial_rJyDfGt0I5KJJft4MVW2F</t>
-  </si>
-  <si>
-    <t>editorial_team_diabetes_mellitus_r3P4fpzz_3EIYFbomlBWN</t>
-  </si>
-  <si>
-    <t>editorial_team_indrastra_global_HVaNp6VIhlF2uG1yOqm7K</t>
-  </si>
-  <si>
-    <t>editorial_team_indrastra_global_RZ99C4A6c7KFG6PBD8J2s</t>
-  </si>
-  <si>
-    <t>editorial_team_jppfa_cfRywELbDC4MHhJ08-LyU</t>
-  </si>
-  <si>
-    <t>editorial_team_militaria_1GBLs1q4OzaRsCkG1ve-S</t>
-  </si>
-  <si>
-    <t>editorial_staff_at_elangdell_press_4X-sFAdIRS7zGYnXsKX3U</t>
-  </si>
-  <si>
-    <t>editorial_team_P_R--ZhOnpRyMnUwEKa9d</t>
   </si>
   <si>
     <t>editorial_board_5Id1HM4p1k_zba3Go5ODm</t>
@@ -6147,13 +6147,13 @@
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C30" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -6249,7 +6249,7 @@
         <v>440</v>
       </c>
       <c r="C33" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -6275,13 +6275,13 @@
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B34" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C34" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -6499,13 +6499,13 @@
     </row>
     <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B41" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C41" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -6755,13 +6755,13 @@
     </row>
     <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="B49" t="s">
         <v>453</v>
       </c>
       <c r="C49" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -6787,13 +6787,13 @@
     </row>
     <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B50" t="s">
         <v>454</v>
       </c>
       <c r="C50" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -6819,13 +6819,13 @@
     </row>
     <row r="51" spans="1:12">
       <c r="A51" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="B51" t="s">
         <v>455</v>
       </c>
       <c r="C51" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -6851,13 +6851,13 @@
     </row>
     <row r="52" spans="1:12">
       <c r="A52" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>424</v>
+        <v>456</v>
       </c>
       <c r="C52" t="s">
-        <v>848</v>
+        <v>875</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -6883,13 +6883,13 @@
     </row>
     <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B53" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C53" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -6915,13 +6915,13 @@
     </row>
     <row r="54" spans="1:12">
       <c r="A54" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B54" t="s">
-        <v>457</v>
+        <v>421</v>
       </c>
       <c r="C54" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -6933,7 +6933,7 @@
         <v>1169</v>
       </c>
       <c r="I54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J54" t="b">
         <v>0</v>
@@ -6947,13 +6947,13 @@
     </row>
     <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="B55" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C55" t="s">
-        <v>877</v>
+        <v>847</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -6965,7 +6965,7 @@
         <v>1170</v>
       </c>
       <c r="I55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55" t="b">
         <v>0</v>
@@ -6979,13 +6979,13 @@
     </row>
     <row r="56" spans="1:12">
       <c r="A56" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B56" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C56" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -7011,13 +7011,13 @@
     </row>
     <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B57" t="s">
         <v>454</v>
       </c>
       <c r="C57" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -7075,13 +7075,13 @@
     </row>
     <row r="59" spans="1:12">
       <c r="A59" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B59" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C59" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -7107,13 +7107,13 @@
     </row>
     <row r="60" spans="1:12">
       <c r="A60" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B60" t="s">
         <v>454</v>
       </c>
       <c r="C60" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -7142,10 +7142,10 @@
         <v>61</v>
       </c>
       <c r="B61" t="s">
-        <v>436</v>
+        <v>459</v>
       </c>
       <c r="C61" t="s">
-        <v>860</v>
+        <v>878</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -7157,7 +7157,7 @@
         <v>1176</v>
       </c>
       <c r="I61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J61" t="b">
         <v>0</v>
@@ -7171,13 +7171,13 @@
     </row>
     <row r="62" spans="1:12">
       <c r="A62" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="B62" t="s">
-        <v>459</v>
+        <v>434</v>
       </c>
       <c r="C62" t="s">
-        <v>878</v>
+        <v>858</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -7189,7 +7189,7 @@
         <v>1177</v>
       </c>
       <c r="I62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J62" t="b">
         <v>0</v>
@@ -7203,13 +7203,13 @@
     </row>
     <row r="63" spans="1:12">
       <c r="A63" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="C63" t="s">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -7331,13 +7331,13 @@
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B67" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C67" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -7381,7 +7381,7 @@
         <v>1183</v>
       </c>
       <c r="I68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J68" t="b">
         <v>0</v>
@@ -7465,7 +7465,7 @@
         <v>466</v>
       </c>
       <c r="C71" t="s">
-        <v>851</v>
+        <v>884</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -7497,7 +7497,7 @@
         <v>467</v>
       </c>
       <c r="C72" t="s">
-        <v>884</v>
+        <v>851</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -7561,7 +7561,7 @@
         <v>468</v>
       </c>
       <c r="C74" t="s">
-        <v>872</v>
+        <v>885</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -7593,7 +7593,7 @@
         <v>469</v>
       </c>
       <c r="C75" t="s">
-        <v>852</v>
+        <v>872</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -7619,13 +7619,13 @@
     </row>
     <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>424</v>
+        <v>470</v>
       </c>
       <c r="C76" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -7651,13 +7651,13 @@
     </row>
     <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C77" t="s">
-        <v>885</v>
+        <v>852</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -7669,7 +7669,7 @@
         <v>1192</v>
       </c>
       <c r="I77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J77" t="b">
         <v>0</v>
@@ -7683,13 +7683,13 @@
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>471</v>
+        <v>432</v>
       </c>
       <c r="C78" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -7747,13 +7747,13 @@
     </row>
     <row r="80" spans="1:12">
       <c r="A80" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="B80" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="C80" t="s">
-        <v>856</v>
+        <v>847</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -7817,7 +7817,7 @@
         <v>473</v>
       </c>
       <c r="C82" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -7846,10 +7846,10 @@
         <v>79</v>
       </c>
       <c r="B83" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C83" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -8003,13 +8003,13 @@
     </row>
     <row r="88" spans="1:12">
       <c r="A88" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B88" t="s">
-        <v>419</v>
+        <v>477</v>
       </c>
       <c r="C88" t="s">
-        <v>843</v>
+        <v>887</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -8035,13 +8035,13 @@
     </row>
     <row r="89" spans="1:12">
       <c r="A89" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B89" t="s">
-        <v>477</v>
+        <v>418</v>
       </c>
       <c r="C89" t="s">
-        <v>887</v>
+        <v>842</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -8067,7 +8067,7 @@
     </row>
     <row r="90" spans="1:12">
       <c r="A90" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B90" t="s">
         <v>478</v>
@@ -8195,13 +8195,13 @@
     </row>
     <row r="94" spans="1:12">
       <c r="A94" t="s">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="B94" t="s">
         <v>481</v>
       </c>
       <c r="C94" t="s">
-        <v>889</v>
+        <v>865</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -8227,13 +8227,13 @@
     </row>
     <row r="95" spans="1:12">
       <c r="A95" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="B95" t="s">
         <v>482</v>
       </c>
       <c r="C95" t="s">
-        <v>865</v>
+        <v>889</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -8355,13 +8355,13 @@
     </row>
     <row r="99" spans="1:12">
       <c r="A99" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="B99" t="s">
         <v>485</v>
       </c>
       <c r="C99" t="s">
-        <v>852</v>
+        <v>846</v>
       </c>
       <c r="D99">
         <v>0</v>
@@ -8387,13 +8387,13 @@
     </row>
     <row r="100" spans="1:12">
       <c r="A100" t="s">
-        <v>88</v>
+        <v>27</v>
       </c>
       <c r="B100" t="s">
         <v>486</v>
       </c>
       <c r="C100" t="s">
-        <v>847</v>
+        <v>852</v>
       </c>
       <c r="D100">
         <v>0</v>
@@ -8486,10 +8486,10 @@
         <v>90</v>
       </c>
       <c r="B103" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C103" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="D103">
         <v>0</v>
@@ -8547,13 +8547,13 @@
     </row>
     <row r="105" spans="1:12">
       <c r="A105" t="s">
-        <v>33</v>
+        <v>92</v>
       </c>
       <c r="B105" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="C105" t="s">
-        <v>855</v>
+        <v>893</v>
       </c>
       <c r="D105">
         <v>0</v>
@@ -8565,7 +8565,7 @@
         <v>1220</v>
       </c>
       <c r="I105">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J105" t="b">
         <v>0</v>
@@ -8579,13 +8579,13 @@
     </row>
     <row r="106" spans="1:12">
       <c r="A106" t="s">
-        <v>92</v>
+        <v>36</v>
       </c>
       <c r="B106" t="s">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="C106" t="s">
-        <v>893</v>
+        <v>858</v>
       </c>
       <c r="D106">
         <v>0</v>
@@ -8597,7 +8597,7 @@
         <v>1221</v>
       </c>
       <c r="I106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J106" t="b">
         <v>0</v>
@@ -8675,13 +8675,13 @@
     </row>
     <row r="109" spans="1:12">
       <c r="A109" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B109" t="s">
         <v>454</v>
       </c>
       <c r="C109" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="D109">
         <v>0</v>
@@ -8806,10 +8806,10 @@
         <v>97</v>
       </c>
       <c r="B113" t="s">
-        <v>434</v>
+        <v>493</v>
       </c>
       <c r="C113" t="s">
-        <v>858</v>
+        <v>897</v>
       </c>
       <c r="D113">
         <v>0</v>
@@ -8838,10 +8838,10 @@
         <v>98</v>
       </c>
       <c r="B114" t="s">
-        <v>493</v>
+        <v>433</v>
       </c>
       <c r="C114" t="s">
-        <v>897</v>
+        <v>857</v>
       </c>
       <c r="D114">
         <v>0</v>
@@ -8867,13 +8867,13 @@
     </row>
     <row r="115" spans="1:12">
       <c r="A115" t="s">
-        <v>99</v>
+        <v>23</v>
       </c>
       <c r="B115" t="s">
-        <v>494</v>
+        <v>423</v>
       </c>
       <c r="C115" t="s">
-        <v>898</v>
+        <v>847</v>
       </c>
       <c r="D115">
         <v>0</v>
@@ -8899,13 +8899,13 @@
     </row>
     <row r="116" spans="1:12">
       <c r="A116" t="s">
-        <v>24</v>
+        <v>95</v>
       </c>
       <c r="B116" t="s">
-        <v>424</v>
+        <v>462</v>
       </c>
       <c r="C116" t="s">
-        <v>848</v>
+        <v>880</v>
       </c>
       <c r="D116">
         <v>0</v>
@@ -8931,13 +8931,13 @@
     </row>
     <row r="117" spans="1:12">
       <c r="A117" t="s">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="B117" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="C117" t="s">
-        <v>880</v>
+        <v>873</v>
       </c>
       <c r="D117">
         <v>0</v>
@@ -8963,13 +8963,13 @@
     </row>
     <row r="118" spans="1:12">
       <c r="A118" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
       <c r="B118" t="s">
-        <v>454</v>
+        <v>421</v>
       </c>
       <c r="C118" t="s">
-        <v>874</v>
+        <v>898</v>
       </c>
       <c r="D118">
         <v>0</v>
@@ -8981,7 +8981,7 @@
         <v>1233</v>
       </c>
       <c r="I118">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J118" t="b">
         <v>0</v>
@@ -8995,13 +8995,13 @@
     </row>
     <row r="119" spans="1:12">
       <c r="A119" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="B119" t="s">
         <v>421</v>
       </c>
       <c r="C119" t="s">
-        <v>899</v>
+        <v>851</v>
       </c>
       <c r="D119">
         <v>0</v>
@@ -9027,13 +9027,13 @@
     </row>
     <row r="120" spans="1:12">
       <c r="A120" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="B120" t="s">
-        <v>421</v>
+        <v>494</v>
       </c>
       <c r="C120" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="D120">
         <v>0</v>
@@ -9045,7 +9045,7 @@
         <v>1235</v>
       </c>
       <c r="I120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J120" t="b">
         <v>0</v>
@@ -9065,7 +9065,7 @@
         <v>495</v>
       </c>
       <c r="C121" t="s">
-        <v>850</v>
+        <v>899</v>
       </c>
       <c r="D121">
         <v>0</v>
@@ -9129,7 +9129,7 @@
         <v>497</v>
       </c>
       <c r="C123" t="s">
-        <v>852</v>
+        <v>901</v>
       </c>
       <c r="D123">
         <v>0</v>
@@ -9161,7 +9161,7 @@
         <v>498</v>
       </c>
       <c r="C124" t="s">
-        <v>851</v>
+        <v>897</v>
       </c>
       <c r="D124">
         <v>0</v>
@@ -9173,7 +9173,7 @@
         <v>1239</v>
       </c>
       <c r="I124">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J124" t="b">
         <v>0</v>
@@ -9190,10 +9190,10 @@
         <v>105</v>
       </c>
       <c r="B125" t="s">
-        <v>421</v>
+        <v>499</v>
       </c>
       <c r="C125" t="s">
-        <v>901</v>
+        <v>852</v>
       </c>
       <c r="D125">
         <v>0</v>
@@ -9205,7 +9205,7 @@
         <v>1240</v>
       </c>
       <c r="I125">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J125" t="b">
         <v>0</v>
@@ -9222,7 +9222,7 @@
         <v>106</v>
       </c>
       <c r="B126" t="s">
-        <v>499</v>
+        <v>421</v>
       </c>
       <c r="C126" t="s">
         <v>902</v>
@@ -9237,7 +9237,7 @@
         <v>1241</v>
       </c>
       <c r="I126">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J126" t="b">
         <v>0</v>
@@ -9257,7 +9257,7 @@
         <v>500</v>
       </c>
       <c r="C127" t="s">
-        <v>903</v>
+        <v>851</v>
       </c>
       <c r="D127">
         <v>0</v>
@@ -9289,7 +9289,7 @@
         <v>501</v>
       </c>
       <c r="C128" t="s">
-        <v>897</v>
+        <v>903</v>
       </c>
       <c r="D128">
         <v>0</v>
@@ -9301,7 +9301,7 @@
         <v>1243</v>
       </c>
       <c r="I128">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J128" t="b">
         <v>0</v>
@@ -9315,10 +9315,10 @@
     </row>
     <row r="129" spans="1:12">
       <c r="A129" t="s">
-        <v>55</v>
+        <v>109</v>
       </c>
       <c r="B129" t="s">
-        <v>502</v>
+        <v>421</v>
       </c>
       <c r="C129" t="s">
         <v>852</v>
@@ -9333,7 +9333,7 @@
         <v>1244</v>
       </c>
       <c r="I129">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J129" t="b">
         <v>0</v>
@@ -9347,10 +9347,10 @@
     </row>
     <row r="130" spans="1:12">
       <c r="A130" t="s">
-        <v>109</v>
+        <v>53</v>
       </c>
       <c r="B130" t="s">
-        <v>421</v>
+        <v>502</v>
       </c>
       <c r="C130" t="s">
         <v>852</v>
@@ -9365,7 +9365,7 @@
         <v>1245</v>
       </c>
       <c r="I130">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J130" t="b">
         <v>0</v>
@@ -9385,7 +9385,7 @@
         <v>503</v>
       </c>
       <c r="C131" t="s">
-        <v>851</v>
+        <v>904</v>
       </c>
       <c r="D131">
         <v>0</v>
@@ -9411,13 +9411,13 @@
     </row>
     <row r="132" spans="1:12">
       <c r="A132" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="B132" t="s">
-        <v>462</v>
+        <v>504</v>
       </c>
       <c r="C132" t="s">
-        <v>880</v>
+        <v>851</v>
       </c>
       <c r="D132">
         <v>0</v>
@@ -9443,13 +9443,13 @@
     </row>
     <row r="133" spans="1:12">
       <c r="A133" t="s">
-        <v>111</v>
+        <v>36</v>
       </c>
       <c r="B133" t="s">
-        <v>504</v>
+        <v>434</v>
       </c>
       <c r="C133" t="s">
-        <v>904</v>
+        <v>858</v>
       </c>
       <c r="D133">
         <v>0</v>
@@ -9507,13 +9507,13 @@
     </row>
     <row r="135" spans="1:12">
       <c r="A135" t="s">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="B135" t="s">
-        <v>431</v>
+        <v>462</v>
       </c>
       <c r="C135" t="s">
-        <v>855</v>
+        <v>880</v>
       </c>
       <c r="D135">
         <v>0</v>
@@ -9571,13 +9571,13 @@
     </row>
     <row r="137" spans="1:12">
       <c r="A137" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B137" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C137" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="D137">
         <v>0</v>
@@ -9667,13 +9667,13 @@
     </row>
     <row r="140" spans="1:12">
       <c r="A140" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="B140" t="s">
-        <v>462</v>
+        <v>509</v>
       </c>
       <c r="C140" t="s">
-        <v>880</v>
+        <v>902</v>
       </c>
       <c r="D140">
         <v>0</v>
@@ -9699,13 +9699,13 @@
     </row>
     <row r="141" spans="1:12">
       <c r="A141" t="s">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="B141" t="s">
-        <v>509</v>
+        <v>462</v>
       </c>
       <c r="C141" t="s">
-        <v>909</v>
+        <v>880</v>
       </c>
       <c r="D141">
         <v>0</v>
@@ -9731,13 +9731,13 @@
     </row>
     <row r="142" spans="1:12">
       <c r="A142" t="s">
-        <v>27</v>
+        <v>116</v>
       </c>
       <c r="B142" t="s">
         <v>510</v>
       </c>
       <c r="C142" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="D142">
         <v>0</v>
@@ -9763,13 +9763,13 @@
     </row>
     <row r="143" spans="1:12">
       <c r="A143" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B143" t="s">
         <v>511</v>
       </c>
       <c r="C143" t="s">
-        <v>901</v>
+        <v>842</v>
       </c>
       <c r="D143">
         <v>0</v>
@@ -9795,13 +9795,13 @@
     </row>
     <row r="144" spans="1:12">
       <c r="A144" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="B144" t="s">
-        <v>454</v>
+        <v>512</v>
       </c>
       <c r="C144" t="s">
-        <v>874</v>
+        <v>910</v>
       </c>
       <c r="D144">
         <v>0</v>
@@ -9827,13 +9827,13 @@
     </row>
     <row r="145" spans="1:12">
       <c r="A145" t="s">
-        <v>50</v>
+        <v>118</v>
       </c>
       <c r="B145" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C145" t="s">
-        <v>868</v>
+        <v>911</v>
       </c>
       <c r="D145">
         <v>0</v>
@@ -9859,13 +9859,13 @@
     </row>
     <row r="146" spans="1:12">
       <c r="A146" t="s">
-        <v>117</v>
+        <v>55</v>
       </c>
       <c r="B146" t="s">
-        <v>513</v>
+        <v>454</v>
       </c>
       <c r="C146" t="s">
-        <v>843</v>
+        <v>873</v>
       </c>
       <c r="D146">
         <v>0</v>
@@ -9891,13 +9891,13 @@
     </row>
     <row r="147" spans="1:12">
       <c r="A147" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B147" t="s">
         <v>514</v>
       </c>
       <c r="C147" t="s">
-        <v>911</v>
+        <v>868</v>
       </c>
       <c r="D147">
         <v>0</v>
@@ -9923,7 +9923,7 @@
     </row>
     <row r="148" spans="1:12">
       <c r="A148" t="s">
-        <v>118</v>
+        <v>53</v>
       </c>
       <c r="B148" t="s">
         <v>515</v>
@@ -9955,13 +9955,13 @@
     </row>
     <row r="149" spans="1:12">
       <c r="A149" t="s">
-        <v>56</v>
+        <v>119</v>
       </c>
       <c r="B149" t="s">
-        <v>454</v>
+        <v>516</v>
       </c>
       <c r="C149" t="s">
-        <v>874</v>
+        <v>913</v>
       </c>
       <c r="D149">
         <v>0</v>
@@ -9987,13 +9987,13 @@
     </row>
     <row r="150" spans="1:12">
       <c r="A150" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="B150" t="s">
-        <v>436</v>
+        <v>454</v>
       </c>
       <c r="C150" t="s">
-        <v>860</v>
+        <v>873</v>
       </c>
       <c r="D150">
         <v>0</v>
@@ -10019,13 +10019,13 @@
     </row>
     <row r="151" spans="1:12">
       <c r="A151" t="s">
-        <v>119</v>
+        <v>38</v>
       </c>
       <c r="B151" t="s">
-        <v>516</v>
+        <v>436</v>
       </c>
       <c r="C151" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="D151">
         <v>0</v>
@@ -10051,13 +10051,13 @@
     </row>
     <row r="152" spans="1:12">
       <c r="A152" t="s">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="B152" t="s">
         <v>517</v>
       </c>
       <c r="C152" t="s">
-        <v>913</v>
+        <v>851</v>
       </c>
       <c r="D152">
         <v>0</v>
@@ -10083,13 +10083,13 @@
     </row>
     <row r="153" spans="1:12">
       <c r="A153" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="B153" t="s">
         <v>518</v>
       </c>
       <c r="C153" t="s">
-        <v>865</v>
+        <v>856</v>
       </c>
       <c r="D153">
         <v>0</v>
@@ -10115,13 +10115,13 @@
     </row>
     <row r="154" spans="1:12">
       <c r="A154" t="s">
-        <v>51</v>
+        <v>121</v>
       </c>
       <c r="B154" t="s">
-        <v>484</v>
+        <v>519</v>
       </c>
       <c r="C154" t="s">
-        <v>890</v>
+        <v>914</v>
       </c>
       <c r="D154">
         <v>0</v>
@@ -10147,13 +10147,13 @@
     </row>
     <row r="155" spans="1:12">
       <c r="A155" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="B155" t="s">
-        <v>519</v>
+        <v>484</v>
       </c>
       <c r="C155" t="s">
-        <v>903</v>
+        <v>890</v>
       </c>
       <c r="D155">
         <v>0</v>
@@ -10179,13 +10179,13 @@
     </row>
     <row r="156" spans="1:12">
       <c r="A156" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="B156" t="s">
         <v>520</v>
       </c>
       <c r="C156" t="s">
-        <v>851</v>
+        <v>901</v>
       </c>
       <c r="D156">
         <v>0</v>
@@ -10211,13 +10211,13 @@
     </row>
     <row r="157" spans="1:12">
       <c r="A157" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="B157" t="s">
         <v>521</v>
       </c>
       <c r="C157" t="s">
-        <v>914</v>
+        <v>865</v>
       </c>
       <c r="D157">
         <v>0</v>
@@ -10275,13 +10275,13 @@
     </row>
     <row r="159" spans="1:12">
       <c r="A159" t="s">
-        <v>39</v>
+        <v>123</v>
       </c>
       <c r="B159" t="s">
         <v>523</v>
       </c>
       <c r="C159" t="s">
-        <v>916</v>
+        <v>889</v>
       </c>
       <c r="D159">
         <v>0</v>
@@ -10293,7 +10293,7 @@
         <v>1274</v>
       </c>
       <c r="I159">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J159" t="b">
         <v>0</v>
@@ -10339,13 +10339,13 @@
     </row>
     <row r="161" spans="1:12">
       <c r="A161" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="B161" t="s">
-        <v>525</v>
+        <v>485</v>
       </c>
       <c r="C161" t="s">
-        <v>852</v>
+        <v>846</v>
       </c>
       <c r="D161">
         <v>0</v>
@@ -10371,13 +10371,13 @@
     </row>
     <row r="162" spans="1:12">
       <c r="A162" t="s">
-        <v>123</v>
+        <v>24</v>
       </c>
       <c r="B162" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C162" t="s">
-        <v>889</v>
+        <v>852</v>
       </c>
       <c r="D162">
         <v>0</v>
@@ -10403,13 +10403,13 @@
     </row>
     <row r="163" spans="1:12">
       <c r="A163" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B163" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C163" t="s">
-        <v>849</v>
+        <v>916</v>
       </c>
       <c r="D163">
         <v>0</v>
@@ -10421,7 +10421,7 @@
         <v>1278</v>
       </c>
       <c r="I163">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J163" t="b">
         <v>0</v>
@@ -10435,13 +10435,13 @@
     </row>
     <row r="164" spans="1:12">
       <c r="A164" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B164" t="s">
-        <v>447</v>
+        <v>527</v>
       </c>
       <c r="C164" t="s">
-        <v>867</v>
+        <v>849</v>
       </c>
       <c r="D164">
         <v>0</v>
@@ -10467,13 +10467,13 @@
     </row>
     <row r="165" spans="1:12">
       <c r="A165" t="s">
-        <v>88</v>
+        <v>49</v>
       </c>
       <c r="B165" t="s">
-        <v>486</v>
+        <v>447</v>
       </c>
       <c r="C165" t="s">
-        <v>847</v>
+        <v>867</v>
       </c>
       <c r="D165">
         <v>0</v>
@@ -10566,10 +10566,10 @@
         <v>125</v>
       </c>
       <c r="B168" t="s">
-        <v>530</v>
+        <v>468</v>
       </c>
       <c r="C168" t="s">
-        <v>852</v>
+        <v>885</v>
       </c>
       <c r="D168">
         <v>0</v>
@@ -10595,10 +10595,10 @@
     </row>
     <row r="169" spans="1:12">
       <c r="A169" t="s">
-        <v>55</v>
+        <v>126</v>
       </c>
       <c r="B169" t="s">
-        <v>531</v>
+        <v>421</v>
       </c>
       <c r="C169" t="s">
         <v>872</v>
@@ -10613,7 +10613,7 @@
         <v>1284</v>
       </c>
       <c r="I169">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J169" t="b">
         <v>0</v>
@@ -10627,13 +10627,13 @@
     </row>
     <row r="170" spans="1:12">
       <c r="A170" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B170" t="s">
-        <v>449</v>
+        <v>530</v>
       </c>
       <c r="C170" t="s">
-        <v>869</v>
+        <v>852</v>
       </c>
       <c r="D170">
         <v>0</v>
@@ -10659,10 +10659,10 @@
     </row>
     <row r="171" spans="1:12">
       <c r="A171" t="s">
-        <v>127</v>
+        <v>53</v>
       </c>
       <c r="B171" t="s">
-        <v>421</v>
+        <v>531</v>
       </c>
       <c r="C171" t="s">
         <v>872</v>
@@ -10677,7 +10677,7 @@
         <v>1286</v>
       </c>
       <c r="I171">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J171" t="b">
         <v>0</v>
@@ -10726,10 +10726,10 @@
         <v>129</v>
       </c>
       <c r="B173" t="s">
-        <v>467</v>
+        <v>449</v>
       </c>
       <c r="C173" t="s">
-        <v>884</v>
+        <v>869</v>
       </c>
       <c r="D173">
         <v>0</v>
@@ -10761,7 +10761,7 @@
         <v>533</v>
       </c>
       <c r="C174" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="D174">
         <v>0</v>
@@ -10793,7 +10793,7 @@
         <v>534</v>
       </c>
       <c r="C175" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="D175">
         <v>0</v>
@@ -10921,7 +10921,7 @@
         <v>537</v>
       </c>
       <c r="C179" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="D179">
         <v>0</v>
@@ -10947,13 +10947,13 @@
     </row>
     <row r="180" spans="1:12">
       <c r="A180" t="s">
-        <v>59</v>
+        <v>135</v>
       </c>
       <c r="B180" t="s">
         <v>538</v>
       </c>
       <c r="C180" t="s">
-        <v>860</v>
+        <v>899</v>
       </c>
       <c r="D180">
         <v>0</v>
@@ -10979,13 +10979,13 @@
     </row>
     <row r="181" spans="1:12">
       <c r="A181" t="s">
-        <v>135</v>
+        <v>59</v>
       </c>
       <c r="B181" t="s">
-        <v>489</v>
+        <v>539</v>
       </c>
       <c r="C181" t="s">
-        <v>894</v>
+        <v>860</v>
       </c>
       <c r="D181">
         <v>0</v>
@@ -11014,7 +11014,7 @@
         <v>136</v>
       </c>
       <c r="B182" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C182" t="s">
         <v>851</v>
@@ -11046,10 +11046,10 @@
         <v>137</v>
       </c>
       <c r="B183" t="s">
-        <v>540</v>
+        <v>489</v>
       </c>
       <c r="C183" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="D183">
         <v>0</v>
@@ -11075,7 +11075,7 @@
     </row>
     <row r="184" spans="1:12">
       <c r="A184" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B184" t="s">
         <v>541</v>
@@ -11107,13 +11107,13 @@
     </row>
     <row r="185" spans="1:12">
       <c r="A185" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="B185" t="s">
-        <v>447</v>
+        <v>542</v>
       </c>
       <c r="C185" t="s">
-        <v>867</v>
+        <v>845</v>
       </c>
       <c r="D185">
         <v>0</v>
@@ -11139,13 +11139,13 @@
     </row>
     <row r="186" spans="1:12">
       <c r="A186" t="s">
-        <v>26</v>
+        <v>138</v>
       </c>
       <c r="B186" t="s">
-        <v>542</v>
+        <v>447</v>
       </c>
       <c r="C186" t="s">
-        <v>845</v>
+        <v>867</v>
       </c>
       <c r="D186">
         <v>0</v>
@@ -11171,13 +11171,13 @@
     </row>
     <row r="187" spans="1:12">
       <c r="A187" t="s">
-        <v>139</v>
+        <v>23</v>
       </c>
       <c r="B187" t="s">
-        <v>543</v>
+        <v>423</v>
       </c>
       <c r="C187" t="s">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="D187">
         <v>0</v>
@@ -11203,13 +11203,13 @@
     </row>
     <row r="188" spans="1:12">
       <c r="A188" t="s">
-        <v>59</v>
+        <v>139</v>
       </c>
       <c r="B188" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C188" t="s">
-        <v>845</v>
+        <v>920</v>
       </c>
       <c r="D188">
         <v>0</v>
@@ -11238,7 +11238,7 @@
         <v>140</v>
       </c>
       <c r="B189" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C189" t="s">
         <v>921</v>
@@ -11270,7 +11270,7 @@
         <v>141</v>
       </c>
       <c r="B190" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C190" t="s">
         <v>922</v>
@@ -11299,13 +11299,13 @@
     </row>
     <row r="191" spans="1:12">
       <c r="A191" t="s">
-        <v>24</v>
+        <v>142</v>
       </c>
       <c r="B191" t="s">
-        <v>424</v>
+        <v>546</v>
       </c>
       <c r="C191" t="s">
-        <v>848</v>
+        <v>865</v>
       </c>
       <c r="D191">
         <v>0</v>
@@ -11331,13 +11331,13 @@
     </row>
     <row r="192" spans="1:12">
       <c r="A192" t="s">
-        <v>58</v>
+        <v>143</v>
       </c>
       <c r="B192" t="s">
-        <v>457</v>
+        <v>547</v>
       </c>
       <c r="C192" t="s">
-        <v>876</v>
+        <v>851</v>
       </c>
       <c r="D192">
         <v>0</v>
@@ -11363,13 +11363,13 @@
     </row>
     <row r="193" spans="1:12">
       <c r="A193" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B193" t="s">
-        <v>419</v>
+        <v>548</v>
       </c>
       <c r="C193" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="D193">
         <v>0</v>
@@ -11395,13 +11395,13 @@
     </row>
     <row r="194" spans="1:12">
       <c r="A194" t="s">
-        <v>142</v>
+        <v>58</v>
       </c>
       <c r="B194" t="s">
-        <v>547</v>
+        <v>457</v>
       </c>
       <c r="C194" t="s">
-        <v>865</v>
+        <v>876</v>
       </c>
       <c r="D194">
         <v>0</v>
@@ -11427,13 +11427,13 @@
     </row>
     <row r="195" spans="1:12">
       <c r="A195" t="s">
-        <v>143</v>
+        <v>17</v>
       </c>
       <c r="B195" t="s">
-        <v>548</v>
+        <v>418</v>
       </c>
       <c r="C195" t="s">
-        <v>851</v>
+        <v>842</v>
       </c>
       <c r="D195">
         <v>0</v>
@@ -11523,13 +11523,13 @@
     </row>
     <row r="198" spans="1:12">
       <c r="A198" t="s">
-        <v>146</v>
+        <v>58</v>
       </c>
       <c r="B198" t="s">
-        <v>550</v>
+        <v>457</v>
       </c>
       <c r="C198" t="s">
-        <v>853</v>
+        <v>876</v>
       </c>
       <c r="D198">
         <v>0</v>
@@ -11555,13 +11555,13 @@
     </row>
     <row r="199" spans="1:12">
       <c r="A199" t="s">
-        <v>93</v>
+        <v>146</v>
       </c>
       <c r="B199" t="s">
-        <v>489</v>
+        <v>550</v>
       </c>
       <c r="C199" t="s">
-        <v>894</v>
+        <v>851</v>
       </c>
       <c r="D199">
         <v>0</v>
@@ -11587,13 +11587,13 @@
     </row>
     <row r="200" spans="1:12">
       <c r="A200" t="s">
-        <v>58</v>
+        <v>147</v>
       </c>
       <c r="B200" t="s">
-        <v>457</v>
+        <v>551</v>
       </c>
       <c r="C200" t="s">
-        <v>876</v>
+        <v>851</v>
       </c>
       <c r="D200">
         <v>0</v>
@@ -11619,13 +11619,13 @@
     </row>
     <row r="201" spans="1:12">
       <c r="A201" t="s">
-        <v>147</v>
+        <v>93</v>
       </c>
       <c r="B201" t="s">
-        <v>551</v>
+        <v>489</v>
       </c>
       <c r="C201" t="s">
-        <v>851</v>
+        <v>894</v>
       </c>
       <c r="D201">
         <v>0</v>
@@ -11657,7 +11657,7 @@
         <v>552</v>
       </c>
       <c r="C202" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="D202">
         <v>0</v>
@@ -11683,13 +11683,13 @@
     </row>
     <row r="203" spans="1:12">
       <c r="A203" t="s">
-        <v>36</v>
+        <v>149</v>
       </c>
       <c r="B203" t="s">
-        <v>434</v>
+        <v>553</v>
       </c>
       <c r="C203" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="D203">
         <v>0</v>
@@ -11718,7 +11718,7 @@
         <v>27</v>
       </c>
       <c r="B204" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C204" t="s">
         <v>923</v>
@@ -11747,13 +11747,13 @@
     </row>
     <row r="205" spans="1:12">
       <c r="A205" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B205" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C205" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="D205">
         <v>0</v>
@@ -11779,13 +11779,13 @@
     </row>
     <row r="206" spans="1:12">
       <c r="A206" t="s">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="B206" t="s">
-        <v>554</v>
+        <v>433</v>
       </c>
       <c r="C206" t="s">
-        <v>924</v>
+        <v>857</v>
       </c>
       <c r="D206">
         <v>0</v>
@@ -11811,13 +11811,13 @@
     </row>
     <row r="207" spans="1:12">
       <c r="A207" t="s">
-        <v>149</v>
+        <v>84</v>
       </c>
       <c r="B207" t="s">
         <v>555</v>
       </c>
       <c r="C207" t="s">
-        <v>860</v>
+        <v>924</v>
       </c>
       <c r="D207">
         <v>0</v>
@@ -11849,7 +11849,7 @@
         <v>556</v>
       </c>
       <c r="C208" t="s">
-        <v>899</v>
+        <v>925</v>
       </c>
       <c r="D208">
         <v>0</v>
@@ -11881,7 +11881,7 @@
         <v>557</v>
       </c>
       <c r="C209" t="s">
-        <v>925</v>
+        <v>864</v>
       </c>
       <c r="D209">
         <v>0</v>
@@ -11907,13 +11907,13 @@
     </row>
     <row r="210" spans="1:12">
       <c r="A210" t="s">
-        <v>41</v>
+        <v>152</v>
       </c>
       <c r="B210" t="s">
         <v>558</v>
       </c>
       <c r="C210" t="s">
-        <v>883</v>
+        <v>898</v>
       </c>
       <c r="D210">
         <v>0</v>
@@ -11939,7 +11939,7 @@
     </row>
     <row r="211" spans="1:12">
       <c r="A211" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B211" t="s">
         <v>559</v>
@@ -11971,7 +11971,7 @@
     </row>
     <row r="212" spans="1:12">
       <c r="A212" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B212" t="s">
         <v>421</v>
@@ -12003,13 +12003,13 @@
     </row>
     <row r="213" spans="1:12">
       <c r="A213" t="s">
-        <v>154</v>
+        <v>41</v>
       </c>
       <c r="B213" t="s">
         <v>560</v>
       </c>
       <c r="C213" t="s">
-        <v>927</v>
+        <v>884</v>
       </c>
       <c r="D213">
         <v>0</v>
@@ -12021,7 +12021,7 @@
         <v>1328</v>
       </c>
       <c r="I213">
-        <v>145</v>
+        <v>1</v>
       </c>
       <c r="J213" t="b">
         <v>0</v>
@@ -12035,13 +12035,13 @@
     </row>
     <row r="214" spans="1:12">
       <c r="A214" t="s">
-        <v>155</v>
+        <v>53</v>
       </c>
       <c r="B214" t="s">
         <v>561</v>
       </c>
       <c r="C214" t="s">
-        <v>864</v>
+        <v>927</v>
       </c>
       <c r="D214">
         <v>0</v>
@@ -12067,13 +12067,13 @@
     </row>
     <row r="215" spans="1:12">
       <c r="A215" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="B215" t="s">
-        <v>562</v>
+        <v>434</v>
       </c>
       <c r="C215" t="s">
-        <v>928</v>
+        <v>858</v>
       </c>
       <c r="D215">
         <v>0</v>
@@ -12099,13 +12099,13 @@
     </row>
     <row r="216" spans="1:12">
       <c r="A216" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B216" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="C216" t="s">
-        <v>855</v>
+        <v>861</v>
       </c>
       <c r="D216">
         <v>0</v>
@@ -12131,13 +12131,13 @@
     </row>
     <row r="217" spans="1:12">
       <c r="A217" t="s">
-        <v>39</v>
+        <v>155</v>
       </c>
       <c r="B217" t="s">
-        <v>437</v>
+        <v>562</v>
       </c>
       <c r="C217" t="s">
-        <v>861</v>
+        <v>928</v>
       </c>
       <c r="D217">
         <v>0</v>
@@ -12233,7 +12233,7 @@
         <v>565</v>
       </c>
       <c r="C220" t="s">
-        <v>931</v>
+        <v>846</v>
       </c>
       <c r="D220">
         <v>0</v>
@@ -12265,7 +12265,7 @@
         <v>566</v>
       </c>
       <c r="C221" t="s">
-        <v>868</v>
+        <v>931</v>
       </c>
       <c r="D221">
         <v>0</v>
@@ -12297,7 +12297,7 @@
         <v>567</v>
       </c>
       <c r="C222" t="s">
-        <v>932</v>
+        <v>868</v>
       </c>
       <c r="D222">
         <v>0</v>
@@ -12329,7 +12329,7 @@
         <v>568</v>
       </c>
       <c r="C223" t="s">
-        <v>847</v>
+        <v>932</v>
       </c>
       <c r="D223">
         <v>0</v>
@@ -12341,7 +12341,7 @@
         <v>1338</v>
       </c>
       <c r="I223">
-        <v>1</v>
+        <v>145</v>
       </c>
       <c r="J223" t="b">
         <v>0</v>
@@ -12361,7 +12361,7 @@
         <v>569</v>
       </c>
       <c r="C224" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="D224">
         <v>0</v>
@@ -12419,13 +12419,13 @@
     </row>
     <row r="226" spans="1:12">
       <c r="A226" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="B226" t="s">
-        <v>571</v>
+        <v>437</v>
       </c>
       <c r="C226" t="s">
-        <v>851</v>
+        <v>861</v>
       </c>
       <c r="D226">
         <v>0</v>
@@ -12451,13 +12451,13 @@
     </row>
     <row r="227" spans="1:12">
       <c r="A227" t="s">
-        <v>164</v>
+        <v>71</v>
       </c>
       <c r="B227" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C227" t="s">
-        <v>865</v>
+        <v>851</v>
       </c>
       <c r="D227">
         <v>0</v>
@@ -12483,10 +12483,10 @@
     </row>
     <row r="228" spans="1:12">
       <c r="A228" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B228" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C228" t="s">
         <v>851</v>
@@ -12515,13 +12515,13 @@
     </row>
     <row r="229" spans="1:12">
       <c r="A229" t="s">
-        <v>39</v>
+        <v>164</v>
       </c>
       <c r="B229" t="s">
-        <v>437</v>
+        <v>573</v>
       </c>
       <c r="C229" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="D229">
         <v>0</v>
@@ -12547,13 +12547,13 @@
     </row>
     <row r="230" spans="1:12">
       <c r="A230" t="s">
-        <v>118</v>
+        <v>165</v>
       </c>
       <c r="B230" t="s">
-        <v>515</v>
+        <v>574</v>
       </c>
       <c r="C230" t="s">
-        <v>912</v>
+        <v>897</v>
       </c>
       <c r="D230">
         <v>0</v>
@@ -12579,13 +12579,13 @@
     </row>
     <row r="231" spans="1:12">
       <c r="A231" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="B231" t="s">
-        <v>574</v>
+        <v>516</v>
       </c>
       <c r="C231" t="s">
-        <v>897</v>
+        <v>913</v>
       </c>
       <c r="D231">
         <v>0</v>
@@ -12617,7 +12617,7 @@
         <v>575</v>
       </c>
       <c r="C232" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="D232">
         <v>0</v>
@@ -12643,13 +12643,13 @@
     </row>
     <row r="233" spans="1:12">
       <c r="A233" t="s">
-        <v>167</v>
+        <v>36</v>
       </c>
       <c r="B233" t="s">
-        <v>576</v>
+        <v>434</v>
       </c>
       <c r="C233" t="s">
-        <v>933</v>
+        <v>858</v>
       </c>
       <c r="D233">
         <v>0</v>
@@ -12675,13 +12675,13 @@
     </row>
     <row r="234" spans="1:12">
       <c r="A234" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B234" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C234" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="D234">
         <v>0</v>
@@ -12707,10 +12707,10 @@
     </row>
     <row r="235" spans="1:12">
       <c r="A235" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B235" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C235" t="s">
         <v>908</v>
@@ -12739,13 +12739,13 @@
     </row>
     <row r="236" spans="1:12">
       <c r="A236" t="s">
-        <v>33</v>
+        <v>169</v>
       </c>
       <c r="B236" t="s">
-        <v>431</v>
+        <v>577</v>
       </c>
       <c r="C236" t="s">
-        <v>855</v>
+        <v>933</v>
       </c>
       <c r="D236">
         <v>0</v>
@@ -12905,7 +12905,7 @@
         <v>582</v>
       </c>
       <c r="C241" t="s">
-        <v>897</v>
+        <v>934</v>
       </c>
       <c r="D241">
         <v>0</v>
@@ -12937,7 +12937,7 @@
         <v>583</v>
       </c>
       <c r="C242" t="s">
-        <v>934</v>
+        <v>925</v>
       </c>
       <c r="D242">
         <v>0</v>
@@ -12969,7 +12969,7 @@
         <v>584</v>
       </c>
       <c r="C243" t="s">
-        <v>925</v>
+        <v>935</v>
       </c>
       <c r="D243">
         <v>0</v>
@@ -13001,7 +13001,7 @@
         <v>585</v>
       </c>
       <c r="C244" t="s">
-        <v>935</v>
+        <v>923</v>
       </c>
       <c r="D244">
         <v>0</v>
@@ -13033,7 +13033,7 @@
         <v>586</v>
       </c>
       <c r="C245" t="s">
-        <v>923</v>
+        <v>936</v>
       </c>
       <c r="D245">
         <v>0</v>
@@ -13065,7 +13065,7 @@
         <v>587</v>
       </c>
       <c r="C246" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="D246">
         <v>0</v>
@@ -13100,7 +13100,7 @@
         <v>588</v>
       </c>
       <c r="C247" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="D247">
         <v>0</v>
@@ -13112,7 +13112,7 @@
         <v>1362</v>
       </c>
       <c r="I247">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J247" t="b">
         <v>0</v>
@@ -13132,7 +13132,7 @@
         <v>589</v>
       </c>
       <c r="C248" t="s">
-        <v>938</v>
+        <v>923</v>
       </c>
       <c r="D248">
         <v>0</v>
@@ -13144,7 +13144,7 @@
         <v>1363</v>
       </c>
       <c r="I248">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J248" t="b">
         <v>0</v>
@@ -13228,7 +13228,7 @@
         <v>592</v>
       </c>
       <c r="C251" t="s">
-        <v>923</v>
+        <v>897</v>
       </c>
       <c r="D251">
         <v>0</v>
@@ -13260,7 +13260,7 @@
         <v>593</v>
       </c>
       <c r="C252" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="D252">
         <v>0</v>
@@ -13292,7 +13292,7 @@
         <v>594</v>
       </c>
       <c r="C253" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="D253">
         <v>0</v>
@@ -13336,7 +13336,7 @@
         <v>1369</v>
       </c>
       <c r="I254">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J254" t="b">
         <v>0</v>
@@ -13368,7 +13368,7 @@
         <v>1370</v>
       </c>
       <c r="I255">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J255" t="b">
         <v>0</v>
@@ -13420,7 +13420,7 @@
         <v>598</v>
       </c>
       <c r="C257" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="D257">
         <v>0</v>
@@ -13519,7 +13519,7 @@
         <v>600</v>
       </c>
       <c r="C260" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="D260">
         <v>0</v>
@@ -13556,11 +13556,8 @@
       <c r="D261">
         <v>0</v>
       </c>
-      <c r="E261" t="s">
-        <v>1084</v>
-      </c>
       <c r="F261" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="G261" t="s">
         <v>1376</v>
@@ -13575,7 +13572,7 @@
         <v>1617</v>
       </c>
       <c r="L261" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="262" spans="1:12">
@@ -13586,7 +13583,7 @@
         <v>602</v>
       </c>
       <c r="C262" t="s">
-        <v>944</v>
+        <v>421</v>
       </c>
       <c r="D262">
         <v>0</v>
@@ -13618,7 +13615,7 @@
         <v>603</v>
       </c>
       <c r="C263" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="D263">
         <v>0</v>
@@ -13650,7 +13647,7 @@
         <v>604</v>
       </c>
       <c r="C264" t="s">
-        <v>421</v>
+        <v>897</v>
       </c>
       <c r="D264">
         <v>0</v>
@@ -13682,7 +13679,7 @@
         <v>605</v>
       </c>
       <c r="C265" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="D265">
         <v>0</v>
@@ -13714,13 +13711,16 @@
         <v>606</v>
       </c>
       <c r="C266" t="s">
-        <v>897</v>
+        <v>944</v>
       </c>
       <c r="D266">
         <v>0</v>
       </c>
+      <c r="E266" t="s">
+        <v>1084</v>
+      </c>
       <c r="F266" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="G266" t="s">
         <v>1381</v>
@@ -13735,7 +13735,7 @@
         <v>1617</v>
       </c>
       <c r="L266" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="267" spans="1:12">
@@ -13746,7 +13746,7 @@
         <v>607</v>
       </c>
       <c r="C267" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="D267">
         <v>0</v>
@@ -13892,7 +13892,7 @@
         <v>1386</v>
       </c>
       <c r="I271">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="J271" t="b">
         <v>0</v>
@@ -13917,8 +13917,11 @@
       <c r="D272">
         <v>0</v>
       </c>
+      <c r="E272" t="s">
+        <v>1087</v>
+      </c>
       <c r="F272" t="s">
-        <v>1105</v>
+        <v>1110</v>
       </c>
       <c r="G272" t="s">
         <v>1387</v>
@@ -13933,7 +13936,7 @@
         <v>1617</v>
       </c>
       <c r="L272" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="273" spans="1:12">
@@ -13949,11 +13952,8 @@
       <c r="D273">
         <v>0</v>
       </c>
-      <c r="E273" t="s">
-        <v>1087</v>
-      </c>
       <c r="F273" t="s">
-        <v>1110</v>
+        <v>1105</v>
       </c>
       <c r="G273" t="s">
         <v>1388</v>
@@ -13968,7 +13968,7 @@
         <v>1617</v>
       </c>
       <c r="L273" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="274" spans="1:12">
@@ -14055,7 +14055,7 @@
         <v>1391</v>
       </c>
       <c r="I276">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="J276" t="b">
         <v>0</v>
@@ -14270,7 +14270,7 @@
         <v>623</v>
       </c>
       <c r="C283" t="s">
-        <v>851</v>
+        <v>921</v>
       </c>
       <c r="D283">
         <v>0</v>
@@ -14282,7 +14282,7 @@
         <v>1398</v>
       </c>
       <c r="I283">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J283" t="b">
         <v>0</v>
@@ -14314,7 +14314,7 @@
         <v>1399</v>
       </c>
       <c r="I284">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J284" t="b">
         <v>0</v>
@@ -14334,7 +14334,7 @@
         <v>625</v>
       </c>
       <c r="C285" t="s">
-        <v>922</v>
+        <v>851</v>
       </c>
       <c r="D285">
         <v>0</v>
@@ -14346,7 +14346,7 @@
         <v>1400</v>
       </c>
       <c r="I285">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J285" t="b">
         <v>0</v>
@@ -14442,7 +14442,7 @@
         <v>1403</v>
       </c>
       <c r="I288">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J288" t="b">
         <v>0</v>
@@ -14474,7 +14474,7 @@
         <v>1404</v>
       </c>
       <c r="I289">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J289" t="b">
         <v>0</v>
@@ -14590,7 +14590,7 @@
         <v>633</v>
       </c>
       <c r="C293" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="D293">
         <v>0</v>
@@ -14622,7 +14622,7 @@
         <v>634</v>
       </c>
       <c r="C294" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="D294">
         <v>0</v>
@@ -15463,7 +15463,7 @@
         <v>660</v>
       </c>
       <c r="C320" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="D320">
         <v>0</v>
@@ -15798,7 +15798,7 @@
         <v>1445</v>
       </c>
       <c r="I330">
-        <v>23</v>
+        <v>245</v>
       </c>
       <c r="J330" t="b">
         <v>0</v>
@@ -15894,7 +15894,7 @@
         <v>1448</v>
       </c>
       <c r="I333">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="J333" t="b">
         <v>0</v>
@@ -15914,7 +15914,7 @@
         <v>674</v>
       </c>
       <c r="C334" t="s">
-        <v>853</v>
+        <v>991</v>
       </c>
       <c r="D334">
         <v>0</v>
@@ -15926,7 +15926,7 @@
         <v>1449</v>
       </c>
       <c r="I334">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J334" t="b">
         <v>0</v>
@@ -15940,10 +15940,10 @@
     </row>
     <row r="335" spans="1:12">
       <c r="A335" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B335" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C335" t="s">
         <v>853</v>
@@ -15978,7 +15978,7 @@
         <v>675</v>
       </c>
       <c r="C336" t="s">
-        <v>991</v>
+        <v>853</v>
       </c>
       <c r="D336">
         <v>0</v>
@@ -15990,7 +15990,7 @@
         <v>1451</v>
       </c>
       <c r="I336">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="J336" t="b">
         <v>0</v>
@@ -16015,17 +16015,14 @@
       <c r="D337">
         <v>0</v>
       </c>
-      <c r="E337" t="s">
-        <v>1093</v>
-      </c>
       <c r="F337" t="s">
-        <v>1093</v>
+        <v>1105</v>
       </c>
       <c r="G337" t="s">
         <v>1452</v>
       </c>
       <c r="I337">
-        <v>6</v>
+        <v>245</v>
       </c>
       <c r="J337" t="b">
         <v>0</v>
@@ -16034,7 +16031,7 @@
         <v>1617</v>
       </c>
       <c r="L337" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="338" spans="1:12">
@@ -16109,22 +16106,19 @@
         <v>679</v>
       </c>
       <c r="C340" t="s">
-        <v>897</v>
+        <v>994</v>
       </c>
       <c r="D340">
         <v>0</v>
       </c>
-      <c r="E340" t="s">
-        <v>1094</v>
-      </c>
       <c r="F340" t="s">
-        <v>1094</v>
+        <v>1105</v>
       </c>
       <c r="G340" t="s">
         <v>1455</v>
       </c>
       <c r="I340">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="J340" t="b">
         <v>0</v>
@@ -16133,7 +16127,7 @@
         <v>1617</v>
       </c>
       <c r="L340" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="341" spans="1:12">
@@ -16144,19 +16138,22 @@
         <v>680</v>
       </c>
       <c r="C341" t="s">
-        <v>980</v>
+        <v>897</v>
       </c>
       <c r="D341">
         <v>0</v>
       </c>
+      <c r="E341" t="s">
+        <v>1093</v>
+      </c>
       <c r="F341" t="s">
-        <v>1105</v>
+        <v>1093</v>
       </c>
       <c r="G341" t="s">
         <v>1456</v>
       </c>
       <c r="I341">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="J341" t="b">
         <v>0</v>
@@ -16165,7 +16162,7 @@
         <v>1617</v>
       </c>
       <c r="L341" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="342" spans="1:12">
@@ -16176,19 +16173,22 @@
         <v>681</v>
       </c>
       <c r="C342" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="D342">
         <v>0</v>
       </c>
+      <c r="E342" t="s">
+        <v>1094</v>
+      </c>
       <c r="F342" t="s">
-        <v>1105</v>
+        <v>1094</v>
       </c>
       <c r="G342" t="s">
         <v>1457</v>
       </c>
       <c r="I342">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="J342" t="b">
         <v>0</v>
@@ -16197,7 +16197,7 @@
         <v>1617</v>
       </c>
       <c r="L342" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="343" spans="1:12">
@@ -16272,7 +16272,7 @@
         <v>684</v>
       </c>
       <c r="C345" t="s">
-        <v>995</v>
+        <v>980</v>
       </c>
       <c r="D345">
         <v>0</v>
@@ -16284,7 +16284,7 @@
         <v>1460</v>
       </c>
       <c r="I345">
-        <v>173</v>
+        <v>28</v>
       </c>
       <c r="J345" t="b">
         <v>0</v>
@@ -16298,13 +16298,13 @@
     </row>
     <row r="346" spans="1:12">
       <c r="A346" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B346" t="s">
         <v>685</v>
       </c>
       <c r="C346" t="s">
-        <v>996</v>
+        <v>421</v>
       </c>
       <c r="D346">
         <v>0</v>
@@ -16316,7 +16316,7 @@
         <v>1461</v>
       </c>
       <c r="I346">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="J346" t="b">
         <v>0</v>
@@ -16330,7 +16330,7 @@
     </row>
     <row r="347" spans="1:12">
       <c r="A347" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B347" t="s">
         <v>686</v>
@@ -16362,13 +16362,13 @@
     </row>
     <row r="348" spans="1:12">
       <c r="A348" t="s">
-        <v>277</v>
+        <v>211</v>
       </c>
       <c r="B348" t="s">
         <v>687</v>
       </c>
       <c r="C348" t="s">
-        <v>421</v>
+        <v>996</v>
       </c>
       <c r="D348">
         <v>0</v>
@@ -16394,7 +16394,7 @@
     </row>
     <row r="349" spans="1:12">
       <c r="A349" t="s">
-        <v>211</v>
+        <v>278</v>
       </c>
       <c r="B349" t="s">
         <v>688</v>
@@ -16426,7 +16426,7 @@
     </row>
     <row r="350" spans="1:12">
       <c r="A350" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B350" t="s">
         <v>689</v>
@@ -16444,7 +16444,7 @@
         <v>1465</v>
       </c>
       <c r="I350">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J350" t="b">
         <v>0</v>
@@ -16458,7 +16458,7 @@
     </row>
     <row r="351" spans="1:12">
       <c r="A351" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B351" t="s">
         <v>690</v>
@@ -16490,13 +16490,13 @@
     </row>
     <row r="352" spans="1:12">
       <c r="A352" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B352" t="s">
         <v>691</v>
       </c>
       <c r="C352" t="s">
-        <v>1000</v>
+        <v>897</v>
       </c>
       <c r="D352">
         <v>0</v>
@@ -16522,13 +16522,13 @@
     </row>
     <row r="353" spans="1:12">
       <c r="A353" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B353" t="s">
         <v>692</v>
       </c>
       <c r="C353" t="s">
-        <v>897</v>
+        <v>1000</v>
       </c>
       <c r="D353">
         <v>0</v>
@@ -16540,7 +16540,7 @@
         <v>1468</v>
       </c>
       <c r="I353">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="J353" t="b">
         <v>0</v>
@@ -16554,13 +16554,13 @@
     </row>
     <row r="354" spans="1:12">
       <c r="A354" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B354" t="s">
         <v>693</v>
       </c>
       <c r="C354" t="s">
-        <v>421</v>
+        <v>897</v>
       </c>
       <c r="D354">
         <v>0</v>
@@ -16572,7 +16572,7 @@
         <v>1469</v>
       </c>
       <c r="I354">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J354" t="b">
         <v>0</v>
@@ -16586,13 +16586,13 @@
     </row>
     <row r="355" spans="1:12">
       <c r="A355" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B355" t="s">
         <v>694</v>
       </c>
       <c r="C355" t="s">
-        <v>897</v>
+        <v>421</v>
       </c>
       <c r="D355">
         <v>0</v>
@@ -16604,7 +16604,7 @@
         <v>1470</v>
       </c>
       <c r="I355">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J355" t="b">
         <v>0</v>
@@ -16618,7 +16618,7 @@
     </row>
     <row r="356" spans="1:12">
       <c r="A356" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B356" t="s">
         <v>695</v>
@@ -16650,7 +16650,7 @@
     </row>
     <row r="357" spans="1:12">
       <c r="A357" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B357" t="s">
         <v>696</v>
@@ -16682,7 +16682,7 @@
     </row>
     <row r="358" spans="1:12">
       <c r="A358" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B358" t="s">
         <v>697</v>
@@ -16714,13 +16714,13 @@
     </row>
     <row r="359" spans="1:12">
       <c r="A359" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B359" t="s">
         <v>698</v>
       </c>
       <c r="C359" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="D359">
         <v>0</v>
@@ -16746,7 +16746,7 @@
     </row>
     <row r="360" spans="1:12">
       <c r="A360" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="B360" t="s">
         <v>699</v>
@@ -16757,17 +16757,14 @@
       <c r="D360">
         <v>0</v>
       </c>
-      <c r="E360" t="s">
-        <v>1095</v>
-      </c>
       <c r="F360" t="s">
-        <v>1095</v>
+        <v>1105</v>
       </c>
       <c r="G360" t="s">
         <v>1475</v>
       </c>
       <c r="I360">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="J360" t="b">
         <v>0</v>
@@ -16776,7 +16773,7 @@
         <v>1617</v>
       </c>
       <c r="L360" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="361" spans="1:12">
@@ -16984,14 +16981,17 @@
       <c r="D367">
         <v>0</v>
       </c>
+      <c r="E367" t="s">
+        <v>1095</v>
+      </c>
       <c r="F367" t="s">
-        <v>1105</v>
+        <v>1095</v>
       </c>
       <c r="G367" t="s">
         <v>1482</v>
       </c>
       <c r="I367">
-        <v>245</v>
+        <v>11</v>
       </c>
       <c r="J367" t="b">
         <v>0</v>
@@ -17000,7 +17000,7 @@
         <v>1617</v>
       </c>
       <c r="L367" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="368" spans="1:12">
@@ -17023,7 +17023,7 @@
         <v>1483</v>
       </c>
       <c r="I368">
-        <v>57</v>
+        <v>173</v>
       </c>
       <c r="J368" t="b">
         <v>0</v>
@@ -17043,7 +17043,7 @@
         <v>708</v>
       </c>
       <c r="C369" t="s">
-        <v>1008</v>
+        <v>421</v>
       </c>
       <c r="D369">
         <v>0</v>
@@ -17055,7 +17055,7 @@
         <v>1484</v>
       </c>
       <c r="I369">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J369" t="b">
         <v>0</v>
@@ -17075,7 +17075,7 @@
         <v>709</v>
       </c>
       <c r="C370" t="s">
-        <v>421</v>
+        <v>1008</v>
       </c>
       <c r="D370">
         <v>0</v>
@@ -17087,7 +17087,7 @@
         <v>1485</v>
       </c>
       <c r="I370">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J370" t="b">
         <v>0</v>
@@ -17131,7 +17131,7 @@
         <v>1618</v>
       </c>
       <c r="M371" t="s">
-        <v>1487</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="372" spans="1:13">
@@ -17154,7 +17154,7 @@
         <v>1487</v>
       </c>
       <c r="I372">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="J372" t="b">
         <v>0</v>
@@ -17174,7 +17174,7 @@
         <v>712</v>
       </c>
       <c r="C373" t="s">
-        <v>1011</v>
+        <v>897</v>
       </c>
       <c r="D373">
         <v>0</v>
@@ -17186,7 +17186,7 @@
         <v>1488</v>
       </c>
       <c r="I373">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="J373" t="b">
         <v>0</v>
@@ -17211,8 +17211,11 @@
       <c r="D374">
         <v>0</v>
       </c>
+      <c r="E374" t="s">
+        <v>1096</v>
+      </c>
       <c r="F374" t="s">
-        <v>1105</v>
+        <v>1096</v>
       </c>
       <c r="G374" t="s">
         <v>1489</v>
@@ -17227,7 +17230,7 @@
         <v>1617</v>
       </c>
       <c r="L374" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="375" spans="1:13">
@@ -17238,22 +17241,19 @@
         <v>714</v>
       </c>
       <c r="C375" t="s">
-        <v>897</v>
+        <v>1011</v>
       </c>
       <c r="D375">
         <v>0</v>
       </c>
-      <c r="E375" t="s">
-        <v>1096</v>
-      </c>
       <c r="F375" t="s">
-        <v>1096</v>
+        <v>1105</v>
       </c>
       <c r="G375" t="s">
         <v>1490</v>
       </c>
       <c r="I375">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J375" t="b">
         <v>0</v>
@@ -17262,7 +17262,7 @@
         <v>1617</v>
       </c>
       <c r="L375" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="376" spans="1:13">
@@ -17317,7 +17317,7 @@
         <v>1492</v>
       </c>
       <c r="I377">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J377" t="b">
         <v>0</v>
@@ -17349,7 +17349,7 @@
         <v>1493</v>
       </c>
       <c r="I378">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="J378" t="b">
         <v>0</v>
@@ -17363,7 +17363,7 @@
     </row>
     <row r="379" spans="1:13">
       <c r="A379" t="s">
-        <v>249</v>
+        <v>306</v>
       </c>
       <c r="B379" t="s">
         <v>718</v>
@@ -17381,7 +17381,7 @@
         <v>1494</v>
       </c>
       <c r="I379">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="J379" t="b">
         <v>0</v>
@@ -17395,7 +17395,7 @@
     </row>
     <row r="380" spans="1:13">
       <c r="A380" t="s">
-        <v>306</v>
+        <v>249</v>
       </c>
       <c r="B380" t="s">
         <v>719</v>
@@ -17413,7 +17413,7 @@
         <v>1495</v>
       </c>
       <c r="I380">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="J380" t="b">
         <v>0</v>
@@ -17509,7 +17509,7 @@
         <v>1498</v>
       </c>
       <c r="I383">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="J383" t="b">
         <v>0</v>
@@ -17541,7 +17541,7 @@
         <v>1499</v>
       </c>
       <c r="I384">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="J384" t="b">
         <v>0</v>
@@ -17566,14 +17566,17 @@
       <c r="D385">
         <v>0</v>
       </c>
+      <c r="E385" t="s">
+        <v>1097</v>
+      </c>
       <c r="F385" t="s">
-        <v>1105</v>
+        <v>1115</v>
       </c>
       <c r="G385" t="s">
         <v>1500</v>
       </c>
       <c r="I385">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J385" t="b">
         <v>0</v>
@@ -17582,18 +17585,18 @@
         <v>1617</v>
       </c>
       <c r="L385" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="386" spans="1:12">
       <c r="A386" t="s">
-        <v>312</v>
+        <v>226</v>
       </c>
       <c r="B386" t="s">
-        <v>725</v>
+        <v>633</v>
       </c>
       <c r="C386" t="s">
-        <v>1019</v>
+        <v>848</v>
       </c>
       <c r="D386">
         <v>0</v>
@@ -17605,7 +17608,7 @@
         <v>1501</v>
       </c>
       <c r="I386">
-        <v>245</v>
+        <v>1</v>
       </c>
       <c r="J386" t="b">
         <v>0</v>
@@ -17619,28 +17622,25 @@
     </row>
     <row r="387" spans="1:12">
       <c r="A387" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B387" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="C387" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="D387">
         <v>0</v>
       </c>
-      <c r="E387" t="s">
-        <v>1097</v>
-      </c>
       <c r="F387" t="s">
-        <v>1115</v>
+        <v>1105</v>
       </c>
       <c r="G387" t="s">
         <v>1502</v>
       </c>
       <c r="I387">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J387" t="b">
         <v>0</v>
@@ -17649,18 +17649,18 @@
         <v>1617</v>
       </c>
       <c r="L387" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="388" spans="1:12">
       <c r="A388" t="s">
-        <v>226</v>
+        <v>313</v>
       </c>
       <c r="B388" t="s">
-        <v>633</v>
+        <v>726</v>
       </c>
       <c r="C388" t="s">
-        <v>846</v>
+        <v>923</v>
       </c>
       <c r="D388">
         <v>0</v>
@@ -17692,7 +17692,7 @@
         <v>727</v>
       </c>
       <c r="C389" t="s">
-        <v>923</v>
+        <v>897</v>
       </c>
       <c r="D389">
         <v>0</v>
@@ -17724,13 +17724,16 @@
         <v>728</v>
       </c>
       <c r="C390" t="s">
-        <v>897</v>
+        <v>1020</v>
       </c>
       <c r="D390">
         <v>0</v>
       </c>
+      <c r="E390" t="s">
+        <v>1098</v>
+      </c>
       <c r="F390" t="s">
-        <v>1105</v>
+        <v>1098</v>
       </c>
       <c r="G390" t="s">
         <v>1505</v>
@@ -17745,7 +17748,7 @@
         <v>1617</v>
       </c>
       <c r="L390" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="391" spans="1:12">
@@ -17761,11 +17764,8 @@
       <c r="D391">
         <v>0</v>
       </c>
-      <c r="E391" t="s">
-        <v>1098</v>
-      </c>
       <c r="F391" t="s">
-        <v>1098</v>
+        <v>1105</v>
       </c>
       <c r="G391" t="s">
         <v>1506</v>
@@ -17780,7 +17780,7 @@
         <v>1617</v>
       </c>
       <c r="L391" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="392" spans="1:12">
@@ -17803,7 +17803,7 @@
         <v>1507</v>
       </c>
       <c r="I392">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="J392" t="b">
         <v>0</v>
@@ -17855,7 +17855,7 @@
         <v>732</v>
       </c>
       <c r="C394" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="D394">
         <v>0</v>
@@ -17977,7 +17977,7 @@
     </row>
     <row r="398" spans="1:12">
       <c r="A398" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B398" t="s">
         <v>736</v>
@@ -18041,13 +18041,13 @@
     </row>
     <row r="400" spans="1:12">
       <c r="A400" t="s">
-        <v>188</v>
+        <v>324</v>
       </c>
       <c r="B400" t="s">
         <v>738</v>
       </c>
       <c r="C400" t="s">
-        <v>897</v>
+        <v>1026</v>
       </c>
       <c r="D400">
         <v>0</v>
@@ -18059,7 +18059,7 @@
         <v>1515</v>
       </c>
       <c r="I400">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J400" t="b">
         <v>0</v>
@@ -18073,13 +18073,13 @@
     </row>
     <row r="401" spans="1:12">
       <c r="A401" t="s">
-        <v>324</v>
+        <v>187</v>
       </c>
       <c r="B401" t="s">
         <v>739</v>
       </c>
       <c r="C401" t="s">
-        <v>1026</v>
+        <v>897</v>
       </c>
       <c r="D401">
         <v>0</v>
@@ -18091,7 +18091,7 @@
         <v>1516</v>
       </c>
       <c r="I401">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J401" t="b">
         <v>0</v>
@@ -18329,7 +18329,7 @@
     </row>
     <row r="409" spans="1:12">
       <c r="A409" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B409" t="s">
         <v>747</v>
@@ -18431,19 +18431,22 @@
         <v>750</v>
       </c>
       <c r="C412" t="s">
-        <v>980</v>
+        <v>1030</v>
       </c>
       <c r="D412">
         <v>0</v>
       </c>
+      <c r="E412" t="s">
+        <v>1099</v>
+      </c>
       <c r="F412" t="s">
-        <v>1105</v>
+        <v>1099</v>
       </c>
       <c r="G412" t="s">
         <v>1527</v>
       </c>
       <c r="I412">
-        <v>3</v>
+        <v>92</v>
       </c>
       <c r="J412" t="b">
         <v>0</v>
@@ -18452,7 +18455,7 @@
         <v>1617</v>
       </c>
       <c r="L412" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="413" spans="1:12">
@@ -18463,7 +18466,7 @@
         <v>751</v>
       </c>
       <c r="C413" t="s">
-        <v>1030</v>
+        <v>980</v>
       </c>
       <c r="D413">
         <v>0</v>
@@ -18475,7 +18478,7 @@
         <v>1528</v>
       </c>
       <c r="I413">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="J413" t="b">
         <v>0</v>
@@ -18649,7 +18652,7 @@
     </row>
     <row r="419" spans="1:12">
       <c r="A419" t="s">
-        <v>217</v>
+        <v>340</v>
       </c>
       <c r="B419" t="s">
         <v>757</v>
@@ -18667,7 +18670,7 @@
         <v>1534</v>
       </c>
       <c r="I419">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="J419" t="b">
         <v>0</v>
@@ -18681,13 +18684,13 @@
     </row>
     <row r="420" spans="1:12">
       <c r="A420" t="s">
-        <v>340</v>
+        <v>218</v>
       </c>
       <c r="B420" t="s">
         <v>758</v>
       </c>
       <c r="C420" t="s">
-        <v>897</v>
+        <v>1034</v>
       </c>
       <c r="D420">
         <v>0</v>
@@ -18699,7 +18702,7 @@
         <v>1535</v>
       </c>
       <c r="I420">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="J420" t="b">
         <v>0</v>
@@ -18719,7 +18722,7 @@
         <v>759</v>
       </c>
       <c r="C421" t="s">
-        <v>1034</v>
+        <v>897</v>
       </c>
       <c r="D421">
         <v>0</v>
@@ -18751,7 +18754,7 @@
         <v>760</v>
       </c>
       <c r="C422" t="s">
-        <v>897</v>
+        <v>1035</v>
       </c>
       <c r="D422">
         <v>0</v>
@@ -18783,7 +18786,7 @@
         <v>761</v>
       </c>
       <c r="C423" t="s">
-        <v>1035</v>
+        <v>897</v>
       </c>
       <c r="D423">
         <v>0</v>
@@ -18827,7 +18830,7 @@
         <v>1539</v>
       </c>
       <c r="I424">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J424" t="b">
         <v>0</v>
@@ -18859,7 +18862,7 @@
         <v>1540</v>
       </c>
       <c r="I425">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J425" t="b">
         <v>0</v>
@@ -18891,7 +18894,7 @@
         <v>1541</v>
       </c>
       <c r="I426">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="J426" t="b">
         <v>0</v>
@@ -18980,17 +18983,14 @@
       <c r="D429">
         <v>0</v>
       </c>
-      <c r="E429" t="s">
-        <v>1099</v>
-      </c>
       <c r="F429" t="s">
-        <v>1099</v>
+        <v>1105</v>
       </c>
       <c r="G429" t="s">
         <v>1544</v>
       </c>
       <c r="I429">
-        <v>92</v>
+        <v>2</v>
       </c>
       <c r="J429" t="b">
         <v>0</v>
@@ -18999,7 +18999,7 @@
         <v>1617</v>
       </c>
       <c r="L429" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="430" spans="1:12">
@@ -19022,7 +19022,7 @@
         <v>1545</v>
       </c>
       <c r="I430">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J430" t="b">
         <v>0</v>
@@ -19054,7 +19054,7 @@
         <v>1546</v>
       </c>
       <c r="I431">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J431" t="b">
         <v>0</v>
@@ -19118,7 +19118,7 @@
         <v>1548</v>
       </c>
       <c r="I433">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J433" t="b">
         <v>0</v>
@@ -19150,7 +19150,7 @@
         <v>1549</v>
       </c>
       <c r="I434">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="J434" t="b">
         <v>0</v>
@@ -19327,7 +19327,7 @@
     </row>
     <row r="440" spans="1:12">
       <c r="A440" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B440" t="s">
         <v>778</v>
@@ -19519,7 +19519,7 @@
     </row>
     <row r="446" spans="1:12">
       <c r="A446" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B446" t="s">
         <v>784</v>
@@ -19825,7 +19825,7 @@
         <v>1570</v>
       </c>
       <c r="I455">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J455" t="b">
         <v>0</v>
@@ -19845,7 +19845,7 @@
         <v>793</v>
       </c>
       <c r="C456" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="D456">
         <v>0</v>
@@ -19877,7 +19877,7 @@
         <v>794</v>
       </c>
       <c r="C457" t="s">
-        <v>923</v>
+        <v>1056</v>
       </c>
       <c r="D457">
         <v>0</v>
@@ -19889,7 +19889,7 @@
         <v>1572</v>
       </c>
       <c r="I457">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J457" t="b">
         <v>0</v>
@@ -19909,7 +19909,7 @@
         <v>795</v>
       </c>
       <c r="C458" t="s">
-        <v>1056</v>
+        <v>923</v>
       </c>
       <c r="D458">
         <v>0</v>
@@ -20063,7 +20063,7 @@
     </row>
     <row r="463" spans="1:12">
       <c r="A463" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="B463" t="s">
         <v>799</v>
@@ -20165,7 +20165,7 @@
         <v>802</v>
       </c>
       <c r="C466" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="D466">
         <v>0</v>
@@ -20229,7 +20229,7 @@
         <v>804</v>
       </c>
       <c r="C468" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="D468">
         <v>0</v>
@@ -20351,25 +20351,28 @@
     </row>
     <row r="472" spans="1:12">
       <c r="A472" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="B472" t="s">
         <v>808</v>
       </c>
       <c r="C472" t="s">
-        <v>852</v>
+        <v>1064</v>
       </c>
       <c r="D472">
         <v>0</v>
       </c>
+      <c r="E472" t="s">
+        <v>1101</v>
+      </c>
       <c r="F472" t="s">
-        <v>1105</v>
+        <v>1116</v>
       </c>
       <c r="G472" t="s">
         <v>1587</v>
       </c>
       <c r="I472">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="J472" t="b">
         <v>0</v>
@@ -20378,18 +20381,18 @@
         <v>1617</v>
       </c>
       <c r="L472" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="473" spans="1:12">
       <c r="A473" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B473" t="s">
         <v>809</v>
       </c>
       <c r="C473" t="s">
-        <v>897</v>
+        <v>852</v>
       </c>
       <c r="D473">
         <v>0</v>
@@ -20415,13 +20418,13 @@
     </row>
     <row r="474" spans="1:12">
       <c r="A474" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B474" t="s">
         <v>810</v>
       </c>
       <c r="C474" t="s">
-        <v>1064</v>
+        <v>897</v>
       </c>
       <c r="D474">
         <v>0</v>
@@ -20433,7 +20436,7 @@
         <v>1589</v>
       </c>
       <c r="I474">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J474" t="b">
         <v>0</v>
@@ -20447,13 +20450,13 @@
     </row>
     <row r="475" spans="1:12">
       <c r="A475" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B475" t="s">
         <v>811</v>
       </c>
       <c r="C475" t="s">
-        <v>421</v>
+        <v>1065</v>
       </c>
       <c r="D475">
         <v>0</v>
@@ -20479,7 +20482,7 @@
     </row>
     <row r="476" spans="1:12">
       <c r="A476" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B476" t="s">
         <v>812</v>
@@ -20511,28 +20514,25 @@
     </row>
     <row r="477" spans="1:12">
       <c r="A477" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="B477" t="s">
         <v>813</v>
       </c>
       <c r="C477" t="s">
-        <v>1065</v>
+        <v>421</v>
       </c>
       <c r="D477">
         <v>0</v>
       </c>
-      <c r="E477" t="s">
-        <v>1101</v>
-      </c>
       <c r="F477" t="s">
-        <v>1116</v>
+        <v>1105</v>
       </c>
       <c r="G477" t="s">
         <v>1592</v>
       </c>
       <c r="I477">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="J477" t="b">
         <v>0</v>
@@ -20541,7 +20541,7 @@
         <v>1617</v>
       </c>
       <c r="L477" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="478" spans="1:12">
@@ -20808,7 +20808,7 @@
         <v>822</v>
       </c>
       <c r="C486" t="s">
-        <v>1071</v>
+        <v>1035</v>
       </c>
       <c r="D486">
         <v>0</v>
@@ -20820,7 +20820,7 @@
         <v>1601</v>
       </c>
       <c r="I486">
-        <v>73</v>
+        <v>2</v>
       </c>
       <c r="J486" t="b">
         <v>0</v>
@@ -20840,7 +20840,7 @@
         <v>823</v>
       </c>
       <c r="C487" t="s">
-        <v>1034</v>
+        <v>1071</v>
       </c>
       <c r="D487">
         <v>0</v>
@@ -20872,7 +20872,7 @@
         <v>824</v>
       </c>
       <c r="C488" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="D488">
         <v>0</v>
@@ -20916,7 +20916,7 @@
         <v>1604</v>
       </c>
       <c r="I489">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="J489" t="b">
         <v>0</v>
@@ -21000,22 +21000,19 @@
         <v>828</v>
       </c>
       <c r="C492" t="s">
-        <v>1075</v>
+        <v>853</v>
       </c>
       <c r="D492">
         <v>0</v>
       </c>
-      <c r="E492" t="s">
-        <v>1102</v>
-      </c>
       <c r="F492" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
       <c r="G492" t="s">
         <v>1607</v>
       </c>
       <c r="I492">
-        <v>382</v>
+        <v>2</v>
       </c>
       <c r="J492" t="b">
         <v>0</v>
@@ -21024,7 +21021,7 @@
         <v>1617</v>
       </c>
       <c r="L492" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="493" spans="1:12">
@@ -21035,7 +21032,7 @@
         <v>829</v>
       </c>
       <c r="C493" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="D493">
         <v>0</v>
@@ -21131,7 +21128,7 @@
         <v>832</v>
       </c>
       <c r="C496" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="D496">
         <v>0</v>
@@ -21163,7 +21160,7 @@
         <v>833</v>
       </c>
       <c r="C497" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="D497">
         <v>0</v>
@@ -21195,19 +21192,22 @@
         <v>834</v>
       </c>
       <c r="C498" t="s">
-        <v>853</v>
+        <v>1078</v>
       </c>
       <c r="D498">
         <v>0</v>
       </c>
+      <c r="E498" t="s">
+        <v>1102</v>
+      </c>
       <c r="F498" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
       <c r="G498" t="s">
         <v>1613</v>
       </c>
       <c r="I498">
-        <v>2</v>
+        <v>101</v>
       </c>
       <c r="J498" t="b">
         <v>0</v>
@@ -21216,7 +21216,7 @@
         <v>1617</v>
       </c>
       <c r="L498" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="499" spans="1:12">
@@ -21242,7 +21242,7 @@
         <v>1614</v>
       </c>
       <c r="I499">
-        <v>101</v>
+        <v>382</v>
       </c>
       <c r="J499" t="b">
         <v>0</v>
